--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 04-Sep-2026 04:44 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 07-Sep-2026 06:06 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>04-Sep-2026 04:44 PM</t>
+          <t>07-Sep-2026 06:06 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  04-Sep-2026 04:44 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  07-Sep-2026 06:06 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>501.9</v>
+        <v>492.05</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>503.6</v>
+        <v>493.25</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>509.9</v>
+        <v>495.75</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>490</v>
+        <v>487.35</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>492.05</v>
+        <v>490.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-9.85</v>
+        <v>-1.35</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-1.96</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7432</v>
+        <v>7410</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7445.5</v>
+        <v>7410</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7470</v>
+        <v>7459.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7376</v>
+        <v>7327</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7410</v>
+        <v>7434</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-0.3</v>
+        <v>24</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25945</v>
+        <v>26065</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25945</v>
+        <v>26150</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26365</v>
+        <v>26195</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>25810</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26065</v>
+        <v>25940</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>0.46</v>
+        <v>-125</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>402</v>
+        <v>404.9</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>400.2</v>
+        <v>404</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>407.4</v>
+        <v>404.75</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>400.2</v>
+        <v>399.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>404.9</v>
+        <v>403.25</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>0.72</v>
+        <v>-1.65</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.41</v>
+        <v>52.97</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.76</v>
+        <v>52.95</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>53.5</v>
+        <v>55.11</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>50.45</v>
+        <v>51.99</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>52.97</v>
+        <v>53.21</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2.56</v>
+        <v>0.24</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>5.08</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1272</v>
+        <v>1283.8</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1289.3</v>
+        <v>1288.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1272</v>
+        <v>1265.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1283.8</v>
+        <v>1268.7</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0.93</v>
+        <v>-15.1</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2901</v>
+        <v>2938</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2900</v>
+        <v>2940</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2965</v>
+        <v>2964.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2882.8</v>
+        <v>2918.5</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1706.5</v>
+        <v>1707.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1699.9</v>
+        <v>1714</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1716.9</v>
+        <v>1716.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1692.4</v>
+        <v>1685.9</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1707.3</v>
+        <v>1694.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0.05</v>
+        <v>-13</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5193</v>
+        <v>5190</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5190</v>
+        <v>5219</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5210.5</v>
+        <v>5242.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5130</v>
+        <v>5104.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5190</v>
+        <v>5242.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-0.06</v>
+        <v>52.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="12">
@@ -1142,22 +1142,22 @@
         <v>405</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>404.95</v>
+        <v>403</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>408.2</v>
+        <v>405.35</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>404.25</v>
+        <v>398.6</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>405</v>
+        <v>398.6</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0</v>
+        <v>-6.4</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>286</v>
+        <v>299.8</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>295.1</v>
+        <v>300.9</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>308.35</v>
+        <v>307</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>294.75</v>
+        <v>298.05</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>299.8</v>
+        <v>303.8</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>13.8</v>
+        <v>4</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>4.83</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2159.4</v>
+        <v>2250</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2154.6</v>
+        <v>2250</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2281</v>
+        <v>2255</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2150.4</v>
+        <v>2198.8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2250</v>
+        <v>2215</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>4.2</v>
+        <v>-35</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8692</v>
+        <v>8650</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8702.5</v>
+        <v>8682</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8740</v>
+        <v>8840.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8641</v>
+        <v>8650</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8650</v>
+        <v>8760</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-42</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>-0.48</v>
+        <v>110</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>433.85</v>
+        <v>429.55</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>433.85</v>
+        <v>428</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>435.15</v>
+        <v>430</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>428.25</v>
+        <v>419</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>429.55</v>
+        <v>420.8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-4.3</v>
+        <v>-8.75</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-0.99</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>169.35</v>
+        <v>169</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>168.98</v>
+        <v>170</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>173.29</v>
+        <v>172.13</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>168.18</v>
+        <v>168.4</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-0.21</v>
+        <v>1</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2541.6</v>
+        <v>2527.3</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2540</v>
+        <v>2511.1</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2553.9</v>
+        <v>2523.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2519.8</v>
+        <v>2489.7</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2527.3</v>
+        <v>2500.9</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-14.3</v>
+        <v>-26.4</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1495.2</v>
+        <v>1492.9</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1489.8</v>
+        <v>1482.7</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1509.9</v>
+        <v>1501.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1484</v>
+        <v>1482.2</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1492.9</v>
+        <v>1498.2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-0.15</v>
+        <v>5.3</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>614.05</v>
+        <v>612.35</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>614</v>
+        <v>613.05</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>619.8</v>
+        <v>617</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>610.55</v>
+        <v>601.9</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>612.35</v>
+        <v>603.7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-1.7</v>
+        <v>-8.65</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-0.28</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6469</v>
+        <v>6386</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6476</v>
+        <v>6351.5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6515.5</v>
+        <v>6400</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6370.5</v>
+        <v>6302.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6386</v>
+        <v>6312.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-83</v>
+        <v>-73.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-1.28</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1071.9</v>
+        <v>1065</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1074.1</v>
+        <v>1066.8</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1060.4</v>
+        <v>1046.9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-0.65</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1637.3</v>
+        <v>1653.1</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1637.3</v>
+        <v>1646</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1661.5</v>
+        <v>1668</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1622.6</v>
+        <v>1646</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1653.1</v>
+        <v>1660</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>15.8</v>
+        <v>6.9</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.97</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1270.3</v>
+        <v>1271</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1280.7</v>
+        <v>1271.9</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1262</v>
+        <v>1261.6</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>0.47</v>
+        <v>-7</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11920</v>
+        <v>11919</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>12005</v>
+        <v>11810</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>12025</v>
+        <v>11860</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11873</v>
+        <v>11727</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11919</v>
+        <v>11800</v>
       </c>
       <c r="I25" s="9" t="n">
+        <v>-119</v>
+      </c>
+      <c r="J25" s="10" t="n">
         <v>-1</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1992.1</v>
+        <v>1970</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1985</v>
+        <v>1968</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1994.2</v>
+        <v>1973</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-22.1</v>
+        <v>-31.4</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-1.11</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1049</v>
+        <v>1060.5</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1050.6</v>
+        <v>1064</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1063.6</v>
+        <v>1070</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1049.7</v>
+        <v>1054.3</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1060.5</v>
+        <v>1060</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>1.1</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2327.3</v>
+        <v>2284.6</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2330</v>
+        <v>2273</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2346.3</v>
+        <v>2295</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2264</v>
+        <v>2242.6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2284.6</v>
+        <v>2287.1</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-42.7</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-1.83</v>
+        <v>2.5</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>704.35</v>
+        <v>690.6</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>682.5</v>
+        <v>695</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>690.6</v>
+        <v>711.55</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-13.75</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>-1.95</v>
+        <v>20.95</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>3.03</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>164.23</v>
+        <v>164.95</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>165.11</v>
+        <v>164.95</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>166.74</v>
+        <v>166.42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>164.5</v>
+        <v>161.67</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>164.95</v>
+        <v>164.7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>0.44</v>
+        <v>-0.25</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>240.44</v>
+        <v>239</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>242.37</v>
+        <v>240</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>242.37</v>
+        <v>240.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>239</v>
+        <v>235.2</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-1.44</v>
+        <v>-2</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-0.6</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>408.6</v>
+        <v>405.35</v>
       </c>
       <c r="E32" s="12" t="n">
+        <v>406.35</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>409.25</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>413.1</v>
-      </c>
       <c r="G32" s="12" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-3.25</v>
+        <v>-1.35</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-0.8</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>491.4</v>
+        <v>485.3</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>494</v>
+        <v>485.4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>496.7</v>
+        <v>488.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>484</v>
+        <v>480.55</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>485.3</v>
+        <v>484.5</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-6.1</v>
+        <v>-0.8</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>-1.24</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1869</v>
+        <v>1840</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1868.1</v>
+        <v>1845</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1870.7</v>
+        <v>1855.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1840</v>
+        <v>1830.4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1840</v>
+        <v>1854</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>-1.55</v>
+        <v>14</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>431.8</v>
+        <v>431.1</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>433</v>
+        <v>432.9</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>439.2</v>
+        <v>434.95</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>429.2</v>
+        <v>418.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>431.1</v>
+        <v>421.45</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-0.7</v>
+        <v>-9.65</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>-0.16</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>402</v>
+        <v>397.4</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>404</v>
+        <v>396.5</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>404.9</v>
+        <v>397.35</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>396.2</v>
+        <v>388.65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>397.4</v>
+        <v>391.4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-4.6</v>
+        <v>-6</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>-1.14</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47000</v>
+        <v>46820</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47195</v>
+        <v>46750</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>47200</v>
+        <v>48550</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>46660</v>
+        <v>46535</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>46820</v>
+        <v>48025</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-180</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>-0.38</v>
+        <v>1205</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>2.57</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>320.05</v>
+        <v>315.7</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>319.4</v>
+        <v>314.9</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>320.65</v>
+        <v>316.7</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>315.7</v>
+        <v>311.2</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>315.7</v>
+        <v>312.9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-4.35</v>
+        <v>-2.8</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-1.36</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5130</v>
+        <v>5101.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5155</v>
+        <v>5126</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5160.5</v>
+        <v>5126</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5089.5</v>
+        <v>5005.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5101.5</v>
+        <v>5042.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-28.5</v>
+        <v>-59</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>293.25</v>
+        <v>289.35</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>295</v>
+        <v>289.35</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>299.55</v>
+        <v>289.4</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>288.45</v>
+        <v>281.15</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>289.35</v>
+        <v>282.45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-3.9</v>
+        <v>-6.9</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-1.33</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>125.8</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>126.3</v>
-      </c>
       <c r="F41" s="9" t="n">
-        <v>127.3</v>
+        <v>126.35</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>125.5</v>
+        <v>124</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>125.5</v>
+        <v>124</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.24</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>804.95</v>
+        <v>807.4</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>808</v>
+        <v>805.8</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>815</v>
+        <v>814.4</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>802.6</v>
+        <v>795</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>807.4</v>
+        <v>805.45</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>0.3</v>
+        <v>-1.95</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>418.3</v>
+        <v>419.05</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>419.9</v>
+        <v>420</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>422.95</v>
+        <v>421.95</v>
       </c>
       <c r="G43" s="9" t="n">
+        <v>416.45</v>
+      </c>
+      <c r="H43" s="9" t="n">
         <v>418.05</v>
       </c>
-      <c r="H43" s="9" t="n">
-        <v>419.05</v>
-      </c>
       <c r="I43" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>0.18</v>
+        <v>-1</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1849.3</v>
+        <v>1839</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1841</v>
+        <v>1838.6</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1859.9</v>
+        <v>1848.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1828</v>
+        <v>1798.3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1839</v>
+        <v>1848.2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1394.7</v>
+        <v>1385</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1397.7</v>
+        <v>1380</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1399.1</v>
+        <v>1395.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1375.5</v>
+        <v>1376.8</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>-0.7</v>
+        <v>10</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>414.8</v>
+        <v>415.35</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>418</v>
+        <v>416.6</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>418</v>
+        <v>420.3</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>412.55</v>
+        <v>413.3</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>415.35</v>
+        <v>418.85</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0.55</v>
+        <v>3.5</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.13</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1971.8</v>
+        <v>1972.8</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1982</v>
+        <v>1958</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1992.9</v>
+        <v>1958.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1962.4</v>
+        <v>1920.4</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1972.8</v>
+        <v>1935</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>0.05</v>
+        <v>-37.8</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1850</v>
+        <v>1829.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1860</v>
+        <v>1836</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1863.9</v>
+        <v>1838.9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1829.2</v>
+        <v>1807.3</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1829.2</v>
+        <v>1813.5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-20.8</v>
+        <v>-15.7</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>-1.12</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>508.85</v>
+        <v>508</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>508.8</v>
+        <v>507.9</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>509.65</v>
+        <v>510.3</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>502</v>
+        <v>501.3</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>508</v>
+        <v>503.9</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-0.85</v>
+        <v>-4.1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-0.17</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1931.3</v>
+        <v>1938.8</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1927</v>
+        <v>1937.1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1948.3</v>
+        <v>1980</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1927</v>
+        <v>1925.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1938.8</v>
+        <v>1974.6</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>7.5</v>
+        <v>35.8</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.39</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>226.51</v>
+        <v>232.4</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>227.64</v>
+        <v>231.99</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>235.47</v>
+        <v>233.18</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>226.27</v>
+        <v>229.63</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>232.4</v>
+        <v>231.02</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>2.6</v>
+        <v>-1.38</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>234.36</v>
+        <v>236.01</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>234</v>
+        <v>235.5</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>242.9</v>
+        <v>248.85</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>233.69</v>
+        <v>234.2</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>236.01</v>
+        <v>238.48</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5071</v>
+        <v>5035</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5071</v>
+        <v>5035</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5083</v>
+        <v>5072</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5013</v>
+        <v>4985</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5035</v>
+        <v>5030</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-36</v>
+        <v>-5</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.71</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>380.7</v>
+        <v>380.9</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>380.45</v>
+        <v>380.9</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>383.25</v>
+        <v>381.8</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>377.35</v>
+        <v>373.8</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>380.9</v>
+        <v>375.5</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>0.05</v>
+        <v>-5.4</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1771.2</v>
+        <v>1749.3</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1770.1</v>
+        <v>1750</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1778.9</v>
+        <v>1752.1</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1740</v>
+        <v>1701.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1749.3</v>
+        <v>1713.9</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-21.9</v>
+        <v>-35.4</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-1.24</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1725.3</v>
+        <v>1712.4</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1728</v>
+        <v>1712.4</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1743.7</v>
+        <v>1728.3</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1705.7</v>
+        <v>1636.5</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1712.4</v>
+        <v>1642.1</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-12.9</v>
+        <v>-70.3</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-0.75</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="E57" s="9" t="n">
         <v>56.25</v>
       </c>
-      <c r="E57" s="9" t="n">
-        <v>56.79</v>
-      </c>
       <c r="F57" s="9" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>55.56</v>
+        <v>56</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>56.12</v>
+        <v>56.2</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>-0.23</v>
+        <v>0.08</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9250</v>
+        <v>9100</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9244</v>
+        <v>9119.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9269</v>
+        <v>9315</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9100</v>
+        <v>9119.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9100</v>
+        <v>9315</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-150</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>-1.62</v>
+        <v>215</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>14445</v>
+        <v>14240</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>14445</v>
+        <v>14227</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>14463</v>
+        <v>14429</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>14070</v>
+        <v>13937</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14240</v>
+        <v>14180</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-205</v>
+        <v>-60</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-1.42</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>681.65</v>
+        <v>681.9</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>681.65</v>
+        <v>685</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>689.75</v>
+        <v>685</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>680.8</v>
+        <v>672.7</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>681.9</v>
+        <v>672.7</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>0.04</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1157</v>
+        <v>1150.5</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1166.8</v>
+        <v>1163.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1151</v>
+        <v>1141.8</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1151</v>
+        <v>1144.2</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-4</v>
+        <v>-6.8</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>-0.35</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7690</v>
+        <v>7630.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7665</v>
+        <v>7658</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7665.5</v>
+        <v>7729</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7590</v>
+        <v>7615</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7630.5</v>
+        <v>7672</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-59.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-0.77</v>
+        <v>41.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2978.2</v>
+        <v>2968.8</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2993</v>
+        <v>2965</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3001</v>
+        <v>2985.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2960.3</v>
+        <v>2936</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2968.8</v>
+        <v>2957.4</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-9.4</v>
+        <v>-11.4</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>-0.32</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>423</v>
+        <v>424.35</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>423.9</v>
+        <v>422.3</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>428.5</v>
+        <v>427.5</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>416.4</v>
+        <v>416.6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>424.35</v>
+        <v>425.75</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>344.6</v>
+        <v>343</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>344.9</v>
+        <v>343</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>344.9</v>
+        <v>343</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>341.8</v>
+        <v>337.6</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>-0.46</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>174.67</v>
+        <v>173.4</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>174.27</v>
+        <v>173.4</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>174.27</v>
+        <v>177.3</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>171.92</v>
+        <v>172.8</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>173.4</v>
+        <v>176</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>-0.73</v>
+        <v>2.6</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2459</v>
+        <v>2437.2</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2454.5</v>
+        <v>2420.2</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2456.7</v>
+        <v>2472</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2422.7</v>
+        <v>2420.2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2437.2</v>
+        <v>2451.9</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>-0.89</v>
+        <v>14.7</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>588.9</v>
+        <v>601.7</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>599</v>
+        <v>605.7</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>585.6</v>
+        <v>594.2</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>9.35</v>
+        <v>1.2</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>1.59</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>878.65</v>
+        <v>878.5</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>880</v>
+        <v>879.05</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>866.1</v>
+        <v>857.1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-2</v>
+        <v>-16.1</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>-0.23</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2001.5</v>
+        <v>1982</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>2000</v>
+        <v>1982</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>2021.7</v>
+        <v>1984</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1971</v>
+        <v>1891.1</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-19.5</v>
+        <v>-59.8</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-0.97</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>853.85</v>
+        <v>848.3</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>853</v>
+        <v>844.5</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>863.6</v>
+        <v>873.85</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>838.6</v>
+        <v>842.2</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>848.3</v>
+        <v>867.3</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-5.55</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>-0.65</v>
+        <v>19</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>2.24</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3310</v>
+        <v>3322</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3318.9</v>
+        <v>3322</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3332.6</v>
+        <v>3327.7</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3268.1</v>
+        <v>3293</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3322</v>
+        <v>3302.4</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>0.36</v>
+        <v>-19.6</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4765.6</v>
+        <v>4856</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4831</v>
+        <v>4884.8</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4936</v>
+        <v>4909.9</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4817.4</v>
+        <v>4835.4</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4856</v>
+        <v>4855.2</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>1.9</v>
+        <v>-0.8</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1200</v>
+        <v>1154</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1178</v>
+        <v>1159.6</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1178</v>
+        <v>1159.7</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1149.7</v>
+        <v>1140</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-46</v>
+        <v>-4</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-3.83</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1319</v>
+        <v>1293.4</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1324.9</v>
+        <v>1271.7</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1331.4</v>
+        <v>1286.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1291.2</v>
+        <v>1263</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1293.4</v>
+        <v>1282.8</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-25.6</v>
+        <v>-10.6</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>-1.94</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2510.8</v>
+        <v>2458.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2511.3</v>
+        <v>2468.8</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2517.8</v>
+        <v>2473.6</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2456</v>
+        <v>2432</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2458.3</v>
+        <v>2432</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-52.5</v>
+        <v>-26.3</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-2.09</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>706.65</v>
+        <v>712.1</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>708.35</v>
+        <v>712.1</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>716.5</v>
+        <v>713</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>708.35</v>
+        <v>707.05</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>712.1</v>
+        <v>710.5</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>0.77</v>
+        <v>-1.6</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>533.5</v>
+        <v>546.4</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>533.7</v>
+        <v>546.4</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>548</v>
+        <v>546.4</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>533.3</v>
+        <v>533.2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>546.4</v>
+        <v>533.2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>2.42</v>
+        <v>-13.2</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5308.5</v>
+        <v>5300</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5319</v>
+        <v>5300</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5322.5</v>
+        <v>5347.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5260</v>
+        <v>5270</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-8.5</v>
+        <v>-30</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>-0.16</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1012.9</v>
+        <v>1011.1</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1020.8</v>
+        <v>1014.8</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1005</v>
+        <v>999.8</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>0.1</v>
+        <v>-5</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>518.5</v>
+        <v>521.65</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>522.15</v>
+        <v>521.6</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>523.95</v>
+        <v>521.6</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>518</v>
+        <v>506.6</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>521.65</v>
+        <v>509.1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>0.61</v>
+        <v>-12.55</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>361.35</v>
+        <v>356.5</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>359.9</v>
+        <v>355</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>360.05</v>
+        <v>356.9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>355.55</v>
+        <v>349.55</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>356.5</v>
+        <v>356.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>-1.34</v>
+        <v>0.4</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1962</v>
+        <v>1973.4</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1984.2</v>
+        <v>1974.2</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1950.4</v>
+        <v>1958</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1973.4</v>
+        <v>1960</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>0.58</v>
+        <v>-13.4</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>35265</v>
+        <v>35655</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35265</v>
+        <v>35660</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>35870</v>
+        <v>35895</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>35265</v>
+        <v>35380</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>35655</v>
+        <v>35565</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>390</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>1.11</v>
+        <v>-90</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>87.5</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>87.81</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>87.98</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>86.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.70999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.79</v>
+        <v>-0.27</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-0.9</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>119.15</v>
+        <v>118.91</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>121</v>
+        <v>119.49</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>121.63</v>
+        <v>119.88</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>118.51</v>
+        <v>117.21</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>118.91</v>
+        <v>117.5</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-0.24</v>
+        <v>-1.41</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>-0.2</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>149.42</v>
+        <v>158.04</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>150.5</v>
+        <v>157</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>159.5</v>
+        <v>157</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>150.5</v>
+        <v>154.5</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>158.04</v>
+        <v>154.8</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>5.77</v>
+        <v>-3.24</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>730</v>
+        <v>719.9</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>732.95</v>
+        <v>720.45</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>717.5</v>
+        <v>709.2</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>720</v>
+        <v>716.2</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-12</v>
+        <v>-3.8</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>-1.64</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1729.5</v>
+        <v>1726.4</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1730</v>
+        <v>1726.4</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1745</v>
+        <v>1727.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1722.5</v>
+        <v>1703.4</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1726.4</v>
+        <v>1706.4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-3.1</v>
+        <v>-20</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>-0.18</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4980</v>
+        <v>4977</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5035</v>
+        <v>5008</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4977</v>
+        <v>4944</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4977</v>
+        <v>5001</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-0.06</v>
+        <v>24</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1004.8</v>
+        <v>1008.5</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>1004.8</v>
+        <v>1004.1</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1008.6</v>
+        <v>1017.9</v>
       </c>
       <c r="G93" s="9" t="n">
+        <v>995</v>
+      </c>
+      <c r="H93" s="9" t="n">
         <v>998</v>
       </c>
-      <c r="H93" s="9" t="n">
-        <v>1008.5</v>
-      </c>
       <c r="I93" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>0.37</v>
+        <v>-10.5</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>374.95</v>
+        <v>376.8</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>375</v>
+        <v>379.25</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>380.45</v>
+        <v>383.75</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>374.15</v>
+        <v>376</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>376.8</v>
+        <v>376.45</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>0.49</v>
+        <v>-0.35</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1130.3</v>
+        <v>1130</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1133</v>
+        <v>1109.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1146.7</v>
+        <v>1109.9</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1125.4</v>
+        <v>1085</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1130</v>
+        <v>1087.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-0.3</v>
+        <v>-42.5</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-0.03</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>137.8</v>
+        <v>137.6</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>137</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137.76</v>
+        <v>137.5</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>136.87</v>
+        <v>135.15</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>137.6</v>
+        <v>135.15</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.2</v>
+        <v>-2.45</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-0.15</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1956.1</v>
+        <v>1965.3</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1950</v>
+        <v>1965.4</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1969</v>
+        <v>1978.4</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1944.2</v>
+        <v>1943.7</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1965.3</v>
+        <v>1959.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>0.47</v>
+        <v>-6.2</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>474.6</v>
+        <v>476.05</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>474.8</v>
+        <v>476.05</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>479</v>
+        <v>477.7</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>474.05</v>
+        <v>473.65</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>476.05</v>
+        <v>474.5</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>0.31</v>
+        <v>-1.55</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>263</v>
+        <v>264.1</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>264</v>
+        <v>264.1</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>266.25</v>
+        <v>264.95</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>262.65</v>
+        <v>262.95</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>0.42</v>
+        <v>-0.6</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1145</v>
+        <v>1165</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1147</v>
+        <v>1164.5</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1170.9</v>
+        <v>1168</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1138.7</v>
+        <v>1130</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1165</v>
+        <v>1147.9</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>1.75</v>
+        <v>-17.1</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5039.5</v>
+        <v>5083.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5044</v>
+        <v>5083.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5126</v>
+        <v>5106.5</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5025.5</v>
+        <v>5021</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5083.5</v>
+        <v>5047</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>0.87</v>
+        <v>-36.5</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>738.4</v>
+        <v>737.85</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>738.4</v>
+        <v>737.95</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>741.25</v>
+        <v>741</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>737.85</v>
+        <v>736.8</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-0.55</v>
+        <v>-1.05</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>539.5</v>
+        <v>539.85</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>537.55</v>
+        <v>539.9</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>540.25</v>
+        <v>541.25</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>534.25</v>
+        <v>528</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>539.85</v>
+        <v>530</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>0.06</v>
+        <v>-9.85</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1308</v>
+        <v>1325</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1305</v>
+        <v>1334.3</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1331.7</v>
+        <v>1335</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1300.1</v>
+        <v>1301</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>1.3</v>
+        <v>-23</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>482.9</v>
+        <v>482.7</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>482.9</v>
+        <v>482</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>488</v>
+        <v>484.2</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>481.35</v>
+        <v>472.1</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>482.7</v>
+        <v>475.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-0.2</v>
+        <v>-7.3</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-0.04</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1260.6</v>
+        <v>1239.6</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1260.6</v>
+        <v>1235</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1262</v>
+        <v>1239.6</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1235</v>
+        <v>1215</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1239.6</v>
+        <v>1220.5</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-21</v>
+        <v>-19.1</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-1.67</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>421.15</v>
+        <v>424.5</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>421.65</v>
+        <v>421.8</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>425.95</v>
+        <v>425.7</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>421.65</v>
+        <v>421</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>0.8</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>583.5</v>
+        <v>575.45</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>584</v>
+        <v>575.85</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>593.6</v>
+        <v>575.9</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>575.45</v>
+        <v>562.25</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-8.050000000000001</v>
+        <v>-13.2</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>-1.38</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1925.2</v>
+        <v>1877.5</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1920.5</v>
+        <v>1880</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1925.2</v>
+        <v>1913</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1855.7</v>
+        <v>1870.1</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1877.5</v>
+        <v>1901.9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-47.7</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-2.48</v>
+        <v>24.4</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1868.5</v>
+        <v>1840</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1855</v>
+        <v>1840</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1871.8</v>
+        <v>1876.7</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1835.2</v>
+        <v>1832.7</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1840</v>
+        <v>1876.7</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-28.5</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>-1.53</v>
+        <v>36.7</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>554</v>
+        <v>562.05</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>554</v>
+        <v>563.15</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>579.4</v>
+        <v>567.6</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>562.05</v>
+        <v>552</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>1.45</v>
+        <v>-10.05</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3975</v>
+        <v>3964.1</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3981</v>
+        <v>3962</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3994.9</v>
+        <v>4004.9</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3964.1</v>
+        <v>3960.9</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>-0.27</v>
+        <v>34.9</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>316.9</v>
+        <v>314</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>320.5</v>
+        <v>315.3</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>313.4</v>
+        <v>310.9</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.9</v>
+        <v>-1.5</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>-0.92</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3501.2</v>
+        <v>3493.3</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3520</v>
+        <v>3470</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3535.8</v>
+        <v>3484.8</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3462</v>
+        <v>3400.1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3493.3</v>
+        <v>3414.2</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-7.9</v>
+        <v>-79.09999999999999</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.23</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2132</v>
+        <v>2110</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2140.1</v>
+        <v>2121.1</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2148</v>
+        <v>2135.5</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2100.6</v>
+        <v>2095.6</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-22</v>
+        <v>-5</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-1.03</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3150</v>
+        <v>3170</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3158.7</v>
+        <v>3154.1</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3185.3</v>
+        <v>3178</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3144.2</v>
+        <v>3145</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>0.63</v>
+        <v>-10</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>341</v>
+        <v>339.7</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>345.05</v>
+        <v>332.35</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>345.2</v>
+        <v>332.35</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>338.2</v>
+        <v>323.15</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>339.7</v>
+        <v>325.6</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-1.3</v>
+        <v>-14.1</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-0.38</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>827.4</v>
+        <v>815.15</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>824.05</v>
+        <v>815.15</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>824.7</v>
+        <v>819.05</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>814.1</v>
+        <v>802.5</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>815.15</v>
+        <v>806</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-12.25</v>
+        <v>-9.15</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-1.48</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12857</v>
+        <v>12694</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12880</v>
+        <v>12691</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12880</v>
+        <v>12833</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12656</v>
+        <v>12618</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12694</v>
+        <v>12760</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-163</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-1.27</v>
+        <v>66</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3170.2</v>
+        <v>3275.4</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3187.8</v>
+        <v>3276.9</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3287.4</v>
+        <v>3374.4</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3165.6</v>
+        <v>3276.9</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3275.4</v>
+        <v>3330.2</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>105.2</v>
+        <v>54.8</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>3.32</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>591.9</v>
+        <v>588.7</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>593.4</v>
+        <v>588.7</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>593.4</v>
+        <v>588.7</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>584.9</v>
+        <v>574.4</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>588.7</v>
+        <v>577.75</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-3.2</v>
+        <v>-10.95</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-0.54</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1537</v>
+        <v>1548.4</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1537</v>
+        <v>1537.5</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1569</v>
+        <v>1544.3</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1531.4</v>
+        <v>1510</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1548.4</v>
+        <v>1520</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>0.74</v>
+        <v>-28.4</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1066.4</v>
+        <v>1096.6</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1067</v>
+        <v>1097</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1101.6</v>
+        <v>1105</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1067</v>
+        <v>1088.1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1096.6</v>
+        <v>1092.1</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>2.83</v>
+        <v>-4.5</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
+        <v>160.7</v>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>164.65</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>160.12</v>
+      </c>
+      <c r="H126" s="12" t="n">
         <v>162</v>
       </c>
-      <c r="E126" s="12" t="n">
-        <v>162.01</v>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>162.9</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>160.26</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>160.7</v>
-      </c>
       <c r="I126" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>-0.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2471</v>
+        <v>2422</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2482</v>
+        <v>2409.9</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2502.7</v>
+        <v>2409.9</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2417.3</v>
+        <v>2340.3</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2422</v>
+        <v>2369.1</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-49</v>
+        <v>-52.9</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-1.98</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>130510</v>
+        <v>129945</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>130950</v>
+        <v>130200</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>131080</v>
+        <v>130300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>129705</v>
+        <v>128705</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>129945</v>
+        <v>128890</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-565</v>
+        <v>-1055</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>-0.43</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2926.5</v>
+        <v>2913.8</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2971</v>
+        <v>2899</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2979.9</v>
+        <v>2920</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2913</v>
+        <v>2871.2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2913.8</v>
+        <v>2880</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-12.7</v>
+        <v>-33.8</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-0.43</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>374</v>
+        <v>374.1</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>376</v>
+        <v>376.05</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>378.95</v>
+        <v>377.5</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>372.75</v>
+        <v>365.9</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>374.1</v>
+        <v>365.9</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>0.03</v>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1330</v>
+        <v>1319.8</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1330.5</v>
+        <v>1319</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1349.5</v>
+        <v>1321.8</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1313.1</v>
+        <v>1284.4</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1319.8</v>
+        <v>1302.5</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-10.2</v>
+        <v>-17.3</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>-0.77</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8697</v>
+        <v>8557.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8700</v>
+        <v>8557.5</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8700</v>
+        <v>8649</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8512</v>
+        <v>8532.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8557.5</v>
+        <v>8603.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-139.5</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>-1.6</v>
+        <v>46</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1416</v>
+        <v>1410.5</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1415</v>
+        <v>1401</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1420</v>
+        <v>1405.7</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1402.5</v>
+        <v>1392.9</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1410.5</v>
+        <v>1398</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-5.5</v>
+        <v>-12.5</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>-0.39</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>84.19</v>
+        <v>84.7</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>84.52</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>85.18000000000001</v>
+        <v>85.63</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>84.26000000000001</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>84.7</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>0.61</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>330.9</v>
+        <v>332.5</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>332.75</v>
+        <v>332.5</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>334.05</v>
+        <v>333.8</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>329.8</v>
+        <v>330.35</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>0.48</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1902</v>
+        <v>1875.6</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1914</v>
+        <v>1876</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1932.8</v>
+        <v>1885.5</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1874</v>
+        <v>1847.5</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1875.6</v>
+        <v>1847.5</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-26.4</v>
+        <v>-28.1</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-1.39</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>12149</v>
+        <v>12058</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>12199</v>
+        <v>12105</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>12348</v>
+        <v>12110</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>12028</v>
+        <v>11679</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>12058</v>
+        <v>11847</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-91</v>
+        <v>-211</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>-0.75</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>235</v>
+        <v>234.65</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>235.44</v>
+        <v>235.98</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>235.44</v>
+        <v>235.98</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>233.6</v>
+        <v>232.77</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>234.65</v>
+        <v>233.7</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-0.35</v>
+        <v>-0.95</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>-0.15</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35865</v>
+        <v>36300</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35865</v>
+        <v>36300</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>36370</v>
+        <v>36495</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35680</v>
+        <v>35625</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36300</v>
+        <v>35825</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>435</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>1.21</v>
+        <v>-475</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5680</v>
+        <v>5610</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5724.5</v>
+        <v>5622</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5634</v>
+        <v>5522</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5643</v>
+        <v>5540</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-14</v>
+        <v>-103</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>-0.25</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>289.5</v>
+        <v>288.1</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>290.25</v>
+        <v>288.1</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>292.15</v>
+        <v>293.8</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>287.8</v>
+        <v>288.1</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>288.1</v>
+        <v>290.95</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>-0.48</v>
+        <v>2.85</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>345.5</v>
+        <v>355.6</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>344.9</v>
+        <v>355.75</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>357.7</v>
+        <v>359.15</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>355.6</v>
+        <v>353.1</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>2.92</v>
+        <v>-2.5</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1638.3</v>
+        <v>1629.5</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1635.2</v>
+        <v>1625.9</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1638.3</v>
+        <v>1628.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1625</v>
+        <v>1575</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1629.5</v>
+        <v>1575</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-8.800000000000001</v>
+        <v>-54.5</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-0.54</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2419.9</v>
+        <v>2465</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2415</v>
+        <v>2454</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2509</v>
+        <v>2468.5</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2410</v>
+        <v>2428</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2465</v>
+        <v>2430</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>1.86</v>
+        <v>-35</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116.9</v>
+        <v>116.41</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.05</v>
+        <v>117.17</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.45</v>
+        <v>115.55</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>117</v>
+        <v>115.6</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>0.58</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8807.5</v>
+        <v>8300</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8500</v>
+        <v>8310</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8500</v>
+        <v>8361.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8250</v>
+        <v>8175</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8300</v>
+        <v>8261</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-507.5</v>
+        <v>-39</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>-5.76</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>265.6</v>
+        <v>266</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>266.9</v>
+        <v>266</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>267.5</v>
+        <v>268.8</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>265.05</v>
+        <v>264.25</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>266</v>
+        <v>266.45</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1247.5</v>
+        <v>1227.2</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1216</v>
+        <v>1199.1</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1232.8</v>
+        <v>1199.1</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1215</v>
+        <v>1125.7</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1227.2</v>
+        <v>1156.5</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-20.3</v>
+        <v>-70.7</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-1.63</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>408.1</v>
+        <v>414.35</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>417.05</v>
+        <v>418.25</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>406.7</v>
+        <v>407.85</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>414.35</v>
+        <v>415</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>6.25</v>
+        <v>0.65</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>1.53</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>313.6</v>
+        <v>318.7</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>313.6</v>
+        <v>319</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>320.2</v>
+        <v>321.4</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>313.2</v>
+        <v>316.05</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>318.7</v>
+        <v>316.4</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>1.63</v>
+        <v>-2.3</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1302.5</v>
+        <v>1322</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1304.1</v>
+        <v>1323.1</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1333</v>
+        <v>1324.2</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1304.1</v>
+        <v>1301.9</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>1.5</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>197</v>
+        <v>196.8</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>197.86</v>
+        <v>196.99</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>200.1</v>
+        <v>196.99</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>194.3</v>
+        <v>187.3</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>196.8</v>
+        <v>187.9</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-0.2</v>
+        <v>-8.9</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>-0.1</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>661</v>
+        <v>658.25</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>661</v>
+        <v>653.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>668.7</v>
+        <v>674.65</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>656.3</v>
+        <v>648.75</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>658.25</v>
+        <v>674.65</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>-0.42</v>
+        <v>16.4</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1715</v>
+        <v>1775</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1715</v>
+        <v>1775</v>
       </c>
       <c r="F155" s="9" t="n">
         <v>1775</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1707.4</v>
+        <v>1727.8</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1775</v>
+        <v>1732</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>3.5</v>
+        <v>-43</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1023.4</v>
+        <v>1016.1</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1026</v>
+        <v>1020.8</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1029.2</v>
+        <v>1021.7</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1016.1</v>
+        <v>1000.6</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-7.3</v>
+        <v>-10.2</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0.71</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>23910</v>
+        <v>23855</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>23850</v>
+        <v>23855</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>24140</v>
+        <v>23920</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>23780</v>
+        <v>23365</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>23855</v>
+        <v>23365</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-55</v>
+        <v>-490</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>-0.23</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1044.2</v>
+        <v>1041</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1044.2</v>
+        <v>1045</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1052.8</v>
+        <v>1046.1</v>
       </c>
       <c r="G158" s="12" t="n">
+        <v>1029.3</v>
+      </c>
+      <c r="H158" s="12" t="n">
         <v>1037</v>
       </c>
-      <c r="H158" s="12" t="n">
-        <v>1041</v>
-      </c>
       <c r="I158" s="12" t="n">
-        <v>-3.2</v>
+        <v>-4</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>-0.31</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>4030</v>
+        <v>3977</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>4042</v>
+        <v>3990</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>4042</v>
+        <v>3998.1</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3974.1</v>
+        <v>3904.1</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3977</v>
+        <v>3927</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-53</v>
+        <v>-50</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>-1.32</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2617</v>
+        <v>2547</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2631.1</v>
+        <v>2536.2</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2631.1</v>
+        <v>2560</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2532.2</v>
+        <v>2526.5</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-70</v>
+        <v>-1</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>-2.67</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1912</v>
+        <v>1899</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1917.3</v>
+        <v>1907.8</v>
       </c>
       <c r="G161" s="9" t="n">
+        <v>1883.1</v>
+      </c>
+      <c r="H161" s="9" t="n">
         <v>1895</v>
       </c>
-      <c r="H161" s="9" t="n">
-        <v>1899</v>
-      </c>
       <c r="I161" s="9" t="n">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-0.89</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>465.9</v>
+        <v>470.9</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>465.95</v>
+        <v>470.95</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>482.7</v>
+        <v>470.95</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>464.95</v>
+        <v>451.5</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>470.9</v>
+        <v>452.85</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>1.07</v>
+        <v>-18.05</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>400.8</v>
+        <v>395.6</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>399.7</v>
+        <v>395</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>403.15</v>
+        <v>396.3</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>394.3</v>
+        <v>387.25</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>395.6</v>
+        <v>389.3</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-5.2</v>
+        <v>-6.3</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>641.35</v>
+        <v>625.1</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>634.5</v>
+        <v>627.15</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>624</v>
+        <v>611.1</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>625.1</v>
+        <v>613.35</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-16.25</v>
+        <v>-11.75</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-2.53</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1696.4</v>
+        <v>1756.1</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1696.4</v>
+        <v>1754.1</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1763</v>
+        <v>1754.1</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1696.4</v>
+        <v>1725</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1756.1</v>
+        <v>1738.5</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>3.52</v>
+        <v>-17.6</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1019.2</v>
+        <v>1010</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1022.9</v>
+        <v>1019.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1008.5</v>
+        <v>1004</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>-0.9</v>
+        <v>5</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
+        <v>368</v>
+      </c>
+      <c r="E168" s="12" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>363</v>
+      </c>
+      <c r="H168" s="12" t="n">
         <v>365.7</v>
       </c>
-      <c r="E168" s="12" t="n">
-        <v>365.1</v>
-      </c>
-      <c r="F168" s="12" t="n">
-        <v>368.5</v>
-      </c>
-      <c r="G168" s="12" t="n">
-        <v>364.1</v>
-      </c>
-      <c r="H168" s="12" t="n">
-        <v>368</v>
-      </c>
       <c r="I168" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>0.63</v>
+        <v>-2.3</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>184.2</v>
+        <v>188.79</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>184.2</v>
+        <v>189</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>189.9</v>
+        <v>190.24</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>182.84</v>
+        <v>184.37</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>188.79</v>
+        <v>185.61</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>2.49</v>
+        <v>-3.18</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2320.1</v>
+        <v>2304</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2330</v>
+        <v>2290.1</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2363.9</v>
+        <v>2299.9</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2302.4</v>
+        <v>2260.1</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2304</v>
+        <v>2270</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-16.1</v>
+        <v>-34</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1598</v>
+        <v>1596.9</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1605.1</v>
+        <v>1575.1</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1623.4</v>
+        <v>1593.6</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1586.9</v>
+        <v>1545.3</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1596.9</v>
+        <v>1564</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-1.1</v>
+        <v>-32.9</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2735.4</v>
+        <v>2698</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2727</v>
+        <v>2690</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2727</v>
+        <v>2709</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2685</v>
+        <v>2679</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2698</v>
+        <v>2683</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-37.4</v>
+        <v>-15</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-1.37</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5027</v>
+        <v>5020</v>
       </c>
       <c r="E173" s="9" t="n">
         <v>5010</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5022</v>
+        <v>5028</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4980</v>
+        <v>4958.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>5020</v>
+        <v>4995</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-7</v>
+        <v>-25</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4905.5</v>
+        <v>4857</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4930</v>
+        <v>4857</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4941</v>
+        <v>4915</v>
       </c>
       <c r="G174" s="12" t="n">
         <v>4823</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4857</v>
+        <v>4914</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>-0.99</v>
+        <v>57</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1289.3</v>
+        <v>1299.1</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1289.9</v>
+        <v>1307</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1308</v>
+        <v>1323</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1260.2</v>
+        <v>1271.2</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1299.1</v>
+        <v>1275.7</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>0.76</v>
+        <v>-23.4</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2815.6</v>
+        <v>2853</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2849</v>
+        <v>2850</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2879</v>
+        <v>2854.4</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2833.2</v>
+        <v>2772.5</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2853</v>
+        <v>2814.5</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>1.33</v>
+        <v>-38.5</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4200</v>
+        <v>4133.1</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4181.2</v>
+        <v>4127</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4200</v>
+        <v>4159.9</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4127.8</v>
+        <v>4100.7</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4133.1</v>
+        <v>4132</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-66.90000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>-1.59</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1284.2</v>
+        <v>1279.4</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1299</v>
+        <v>1283.8</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1326</v>
+        <v>1305.1</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1277</v>
+        <v>1275.3</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1279.4</v>
+        <v>1291</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-0.37</v>
+        <v>11.6</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11275</v>
+        <v>11408</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11357</v>
+        <v>11370</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11434</v>
+        <v>11370</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11292</v>
+        <v>11175</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11408</v>
+        <v>11175</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>133</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>1.18</v>
+        <v>-233</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>189</v>
+        <v>187.22</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>189</v>
+        <v>186.5</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>189.95</v>
+        <v>188.45</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>187.05</v>
+        <v>183.2</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>187.22</v>
+        <v>186.04</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.78</v>
+        <v>-1.18</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>585.35</v>
+        <v>582.15</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>581.05</v>
+        <v>580.1</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>589.4</v>
+        <v>586.75</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>579.45</v>
+        <v>573</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>582.15</v>
+        <v>573</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-3.2</v>
+        <v>-9.15</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-0.55</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>270.5</v>
+        <v>272.1</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>272</v>
+        <v>272.1</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>274.5</v>
+        <v>272.5</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>268.85</v>
+        <v>267</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>272.1</v>
+        <v>268</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>0.59</v>
+        <v>-4.1</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1189.7</v>
+        <v>1176.4</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1167</v>
+        <v>1164.4</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1170</v>
+        <v>1167.2</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-8</v>
+        <v>-2.8</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-0.68</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>175.72</v>
+        <v>176.4</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>176.74</v>
+        <v>175.89</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>178.75</v>
+        <v>176.47</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>176.4</v>
+        <v>172.65</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>176.4</v>
+        <v>172.8</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>0.39</v>
+        <v>-3.6</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1143</v>
+        <v>1120</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1146</v>
+        <v>1114.2</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1146</v>
+        <v>1163</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1120</v>
+        <v>1114.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1120</v>
+        <v>1156.9</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-23</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>-2.01</v>
+        <v>36.9</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>3.29</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  04-Sep-2026 04:44 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  07-Sep-2026 06:06 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04-Sep-2026 04:44 PM</t>
+          <t>07-Sep-2026 06:06 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 07-Sep-2026 06:06 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 08-Sep-2026 05:04 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>07-Sep-2026 06:06 PM</t>
+          <t>08-Sep-2026 05:04 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  07-Sep-2026 06:06 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  08-Sep-2026 05:04 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>492.05</v>
+        <v/>
       </c>
       <c r="E3" s="9" t="n">
-        <v>493.25</v>
+        <v>490.7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>495.75</v>
+        <v>504.75</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>487.35</v>
+        <v>486.5</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>490.7</v>
+        <v>503.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-1.35</v>
+        <v/>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.27</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7410</v>
+        <v/>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7410</v>
+        <v>7389</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7459.5</v>
+        <v>7472</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7327</v>
+        <v>7340</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7434</v>
+        <v>7387</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>0.32</v>
+        <v/>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>25860</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>26065</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>26150</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>26195</v>
-      </c>
       <c r="G5" s="9" t="n">
-        <v>25810</v>
+        <v>25440</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25940</v>
+        <v>25555</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-125</v>
+        <v/>
       </c>
       <c r="J5" s="10" t="n">
-        <v>-0.48</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>404.9</v>
+        <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>404.75</v>
+        <v>401</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>399.5</v>
+        <v>394.45</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>403.25</v>
+        <v>396.95</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-1.65</v>
+        <v/>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-0.41</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>52.97</v>
+        <v>53.21</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>52.95</v>
+        <v>53.07</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>55.11</v>
+        <v>53.07</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>51.99</v>
+        <v>51.63</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>53.21</v>
+        <v>52.24</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>0.45</v>
+        <v>-0.97</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1283.8</v>
+        <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1287</v>
+        <v>1267.9</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1288.5</v>
+        <v>1268</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1265.5</v>
+        <v>1255.7</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1268.7</v>
+        <v>1262.8</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-15.1</v>
+        <v/>
       </c>
       <c r="J8" s="10" t="n">
-        <v>-1.18</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2940</v>
+        <v>2933</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2964.4</v>
+        <v>2968.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2918.5</v>
+        <v>2918</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2950</v>
+        <v>2953.1</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>12</v>
+        <v>3.1</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1707.3</v>
+        <v/>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1714</v>
+        <v>1694</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1716.4</v>
+        <v>1713.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1685.9</v>
+        <v>1685.2</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1694.3</v>
+        <v>1710</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-13</v>
+        <v/>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-0.76</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5190</v>
+        <v/>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5219</v>
+        <v>5172.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5242.5</v>
+        <v>5206.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5104.5</v>
+        <v>5129.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5242.5</v>
+        <v>5181</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>1.01</v>
+        <v/>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>405</v>
+        <v>398.6</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>405.35</v>
+        <v>400.95</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>398.6</v>
+        <v>395.15</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>398.6</v>
+        <v>398.3</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-6.4</v>
+        <v>-0.3</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-1.58</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>299.8</v>
+        <v/>
       </c>
       <c r="E13" s="9" t="n">
-        <v>300.9</v>
+        <v>303.8</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>307</v>
+        <v>304.15</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>298.05</v>
+        <v>296.5</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>303.8</v>
+        <v>298</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>1.33</v>
+        <v/>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2250</v>
+        <v>2206.5</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2250</v>
+        <v>2204.6</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2255</v>
+        <v>2204.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2198.8</v>
+        <v>2165</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2215</v>
+        <v>2185</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-35</v>
+        <v>-21.5</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-1.56</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8650</v>
+        <v/>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8682</v>
+        <v>8761.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8840.5</v>
+        <v>8850</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8650</v>
+        <v>8745</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8760</v>
+        <v>8837.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>1.27</v>
+        <v/>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>429.55</v>
+        <v>420.8</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>428</v>
+        <v>420.8</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>430</v>
+        <v>421.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>419</v>
+        <v>410.05</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>420.8</v>
+        <v>411.5</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-8.75</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-2.04</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>170</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>172.13</v>
+        <v>170.17</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>168.4</v>
+        <v>167.75</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>0.59</v>
+        <v>-1</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2527.3</v>
+        <v>2500.9</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2511.1</v>
+        <v>2499</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2523.5</v>
+        <v>2499</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2489.7</v>
+        <v>2474.1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2500.9</v>
+        <v>2481.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-26.4</v>
+        <v>-19.3</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-1.04</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1492.9</v>
+        <v/>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1482.7</v>
+        <v>1498.2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1501.5</v>
+        <v>1507.4</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1482.2</v>
+        <v>1485</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1498.2</v>
+        <v>1500.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>0.36</v>
+        <v/>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>612.35</v>
+        <v/>
       </c>
       <c r="E20" s="12" t="n">
-        <v>613.05</v>
+        <v>604.4</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>601.9</v>
+        <v>602</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>603.7</v>
+        <v>609.4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-8.65</v>
+        <v/>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-1.41</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6386</v>
+        <v/>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6351.5</v>
+        <v>6335</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6400</v>
+        <v>6356.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6302.5</v>
+        <v>6305</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6312.5</v>
+        <v>6314.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-73.5</v>
+        <v/>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-1.15</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1065</v>
+        <v/>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1065</v>
+        <v>1055.7</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1066.8</v>
+        <v>1074.8</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1046.9</v>
+        <v>1051.4</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1053</v>
+        <v>1073.7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-12</v>
+        <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-1.13</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1653.1</v>
+        <v/>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1646</v>
+        <v>1660.5</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1668</v>
+        <v>1698.8</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>0.42</v>
+        <v/>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1273</v>
+        <v/>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1271</v>
+        <v>1262.8</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1271.9</v>
+        <v>1264.9</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1261.6</v>
+        <v>1239.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1266</v>
+        <v>1244.9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-7</v>
+        <v/>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-0.55</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11919</v>
+        <v>11800</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11810</v>
+        <v>11727</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11860</v>
+        <v>11883</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11727</v>
+        <v>11716</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11800</v>
+        <v>11880</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-119</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-1</v>
+        <v>80</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1968</v>
+        <v>1938.6</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1973</v>
+        <v>1951.9</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1938.6</v>
+        <v>1933</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1938.6</v>
+        <v>1938.1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-31.4</v>
+        <v>-0.5</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-1.59</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1060.5</v>
+        <v>1060</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1064</v>
+        <v>1058.8</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1070</v>
+        <v>1059.6</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1054.3</v>
+        <v>1050</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1060</v>
+        <v>1054.1</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-0.5</v>
+        <v>-5.9</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2284.6</v>
+        <v/>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2273</v>
+        <v>2279.4</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2295</v>
+        <v>2305.5</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2242.6</v>
+        <v>2237.2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2287.1</v>
+        <v>2258</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>0.11</v>
+        <v/>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>690.6</v>
+        <v>711.55</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>695</v>
+        <v>712.05</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>695</v>
+        <v>702.8</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>711.55</v>
+        <v>711.45</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>3.03</v>
+        <v>-0.1</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>164.95</v>
+        <v>164.7</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>164.95</v>
+        <v>165.95</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>166.42</v>
+        <v>172.4</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>161.67</v>
+        <v>163.3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>164.7</v>
+        <v>171.58</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>-0.15</v>
+        <v>6.88</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>4.18</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>240</v>
+        <v>236.8</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>240.9</v>
+        <v>237.7</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>235.2</v>
+        <v>234.54</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>237</v>
+        <v>236.6</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-0.84</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>406.35</v>
+        <v>408</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>409.25</v>
+        <v>416</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>404</v>
+        <v>406.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>404</v>
+        <v>410.55</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>-0.33</v>
+        <v>6.55</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>485.3</v>
+        <v/>
       </c>
       <c r="E33" s="9" t="n">
-        <v>485.4</v>
+        <v>484.5</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>488.95</v>
+        <v>485.65</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>480.55</v>
+        <v>476.15</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>484.5</v>
+        <v>479.45</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-0.8</v>
+        <v/>
       </c>
       <c r="J33" s="10" t="n">
-        <v>-0.16</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1840</v>
+        <v>1854</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1845</v>
+        <v>1846.2</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1855.5</v>
+        <v>1848.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1830.4</v>
+        <v>1829</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1854</v>
+        <v>1844</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>0.76</v>
+        <v>-10</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>431.1</v>
+        <v>421.45</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>432.9</v>
+        <v>422.5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>434.95</v>
+        <v>426.7</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>418.55</v>
+        <v>419.85</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>421.45</v>
+        <v>422.15</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-9.65</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>-2.24</v>
+        <v>0.7</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>397.4</v>
+        <v>391.4</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>396.5</v>
+        <v>392.15</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>397.35</v>
+        <v>399.9</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>388.65</v>
+        <v>390.9</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>391.4</v>
+        <v>392.3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>-1.51</v>
+        <v>0.9</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>46820</v>
+        <v>48025</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>46750</v>
+        <v>48200</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48550</v>
+        <v>48955</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>46535</v>
+        <v>48100</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48025</v>
+        <v>48785</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1205</v>
+        <v>760</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>2.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>315.7</v>
+        <v>312.9</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>314.9</v>
+        <v>311.1</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>316.7</v>
+        <v>314.25</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>311.2</v>
+        <v>301.4</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>312.9</v>
+        <v>303.85</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-2.8</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-0.89</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5101.5</v>
+        <v>5042.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5126</v>
+        <v>5036</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5126</v>
+        <v>5091.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5005.5</v>
+        <v>5012</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5042.5</v>
+        <v>5064</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-59</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>-1.16</v>
+        <v>21.5</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>289.35</v>
+        <v>282.45</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>289.35</v>
+        <v>282.8</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>289.4</v>
+        <v>283.7</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>281.15</v>
+        <v>280.3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>282.45</v>
+        <v>281.65</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-6.9</v>
+        <v>-0.8</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-2.38</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>125.5</v>
+        <v>124</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>125.8</v>
+        <v>124.02</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>126.35</v>
+        <v>124.84</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>124</v>
+        <v>123.85</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124</v>
+        <v>124.68</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>-1.2</v>
+        <v>0.68</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>807.4</v>
+        <v/>
       </c>
       <c r="E42" s="12" t="n">
-        <v>805.8</v>
+        <v>805.45</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>814.4</v>
+        <v>811.85</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>795</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>805.45</v>
+        <v>797.6</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-1.95</v>
+        <v/>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-0.24</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>419.05</v>
+        <v/>
       </c>
       <c r="E43" s="9" t="n">
-        <v>420</v>
+        <v>416.85</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>421.95</v>
+        <v>420.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>416.45</v>
+        <v>415</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>418.05</v>
+        <v>418.65</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-1</v>
+        <v/>
       </c>
       <c r="J43" s="10" t="n">
-        <v>-0.24</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1839</v>
+        <v/>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1838.6</v>
+        <v>1834</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1848.2</v>
+        <v>1834</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1798.3</v>
+        <v>1810</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1848.2</v>
+        <v>1823.4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>0.5</v>
+        <v/>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1385</v>
+        <v/>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1380</v>
+        <v>1393.4</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1395.7</v>
+        <v>1398.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1376.8</v>
+        <v>1377.2</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>0.72</v>
+        <v/>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>415.35</v>
+        <v>418.85</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>416.6</v>
+        <v>418.1</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>420.3</v>
+        <v>423.6</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>413.3</v>
+        <v>416.05</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>418.85</v>
+        <v>420.25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1972.8</v>
+        <v>1935</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1958</v>
+        <v>1935</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1958.6</v>
+        <v>1954.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1920.4</v>
+        <v>1914.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1935</v>
+        <v>1950</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-37.8</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-1.92</v>
+        <v>15</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1829.2</v>
+        <v>1813.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1836</v>
+        <v>1814</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1838.9</v>
+        <v>1841.3</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1807.3</v>
+        <v>1799.1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1813.5</v>
+        <v>1819.9</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>-0.86</v>
+        <v>6.4</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>508</v>
+        <v>503.9</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>507.9</v>
+        <v>503</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>510.3</v>
+        <v>512.8</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>501.3</v>
+        <v>499.05</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>503.9</v>
+        <v>502</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-4.1</v>
+        <v>-1.9</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1938.8</v>
+        <v>1974.6</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1937.1</v>
+        <v>1979</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1980</v>
+        <v>1979.1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1925.1</v>
+        <v>1940.5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1974.6</v>
+        <v>1951.1</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>1.85</v>
+        <v>-23.5</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>232.4</v>
+        <v/>
       </c>
       <c r="E51" s="9" t="n">
-        <v>231.99</v>
+        <v>230.8</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>233.18</v>
+        <v>234.4</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>229.63</v>
+        <v>227.56</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>231.02</v>
+        <v>231.9</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-1.38</v>
+        <v/>
       </c>
       <c r="J51" s="10" t="n">
-        <v>-0.59</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>236.01</v>
+        <v>238.48</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>235.5</v>
+        <v>238.6</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>248.85</v>
+        <v>239.17</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>234.2</v>
+        <v>232.16</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>238.48</v>
+        <v>232.97</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>1.05</v>
+        <v>-5.51</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5035</v>
+        <v/>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5035</v>
+        <v>5007</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5072</v>
+        <v>5040</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4985</v>
+        <v>4965</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-5</v>
+        <v/>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.1</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>380.9</v>
+        <v>375.5</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>380.9</v>
+        <v>375.25</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>381.8</v>
+        <v>377.95</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>373.8</v>
+        <v>373.75</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>375.5</v>
+        <v>375</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-5.4</v>
+        <v>-0.5</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-1.42</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1749.3</v>
+        <v/>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1750</v>
+        <v>1713.9</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1752.1</v>
+        <v>1739.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1701.2</v>
+        <v>1671.8</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1713.9</v>
+        <v>1700.5</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-35.4</v>
+        <v/>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-2.02</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1712.4</v>
+        <v/>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1712.4</v>
+        <v>1642</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1728.3</v>
+        <v>1659.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1636.5</v>
+        <v>1620.1</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1642.1</v>
+        <v>1647.8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-70.3</v>
+        <v/>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-4.11</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>56.12</v>
+        <v>56.2</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>56.25</v>
+        <v>56.2</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>56.8</v>
+        <v>56.36</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>56</v>
+        <v>55.2</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>56.2</v>
+        <v>55.44</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>0.14</v>
+        <v>-0.76</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9100</v>
+        <v>9315</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9119.5</v>
+        <v>9375.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9315</v>
+        <v>9588</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9119.5</v>
+        <v>9253</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9315</v>
+        <v>9575</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>14240</v>
+        <v>14180</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>14227</v>
+        <v>14128</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>14429</v>
+        <v>14229</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13937</v>
+        <v>14052</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14180</v>
+        <v>14100</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>681.9</v>
+        <v/>
       </c>
       <c r="E60" s="12" t="n">
-        <v>685</v>
+        <v>672.4</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>685</v>
+        <v>676.4</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>672.7</v>
+        <v>665</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>672.7</v>
+        <v>675.1</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-9.199999999999999</v>
+        <v/>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-1.35</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
+        <v>1144.2</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>1146.5</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>1154.5</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>1144</v>
+      </c>
+      <c r="H61" s="9" t="n">
         <v>1151</v>
       </c>
-      <c r="E61" s="9" t="n">
-        <v>1150.5</v>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>1163.2</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>1141.8</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>1144.2</v>
-      </c>
       <c r="I61" s="9" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-0.59</v>
+        <v>6.8</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7630.5</v>
+        <v/>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7658</v>
+        <v>7700</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7729</v>
+        <v>7747.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7615</v>
+        <v>7655</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7672</v>
+        <v>7747.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>0.54</v>
+        <v/>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2968.8</v>
+        <v/>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2965</v>
+        <v>2980.3</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2985.3</v>
+        <v>3029.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2936</v>
+        <v>2962.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2957.4</v>
+        <v>3013.2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-11.4</v>
+        <v/>
       </c>
       <c r="J63" s="10" t="n">
-        <v>-0.38</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>424.35</v>
+        <v>425.75</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>422.3</v>
+        <v>424.95</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>427.5</v>
+        <v>427.2</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>416.6</v>
+        <v>415.55</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>425.75</v>
+        <v>418.15</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>0.33</v>
+        <v>-7.6</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>343</v>
+        <v>343.05</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>343</v>
+        <v>345.9</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>337.6</v>
+        <v>341.45</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>342</v>
+        <v>344.15</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>-0.29</v>
+        <v>2.15</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>173.4</v>
+        <v>176</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.4</v>
+        <v>175.09</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>177.3</v>
+        <v>176.2</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>172.8</v>
+        <v>173.84</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>176</v>
+        <v>175.09</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>1.5</v>
+        <v>-0.91</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2437.2</v>
+        <v>2451.9</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2420.2</v>
+        <v>2469.9</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2472</v>
+        <v>2492</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2420.2</v>
+        <v>2439</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2451.9</v>
+        <v>2474.5</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>14.7</v>
+        <v>22.6</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>0.6</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>601.7</v>
+        <v>599.9</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>605.7</v>
+        <v>601</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>594.2</v>
+        <v>586.15</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>597.9</v>
+        <v>589.1</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>0.2</v>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>878.5</v>
+        <v>866.5</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>879.05</v>
+        <v>870.95</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>857.1</v>
+        <v>855.15</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>861.9</v>
+        <v>865</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-16.1</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>-1.83</v>
+        <v>3.1</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1982</v>
+        <v>1920</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1984</v>
+        <v>1926.3</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1891.1</v>
+        <v>1885.1</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1922.2</v>
+        <v>1906.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-59.8</v>
+        <v>-15.6</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-3.02</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>848.3</v>
+        <v>867.3</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>844.5</v>
+        <v>869</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>873.85</v>
+        <v>899.85</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>842.2</v>
+        <v>865</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>867.3</v>
+        <v>895.35</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>19</v>
+        <v>28.05</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>2.24</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3322</v>
+        <v/>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3322</v>
+        <v>3302.4</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3327.7</v>
+        <v>3318.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3293</v>
+        <v>3277</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3302.4</v>
+        <v>3306.8</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-19.6</v>
+        <v/>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-0.59</v>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4856</v>
+        <v/>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4884.8</v>
+        <v>4904.1</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4909.9</v>
+        <v>5072</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4835.4</v>
+        <v>4903.7</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4855.2</v>
+        <v>5031.1</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-0.8</v>
+        <v/>
       </c>
       <c r="J75" s="10" t="n">
-        <v>-0.02</v>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1154</v>
+        <v/>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1159.6</v>
+        <v>1147</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1159.7</v>
+        <v>1147.6</v>
       </c>
       <c r="G76" s="12" t="n">
+        <v>1135.4</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>1140</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>1150</v>
-      </c>
       <c r="I76" s="12" t="n">
-        <v>-4</v>
+        <v/>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-0.35</v>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1293.4</v>
+        <v>1282.8</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1271.7</v>
+        <v>1281.4</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1286.8</v>
+        <v>1290</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1263</v>
+        <v>1268.2</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1282.8</v>
+        <v>1277</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-10.6</v>
+        <v>-5.8</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>-0.82</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2458.3</v>
+        <v/>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2468.8</v>
+        <v>2443.5</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2473.6</v>
+        <v>2454</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2432</v>
+        <v>2447.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-26.3</v>
+        <v/>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-1.07</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>712.1</v>
+        <v>710.5</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>712.1</v>
+        <v>707.1</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>713</v>
+        <v>708.9</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>707.05</v>
+        <v>703</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-1.6</v>
+        <v>-7.5</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-0.22</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>546.4</v>
+        <v>533.2</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>546.4</v>
+        <v>539.9</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>546.4</v>
+        <v>547.8</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>533.2</v>
+        <v>533.65</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>-2.42</v>
+        <v>0.6</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5300</v>
+        <v>5305</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5347.5</v>
+        <v>5339.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5270</v>
+        <v>5285</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5270</v>
+        <v>5333.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-0.57</v>
+        <v>63.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1011</v>
+        <v/>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1011.1</v>
+        <v>1014</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1014.8</v>
+        <v>1024.7</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>999.8</v>
+        <v>1007.5</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-5</v>
+        <v/>
       </c>
       <c r="J82" s="10" t="n">
-        <v>-0.49</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>521.65</v>
+        <v>509.1</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>521.6</v>
+        <v>520</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>521.6</v>
+        <v>537</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>506.6</v>
+        <v>520</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>509.1</v>
+        <v>532.85</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-12.55</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>-2.41</v>
+        <v>23.75</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>4.67</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>356.5</v>
+        <v>356.9</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>355</v>
+        <v>353.4</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>356.9</v>
+        <v>355.95</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>349.55</v>
+        <v>346</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>356.9</v>
+        <v>347</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>0.11</v>
+        <v>-9.9</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1973.4</v>
+        <v/>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1974.2</v>
+        <v>1990.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1958</v>
+        <v>1956.7</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1960</v>
+        <v>1980</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-13.4</v>
+        <v/>
       </c>
       <c r="J85" s="10" t="n">
-        <v>-0.68</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>35655</v>
+        <v/>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35660</v>
+        <v>35335</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>35895</v>
+        <v>35725</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>35380</v>
+        <v>34970</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>35565</v>
+        <v>35060</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-90</v>
+        <v/>
       </c>
       <c r="J86" s="10" t="n">
-        <v>-0.25</v>
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.70999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86.29000000000001</v>
+        <v>86.44</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.79000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.90000000000001</v>
+        <v>86.02</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.44</v>
+        <v>86.5</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>-0.31</v>
+        <v>0.06</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>118.91</v>
+        <v>117.5</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>119.49</v>
+        <v>117.5</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>119.88</v>
+        <v>117.75</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>117.21</v>
+        <v>116</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>117.5</v>
+        <v>116.54</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-1.41</v>
+        <v>-0.96</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>-1.19</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>158.04</v>
+        <v/>
       </c>
       <c r="E89" s="9" t="n">
-        <v>157</v>
+        <v>153.25</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>157</v>
+        <v>154.49</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>154.5</v>
+        <v>152.7</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>154.8</v>
+        <v>154.02</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-3.24</v>
+        <v/>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-2.05</v>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
+        <v>716.2</v>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>712.6</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>723.55</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>712.6</v>
+      </c>
+      <c r="H90" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="E90" s="12" t="n">
-        <v>719.9</v>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>720.45</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>709.2</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>716.2</v>
-      </c>
       <c r="I90" s="12" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>-0.53</v>
+        <v>3.8</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1726.4</v>
+        <v/>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1726.4</v>
+        <v>1700.1</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1727.9</v>
+        <v>1714.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1703.4</v>
+        <v>1681</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1706.4</v>
+        <v>1684.5</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-20</v>
+        <v/>
       </c>
       <c r="J91" s="10" t="n">
-        <v>-1.16</v>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4977</v>
+        <v/>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4950</v>
+        <v>4971</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5008</v>
+        <v>5022.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4944</v>
+        <v>4952</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>0.48</v>
+        <v/>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1008.5</v>
+        <v>998</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>1004.1</v>
+        <v>991.6</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1017.9</v>
+        <v>1004.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>995</v>
+        <v>988.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>998</v>
+        <v>997.7</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-10.5</v>
+        <v>-0.3</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>-1.04</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>376.8</v>
+        <v>376.45</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>379.25</v>
+        <v>376.45</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>383.75</v>
+        <v>376.95</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>376.45</v>
+        <v>373.05</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-0.35</v>
+        <v>-3.4</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>-0.09</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1130</v>
+        <v>1087.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1109.5</v>
+        <v>1095</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1109.9</v>
+        <v>1095</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1085</v>
+        <v>1078.9</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1087.5</v>
+        <v>1082</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-42.5</v>
+        <v>-5.5</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-3.76</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>137.6</v>
+        <v>135.15</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>137</v>
+        <v>134.88</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137.5</v>
+        <v>135.65</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>135.15</v>
+        <v>133.02</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>135.15</v>
+        <v>134.35</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-2.45</v>
+        <v>-0.8</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-1.78</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1965.3</v>
+        <v>1959.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1965.4</v>
+        <v>1959.9</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1978.4</v>
+        <v>1996.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1943.7</v>
+        <v>1959.9</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1959.1</v>
+        <v>1967.2</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>-0.32</v>
+        <v>8.1</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>476.05</v>
+        <v/>
       </c>
       <c r="E98" s="12" t="n">
-        <v>476.05</v>
+        <v>474.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>477.7</v>
+        <v>474.9</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>473.65</v>
+        <v>472</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>474.5</v>
+        <v>472.45</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-1.55</v>
+        <v/>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-0.33</v>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>264.95</v>
+        <v>265.9</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>262.95</v>
+        <v>262.7</v>
       </c>
       <c r="H99" s="9" t="n">
         <v>263.5</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-0.23</v>
+        <v>0</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1165</v>
+        <v/>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1164.5</v>
+        <v>1147.9</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1168</v>
+        <v>1151</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1147.9</v>
+        <v>1136.3</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-17.1</v>
+        <v/>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-1.47</v>
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5083.5</v>
+        <v/>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5083.5</v>
+        <v>5026</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5106.5</v>
+        <v>5170</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5021</v>
+        <v>4972</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5047</v>
+        <v>4990.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-36.5</v>
+        <v/>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-0.72</v>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>737.85</v>
+        <v/>
       </c>
       <c r="E102" s="12" t="n">
-        <v>737.95</v>
+        <v>733.95</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>736.8</v>
+        <v>738.75</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-1.05</v>
+        <v/>
       </c>
       <c r="J102" s="10" t="n">
-        <v>-0.14</v>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>539.85</v>
+        <v>530</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>539.9</v>
+        <v>527.05</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>541.25</v>
+        <v>528.85</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>528</v>
+        <v>522.3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>530</v>
+        <v>526.5</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-9.85</v>
+        <v>-3.5</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>-1.82</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1334.3</v>
+        <v>1306.4</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1335</v>
+        <v>1315</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1301</v>
+        <v>1295.7</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1302</v>
+        <v>1297.3</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-23</v>
+        <v>-4.7</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>-1.74</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>482.7</v>
+        <v>475.4</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>484.2</v>
+        <v>484</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>472.1</v>
+        <v>471.5</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>475.4</v>
+        <v>480.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>-1.51</v>
+        <v>5</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1239.6</v>
+        <v>1220.5</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1235</v>
+        <v>1220.4</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1239.6</v>
+        <v>1254.6</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1215</v>
+        <v>1213.7</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1220.5</v>
+        <v>1250.2</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>-1.54</v>
+        <v>29.7</v>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v>2.43</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>421.8</v>
+        <v>422.3</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>425.7</v>
+        <v>423.85</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>422.1</v>
+        <v>419.25</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-2.4</v>
+        <v>-2.85</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-0.57</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>575.45</v>
+        <v>562.25</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>575.85</v>
+        <v>562.25</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>575.9</v>
+        <v>563.35</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>560</v>
+        <v>556.4</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>562.25</v>
+        <v>562</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-13.2</v>
+        <v>-0.25</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>-2.29</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1877.5</v>
+        <v/>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1880</v>
+        <v>1881.4</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1913</v>
+        <v>1920</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1870.1</v>
+        <v>1881.4</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1901.9</v>
+        <v>1912.5</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>1.3</v>
+        <v/>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1840</v>
+        <v/>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1840</v>
+        <v>1870.8</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1876.7</v>
+        <v>1952</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1832.7</v>
+        <v>1862.7</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1876.7</v>
+        <v>1946.9</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>1.99</v>
+        <v/>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>562.05</v>
+        <v/>
       </c>
       <c r="E111" s="9" t="n">
-        <v>563.15</v>
+        <v>551</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>567.6</v>
+        <v>563</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>548</v>
+        <v>545.4</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-10.05</v>
+        <v/>
       </c>
       <c r="J111" s="10" t="n">
-        <v>-1.79</v>
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3962</v>
+        <v>3988.7</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4004.9</v>
+        <v>3988.7</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3960.9</v>
+        <v>3946.1</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>0.88</v>
+        <v>-52.9</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>314</v>
+        <v>311.1</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>315.3</v>
+        <v>311.9</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>310.9</v>
+        <v>308.3</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>312.5</v>
+        <v>308.3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-1.5</v>
+        <v>-4.2</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>-0.48</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3493.3</v>
+        <v/>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3470</v>
+        <v>3420</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3484.8</v>
+        <v>3440</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3400.1</v>
+        <v>3380</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3414.2</v>
+        <v>3389.1</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-79.09999999999999</v>
+        <v/>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-2.26</v>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2121.1</v>
+        <v>2114.7</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2135.5</v>
+        <v>2116</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2095.6</v>
+        <v>2094.6</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2105</v>
+        <v>2104.7</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-5</v>
+        <v>-0.3</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-0.24</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3154.1</v>
+        <v>3145</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3178</v>
+        <v>3163</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3145</v>
+        <v>3096.3</v>
       </c>
       <c r="H117" s="9" t="n">
         <v>3160</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-0.32</v>
+        <v>0</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>339.7</v>
+        <v>325.6</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>332.35</v>
+        <v>328.05</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>332.35</v>
+        <v>329</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>323.15</v>
+        <v>323.4</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>325.6</v>
+        <v>325</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-14.1</v>
+        <v>-0.6</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-4.15</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>815.15</v>
+        <v/>
       </c>
       <c r="E119" s="9" t="n">
-        <v>815.15</v>
+        <v>806.55</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>819.05</v>
+        <v>825.45</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>802.5</v>
+        <v>801.35</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>806</v>
+        <v>823.9</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-9.15</v>
+        <v/>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-1.12</v>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12694</v>
+        <v>12760</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12691</v>
+        <v>12758</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12833</v>
+        <v>12758</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12618</v>
+        <v>12582</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12760</v>
+        <v>12641</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>0.52</v>
+        <v>-119</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3275.4</v>
+        <v>3330.2</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3276.9</v>
+        <v>3350</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3374.4</v>
+        <v>3366.4</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3276.9</v>
+        <v>3279.9</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3330.2</v>
+        <v>3342</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>54.8</v>
+        <v>11.8</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>1.67</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>588.7</v>
+        <v/>
       </c>
       <c r="E123" s="9" t="n">
-        <v>588.7</v>
+        <v>578</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>588.7</v>
+        <v>588.75</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>574.4</v>
+        <v>577.3</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>577.75</v>
+        <v>582.2</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-10.95</v>
+        <v/>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-1.86</v>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1548.4</v>
+        <v/>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1537.5</v>
+        <v>1511</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1544.3</v>
+        <v>1527</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1510</v>
+        <v>1485</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1520</v>
+        <v>1498.7</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-28.4</v>
+        <v/>
       </c>
       <c r="J124" s="10" t="n">
-        <v>-1.83</v>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1096.6</v>
+        <v/>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1097</v>
+        <v>1088</v>
       </c>
       <c r="F125" s="9" t="n">
         <v>1105</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1088.1</v>
+        <v>1088</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1092.1</v>
+        <v>1103.2</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-4.5</v>
+        <v/>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-0.41</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>160.7</v>
+        <v>162</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>160.5</v>
+        <v>162.8</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>164.65</v>
+        <v>164.5</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>160.12</v>
+        <v>161.17</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>162</v>
+        <v>163.85</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2422</v>
+        <v/>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2409.9</v>
+        <v>2374</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2409.9</v>
+        <v>2374</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2340.3</v>
+        <v>2335.1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2369.1</v>
+        <v>2355</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-52.9</v>
+        <v/>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-2.18</v>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>129945</v>
+        <v>128890</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>130200</v>
+        <v>128750</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>130300</v>
+        <v>129290</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128705</v>
+        <v>128000</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128890</v>
+        <v>128245</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-1055</v>
+        <v>-645</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2913.8</v>
+        <v>2880</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2899</v>
+        <v>2890</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2920</v>
+        <v>2899.7</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2871.2</v>
+        <v>2868.8</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2880</v>
+        <v>2899.7</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>-1.16</v>
+        <v>19.7</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>374.1</v>
+        <v>365.9</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>376.05</v>
+        <v>370.7</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>377.5</v>
+        <v>378.3</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>365.9</v>
+        <v>367.8</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>365.9</v>
+        <v>371.05</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>-2.19</v>
+        <v>5.15</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1319.8</v>
+        <v>1302.5</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1319</v>
+        <v>1274.5</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1321.8</v>
+        <v>1298.3</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1284.4</v>
+        <v>1251.9</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1302.5</v>
+        <v>1292</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-17.3</v>
+        <v>-10.5</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>-1.31</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8557.5</v>
+        <v>8603.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8557.5</v>
+        <v>8552</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8649</v>
+        <v>8754</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8532.5</v>
+        <v>8505.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8603.5</v>
+        <v>8731</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>46</v>
+        <v>127.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>0.54</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1410.5</v>
+        <v>1398</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1401</v>
+        <v>1397.4</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1405.7</v>
+        <v>1415.1</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>1392.9</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>-0.89</v>
+        <v>2.5</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>84.7</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>85.29000000000001</v>
+        <v>84.06</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>85.63</v>
+        <v>84.78</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>83.54000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>83.84999999999999</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>-1</v>
+        <v>0.86</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>332.5</v>
+        <v>330</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>333.8</v>
+        <v>333.2</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>330.35</v>
+        <v>328.65</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>332</v>
+        <v>330.8</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>-0.15</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1875.6</v>
+        <v>1847.5</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1876</v>
+        <v>1852</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1885.5</v>
+        <v>1857.2</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1847.5</v>
+        <v>1820.4</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1847.5</v>
+        <v>1833.8</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-28.1</v>
+        <v>-13.7</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-1.5</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>12058</v>
+        <v>11847</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>12105</v>
+        <v>11750</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>12110</v>
+        <v>11815</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11679</v>
+        <v>11636</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11847</v>
+        <v>11780</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-211</v>
+        <v>-67</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>-1.75</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>234.65</v>
+        <v>233.7</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>235.98</v>
+        <v>234.8</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>235.98</v>
+        <v>238</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>232.77</v>
+        <v>232.22</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>233.7</v>
+        <v>236</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>-0.4</v>
+        <v>2.3</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36300</v>
+        <v>35825</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>36300</v>
+        <v>35700</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>36495</v>
+        <v>36540</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35625</v>
+        <v>35505</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35825</v>
+        <v>35915</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-475</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>-1.31</v>
+        <v>90</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5643</v>
+        <v>5540</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5610</v>
+        <v>5550</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5622</v>
+        <v>5600</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5522</v>
+        <v>5491</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5540</v>
+        <v>5560</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-103</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-1.83</v>
+        <v>20</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>288.1</v>
+        <v/>
       </c>
       <c r="E142" s="12" t="n">
-        <v>288.1</v>
+        <v>290.95</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>293.8</v>
+        <v>291</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>288.1</v>
+        <v>285</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>290.95</v>
+        <v>285.8</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>0.99</v>
+        <v/>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>355.6</v>
+        <v>353.1</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>355.75</v>
+        <v>352.05</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>359.15</v>
+        <v>356.5</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>353</v>
+        <v>351.15</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>353.1</v>
+        <v>355.9</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>-0.7</v>
+        <v>2.8</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1629.5</v>
+        <v>1575</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1625.9</v>
+        <v>1579.8</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1628.9</v>
+        <v>1593</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1575</v>
+        <v>1593</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-54.5</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>-3.34</v>
+        <v>18</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2465</v>
+        <v>2430</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2454</v>
+        <v>2416.4</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2468.5</v>
+        <v>2428.4</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2428</v>
+        <v>2390.1</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2430</v>
+        <v>2395</v>
       </c>
       <c r="I145" s="9" t="n">
         <v>-35</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>117</v>
+        <v>115.6</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116.41</v>
+        <v>115.75</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117.17</v>
+        <v>116.68</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>115.55</v>
+        <v>114.95</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>115.6</v>
+        <v>116</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>-1.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8300</v>
+        <v>8261</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8310</v>
+        <v>8301</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8361.5</v>
+        <v>8433</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8175</v>
+        <v>8301</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8261</v>
+        <v>8373.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-39</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>-0.47</v>
+        <v>112.5</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>266</v>
+        <v/>
       </c>
       <c r="E148" s="12" t="n">
-        <v>266</v>
+        <v>265.65</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>268.8</v>
+        <v>267.25</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>264.25</v>
+        <v>263</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>266.45</v>
+        <v>265.75</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>0.17</v>
+        <v/>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1227.2</v>
+        <v>1156.5</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1199.1</v>
+        <v>1161.5</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1199.1</v>
+        <v>1243</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1125.7</v>
+        <v>1153.6</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1156.5</v>
+        <v>1231.3</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-70.7</v>
-      </c>
-      <c r="J149" s="10" t="n">
-        <v>-5.76</v>
+        <v>74.8</v>
+      </c>
+      <c r="J149" s="13" t="n">
+        <v>6.47</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>414.35</v>
+        <v/>
       </c>
       <c r="E150" s="12" t="n">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>418.25</v>
+        <v>419.1</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>407.85</v>
+        <v>413</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>415</v>
+        <v>418.5</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>0.16</v>
+        <v/>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>318.7</v>
+        <v>316.4</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>319</v>
+        <v>316.8</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>321.4</v>
+        <v>318</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>316.05</v>
+        <v>314</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>316.4</v>
+        <v>317.85</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-0.72</v>
+        <v>1.45</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1323.1</v>
+        <v>1304.1</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1324.2</v>
+        <v>1306.8</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1301.9</v>
+        <v>1288</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1309.5</v>
+        <v>1294.9</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-12.5</v>
+        <v>-14.6</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>-0.95</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>196.8</v>
+        <v>187.9</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>196.99</v>
+        <v>188.5</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>196.99</v>
+        <v>190.8</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>187.3</v>
+        <v>186.05</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>187.9</v>
+        <v>186.1</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-8.9</v>
+        <v>-1.8</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>-4.52</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>658.25</v>
+        <v/>
       </c>
       <c r="E154" s="12" t="n">
-        <v>653.1</v>
+        <v>671</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>674.65</v>
+        <v>675</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>648.75</v>
+        <v>661.35</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>674.65</v>
+        <v>668</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>2.49</v>
+        <v/>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1775</v>
+        <v>1732</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1775</v>
+        <v>1734.6</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1775</v>
+        <v>1739.9</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1727.8</v>
+        <v>1696.6</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1732</v>
+        <v>1696.6</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-43</v>
+        <v>-35.4</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-2.42</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1020.8</v>
+        <v>1004.9</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1021.7</v>
+        <v>1011.2</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1000.6</v>
+        <v>1002.1</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1005.9</v>
+        <v>1008</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>-1</v>
+        <v>2.1</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>23855</v>
+        <v>23365</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>23855</v>
+        <v>23500</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>23920</v>
+        <v>23560</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>23365</v>
+        <v>23130</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>23365</v>
+        <v>23160</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-490</v>
+        <v>-205</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>-2.05</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1045</v>
+        <v>1030</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1046.1</v>
+        <v>1031.9</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1029.3</v>
+        <v>1017.2</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>-0.38</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3977</v>
+        <v>3927</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3990</v>
+        <v>3911</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3998.1</v>
+        <v>3998.8</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3904.1</v>
+        <v>3911</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3927</v>
+        <v>3951.3</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-50</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-1.26</v>
+        <v>24.3</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2547</v>
+        <v/>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2536.2</v>
+        <v>2546</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2560</v>
+        <v>2546</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2526.5</v>
+        <v>2517</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2546</v>
+        <v>2522</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-1</v>
+        <v/>
       </c>
       <c r="J160" s="10" t="n">
-        <v>-0.04</v>
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1899</v>
+        <v>1892</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1907.8</v>
+        <v>1895.6</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1883.1</v>
+        <v>1876.8</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1895</v>
+        <v>1885.9</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-4</v>
+        <v>-9.1</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-0.21</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>470.9</v>
+        <v/>
       </c>
       <c r="E162" s="12" t="n">
-        <v>470.95</v>
+        <v>453.1</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>470.95</v>
+        <v>458.85</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>451.5</v>
+        <v>449</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>452.85</v>
+        <v>453.5</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-18.05</v>
+        <v/>
       </c>
       <c r="J162" s="10" t="n">
-        <v>-3.83</v>
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>395.6</v>
+        <v>389.3</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>395</v>
+        <v>389.3</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>396.3</v>
+        <v>390.65</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>387.25</v>
+        <v>383.5</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>389.3</v>
+        <v>387.55</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-6.3</v>
+        <v>-1.75</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-1.59</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>625.1</v>
+        <v>613.35</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>625</v>
+        <v>611.6</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>627.15</v>
+        <v>614.95</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>611.1</v>
+        <v>605.5</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>613.35</v>
+        <v>607.7</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-11.75</v>
+        <v>-5.65</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-1.88</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1756.1</v>
+        <v/>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1754.1</v>
+        <v>1746.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1754.1</v>
+        <v>1760</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1725</v>
+        <v>1718.2</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1738.5</v>
+        <v>1752.8</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-17.6</v>
+        <v/>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-1</v>
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1019.9</v>
+        <v>1018.7</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1004</v>
+        <v>1007.9</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1015</v>
+        <v>1014.1</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>368</v>
+        <v>365.7</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>366.9</v>
+        <v>364.65</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>369.8</v>
+        <v>367.2</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>363</v>
+        <v>362.25</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>365.7</v>
+        <v>365.55</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-2.3</v>
+        <v>-0.15</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>-0.62</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>188.79</v>
+        <v>185.61</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>189</v>
+        <v>185.9</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>190.24</v>
+        <v>186.5</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>184.37</v>
+        <v>183.61</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>185.61</v>
+        <v>184.15</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-3.18</v>
+        <v>-1.46</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>-1.68</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2304</v>
+        <v>2270</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2290.1</v>
+        <v>2270</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2299.9</v>
+        <v>2274.5</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2260.1</v>
+        <v>2244</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2270</v>
+        <v>2255.5</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-34</v>
+        <v>-14.5</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-1.48</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1596.9</v>
+        <v>1564</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1575.1</v>
+        <v>1556.1</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1593.6</v>
+        <v>1569.9</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1545.3</v>
+        <v>1541.4</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-32.9</v>
+        <v>-5</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>-2.06</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2698</v>
+        <v/>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2690</v>
+        <v>2683.4</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2709</v>
+        <v>2683.4</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2679</v>
+        <v>2626.2</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2683</v>
+        <v>2638.7</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-15</v>
+        <v/>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5020</v>
+        <v>4995</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>5010</v>
+        <v>4975</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5028</v>
+        <v>5015.5</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4958.5</v>
+        <v>4969</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4995</v>
+        <v>4987</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-25</v>
+        <v>-8</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-0.5</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4857</v>
+        <v>4914</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4857</v>
+        <v>4900</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4915</v>
+        <v>4983.5</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4823</v>
+        <v>4887</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4914</v>
+        <v>4960</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="J174" s="13" t="n">
-        <v>1.17</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1299.1</v>
+        <v/>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1307</v>
+        <v>1275</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1323</v>
+        <v>1283.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1271.2</v>
+        <v>1257.6</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1275.7</v>
+        <v>1270.2</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-23.4</v>
+        <v/>
       </c>
       <c r="J175" s="10" t="n">
-        <v>-1.8</v>
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2853</v>
+        <v>2814.5</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2850</v>
+        <v>2800.5</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2854.4</v>
+        <v>2812.8</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2772.5</v>
+        <v>2770.4</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2814.5</v>
+        <v>2793.6</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-38.5</v>
+        <v>-20.9</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-1.35</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4133.1</v>
+        <v>4132</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4127</v>
+        <v>4139</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4159.9</v>
+        <v>4156.8</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4100.7</v>
+        <v>4078</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4132</v>
+        <v>4133.2</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-0.03</v>
+        <v>1.2</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1279.4</v>
+        <v/>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1283.8</v>
+        <v>1291</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1305.1</v>
+        <v>1293.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1275.3</v>
+        <v>1245.9</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1291</v>
+        <v>1252.5</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>0.91</v>
+        <v/>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11408</v>
+        <v>11175</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11370</v>
+        <v>11175</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11370</v>
+        <v>11215</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11175</v>
+        <v>10995</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11175</v>
+        <v>11009</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-233</v>
+        <v>-166</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>-2.04</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>187.22</v>
+        <v>186.04</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>186.5</v>
+        <v>184.41</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>188.45</v>
+        <v>185.15</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>183.2</v>
+        <v>181.4</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>186.04</v>
+        <v>183.22</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.18</v>
+        <v>-2.82</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.63</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>582.15</v>
+        <v>573</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>580.1</v>
+        <v>575.5</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>586.75</v>
+        <v>576.75</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>573</v>
+        <v>569.95</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>573</v>
+        <v>576.75</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-9.15</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>-1.57</v>
+        <v>3.75</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>272.1</v>
+        <v>268</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>272.1</v>
+        <v>269.3</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>272.5</v>
+        <v>272.8</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>267</v>
+        <v>269.15</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>-1.51</v>
+        <v>4</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1170</v>
+        <v>1167.2</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1176.4</v>
+        <v>1169.2</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1164.4</v>
+        <v>1141.3</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1167.2</v>
+        <v>1144.8</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-2.8</v>
+        <v>-22.4</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-0.24</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>176.4</v>
+        <v>172.8</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>175.89</v>
+        <v>172.8</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>176.47</v>
+        <v>172.9</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>172.65</v>
+        <v>171.13</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>172.8</v>
+        <v>171.5</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-3.6</v>
+        <v>-1.3</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>-2.04</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1120</v>
+        <v>1156.9</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1114.2</v>
+        <v>1161.7</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1163</v>
+        <v>1167.7</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1114.1</v>
+        <v>1142</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1156.9</v>
+        <v>1145.5</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>3.29</v>
+        <v>-11.4</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>-0.99</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  07-Sep-2026 06:06 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  08-Sep-2026 05:04 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-Sep-2026 06:06 PM</t>
+          <t>08-Sep-2026 05:04 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 08-Sep-2026 05:04 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 09-Sep-2026 05:02 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>08-Sep-2026 05:04 PM</t>
+          <t>09-Sep-2026 05:02 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  08-Sep-2026 05:04 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  09-Sep-2026 05:02 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v/>
+        <v>503.7</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>490.7</v>
+        <v>503.7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>504.75</v>
+        <v>503.7</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>486.5</v>
+        <v>494.5</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>503.7</v>
+        <v>496.2</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v/>
+        <v>-7.5</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v/>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v/>
+        <v>7387</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7389</v>
+        <v>7377</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7472</v>
+        <v>7480</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7340</v>
+        <v>7361</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7387</v>
+        <v>7401.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v/>
+        <v>14.5</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v/>
+        <v>25555</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25860</v>
+        <v>25555</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26065</v>
+        <v>25705</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25440</v>
+        <v>25190</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25555</v>
+        <v>25225</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v/>
+        <v>-330</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v/>
+        <v>396.95</v>
       </c>
       <c r="E6" s="12" t="n">
+        <v>396.85</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>394.45</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>396.95</v>
-      </c>
       <c r="I6" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v/>
+        <v>3.05</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>53.21</v>
+        <v>52.24</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>53.07</v>
+        <v>52.19</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>53.07</v>
+        <v>52.22</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>51.63</v>
+        <v>51.23</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>52.24</v>
+        <v>51.33</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-1.82</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v/>
+        <v>1262.8</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1267.9</v>
+        <v>1260</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1255.7</v>
+        <v>1255.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1262.8</v>
+        <v>1257.7</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v/>
+        <v>-5.1</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v/>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2950</v>
+        <v>2953.1</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2933</v>
+        <v>2959.9</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2968.8</v>
+        <v>3142</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2918</v>
+        <v>2935.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2953.1</v>
+        <v>3104.7</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>3.1</v>
+        <v>151.6</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.11</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v/>
+        <v>1710</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1694</v>
+        <v>1719</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1713.1</v>
+        <v>1785.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1685.2</v>
+        <v>1706</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v/>
+        <v>65</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v/>
+        <v>5181</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5172.5</v>
+        <v>5181</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5206.5</v>
+        <v>5222</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5129.5</v>
+        <v>5139</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5181</v>
+        <v>5139</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v/>
+        <v>-42</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v/>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>398.6</v>
+        <v>398.3</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>398</v>
+        <v>396.3</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>400.95</v>
+        <v>400.8</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>395.15</v>
+        <v>395</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>398.3</v>
+        <v>397</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v/>
+        <v>298</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>303.8</v>
+        <v>297.95</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>304.15</v>
+        <v>303.65</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>296.5</v>
+        <v>291.6</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>298</v>
+        <v>299.05</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v/>
+        <v>1.05</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2206.5</v>
+        <v>2185</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2204.6</v>
+        <v>2182</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2204.8</v>
+        <v>2194.9</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>2165</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2185</v>
+        <v>2168</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-21.5</v>
+        <v>-17</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-0.97</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v/>
+        <v>8837.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8761.5</v>
+        <v>8825</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8850</v>
+        <v>8974.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8745</v>
+        <v>8803.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8837.5</v>
+        <v>8967</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v/>
+        <v>129.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>420.8</v>
+        <v>411.5</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>420.8</v>
+        <v>410</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>421.2</v>
+        <v>424.3</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>410.05</v>
+        <v>408</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>411.5</v>
+        <v>422.25</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-2.21</v>
+        <v>10.75</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>2.61</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>170</v>
+        <v>167.12</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>170.17</v>
+        <v>169.27</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>167.75</v>
+        <v>166.22</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>-0.59</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2500.9</v>
+        <v>2481.6</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2499</v>
+        <v>2459.1</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2499</v>
+        <v>2489</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2474.1</v>
+        <v>2457.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2481.6</v>
+        <v>2489</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>-0.77</v>
+        <v>7.4</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v/>
+        <v>1500.8</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1498.2</v>
+        <v>1492.8</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1507.4</v>
+        <v>1507</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1485</v>
+        <v>1465.6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1500.8</v>
+        <v>1474.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v/>
+        <v>-26</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v/>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v/>
+        <v>609.4</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>604.4</v>
+        <v>610.9</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>612</v>
+        <v>624.4</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>602</v>
+        <v>608.55</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>609.4</v>
+        <v>612.3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v/>
+        <v>2.9</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v/>
+        <v>6314.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6335</v>
+        <v>6295</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6356.5</v>
+        <v>6321.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6305</v>
+        <v>6203.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6314.5</v>
+        <v>6221.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v/>
+        <v>-93</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v/>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v/>
+        <v>1073.7</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1055.7</v>
+        <v>1070.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1074.8</v>
+        <v>1077.9</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1051.4</v>
+        <v>1060.5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1073.7</v>
+        <v>1060.5</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v/>
+        <v>-13.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v/>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v/>
+        <v>1692</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1660.5</v>
+        <v>1685</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1698.8</v>
+        <v>1704</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1655</v>
+        <v>1672</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1692</v>
+        <v>1698.9</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v/>
+        <v>6.9</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v/>
+        <v>1244.9</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1262.8</v>
+        <v>1236</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1264.9</v>
+        <v>1257.4</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1239.5</v>
+        <v>1234.7</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1244.9</v>
+        <v>1238.5</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v/>
+        <v>-6.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v/>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11800</v>
+        <v>11880</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11727</v>
+        <v>11841</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11883</v>
+        <v>11896</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11716</v>
+        <v>11740</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>0.68</v>
+        <v>-90</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1938.6</v>
+        <v>1938.1</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1938.6</v>
+        <v>1939.1</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1951.9</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1933</v>
+        <v>1921.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-0.5</v>
+        <v>-11.1</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-0.03</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1060</v>
+        <v>1054.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1058.8</v>
+        <v>1045.1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1059.6</v>
+        <v>1060.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1050</v>
+        <v>1038.5</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-5.9</v>
+        <v>-14.8</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v/>
+        <v>2258</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2279.4</v>
+        <v>2220</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2305.5</v>
+        <v>2248.5</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2237.2</v>
+        <v>2191.3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2258</v>
+        <v>2208.6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v/>
+        <v>-49.4</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v/>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>711.55</v>
+        <v>711.45</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>712.05</v>
+        <v>710.05</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>742</v>
+        <v>710.05</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>702.8</v>
+        <v>689</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>711.45</v>
+        <v>700.05</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-0.1</v>
+        <v>-11.4</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-0.01</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>164.7</v>
+        <v>171.58</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>165.95</v>
+        <v>170.6</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>172.4</v>
+        <v>174.96</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>163.3</v>
+        <v>168.65</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>171.58</v>
+        <v>171.7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>6.88</v>
+        <v>0.12</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>4.18</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>237</v>
+        <v>236.6</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>236.8</v>
+        <v>236.65</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>237.7</v>
+        <v>237.15</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>234.54</v>
+        <v>234.05</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>236.6</v>
+        <v>234.1</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-0.4</v>
+        <v>-2.5</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-0.17</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>404</v>
+        <v>410.55</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>408</v>
+        <v>411.55</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>416</v>
+        <v>413.85</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>406.5</v>
+        <v>406</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>410.55</v>
+        <v>406</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>1.62</v>
+        <v>-4.55</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v/>
+        <v>479.45</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>484.5</v>
+        <v>483.9</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>485.65</v>
+        <v>483.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>476.15</v>
+        <v>468</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>479.45</v>
+        <v>470.8</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v/>
+        <v>-8.65</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v/>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1854</v>
+        <v>1844</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1846.2</v>
+        <v>1830.5</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1848.8</v>
+        <v>1834.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1829</v>
+        <v>1813</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1844</v>
+        <v>1814.7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-10</v>
+        <v>-29.3</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-0.54</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>421.45</v>
+        <v>422.15</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>422.5</v>
+        <v>422.15</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>426.7</v>
+        <v>436</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>419.85</v>
+        <v>421.65</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>422.15</v>
+        <v>433.7</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0.7</v>
+        <v>11.55</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>0.17</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>391.4</v>
+        <v>392.3</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>392.15</v>
+        <v>394</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>399.9</v>
+        <v>403.95</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>390.9</v>
+        <v>393</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>392.3</v>
+        <v>395</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0.23</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48025</v>
+        <v>48785</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48200</v>
+        <v>48475</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48955</v>
+        <v>49100</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>48100</v>
+        <v>48360</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48785</v>
+        <v>49100</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>760</v>
+        <v>315</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>1.58</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>312.9</v>
+        <v>303.85</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>311.1</v>
+        <v>300.15</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>314.25</v>
+        <v>306.5</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>301.4</v>
+        <v>298.65</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>303.85</v>
+        <v>303.55</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-9.050000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-2.89</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5042.5</v>
+        <v>5064</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5036</v>
+        <v>5064</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5091.5</v>
+        <v>5113</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5012</v>
+        <v>5023</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5064</v>
+        <v>5090</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>21.5</v>
+        <v>26</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>282.45</v>
+        <v>281.65</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>282.8</v>
+        <v>279.85</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>283.7</v>
+        <v>279.85</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>280.3</v>
+        <v>276.1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>281.65</v>
+        <v>277.2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-0.8</v>
+        <v>-4.45</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-0.28</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124</v>
+        <v>124.68</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>124.02</v>
+        <v>124.42</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>124.84</v>
+        <v>125.38</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>123.85</v>
+        <v>124.04</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124.68</v>
+        <v>124.08</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>0.55</v>
+        <v>-0.6</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v/>
+        <v>797.6</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>805.45</v>
+        <v>797.6</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>811.85</v>
+        <v>804.65</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>797.6</v>
+        <v>786.9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v/>
+        <v>-10.7</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v/>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v/>
+        <v>418.65</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>416.85</v>
+        <v>414.6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>420.3</v>
+        <v>417.95</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>415</v>
+        <v>414.5</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>418.65</v>
+        <v>415.6</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v/>
+        <v>-3.05</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v/>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v/>
+        <v>1823.4</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1834</v>
+        <v>1828.4</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1834</v>
+        <v>1843.4</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1823.4</v>
+        <v>1829</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v/>
+        <v>5.6</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v/>
+        <v>1384</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1393.4</v>
+        <v>1380</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1398.4</v>
+        <v>1388.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1377.2</v>
+        <v>1363.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1384</v>
+        <v>1363.1</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v/>
+        <v>-20.9</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v/>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>418.85</v>
+        <v>420.25</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>418.1</v>
+        <v>420.85</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>423.6</v>
+        <v>435.35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>416.05</v>
+        <v>419.8</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>420.25</v>
+        <v>431</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>1.4</v>
+        <v>10.75</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>0.33</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1935</v>
+        <v>1950</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1935</v>
+        <v>1815.5</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1954.4</v>
+        <v>1877.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1914.1</v>
+        <v>1780.7</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1950</v>
+        <v>1845</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>0.78</v>
+        <v>-105</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-5.38</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1813.5</v>
+        <v>1819.9</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1841.3</v>
+        <v>1815</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1799.1</v>
+        <v>1789.8</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1819.9</v>
+        <v>1800</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>0.35</v>
+        <v>-19.9</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>503.9</v>
+        <v>502</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>512.8</v>
+        <v>512.45</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>499.05</v>
+        <v>499.5</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>-0.38</v>
+        <v>8</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1974.6</v>
+        <v>1951.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1979</v>
+        <v>1946.1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1979.1</v>
+        <v>1967.6</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1940.5</v>
+        <v>1918.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1951.1</v>
+        <v>1962.7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>-1.19</v>
+        <v>11.6</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v/>
+        <v>231.9</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>230.8</v>
+        <v>229.95</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>234.4</v>
+        <v>234.42</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>227.56</v>
+        <v>228.57</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>231.9</v>
+        <v>232.96</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v/>
+        <v>1.06</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>238.48</v>
+        <v>232.97</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>238.6</v>
+        <v>232.95</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>239.17</v>
+        <v>235.57</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>232.16</v>
+        <v>230.23</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>232.97</v>
+        <v>231.67</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-5.51</v>
+        <v>-1.3</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-2.31</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v/>
+        <v>5040</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5007</v>
+        <v>5020</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5040</v>
+        <v>5182.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4965</v>
+        <v>5020</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5040</v>
+        <v>5170.5</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v/>
+        <v>130.5</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>375.5</v>
+        <v>375</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>375.25</v>
+        <v>374.7</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>377.95</v>
+        <v>374.7</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>373.75</v>
+        <v>368.05</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>375</v>
+        <v>371.55</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-0.5</v>
+        <v>-3.45</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-0.13</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v/>
+        <v>1700.5</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1713.9</v>
+        <v>1710.7</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1739.2</v>
+        <v>1740</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1671.8</v>
+        <v>1690</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1700.5</v>
+        <v>1733.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v/>
+        <v>33.1</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v/>
+        <v>1647.8</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1642</v>
+        <v>1647.8</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1659.9</v>
+        <v>1672</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1620.1</v>
+        <v>1630</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1647.8</v>
+        <v>1641.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v/>
+        <v>-5.9</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v/>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>56.2</v>
+        <v>55.44</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>56.2</v>
+        <v>55.48</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>56.36</v>
+        <v>55.92</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>55.44</v>
+        <v>55.25</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.76</v>
+        <v>-0.19</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>-1.35</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9315</v>
+        <v>9575</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9375.5</v>
+        <v>9575</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9588</v>
+        <v>9615</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9253</v>
+        <v>9410</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9575</v>
+        <v>9488</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>260</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>2.79</v>
+        <v>-87</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>14180</v>
+        <v>14100</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>14128</v>
+        <v>14100</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>14229</v>
+        <v>14271</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>14052</v>
+        <v>13773</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14100</v>
+        <v>13845</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-80</v>
+        <v>-255</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v/>
+        <v>675.1</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>672.4</v>
+        <v>670.2</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>676.4</v>
+        <v>672.1</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>665</v>
+        <v>654.7</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>675.1</v>
+        <v>655.1</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v/>
+        <v>-20</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v/>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1144.2</v>
+        <v>1151</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1146.5</v>
+        <v>1146</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1154.5</v>
+        <v>1151</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1144</v>
+        <v>1136.4</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>0.59</v>
+        <v>-6</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v/>
+        <v>7747.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7700</v>
+        <v>7687</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7747.5</v>
+        <v>7784.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7655</v>
+        <v>7664.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7747.5</v>
+        <v>7734.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v/>
+        <v>-13</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v/>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v/>
+        <v>3013.2</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2980.3</v>
+        <v>3009</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3029.3</v>
+        <v>3036</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2962.2</v>
+        <v>2977.7</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3013.2</v>
+        <v>2989.2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v/>
+        <v>-24</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v/>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>425.75</v>
+        <v>418.15</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>424.95</v>
+        <v>418.1</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>427.2</v>
+        <v>420</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>415.55</v>
+        <v>409.7</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>418.15</v>
+        <v>410.75</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-7.6</v>
+        <v>-7.4</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-1.79</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>342</v>
+        <v>344.15</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>343.05</v>
+        <v>341.5</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>345.9</v>
+        <v>345</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>341.45</v>
+        <v>341.5</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>344.15</v>
+        <v>345</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>2.15</v>
+        <v>0.85</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>176</v>
+        <v>175.09</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>175.09</v>
+        <v>173.7</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>176.2</v>
+        <v>175.59</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>173.84</v>
+        <v>173.61</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>175.09</v>
+        <v>174.9</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.91</v>
+        <v>-0.19</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-0.52</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2451.9</v>
+        <v>2474.5</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2469.9</v>
+        <v>2486.9</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2492</v>
+        <v>2486.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2439</v>
+        <v>2400.1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2474.5</v>
+        <v>2435</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>0.92</v>
+        <v>-39.5</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>597.9</v>
+        <v>568.1</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>599.9</v>
+        <v>564</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>601</v>
+        <v>579.75</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>586.15</v>
+        <v>556.5</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>589.1</v>
+        <v>574.6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>-1.47</v>
+        <v>6.5</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>861.9</v>
+        <v>865</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>866.5</v>
+        <v>867.95</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>870.95</v>
+        <v>867.95</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>855.15</v>
+        <v>856.1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>865</v>
+        <v>863.8</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>0.36</v>
+        <v>-1.2</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1922.2</v>
+        <v>1906.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1920</v>
+        <v>1905.5</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1926.3</v>
+        <v>1908.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1885.1</v>
+        <v>1855</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1906.6</v>
+        <v>1857.1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-15.6</v>
+        <v>-49.5</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>867.3</v>
+        <v>895.35</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>869</v>
+        <v>899.75</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>899.85</v>
+        <v>901.8</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>865</v>
+        <v>878.1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>895.35</v>
+        <v>884.8</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>28.05</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>3.23</v>
+        <v>-10.55</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v/>
+        <v>3306.8</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3302.4</v>
+        <v>3305</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3318.2</v>
+        <v>3320</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3277</v>
+        <v>3279</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3306.8</v>
+        <v>3300</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v/>
+        <v>-6.8</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v/>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v/>
+        <v>5031.1</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4904.1</v>
+        <v>5031.1</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>5072</v>
+        <v>5097.4</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4903.7</v>
+        <v>5000.5</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>5031.1</v>
+        <v>5000.5</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v/>
+        <v>-30.6</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v/>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v/>
+        <v>1140</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1147</v>
+        <v>1136</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1147.6</v>
+        <v>1143.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1135.4</v>
+        <v>1118.9</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1140</v>
+        <v>1120.4</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v/>
+        <v>-19.6</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v/>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1282.8</v>
+        <v>1277</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1281.4</v>
+        <v>1248.8</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1290</v>
+        <v>1264.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1268.2</v>
+        <v>1222.7</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1277</v>
+        <v>1229.8</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-5.8</v>
+        <v>-47.2</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>-0.45</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v/>
+        <v>2447.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2443.5</v>
+        <v>2444</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2454</v>
+        <v>2446.4</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2433</v>
+        <v>2410.9</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2447.3</v>
+        <v>2440</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v/>
+        <v>-7.3</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v/>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>707.1</v>
+        <v>698</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>708.9</v>
+        <v>700</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-7.5</v>
+        <v>-15.9</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-1.06</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>539.9</v>
+        <v>533.7</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>547.8</v>
+        <v>534.6</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>533.65</v>
+        <v>508.95</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>533.8</v>
+        <v>514</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>0.11</v>
+        <v>-19.8</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5270</v>
+        <v>5333.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5305</v>
+        <v>5266.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5339.5</v>
+        <v>5297</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5285</v>
+        <v>5205.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5333.5</v>
+        <v>5218</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>1.2</v>
+        <v>-115.5</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v/>
+        <v>1009</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1014</v>
+        <v>1013.9</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1024.7</v>
+        <v>1032.4</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1007.5</v>
+        <v>1010.7</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1009</v>
+        <v>1026.9</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v/>
+        <v>17.9</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>509.1</v>
+        <v>532.85</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>520</v>
+        <v>538.4</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>520</v>
+        <v>530.5</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>532.85</v>
+        <v>532.3</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>4.67</v>
+        <v>-0.55</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>356.9</v>
+        <v>347</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>353.4</v>
+        <v>345.55</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>355.95</v>
+        <v>350.9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>346</v>
+        <v>343.55</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>347</v>
+        <v>348.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>-2.77</v>
+        <v>1.9</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v/>
+        <v>1980</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1990.8</v>
+        <v>1979.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1956.7</v>
+        <v>1936</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1980</v>
+        <v>1945</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v/>
+        <v>-35</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v/>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v/>
+        <v>35060</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35335</v>
+        <v>35190</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>35725</v>
+        <v>35285</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>34970</v>
+        <v>34055</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>35060</v>
+        <v>34180</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v/>
+        <v>-880</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v/>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.44</v>
+        <v>86.5</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86.44</v>
+        <v>86.48</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>87.09999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>86.02</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>117.5</v>
+        <v>116.54</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>117.5</v>
+        <v>116.05</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>117.75</v>
+        <v>118.89</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>116</v>
+        <v>115.82</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>116.54</v>
+        <v>117.95</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-0.96</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>-0.82</v>
+        <v>1.41</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v/>
+        <v>154.02</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>153.25</v>
+        <v>154</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>154.49</v>
+        <v>155.15</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>152.7</v>
+        <v>151.95</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>154.02</v>
+        <v>152.92</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v/>
+        <v>-1.1</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v/>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>716.2</v>
+        <v>720</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>712.6</v>
+        <v>716.15</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>723.55</v>
+        <v>723.25</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>712.6</v>
+        <v>715</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>720</v>
+        <v>722.75</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v/>
+        <v>1684.5</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1700.1</v>
+        <v>1684</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1714.1</v>
+        <v>1697.2</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1681</v>
+        <v>1670</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1684.5</v>
+        <v>1671.9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v/>
+        <v>-12.6</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v/>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v/>
+        <v>5000</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4971</v>
+        <v>4950</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5022.5</v>
+        <v>5009</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4952</v>
+        <v>4950</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5000</v>
+        <v>4975</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v/>
+        <v>-25</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>998</v>
+        <v>997.7</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>991.6</v>
+        <v>994</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1004.7</v>
+        <v>1010</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>988.3</v>
+        <v>994</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>997.7</v>
+        <v>1004</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>-0.03</v>
+        <v>6.3</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="F94" s="12" t="n">
         <v>376.45</v>
       </c>
-      <c r="E94" s="12" t="n">
-        <v>376.45</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>376.95</v>
-      </c>
       <c r="G94" s="12" t="n">
-        <v>370</v>
+        <v>369.75</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>373.05</v>
+        <v>373.7</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>-0.9</v>
+        <v>0.65</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1087.5</v>
+        <v>1082</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1095</v>
+        <v>1059</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1095</v>
+        <v>1059</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1078.9</v>
+        <v>1026.5</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1082</v>
+        <v>1035</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-5.5</v>
+        <v>-47</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-0.51</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>135.15</v>
+        <v>134.35</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>134.88</v>
+        <v>133.3</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>135.65</v>
+        <v>136.14</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>133.02</v>
+        <v>133.06</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>134.35</v>
+        <v>135.6</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>-0.59</v>
+        <v>1.25</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1959.1</v>
+        <v>1967.2</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1959.9</v>
+        <v>1956</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1996.9</v>
+        <v>1983.5</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1959.9</v>
+        <v>1948</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1967.2</v>
+        <v>1963.6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>0.41</v>
+        <v>-3.6</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v/>
+        <v>472.45</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>474.5</v>
+        <v>471.95</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>474.9</v>
+        <v>475</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>472.45</v>
+        <v>469.5</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v/>
+        <v>-2.95</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v/>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="99">
@@ -4100,22 +4100,22 @@
         <v>263.5</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>263.5</v>
+        <v>263.65</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>265.9</v>
+        <v>264.5</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>262.7</v>
+        <v>260.2</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>263.5</v>
+        <v>260.8</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>0</v>
+        <v>-2.7</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v/>
+        <v>1136.3</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1147.9</v>
+        <v>1139.6</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1135</v>
+        <v>1130.6</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1136.3</v>
+        <v>1146.5</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v/>
+        <v>10.2</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v/>
+        <v>4990.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5026</v>
+        <v>5009</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4972</v>
+        <v>4960</v>
       </c>
       <c r="H101" s="9" t="n">
         <v>4990.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v/>
+        <v>738.75</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>733.95</v>
+        <v>739</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>740</v>
+        <v>794</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>738.75</v>
+        <v>783.3</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v/>
+        <v>44.55</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>6.03</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>530</v>
+        <v>526.5</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>527.05</v>
+        <v>526.5</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>528.85</v>
+        <v>541.7</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>522.3</v>
+        <v>521.5</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>526.5</v>
+        <v>534.8</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>-0.66</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1302</v>
+        <v>1297.3</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1306.4</v>
+        <v>1303.9</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1295.7</v>
+        <v>1290.1</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1297.3</v>
+        <v>1310</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>-0.36</v>
+        <v>12.7</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>475.4</v>
+        <v>480.4</v>
       </c>
       <c r="E105" s="9" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>479.25</v>
+      </c>
+      <c r="G105" s="9" t="n">
         <v>473</v>
       </c>
-      <c r="F105" s="9" t="n">
-        <v>484</v>
-      </c>
-      <c r="G105" s="9" t="n">
-        <v>471.5</v>
-      </c>
       <c r="H105" s="9" t="n">
-        <v>480.4</v>
+        <v>475.95</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>1.05</v>
+        <v>-4.45</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1220.5</v>
+        <v>1250.2</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1220.4</v>
+        <v>1248.9</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1254.6</v>
+        <v>1248.9</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1213.7</v>
+        <v>1234.3</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1250.2</v>
+        <v>1239.2</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>2.43</v>
+        <v>-11</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>422.1</v>
+        <v>419.25</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>422.3</v>
+        <v>418.2</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>423.85</v>
+        <v>420.65</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>419</v>
+        <v>413.95</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>419.25</v>
+        <v>414</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-2.85</v>
+        <v>-5.25</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-0.68</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>562.25</v>
+        <v>562</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>562.25</v>
+        <v>558.3</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>563.35</v>
+        <v>559.25</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>556.4</v>
+        <v>551.25</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>562</v>
+        <v>553.1</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-0.25</v>
+        <v>-8.9</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>-0.04</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v/>
+        <v>1912.5</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1881.4</v>
+        <v>1905.2</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1920</v>
+        <v>1962</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1881.4</v>
+        <v>1901.2</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1912.5</v>
+        <v>1919.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v/>
+        <v>7.2</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v/>
+        <v>1946.9</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1870.8</v>
+        <v>1946.9</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1862.7</v>
+        <v>1917.9</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1946.9</v>
+        <v>1937</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v/>
+        <v>-9.9</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v/>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v/>
+        <v>563</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>563</v>
+        <v>564.75</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>545.4</v>
+        <v>550.45</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v/>
+        <v>-8</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v/>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3988.7</v>
+        <v>3935.3</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3988.7</v>
+        <v>4020.2</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-52.9</v>
+        <v>-23.5</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>-1.32</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>312.5</v>
+        <v>308.3</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>311.1</v>
+        <v>307.9</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>311.9</v>
+        <v>314.4</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>308.3</v>
+        <v>307</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-1.34</v>
+        <v>2.1</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v/>
+        <v>3389.1</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3420</v>
+        <v>3375</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3440</v>
+        <v>3375</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3380</v>
+        <v>3326.1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3389.1</v>
+        <v>3364</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v/>
+        <v>-25.1</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v/>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2105</v>
+        <v>2104.7</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2114.7</v>
+        <v>2091</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2116</v>
+        <v>2120</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2094.6</v>
+        <v>2090</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2104.7</v>
+        <v>2100</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-0.3</v>
+        <v>-4.7</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="117">
@@ -4712,22 +4712,22 @@
         <v>3160</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3145</v>
+        <v>3135.3</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3163</v>
+        <v>3151.3</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3096.3</v>
+        <v>3118</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3160</v>
+        <v>3150</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>325.6</v>
+        <v>325</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>328.05</v>
+        <v>323</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>323.4</v>
+        <v>312.3</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-0.6</v>
+        <v>-5</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-0.18</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v/>
+        <v>823.9</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>806.55</v>
+        <v>821.85</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>825.45</v>
+        <v>823</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>801.35</v>
+        <v>808.45</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>823.9</v>
+        <v>813.9</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v/>
+        <v>-10</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v/>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12760</v>
+        <v>12641</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12758</v>
+        <v>12609</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12758</v>
+        <v>12692</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12582</v>
+        <v>12537</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12641</v>
+        <v>12618</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-119</v>
+        <v>-23</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>-0.93</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3330.2</v>
+        <v>3342</v>
       </c>
       <c r="E122" s="12" t="n">
+        <v>3362</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>3398</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>3323.5</v>
+      </c>
+      <c r="H122" s="12" t="n">
         <v>3350</v>
       </c>
-      <c r="F122" s="12" t="n">
-        <v>3366.4</v>
-      </c>
-      <c r="G122" s="12" t="n">
-        <v>3279.9</v>
-      </c>
-      <c r="H122" s="12" t="n">
-        <v>3342</v>
-      </c>
       <c r="I122" s="12" t="n">
-        <v>11.8</v>
+        <v>8</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>0.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v/>
+        <v>582.2</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>578</v>
+        <v>582.2</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>588.75</v>
+        <v>605</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>577.3</v>
+        <v>580.7</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>582.2</v>
+        <v>602.1</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v/>
+        <v>19.9</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v/>
+        <v>1498.7</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1511</v>
+        <v>1497</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1527</v>
+        <v>1497</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1485</v>
+        <v>1463</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1498.7</v>
+        <v>1468.5</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v/>
+        <v>-30.2</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v/>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v/>
+        <v>1103.2</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1088</v>
+        <v>1101.5</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1103.2</v>
+        <v>1084.3</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v/>
+        <v>-18.9</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>162</v>
+        <v>163.85</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>162.8</v>
+        <v>162.99</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>164.5</v>
+        <v>165.04</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>161.17</v>
+        <v>162.5</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>163.85</v>
+        <v>163.7</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>1.14</v>
+        <v>-0.15</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v/>
+        <v>2355</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2374</v>
+        <v>2325.7</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2374</v>
+        <v>2326.6</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2335.1</v>
+        <v>2286.8</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2355</v>
+        <v>2307.5</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v/>
+        <v>-47.5</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v/>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128890</v>
+        <v>128245</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>128750</v>
+        <v>128400</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>129290</v>
+        <v>129090</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128000</v>
+        <v>127545</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128245</v>
+        <v>128315</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-645</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-0.5</v>
+        <v>70</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2880</v>
+        <v>2899.7</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2890</v>
+        <v>2854.1</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2899.7</v>
+        <v>2865.3</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2868.8</v>
+        <v>2795.6</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2899.7</v>
+        <v>2815</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>0.68</v>
+        <v>-84.7</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>365.9</v>
+        <v>371.05</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>370.7</v>
+        <v>372</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>378.3</v>
+        <v>386</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>367.8</v>
+        <v>371.65</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>371.05</v>
+        <v>377.6</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>5.15</v>
+        <v>6.55</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1302.5</v>
+        <v>1292</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1274.5</v>
+        <v>1281</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1298.3</v>
+        <v>1286.6</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1251.9</v>
+        <v>1255</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1292</v>
+        <v>1267</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-10.5</v>
+        <v>-25</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8603.5</v>
+        <v>8731</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8552</v>
+        <v>8740</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8754</v>
+        <v>8949.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8505.5</v>
+        <v>8700</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8731</v>
+        <v>8775.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>127.5</v>
+        <v>44.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>1.48</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1397.4</v>
+        <v>1400.5</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1415.1</v>
+        <v>1405.9</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1392.9</v>
+        <v>1389.2</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1400.5</v>
+        <v>1393</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>0.18</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>83.84999999999999</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>84.06</v>
+        <v>84.7</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>84.78</v>
+        <v>85.89</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>83.73999999999999</v>
+        <v>84.53</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>84.70999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.86</v>
+        <v>1.09</v>
       </c>
       <c r="J134" s="13" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>332</v>
+        <v>330.8</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>330</v>
+        <v>331.1</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>333.2</v>
+        <v>337.5</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>328.65</v>
+        <v>330.9</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>330.8</v>
+        <v>334.5</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-0.36</v>
+        <v>3.7</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1847.5</v>
+        <v>1833.8</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1852</v>
+        <v>1821</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1857.2</v>
+        <v>1836.2</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1820.4</v>
+        <v>1796.1</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1833.8</v>
+        <v>1800</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-13.7</v>
+        <v>-33.8</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-0.74</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11847</v>
+        <v>11780</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11750</v>
+        <v>11762</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11815</v>
+        <v>11762</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11636</v>
+        <v>11550</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11780</v>
+        <v>11630</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-67</v>
+        <v>-150</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>-0.57</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>233.7</v>
+        <v>236</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>234.8</v>
+        <v>237.8</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>238</v>
+        <v>239.27</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>232.22</v>
+        <v>234.02</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>236</v>
+        <v>234.02</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>0.98</v>
+        <v>-1.98</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
+        <v>35915</v>
+      </c>
+      <c r="E139" s="9" t="n">
         <v>35825</v>
       </c>
-      <c r="E139" s="9" t="n">
-        <v>35700</v>
-      </c>
       <c r="F139" s="9" t="n">
-        <v>36540</v>
+        <v>35825</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35505</v>
+        <v>35200</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35915</v>
+        <v>35395</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>0.25</v>
+        <v>-520</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5540</v>
+        <v>5560</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5550</v>
+        <v>5490</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5600</v>
+        <v>5490</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5491</v>
+        <v>5372.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5560</v>
+        <v>5419</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>0.36</v>
+        <v>-141</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v/>
+        <v>285.8</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>290.95</v>
+        <v>285.8</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>291</v>
+        <v>288.5</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>285</v>
+        <v>284.15</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>285.8</v>
+        <v>285.9</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v/>
+        <v>0.1</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>353.1</v>
+        <v>355.9</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>352.05</v>
+        <v>354.35</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>356.5</v>
+        <v>355.3</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>351.15</v>
+        <v>350.1</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>355.9</v>
+        <v>351.4</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>0.79</v>
+        <v>-4.5</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1575</v>
+        <v>1593</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1579.8</v>
+        <v>1579</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1593</v>
+        <v>1585.6</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1593</v>
+        <v>1572</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J144" s="13" t="n">
-        <v>1.14</v>
+        <v>-21</v>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2430</v>
+        <v>2395</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2416.4</v>
+        <v>2395</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2428.4</v>
+        <v>2402</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2390.1</v>
+        <v>2367.6</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-35</v>
+        <v>-1</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-1.44</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>115.6</v>
+        <v>116</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>115.75</v>
+        <v>115.25</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>116.68</v>
+        <v>117</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>114.95</v>
+        <v>115.25</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116</v>
+        <v>115.61</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>0.35</v>
+        <v>-0.39</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8261</v>
+        <v>8373.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8301</v>
+        <v>8373.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8433</v>
+        <v>8407</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8301</v>
+        <v>8302</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8373.5</v>
+        <v>8354</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>1.36</v>
+        <v>-19.5</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v/>
+        <v>265.75</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>265.65</v>
+        <v>265</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>267.25</v>
+        <v>269.25</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>263</v>
+        <v>264.5</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>265.75</v>
+        <v>265.85</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v/>
+        <v>0.1</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1156.5</v>
+        <v>1231.3</v>
       </c>
       <c r="E149" s="9" t="n">
+        <v>1231.3</v>
+      </c>
+      <c r="F149" s="9" t="n">
+        <v>1232</v>
+      </c>
+      <c r="G149" s="9" t="n">
         <v>1161.5</v>
       </c>
-      <c r="F149" s="9" t="n">
-        <v>1243</v>
-      </c>
-      <c r="G149" s="9" t="n">
-        <v>1153.6</v>
-      </c>
       <c r="H149" s="9" t="n">
-        <v>1231.3</v>
+        <v>1169.2</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="J149" s="13" t="n">
-        <v>6.47</v>
+        <v>-62.1</v>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>-5.04</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v/>
+        <v>418.5</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>413</v>
+        <v>415.3</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>419.1</v>
+        <v>420.4</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>413</v>
+        <v>414.7</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>418.5</v>
+        <v>416</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v/>
+        <v>-2.5</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v/>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>316.4</v>
+        <v>317.85</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>316.8</v>
+        <v>316.55</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>318</v>
+        <v>317.35</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>314</v>
+        <v>313.6</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>317.85</v>
+        <v>314.5</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>0.46</v>
+        <v>-3.35</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1309.5</v>
+        <v>1294.9</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1304.1</v>
+        <v>1283.5</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1306.8</v>
+        <v>1294.7</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1288</v>
+        <v>1277.2</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1294.9</v>
+        <v>1279</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-14.6</v>
+        <v>-15.9</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>-1.11</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>187.9</v>
+        <v>186.1</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>188.5</v>
+        <v>185.98</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>190.8</v>
+        <v>189.4</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>186.05</v>
+        <v>185.36</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>186.1</v>
+        <v>186.4</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>-0.96</v>
+        <v>0.3</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v/>
+        <v>668</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>671</v>
+        <v>665.35</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>675</v>
+        <v>674.45</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>661.35</v>
+        <v>657.25</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>668</v>
+        <v>668.4</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v/>
+        <v>0.4</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1732</v>
+        <v>1696.6</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1734.6</v>
+        <v>1703.6</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1739.9</v>
+        <v>1703.6</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1696.6</v>
+        <v>1676</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1696.6</v>
+        <v>1684</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-35.4</v>
+        <v>-12.6</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-2.04</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1005.9</v>
+        <v>1008</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1004.9</v>
+        <v>999</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1011.2</v>
+        <v>1012.2</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1002.1</v>
+        <v>992.4</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1008</v>
+        <v>1000.5</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>0.21</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>23365</v>
+        <v>23160</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>23500</v>
+        <v>23160</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>23560</v>
+        <v>23240</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>23130</v>
+        <v>22900</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>23160</v>
+        <v>22950</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-205</v>
+        <v>-210</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1030</v>
+        <v>1018.2</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1031.9</v>
+        <v>1034.8</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1017.2</v>
+        <v>1013</v>
       </c>
       <c r="H158" s="12" t="n">
         <v>1029</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-0.77</v>
+        <v>0</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3927</v>
+        <v>3951.3</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3911</v>
+        <v>3932</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3998.8</v>
+        <v>4003</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3911</v>
+        <v>3911.8</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3951.3</v>
+        <v>3949.1</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>0.62</v>
+        <v>-2.2</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v/>
+        <v>2522</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2546</v>
+        <v>2519.8</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2546</v>
+        <v>2532</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2517</v>
+        <v>2509.7</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v/>
+        <v>-2</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v/>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1895</v>
+        <v>1885.9</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1892</v>
+        <v>1892.6</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1895.6</v>
+        <v>1898.6</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1876.8</v>
+        <v>1864.9</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1885.9</v>
+        <v>1864.9</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-9.1</v>
+        <v>-21</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-0.48</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v/>
+        <v>453.5</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>453.1</v>
+        <v>453.95</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>458.85</v>
+        <v>457.9</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>449</v>
+        <v>447.7</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>453.5</v>
+        <v>449.3</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v/>
+        <v>-4.2</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v/>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>389.3</v>
+        <v>387.55</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>389.3</v>
+        <v>386.8</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>390.65</v>
+        <v>388.6</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>383.5</v>
+        <v>382.6</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>387.55</v>
+        <v>386.8</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-1.75</v>
+        <v>-0.75</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-0.45</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>613.35</v>
+        <v>607.7</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>611.6</v>
+        <v>604.7</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>614.95</v>
+        <v>607.95</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>605.5</v>
+        <v>600.55</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>607.7</v>
+        <v>603.05</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-5.65</v>
+        <v>-4.65</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-0.92</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v/>
+        <v>1752.8</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1746.9</v>
+        <v>1752</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1760</v>
+        <v>1784</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1718.2</v>
+        <v>1734.9</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1752.8</v>
+        <v>1772.8</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v/>
+        <v>20</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1015</v>
+        <v>1014.1</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1015</v>
+        <v>1010.8</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1018.7</v>
+        <v>1013.7</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1007.9</v>
+        <v>1001</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1014.1</v>
+        <v>1001</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-0.9</v>
+        <v>-13.1</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>-0.09</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>365.7</v>
+        <v>365.55</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>364.65</v>
+        <v>364.1</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>367.2</v>
+        <v>373.7</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>362.25</v>
+        <v>363.15</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>365.55</v>
+        <v>370</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-0.04</v>
+        <v>4.45</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>185.61</v>
+        <v>184.15</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>185.9</v>
+        <v>184.8</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>186.5</v>
+        <v>190.26</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>183.61</v>
+        <v>183.41</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>184.15</v>
+        <v>188.75</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>-0.79</v>
+        <v>4.6</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2270</v>
+        <v>2255.5</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2270</v>
+        <v>2237</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2274.5</v>
+        <v>2237</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2244</v>
+        <v>2193.2</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2255.5</v>
+        <v>2208</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-14.5</v>
+        <v>-47.5</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.64</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1556.1</v>
+        <v>1531</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1569.9</v>
+        <v>1531</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1541.4</v>
+        <v>1498</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-5</v>
+        <v>-51</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>-0.32</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v/>
+        <v>2638.7</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2683.4</v>
+        <v>2649.4</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2683.4</v>
+        <v>2708.6</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2626.2</v>
+        <v>2596.3</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2638.7</v>
+        <v>2678.3</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v/>
+        <v>39.6</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4995</v>
+        <v>4987</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4975</v>
+        <v>5010</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5015.5</v>
+        <v>5019</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4969</v>
+        <v>4968</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>-0.16</v>
+        <v>18</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4914</v>
+        <v>4960</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4900</v>
+        <v>4960</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4983.5</v>
+        <v>4992</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4887</v>
+        <v>4925</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4960</v>
+        <v>4930</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>-30</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v/>
+        <v>1270.2</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1283.9</v>
+        <v>1322.4</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1257.6</v>
+        <v>1271.6</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1270.2</v>
+        <v>1305.7</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v/>
+        <v>35.5</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2814.5</v>
+        <v>2793.6</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2800.5</v>
+        <v>2793.6</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2812.8</v>
+        <v>2841.8</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2770.4</v>
+        <v>2782</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2793.6</v>
+        <v>2820</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-20.9</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>-0.74</v>
+        <v>26.4</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4132</v>
+        <v>4133.2</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4139</v>
+        <v>4102</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4156.8</v>
+        <v>4217.5</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4078</v>
+        <v>4071.3</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4133.2</v>
+        <v>4151.1</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>1.2</v>
+        <v>17.9</v>
       </c>
       <c r="J177" s="13" t="n">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v/>
+        <v>1252.5</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1291</v>
+        <v>1252</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1293.9</v>
+        <v>1279</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1245.9</v>
+        <v>1245</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1252.5</v>
+        <v>1266.7</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v/>
+        <v>14.2</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11175</v>
+        <v>11009</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11175</v>
+        <v>10975</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11215</v>
+        <v>10998</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10995</v>
+        <v>10860</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11009</v>
+        <v>10900</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-166</v>
+        <v>-109</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>-1.49</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>186.04</v>
+        <v>183.22</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>184.41</v>
+        <v>181.75</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>185.15</v>
+        <v>183.89</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>181.4</v>
+        <v>180.82</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>183.22</v>
+        <v>183.89</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>-1.52</v>
+        <v>0.67</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>573</v>
+        <v>576.75</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>575.5</v>
+        <v>573.5</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>576.75</v>
+        <v>578.35</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>569.95</v>
+        <v>568.55</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>576.75</v>
+        <v>575.7</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>0.65</v>
+        <v>-1.05</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>269.3</v>
+        <v>271.5</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>272.8</v>
+        <v>275.75</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>269.15</v>
+        <v>268.55</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>272</v>
+        <v>272.5</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J182" s="13" t="n">
-        <v>1.49</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1167.2</v>
+        <v>1144.8</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1165</v>
+        <v>1144</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1169.2</v>
+        <v>1147</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1141.3</v>
+        <v>1136</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1144.8</v>
+        <v>1143.8</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-22.4</v>
+        <v>-1</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-1.92</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>172.8</v>
+        <v>171.5</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>172.8</v>
+        <v>168.7</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>172.9</v>
+        <v>169.15</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>171.13</v>
+        <v>166.37</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>171.5</v>
+        <v>167</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.3</v>
+        <v>-4.5</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>-0.75</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1156.9</v>
+        <v>1145.5</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1161.7</v>
+        <v>1150</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1167.7</v>
+        <v>1158</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1142</v>
+        <v>1126.5</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1145.5</v>
+        <v>1127.4</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-11.4</v>
+        <v>-18.1</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>-0.99</v>
+        <v>-1.58</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  08-Sep-2026 05:04 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  09-Sep-2026 05:02 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-Sep-2026 05:04 PM</t>
+          <t>09-Sep-2026 05:02 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 09-Sep-2026 05:02 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 10-Sep-2026 04:54 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>09-Sep-2026 05:02 PM</t>
+          <t>10-Sep-2026 04:54 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  09-Sep-2026 05:02 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  10-Sep-2026 04:54 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>503.7</v>
+        <v>496.2</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>503.7</v>
+        <v>496.2</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>503.7</v>
+        <v>511.95</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>494.5</v>
+        <v>495.45</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>496.2</v>
+        <v>504.05</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-7.5</v>
+        <v>7.85</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-1.49</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7387</v>
+        <v>7401.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7377</v>
+        <v>7400</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7480</v>
+        <v>7418.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7361</v>
+        <v>7287</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7401.5</v>
+        <v>7329</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>14.5</v>
+        <v>-72.5</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>0.2</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25555</v>
+        <v>25225</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25555</v>
+        <v>25245</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25705</v>
+        <v>25395</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25190</v>
+        <v>25205</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25225</v>
+        <v>25260</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-330</v>
+        <v>35</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>-1.29</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>396.95</v>
+        <v>400</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>396.85</v>
+        <v>398</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>402.05</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>393.55</v>
+        <v>395.85</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>400</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>0.77</v>
+        <v>0</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>52.24</v>
+        <v>51.33</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>52.19</v>
+        <v>51.35</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>52.22</v>
+        <v>51.82</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>51.23</v>
+        <v>50.75</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>51.33</v>
+        <v>50.89</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>-1.74</v>
+        <v>-0.44</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1262.8</v>
+        <v>1257.7</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1260</v>
+        <v>1259.2</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1272</v>
+        <v>1260.3</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1255.1</v>
+        <v>1250.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1257.7</v>
+        <v>1254.3</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>-0.4</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2953.1</v>
+        <v>3104.7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2959.9</v>
+        <v>3114.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3142</v>
+        <v>3114.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2935.2</v>
+        <v>3041.1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>151.6</v>
+        <v>-27.5</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>5.13</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1719</v>
+        <v>1779.9</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1785.9</v>
+        <v>1780</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1706</v>
+        <v>1750.4</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>65</v>
+        <v>-7</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>3.8</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5181</v>
+        <v>5139</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5181</v>
+        <v>5166</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5222</v>
+        <v>5185</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5139</v>
+        <v>5104.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5139</v>
+        <v>5138</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-42</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>398.3</v>
+        <v>397</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>396.3</v>
+        <v>395.5</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>400.8</v>
+        <v>397.55</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>395</v>
+        <v>394.05</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>397</v>
+        <v>395.6</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>-0.33</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>298</v>
+        <v>299.05</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>297.95</v>
+        <v>297</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>303.65</v>
+        <v>301.35</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>291.6</v>
+        <v>296.15</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>299.05</v>
+        <v>297.3</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1.05</v>
+        <v>-1.75</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.35</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2185</v>
+        <v>2168</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2194.9</v>
+        <v>2194.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2165</v>
+        <v>2158.4</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2168</v>
+        <v>2194.8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-17</v>
+        <v>26.8</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-0.78</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8837.5</v>
+        <v>8967</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8825</v>
+        <v>9000</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8974.5</v>
+        <v>9024</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8803.5</v>
+        <v>8875</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8967</v>
+        <v>8900</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>129.5</v>
+        <v>-67</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>1.47</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>411.5</v>
+        <v>422.25</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>410</v>
+        <v>423.6</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>424.3</v>
+        <v>423.65</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>408</v>
+        <v>416.4</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>422.25</v>
+        <v>419.55</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10.75</v>
+        <v>-2.7</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>2.61</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>167.12</v>
+        <v>166.5</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>169.27</v>
+        <v>167.04</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>166.22</v>
+        <v>164.71</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>167</v>
+        <v>166.12</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-1.18</v>
+        <v>-0.88</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2481.6</v>
+        <v>2489</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2459.1</v>
+        <v>2485.1</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2489</v>
+        <v>2498.1</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2457.4</v>
+        <v>2468.6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2489</v>
+        <v>2498.1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>0.3</v>
+        <v>9.1</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1500.8</v>
+        <v>1474.8</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1492.8</v>
+        <v>1468.2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1507</v>
+        <v>1474.8</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1465.6</v>
+        <v>1451.7</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1474.8</v>
+        <v>1459</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-26</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-1.73</v>
+        <v>-15.8</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>609.4</v>
+        <v>612.3</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>610.9</v>
+        <v>613.5</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>624.4</v>
+        <v>616</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>608.55</v>
+        <v>600.25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>612.3</v>
+        <v>602.7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>2.9</v>
+        <v>-9.6</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.48</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6314.5</v>
+        <v>6221.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6295</v>
+        <v>6221.5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6321.5</v>
+        <v>6395</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6203.5</v>
+        <v>6209.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6221.5</v>
+        <v>6356</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-93</v>
+        <v>134.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-1.47</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1073.7</v>
+        <v>1060.5</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1070.9</v>
+        <v>1058.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1077.9</v>
+        <v>1062</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1060.5</v>
+        <v>1047.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1060.5</v>
+        <v>1054.7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>-1.23</v>
+        <v>-5.8</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1692</v>
+        <v>1698.9</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1685</v>
+        <v>1693.4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1704</v>
+        <v>1693.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1672</v>
+        <v>1655</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1698.9</v>
+        <v>1668.4</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>6.9</v>
+        <v>-30.5</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.41</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1244.9</v>
+        <v>1238.5</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1236</v>
+        <v>1242.1</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1257.4</v>
+        <v>1255.2</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1234.7</v>
+        <v>1240.4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1238.5</v>
+        <v>1246</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-6.4</v>
+        <v>7.5</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-0.51</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11841</v>
+        <v>11771</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11896</v>
+        <v>11820</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11740</v>
+        <v>11673</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-90</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-0.76</v>
+        <v>-22</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1939.1</v>
+        <v>1932.9</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1951.9</v>
+        <v>1942.7</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1921.5</v>
+        <v>1921.1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1927</v>
+        <v>1940.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-11.1</v>
+        <v>13.5</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-0.57</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1045.1</v>
+        <v>1042.5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1060.1</v>
+        <v>1048.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1038.5</v>
+        <v>1036.5</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1039.3</v>
+        <v>1043.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-14.8</v>
+        <v>4.2</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2258</v>
+        <v>2208.6</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2248.5</v>
+        <v>2234.8</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2191.3</v>
+        <v>2188</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2208.6</v>
+        <v>2193</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-49.4</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-2.19</v>
+        <v>-15.6</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>711.45</v>
+        <v>700.05</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>710.05</v>
+        <v>703</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>710.05</v>
+        <v>714</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>689</v>
+        <v>693.3</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>700.05</v>
+        <v>705.15</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-11.4</v>
+        <v>5.1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-1.6</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>171.58</v>
+        <v>171.7</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>170.6</v>
+        <v>171.9</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>174.96</v>
+        <v>174.01</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>168.65</v>
+        <v>169.41</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>171.7</v>
+        <v>174</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.3</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>236.6</v>
+        <v>234.1</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>236.65</v>
+        <v>235</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>237.15</v>
+        <v>239.46</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>234.05</v>
+        <v>234.84</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>234.1</v>
+        <v>237.62</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2.5</v>
+        <v>3.52</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-1.06</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>410.55</v>
+        <v>406</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>411.55</v>
+        <v>407</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>413.85</v>
+        <v>407.2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>-1.11</v>
+        <v>-1</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>479.45</v>
+        <v>470.8</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>483.9</v>
+        <v>471</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>483.9</v>
+        <v>473.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>468</v>
+        <v>460.95</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>470.8</v>
+        <v>463.8</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-8.65</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>-1.8</v>
+        <v>-7</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1844</v>
+        <v>1814.7</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1830.5</v>
+        <v>1815.1</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1834.8</v>
+        <v>1849</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1814.7</v>
+        <v>1839</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-29.3</v>
+        <v>24.3</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-1.59</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>422.15</v>
+        <v>433.7</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>422.15</v>
+        <v>434.2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>436</v>
+        <v>435.45</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>421.65</v>
+        <v>427.05</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>433.7</v>
+        <v>429.5</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>11.55</v>
+        <v>-4.2</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>2.74</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>392.3</v>
+        <v>395</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>403.95</v>
+        <v>397.95</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>393</v>
+        <v>388.45</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>395</v>
+        <v>391.65</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>2.7</v>
+        <v>-3.35</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48785</v>
+        <v>49100</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48475</v>
+        <v>48865</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>49100</v>
+        <v>49080</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>48360</v>
+        <v>48480</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>49100</v>
+        <v>48775</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>315</v>
+        <v>-325</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0.65</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>303.85</v>
+        <v>303.55</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>300.15</v>
+        <v>302.95</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>306.5</v>
+        <v>306.1</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>298.65</v>
+        <v>301.75</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>303.55</v>
+        <v>303</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0.55</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5064</v>
+        <v>5090</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5064</v>
+        <v>5108</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5113</v>
+        <v>5108</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5023</v>
+        <v>4997</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5090</v>
+        <v>5009</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>26</v>
+        <v>-81</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.51</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>281.65</v>
+        <v>277.2</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>279.85</v>
+        <v>279</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>279.85</v>
+        <v>282.7</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>276.1</v>
+        <v>275</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>277.2</v>
+        <v>275.8</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>-1.58</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124.68</v>
+        <v>124.08</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>124.42</v>
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>125.38</v>
+        <v>127.6</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>124.04</v>
+        <v>123.7</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124.08</v>
+        <v>124.6</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.6</v>
+        <v>0.52</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.48</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>797.6</v>
+        <v>786.9</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>797.6</v>
+        <v>788.9</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>804.65</v>
+        <v>791.75</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>785</v>
+        <v>780.3</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>786.9</v>
+        <v>782.2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>-1.34</v>
+        <v>-4.7</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>418.65</v>
+        <v>415.6</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>414.6</v>
+        <v>415.5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>417.95</v>
+        <v>423.15</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>414.5</v>
+        <v>415.3</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>415.6</v>
+        <v>417.75</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-3.05</v>
+        <v>2.15</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>-0.73</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1823.4</v>
+        <v>1829</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1828.4</v>
+        <v>1827.1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1843.4</v>
+        <v>1868.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1809</v>
+        <v>1804.2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1829</v>
+        <v>1859</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>0.31</v>
+        <v>30</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1384</v>
+        <v>1363.1</v>
       </c>
       <c r="E45" s="9" t="n">
+        <v>1366.8</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>1380</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1388.7</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>1363.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1363.1</v>
+        <v>1373.3</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-20.9</v>
+        <v>10.2</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-1.51</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>420.25</v>
+        <v>431</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>420.85</v>
+        <v>433</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>435.35</v>
+        <v>436.3</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>419.8</v>
+        <v>430</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>2.56</v>
+        <v>1</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1950</v>
+        <v>1845</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1815.5</v>
+        <v>1842</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1877.6</v>
+        <v>1878</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1780.7</v>
+        <v>1821</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1845</v>
+        <v>1833.1</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-105</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-5.38</v>
+        <v>-11.9</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1819.9</v>
+        <v>1800</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1815</v>
+        <v>1804.5</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1789.8</v>
+        <v>1796.9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1800</v>
+        <v>1808.5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-19.9</v>
+        <v>8.5</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>-1.09</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>512.45</v>
+        <v>509.95</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>499.5</v>
+        <v>503.7</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>510</v>
+        <v>504.15</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>8</v>
+        <v>-5.85</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>1.59</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1951.1</v>
+        <v>1962.7</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1946.1</v>
+        <v>1948.8</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1967.6</v>
+        <v>1972</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1918.1</v>
+        <v>1947</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1962.7</v>
+        <v>1961.9</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>11.6</v>
+        <v>-0.8</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.59</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>231.9</v>
+        <v>232.96</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>229.95</v>
+        <v>234</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>234.42</v>
+        <v>234</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>228.57</v>
+        <v>229.74</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>232.96</v>
+        <v>230</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1.06</v>
+        <v>-2.96</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>0.46</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>232.97</v>
+        <v>231.67</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>232.95</v>
+        <v>232</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>235.57</v>
+        <v>232.99</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>230.23</v>
+        <v>224.95</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>231.67</v>
+        <v>226.45</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-5.22</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5040</v>
+        <v>5170.5</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5020</v>
+        <v>5170.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5182.5</v>
+        <v>5237</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5020</v>
+        <v>5069.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5170.5</v>
+        <v>5155</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>130.5</v>
+        <v>-15.5</v>
       </c>
       <c r="J53" s="13" t="n">
-        <v>2.59</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>375</v>
+        <v>371.55</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>374.7</v>
+        <v>370.45</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>374.7</v>
+        <v>377.75</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>368.05</v>
+        <v>369</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>371.55</v>
+        <v>376.45</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-3.45</v>
+        <v>4.9</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-0.92</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1700.5</v>
+        <v>1733.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1710.7</v>
+        <v>1730</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1740</v>
+        <v>1762.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1690</v>
+        <v>1712</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1733.6</v>
+        <v>1745.3</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>1.95</v>
+        <v>11.7</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1647.8</v>
+        <v>1641.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1647.8</v>
+        <v>1642</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1672</v>
+        <v>1664.8</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1630</v>
+        <v>1633.5</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1641.9</v>
+        <v>1645.8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-0.36</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>55.44</v>
+        <v>55.25</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>55.48</v>
+        <v>55.01</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>54.8</v>
+        <v>54.2</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>55.25</v>
+        <v>54.34</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>-0.34</v>
+        <v>-0.91</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9575</v>
+        <v>9488</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9575</v>
+        <v>9600.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9615</v>
+        <v>9604</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9410</v>
+        <v>9386.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9488</v>
+        <v>9438.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-87</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>-0.91</v>
+        <v>-49.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>14100</v>
+        <v>13845</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>14100</v>
+        <v>13845</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>14271</v>
+        <v>13867</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13773</v>
+        <v>13355</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13845</v>
+        <v>13500</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-255</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>-1.81</v>
+        <v>-345</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>675.1</v>
+        <v>655.1</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>670.2</v>
+        <v>653.6</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>672.1</v>
+        <v>662.4</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>654.7</v>
+        <v>651.9</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>655.1</v>
+        <v>655.85</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-20</v>
+        <v>0.75</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-2.96</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1151</v>
+        <v>1147.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1136.4</v>
+        <v>1134.9</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-0.52</v>
+        <v>-2</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7747.5</v>
+        <v>7734.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7687</v>
+        <v>7713</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7784.5</v>
+        <v>7746</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7664.5</v>
+        <v>7637.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7734.5</v>
+        <v>7697</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-13</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-0.17</v>
+        <v>-37.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3013.2</v>
+        <v>2989.2</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3009</v>
+        <v>2989.2</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3036</v>
+        <v>3002.2</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2977.7</v>
+        <v>2951</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2989.2</v>
+        <v>2958.4</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-24</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>-0.8</v>
+        <v>-30.8</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>418.15</v>
+        <v>410.75</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>418.1</v>
+        <v>411</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>409.7</v>
+        <v>411</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>410.75</v>
+        <v>420.85</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-7.4</v>
+        <v>10.1</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-1.77</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>344.15</v>
+        <v>345</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>341.5</v>
+        <v>343.85</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>345</v>
+        <v>347.05</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>341.5</v>
+        <v>343.75</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>0.25</v>
+        <v>1</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>175.09</v>
+        <v>174.9</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.7</v>
+        <v>174</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>175.59</v>
+        <v>176.5</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>173.61</v>
+        <v>173.25</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>174.9</v>
+        <v>174.49</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>-0.11</v>
+        <v>-0.41</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2474.5</v>
+        <v>2435</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2486.9</v>
+        <v>2445.9</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2486.9</v>
+        <v>2449.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2400.1</v>
+        <v>2403.1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2435</v>
+        <v>2415</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-39.5</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>-1.6</v>
+        <v>-20</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>568.1</v>
+        <v>574.6</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>579.75</v>
+        <v>575</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>556.5</v>
+        <v>564.45</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>574.6</v>
+        <v>570.75</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>6.5</v>
+        <v>-3.85</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>1.14</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>865</v>
+        <v>863.8</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>867.95</v>
+        <v>863.8</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>867.95</v>
+        <v>872.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>856.1</v>
+        <v>859</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>863.8</v>
+        <v>869.9</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>-0.14</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1906.6</v>
+        <v>1857.1</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1905.5</v>
+        <v>1850</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1908.2</v>
+        <v>1874.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1855</v>
+        <v>1836</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1857.1</v>
+        <v>1872</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-49.5</v>
+        <v>14.9</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-2.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>895.35</v>
+        <v>884.8</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>899.75</v>
+        <v>870.1</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>901.8</v>
+        <v>905.85</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>878.1</v>
+        <v>870.1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>884.8</v>
+        <v>899.25</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-10.55</v>
+        <v>14.45</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>-1.18</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3306.8</v>
+        <v>3300</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3305</v>
+        <v>3290</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3320</v>
+        <v>3324.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3279</v>
+        <v>3279.9</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3300</v>
+        <v>3319</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-6.8</v>
+        <v>19</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-0.21</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="74">
@@ -3264,7 +3264,7 @@
       <c r="I74" s="12" t="n">
         <v/>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>5031.1</v>
+        <v>5000.5</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>5031.1</v>
+        <v>5015</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>5097.4</v>
+        <v>5052.4</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>5000.5</v>
+        <v>4914.6</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>5000.5</v>
+        <v>4950</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-30.6</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>-0.61</v>
+        <v>-50.5</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1140</v>
+        <v>1120.4</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1136</v>
+        <v>1121</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1143.5</v>
+        <v>1126</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1118.9</v>
+        <v>1105.5</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1120.4</v>
+        <v>1116</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>-1.72</v>
+        <v>-4.4</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1277</v>
+        <v>1229.8</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1248.8</v>
+        <v>1224.8</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1264.8</v>
+        <v>1237</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1222.7</v>
+        <v>1196.9</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1229.8</v>
+        <v>1207</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-47.2</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-3.7</v>
+        <v>-22.8</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2447.3</v>
+        <v>2440</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2444</v>
+        <v>2430</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2446.4</v>
+        <v>2448.1</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2410.9</v>
+        <v>2401</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2440</v>
+        <v>2433.8</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>-0.3</v>
+        <v>-6.2</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>698</v>
+        <v>687.1</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>700</v>
+        <v>694.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>687.1</v>
+        <v>686.2</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>687.1</v>
+        <v>693.8</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-15.9</v>
+        <v>6.7</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-2.26</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>533.8</v>
+        <v>514</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>533.7</v>
+        <v>515.15</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>534.6</v>
+        <v>526.15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>508.95</v>
+        <v>508.7</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>514</v>
+        <v>526.15</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-19.8</v>
+        <v>12.15</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>-3.71</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5333.5</v>
+        <v>5218</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5266.5</v>
+        <v>5235</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5297</v>
+        <v>5280</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5205.5</v>
+        <v>5169</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5218</v>
+        <v>5280</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-115.5</v>
+        <v>62</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>-2.17</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1009</v>
+        <v>1026.9</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1013.9</v>
+        <v>1027.5</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1032.4</v>
+        <v>1029.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1010.7</v>
+        <v>1007.8</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1026.9</v>
+        <v>1014</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>17.9</v>
+        <v>-12.9</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>1.77</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>532.85</v>
+        <v>532.3</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>538.4</v>
+        <v>539.15</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>530.5</v>
+        <v>525.7</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>532.3</v>
+        <v>527.3</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>-0.1</v>
+        <v>-5</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="E84" s="12" t="n">
         <v>347</v>
       </c>
-      <c r="E84" s="12" t="n">
-        <v>345.55</v>
-      </c>
       <c r="F84" s="12" t="n">
-        <v>350.9</v>
+        <v>353.85</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>343.55</v>
+        <v>346.95</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>348.9</v>
+        <v>352.65</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>0.55</v>
+        <v>3.75</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1980</v>
+        <v>1945</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1973</v>
+        <v>1940</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1979.6</v>
+        <v>1950</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>1936</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1945</v>
+        <v>1942.3</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-35</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-1.77</v>
+        <v>-2.7</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>35060</v>
+        <v>34180</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35190</v>
+        <v>34370</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>35285</v>
+        <v>34400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>34055</v>
+        <v>33875</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34180</v>
+        <v>34150</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-880</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-2.51</v>
+        <v>-30</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86.48</v>
+        <v>86</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.95</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.90000000000001</v>
+        <v>85.81999999999999</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86</v>
+        <v>86.84</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-0.58</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>116.54</v>
+        <v>117.95</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>116.05</v>
+        <v>117.95</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>118.89</v>
+        <v>118.63</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>115.82</v>
+        <v>116.06</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>117.95</v>
+        <v>116.63</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>1.41</v>
+        <v>-1.32</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>1.21</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>154.02</v>
+        <v>152.92</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>154</v>
+        <v>152.35</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>155.15</v>
+        <v>154.45</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>151.95</v>
+        <v>152</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>152.92</v>
+        <v>153.46</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.1</v>
+        <v>0.54</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-0.71</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>720</v>
+        <v>722.75</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>716.15</v>
+        <v>718.4</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>723.25</v>
+        <v>720.6</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>715</v>
+        <v>712.55</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>722.75</v>
+        <v>715.75</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>2.75</v>
+        <v>-7</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0.38</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1684.5</v>
+        <v>1671.9</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1684</v>
+        <v>1672.3</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1697.2</v>
+        <v>1683.2</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1670</v>
+        <v>1626</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1671.9</v>
+        <v>1637.7</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>-0.75</v>
+        <v>-34.2</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>5000</v>
+        <v>4975</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4950</v>
+        <v>4964.5</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5009</v>
+        <v>4966</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4950</v>
+        <v>4877</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4975</v>
+        <v>4945</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-0.5</v>
+        <v>-30</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>997.7</v>
+        <v>1004</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>994</v>
+        <v>1001.9</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1010</v>
+        <v>1002.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>994</v>
+        <v>986.7</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>1004</v>
+        <v>993.3</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>6.3</v>
+        <v>-10.7</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>0.63</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>373.05</v>
+        <v>373.7</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>371.75</v>
+        <v>376.2</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>376.45</v>
+        <v>376.2</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>369.75</v>
+        <v>368.7</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>373.7</v>
+        <v>372</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>0.65</v>
+        <v>-1.7</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>0.17</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1082</v>
+        <v>1035</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1059</v>
+        <v>1039.6</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1059</v>
+        <v>1046.6</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1026.5</v>
+        <v>1027.3</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1035</v>
+        <v>1036.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-47</v>
+        <v>1.5</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>134.35</v>
+        <v>135.6</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>133.3</v>
+        <v>134.31</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>136.14</v>
+        <v>136.15</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>133.06</v>
+        <v>134.31</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>135.6</v>
+        <v>134.94</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>1.25</v>
+        <v>-0.66</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>0.93</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1967.2</v>
+        <v>1963.6</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1956</v>
+        <v>1954.6</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1983.5</v>
+        <v>1979.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1948</v>
+        <v>1953.1</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1963.6</v>
+        <v>1970.9</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-3.6</v>
+        <v>7.3</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-0.18</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>472.45</v>
+        <v>469.5</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>471.95</v>
+        <v>470.85</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>475</v>
+        <v>476.4</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>469.5</v>
+        <v>467.75</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>-0.62</v>
+        <v>-1.75</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>263.5</v>
+        <v>260.8</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>263.65</v>
+        <v>261</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>264.5</v>
+        <v>263.9</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>260.2</v>
+        <v>259.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>260.8</v>
+        <v>259.3</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-1.02</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1136.3</v>
+        <v>1146.5</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1139.6</v>
+        <v>1149.7</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1158</v>
+        <v>1151.7</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1130.6</v>
+        <v>1131</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1146.5</v>
+        <v>1137</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>10.2</v>
+        <v>-9.5</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>0.9</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="101">
@@ -4168,22 +4168,22 @@
         <v>4990.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5009</v>
+        <v>4991.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5070</v>
+        <v>5004.5</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4960</v>
+        <v>4887</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>4990.5</v>
+        <v>4915.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>738.75</v>
+        <v>783.3</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>739</v>
+        <v>785</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>794</v>
+        <v>790.5</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>731</v>
+        <v>760.1</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>783.3</v>
+        <v>762.15</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>44.55</v>
+        <v>-21.15</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>6.03</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>526.5</v>
+        <v>534.8</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>526.5</v>
+        <v>529.9</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>541.7</v>
+        <v>534.05</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>521.5</v>
+        <v>527.5</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>534.8</v>
+        <v>530.45</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>-4.35</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>1.58</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1297.3</v>
+        <v>1310</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1303.9</v>
+        <v>1301</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1313</v>
+        <v>1311.3</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1290.1</v>
+        <v>1292.7</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>12.7</v>
+        <v>-6</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>0.98</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>480.4</v>
+        <v>475.95</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>477.1</v>
+        <v>474.95</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>479.25</v>
+        <v>480.9</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>473</v>
+        <v>467.95</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>475.95</v>
+        <v>473.8</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>-0.93</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1250.2</v>
+        <v>1239.2</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1248.9</v>
+        <v>1239.2</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1248.9</v>
+        <v>1254.2</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1234.3</v>
+        <v>1224.5</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1239.2</v>
+        <v>1243.9</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-11</v>
+        <v>4.7</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-0.88</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>419.25</v>
+        <v>414</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>418.2</v>
+        <v>413.7</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>420.65</v>
+        <v>416.55</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>413.95</v>
+        <v>412.8</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>414</v>
+        <v>416.55</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-5.25</v>
+        <v>2.55</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-1.25</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>562</v>
+        <v>553.1</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>558.3</v>
+        <v>554.5</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>559.25</v>
+        <v>559.5</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>551.25</v>
+        <v>548.75</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>553.1</v>
+        <v>550.95</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>-1.58</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1912.5</v>
+        <v>1919.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1905.2</v>
+        <v>1917.2</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1962</v>
+        <v>1927</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1901.2</v>
+        <v>1880.9</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1919.7</v>
+        <v>1916.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>7.2</v>
+        <v>-3</v>
       </c>
       <c r="J109" s="13" t="n">
-        <v>0.38</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1946.9</v>
+        <v>1937</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1946.9</v>
+        <v>1932.6</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1955</v>
+        <v>1950.5</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1917.9</v>
+        <v>1920.9</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-9.9</v>
+        <v>8</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>-0.51</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>564.75</v>
+        <v>558</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>550.45</v>
+        <v>543.8</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>555</v>
+        <v>552.3</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>-1.42</v>
+        <v>-2.7</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3935.3</v>
+        <v>3949.4</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4020.2</v>
+        <v>3965.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3922.6</v>
+        <v>3910</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-23.5</v>
+        <v>32.4</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>-0.6</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>307.9</v>
+        <v>309.05</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>314.4</v>
+        <v>311.4</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>307</v>
+        <v>306.3</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3389.1</v>
+        <v>3364</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3375</v>
+        <v>3364</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3375</v>
+        <v>3411.2</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3326.1</v>
+        <v>3352.5</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3364</v>
+        <v>3377.9</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-25.1</v>
+        <v>13.9</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.74</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2104.7</v>
+        <v>2100</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2120</v>
+        <v>2098.2</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2090</v>
+        <v>2060.3</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2100</v>
+        <v>2077.8</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>-0.22</v>
+        <v>-22.2</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3160</v>
+        <v>3150</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3135.3</v>
+        <v>3141.7</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3151.3</v>
+        <v>3146.9</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3118</v>
+        <v>3097.7</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3150</v>
+        <v>3123.8</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-0.32</v>
+        <v>-26.2</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>323</v>
+        <v>319.4</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>328</v>
+        <v>335.1</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>312.3</v>
+        <v>318.25</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>320</v>
+        <v>330.8</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-5</v>
+        <v>10.8</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-1.54</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>823.9</v>
+        <v>813.9</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>821.85</v>
+        <v>813.9</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>823</v>
+        <v>813.9</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>808.45</v>
+        <v>799.55</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>813.9</v>
+        <v>803</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>-1.21</v>
+        <v>-10.9</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12641</v>
+        <v>12618</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12609</v>
+        <v>12679</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12692</v>
+        <v>12693</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12537</v>
+        <v>12517</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12618</v>
+        <v>12590</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-23</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-0.18</v>
+        <v>-28</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3342</v>
+        <v>3350</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3362</v>
+        <v>3311.9</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3398</v>
+        <v>3335.5</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3323.5</v>
+        <v>3285</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>8</v>
+        <v>-50</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>0.24</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>582.2</v>
+        <v>602.1</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>582.2</v>
+        <v>605.15</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>605</v>
+        <v>607.5</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>580.7</v>
+        <v>590.6</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>602.1</v>
+        <v>595.65</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>19.9</v>
+        <v>-6.45</v>
       </c>
       <c r="J123" s="13" t="n">
-        <v>3.42</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1498.7</v>
+        <v>1468.5</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1497</v>
+        <v>1465.8</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1497</v>
+        <v>1483.7</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1463</v>
+        <v>1452</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1468.5</v>
+        <v>1479.9</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-30.2</v>
+        <v>11.4</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>-2.02</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1103.2</v>
+        <v>1084.3</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1101.5</v>
+        <v>1081.5</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1081</v>
+        <v>1081.5</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1084.3</v>
+        <v>1100.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-18.9</v>
+        <v>16.5</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-1.71</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>163.85</v>
+        <v>163.7</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>162.99</v>
+        <v>163.7</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>165.04</v>
+        <v>164.7</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>162.5</v>
+        <v>162.33</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>163.7</v>
+        <v>163.2</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>-0.09</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2355</v>
+        <v>2307.5</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2325.7</v>
+        <v>2320</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2326.6</v>
+        <v>2329</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2286.8</v>
+        <v>2290.2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2307.5</v>
+        <v>2291.7</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-47.5</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>-2.02</v>
+        <v>-15.8</v>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128245</v>
+        <v>128315</v>
       </c>
       <c r="E128" s="12" t="n">
         <v>128400</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>129090</v>
+        <v>129245</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>127545</v>
+        <v>128000</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128315</v>
+        <v>128270</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>70</v>
+        <v>-45</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2899.7</v>
+        <v>2815</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2854.1</v>
+        <v>2815.4</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2865.3</v>
+        <v>2853.9</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2795.6</v>
+        <v>2807.4</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2815</v>
+        <v>2841.5</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-84.7</v>
+        <v>26.5</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-2.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>382</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>383</v>
+      </c>
+      <c r="G130" s="12" t="n">
         <v>371.05</v>
       </c>
-      <c r="E130" s="12" t="n">
-        <v>372</v>
-      </c>
-      <c r="F130" s="12" t="n">
-        <v>386</v>
-      </c>
-      <c r="G130" s="12" t="n">
-        <v>371.65</v>
-      </c>
       <c r="H130" s="12" t="n">
-        <v>377.6</v>
+        <v>373.35</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>6.55</v>
+        <v>-4.25</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>1.77</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1292</v>
+        <v>1267</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1281</v>
+        <v>1266.9</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1286.6</v>
+        <v>1277.9</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1255</v>
+        <v>1246.9</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-1.93</v>
+        <v>-2</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8731</v>
+        <v>8775.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8740</v>
+        <v>8748</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8949.5</v>
+        <v>8771.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8700</v>
+        <v>8622</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8775.5</v>
+        <v>8700.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>44.5</v>
+        <v>-75</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>0.51</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1400.5</v>
+        <v>1393</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1400.5</v>
+        <v>1396.8</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1405.9</v>
+        <v>1402.8</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1389.2</v>
+        <v>1377.7</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1393</v>
+        <v>1386.2</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>-0.54</v>
+        <v>-6.8</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>84.70999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>84.7</v>
+        <v>86</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>85.89</v>
+        <v>86.12</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>84.53</v>
+        <v>84.17</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>85.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>1.09</v>
+        <v>-1.2</v>
       </c>
       <c r="J134" s="13" t="n">
-        <v>1.29</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>330.8</v>
+        <v>334.5</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>331.1</v>
+        <v>335.65</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>337.5</v>
+        <v>335.7</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>330.9</v>
+        <v>333.1</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>334.5</v>
+        <v>335</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>1.12</v>
+        <v>0.5</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1833.8</v>
+        <v>1800</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1821</v>
+        <v>1799.8</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1836.2</v>
+        <v>1806.4</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1796.1</v>
+        <v>1777.5</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>-1.84</v>
+        <v>-8</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11780</v>
+        <v>11630</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11762</v>
+        <v>11680</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11762</v>
+        <v>11814</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11550</v>
+        <v>11627</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11630</v>
+        <v>11725</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-150</v>
+        <v>95</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>-1.27</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>236</v>
+        <v>234.02</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>237.8</v>
+        <v>236.1</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>239.27</v>
+        <v>239.8</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>234.02</v>
+        <v>235.6</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>234.02</v>
+        <v>237.27</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-1.98</v>
+        <v>3.25</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>-0.84</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35915</v>
+        <v>35395</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35825</v>
+        <v>35300</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35825</v>
+        <v>35900</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35200</v>
+        <v>34960</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35395</v>
+        <v>35750</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-520</v>
+        <v>355</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>-1.45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
+        <v>5419</v>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>5404.5</v>
+      </c>
+      <c r="F141" s="9" t="n">
         <v>5560</v>
       </c>
-      <c r="E141" s="9" t="n">
-        <v>5490</v>
-      </c>
-      <c r="F141" s="9" t="n">
-        <v>5490</v>
-      </c>
       <c r="G141" s="9" t="n">
-        <v>5372.5</v>
+        <v>5370.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5419</v>
+        <v>5509.5</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-141</v>
+        <v>90.5</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>-2.54</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>285.8</v>
+        <v>285.9</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>285.8</v>
+        <v>284</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>288.5</v>
+        <v>290.7</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>284.15</v>
+        <v>283.05</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>285.9</v>
+        <v>288.7</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>0.03</v>
+        <v>2.8</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>355.9</v>
+        <v>351.4</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>354.35</v>
+        <v>350</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>355.3</v>
+        <v>354.75</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>350.1</v>
+        <v>349.3</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>351.4</v>
+        <v>352.8</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>-1.26</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1593</v>
+        <v>1572</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1585.6</v>
+        <v>1577.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1566</v>
+        <v>1553.5</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-21</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>-1.32</v>
+        <v>-3</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2395</v>
+        <v>2386.9</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2402</v>
+        <v>2397.6</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2367.6</v>
+        <v>2352</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2394</v>
+        <v>2365</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>-0.04</v>
+        <v>-29</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116</v>
+        <v>115.61</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>115.25</v>
+        <v>115.5</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117</v>
+        <v>118.2</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>115.25</v>
+        <v>115.47</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>115.61</v>
+        <v>116.85</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.39</v>
+        <v>1.24</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-0.34</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8373.5</v>
+        <v>8354</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8373.5</v>
+        <v>8330.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8407</v>
+        <v>8387.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8302</v>
+        <v>8272.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8354</v>
+        <v>8358</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-19.5</v>
+        <v>4</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>-0.23</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>265.75</v>
+        <v>265.85</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>265</v>
+        <v>265.85</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>269.25</v>
+        <v>271.75</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>264.5</v>
+        <v>265.3</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>265.85</v>
+        <v>271.75</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>0.04</v>
+        <v>5.9</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1231.3</v>
+        <v>1169.2</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1231.3</v>
+        <v>1175</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1161.5</v>
+        <v>1159.9</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1169.2</v>
+        <v>1221.3</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-62.1</v>
+        <v>52.1</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-5.04</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>418.5</v>
+        <v>416</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>415.3</v>
+        <v>413</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>420.4</v>
+        <v>417.2</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>414.7</v>
+        <v>409.05</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>416</v>
+        <v>410.8</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>-0.6</v>
+        <v>-5.2</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>317.85</v>
+        <v>314.5</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>316.55</v>
+        <v>313.9</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>317.35</v>
+        <v>316.9</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>313.6</v>
+        <v>312.65</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>314.5</v>
+        <v>313.8</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-1.05</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1294.9</v>
+        <v>1279</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1283.5</v>
+        <v>1278.5</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1294.7</v>
+        <v>1285.3</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1277.2</v>
+        <v>1266.3</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-1.23</v>
+        <v>-5</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>186.1</v>
+        <v>186.4</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>185.98</v>
+        <v>186.51</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>189.4</v>
+        <v>187.03</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>185.36</v>
+        <v>183.1</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>186.4</v>
+        <v>183.75</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>0.3</v>
+        <v>-2.65</v>
       </c>
       <c r="J153" s="13" t="n">
-        <v>0.16</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>668</v>
+        <v>668.4</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>665.35</v>
+        <v>663</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>674.45</v>
+        <v>671</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>657.25</v>
+        <v>660.55</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>668.4</v>
+        <v>666.3</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>0.4</v>
+        <v>-2.1</v>
       </c>
       <c r="J154" s="13" t="n">
-        <v>0.06</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1696.6</v>
+        <v>1684</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1703.6</v>
+        <v>1684</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1703.6</v>
+        <v>1706.2</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1676</v>
+        <v>1674.5</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1684</v>
+        <v>1700.6</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-12.6</v>
+        <v>16.6</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1008</v>
+        <v>1000.5</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1012.2</v>
+        <v>1011.9</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>992.4</v>
+        <v>1001</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1000.5</v>
+        <v>1009.7</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>23160</v>
+        <v>22950</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>23160</v>
+        <v>22910</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>23240</v>
+        <v>22990</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22900</v>
+        <v>22700</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22950</v>
+        <v>22785</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-210</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-0.91</v>
+        <v>-165</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="158">
@@ -6106,22 +6106,22 @@
         <v>1029</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1018.2</v>
+        <v>1030</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1034.8</v>
+        <v>1039</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1013</v>
+        <v>1020.9</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3951.3</v>
+        <v>3949.1</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3932</v>
+        <v>3949</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>4003</v>
+        <v>3987.9</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3911.8</v>
+        <v>3905.2</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3949.1</v>
+        <v>3954.4</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>-0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2519.8</v>
+        <v>2517</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2532</v>
+        <v>2551.7</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2509.7</v>
+        <v>2504</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>-0.08</v>
+        <v>-1</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1885.9</v>
+        <v>1864.9</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1892.6</v>
+        <v>1865.9</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1898.6</v>
+        <v>1875.3</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1864.9</v>
+        <v>1840.5</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1864.9</v>
+        <v>1861</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-21</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>-1.11</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>453.5</v>
+        <v>449.3</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>453.95</v>
+        <v>451</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>457.9</v>
+        <v>459.8</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>447.7</v>
+        <v>450.3</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>449.3</v>
+        <v>455.55</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-4.2</v>
+        <v>6.25</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v>-0.93</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>387.55</v>
+        <v>386.8</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>386.8</v>
+        <v>390</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>388.6</v>
+        <v>390</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>382.6</v>
+        <v>383</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>386.8</v>
+        <v>384</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>-0.19</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>607.7</v>
+        <v>603.05</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>604.7</v>
+        <v>603.05</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>607.95</v>
+        <v>617.05</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>600.55</v>
+        <v>603.05</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>603.05</v>
+        <v>610.55</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-4.65</v>
+        <v>7.5</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-0.77</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1752.8</v>
+        <v>1772.8</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1734.9</v>
+        <v>1753.7</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1772.8</v>
+        <v>1764.4</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>20</v>
+        <v>-8.4</v>
       </c>
       <c r="J165" s="13" t="n">
-        <v>1.14</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1014.1</v>
+        <v>1001</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1010.8</v>
+        <v>1004</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1013.7</v>
+        <v>1005.6</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1001</v>
+        <v>992.5</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>-1.29</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>365.55</v>
+        <v>370</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>364.1</v>
+        <v>369.7</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>373.7</v>
+        <v>369.7</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>363.15</v>
+        <v>363.95</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>4.45</v>
+        <v>-3</v>
       </c>
       <c r="J168" s="13" t="n">
-        <v>1.22</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>184.15</v>
+        <v>188.75</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>184.8</v>
+        <v>189</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>190.26</v>
+        <v>189</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>183.41</v>
+        <v>185</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>188.75</v>
+        <v>186.78</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>4.6</v>
+        <v>-1.97</v>
       </c>
       <c r="J169" s="13" t="n">
-        <v>2.5</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2255.5</v>
+        <v>2208</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2237</v>
+        <v>2199</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2237</v>
+        <v>2232</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2193.2</v>
+        <v>2190.6</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2208</v>
+        <v>2204.1</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-47.5</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>-2.11</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1531</v>
+        <v>1511.9</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1531</v>
+        <v>1544.7</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1498</v>
+        <v>1498.1</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1508</v>
+        <v>1525.8</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-51</v>
+        <v>17.8</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>-3.27</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2638.7</v>
+        <v>2678.3</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2649.4</v>
+        <v>2670</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2708.6</v>
+        <v>2674.5</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2596.3</v>
+        <v>2632.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2678.3</v>
+        <v>2652</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>39.6</v>
+        <v>-26.3</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>1.5</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>5010</v>
+        <v>5000.5</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5019</v>
+        <v>5021</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4968</v>
+        <v>4974.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>5005</v>
+        <v>5021</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>0.36</v>
+        <v>16</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4960</v>
+        <v>4930</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4960</v>
+        <v>5000</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4992</v>
+        <v>5000</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4925</v>
+        <v>4921</v>
       </c>
       <c r="H174" s="12" t="n">
         <v>4930</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1270.2</v>
+        <v>1305.7</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1273</v>
+        <v>1305.7</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1322.4</v>
+        <v>1309.3</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1271.6</v>
+        <v>1287.8</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1305.7</v>
+        <v>1296.3</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>35.5</v>
+        <v>-9.4</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>2.79</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2793.6</v>
+        <v>2820</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2793.6</v>
+        <v>2811</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2841.8</v>
+        <v>2835</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2782</v>
+        <v>2800</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2820</v>
+        <v>2818.7</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>26.4</v>
+        <v>-1.3</v>
       </c>
       <c r="J176" s="13" t="n">
-        <v>0.95</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4133.2</v>
+        <v>4151.1</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4102</v>
+        <v>4151.1</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4217.5</v>
+        <v>4184.8</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4071.3</v>
+        <v>4098.7</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4151.1</v>
+        <v>4121.5</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>17.9</v>
+        <v>-29.6</v>
       </c>
       <c r="J177" s="13" t="n">
-        <v>0.43</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1252.5</v>
+        <v>1266.7</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1252</v>
+        <v>1260.4</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1245</v>
+        <v>1253.6</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1266.7</v>
+        <v>1256.7</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>14.2</v>
+        <v>-10</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>1.13</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11009</v>
+        <v>10900</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10975</v>
+        <v>10896</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>10998</v>
+        <v>10979</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10860</v>
+        <v>10858</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>10900</v>
+        <v>10979</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-109</v>
+        <v>79</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>-0.99</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>183.22</v>
+        <v>183.89</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>181.75</v>
+        <v>182.69</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>183.89</v>
+        <v>184.44</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>180.82</v>
+        <v>177.62</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>183.89</v>
+        <v>179.2</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>0.67</v>
+        <v>-4.69</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>0.37</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>576.75</v>
+        <v>575.7</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>573.5</v>
+        <v>578</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>578.35</v>
+        <v>578.6</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>568.55</v>
+        <v>572.5</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>575.7</v>
+        <v>575.3</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>-0.18</v>
+        <v>-0.4</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>272</v>
+        <v>272.5</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>271.5</v>
+        <v>273.75</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>275.75</v>
+        <v>275.1</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>268.55</v>
+        <v>268.8</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>272.5</v>
+        <v>269.05</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>0.5</v>
+        <v>-3.45</v>
       </c>
       <c r="J182" s="13" t="n">
-        <v>0.18</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1144.8</v>
+        <v>1143.8</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1144</v>
+        <v>1142.5</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1147</v>
+        <v>1158.9</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1136</v>
+        <v>1131.4</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1143.8</v>
+        <v>1158.5</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-1</v>
+        <v>14.7</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-0.09</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>171.5</v>
+        <v>167</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>168.7</v>
+        <v>167.9</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>169.15</v>
+        <v>169.19</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>166.37</v>
+        <v>166</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>167</v>
+        <v>166.3</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-2.62</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1145.5</v>
+        <v>1127.4</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1158</v>
+        <v>1136.3</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1126.5</v>
+        <v>1108.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1127.4</v>
+        <v>1117.8</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>-1.58</v>
+        <v>-9.6</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  09-Sep-2026 05:02 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  10-Sep-2026 04:54 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09-Sep-2026 05:02 PM</t>
+          <t>10-Sep-2026 04:54 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 10-Sep-2026 04:54 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 11-Sep-2026 04:55 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>10-Sep-2026 04:54 PM</t>
+          <t>11-Sep-2026 04:55 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  10-Sep-2026 04:54 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  11-Sep-2026 04:55 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>496.2</v>
+        <v>503.05</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>496.2</v>
+        <v>503</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>511.95</v>
+        <v>503</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>495.45</v>
+        <v>490.05</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>504.05</v>
+        <v>492.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>7.85</v>
+        <v>-10.35</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1.58</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7401.5</v>
+        <v>7329</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7400</v>
+        <v>7294</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7418.5</v>
+        <v>7324</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7287</v>
+        <v>7173</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7329</v>
+        <v>7274</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-72.5</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>-0.98</v>
+        <v>-55</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25225</v>
+        <v>25260</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25245</v>
+        <v>25260</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25395</v>
+        <v>25635</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25205</v>
+        <v>25135</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25260</v>
+        <v>25550</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.14</v>
+        <v>290</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         <v>400</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>402.05</v>
+        <v>396.2</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>395.85</v>
+        <v>391</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>51.33</v>
+        <v>50.89</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>51.35</v>
+        <v>50.5</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>51.82</v>
+        <v>50.65</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>50.75</v>
+        <v>49.4</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>50.89</v>
+        <v>50.44</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-0.86</v>
+        <v>-0.45</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1257.7</v>
+        <v>1254.3</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1259.2</v>
+        <v>1251.4</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1260.3</v>
+        <v>1251.7</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1250.1</v>
+        <v>1230.6</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1254.3</v>
+        <v>1246.5</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>-0.27</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3114.5</v>
+        <v>3040</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3114.5</v>
+        <v>3065</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>3041.1</v>
+        <v>2999</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-27.5</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-0.89</v>
+        <v>-17.2</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1779.9</v>
+        <v>1755</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1780</v>
+        <v>1771.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1750.4</v>
+        <v>1750.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1768</v>
+        <v>1764.6</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>-0.39</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5139</v>
+        <v>5138</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5166</v>
+        <v>5122</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5185</v>
+        <v>5128</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5104.5</v>
+        <v>5051</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5138</v>
+        <v>5087.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>-0.02</v>
+        <v>-50.5</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>397</v>
+        <v>395.6</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>395.5</v>
+        <v>393</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>397.55</v>
+        <v>393.55</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>394.05</v>
+        <v>387.65</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>395.6</v>
+        <v>391.85</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>-0.35</v>
+        <v>-3.75</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>299.05</v>
+        <v>297.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>301.35</v>
+        <v>307.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>296.15</v>
+        <v>289.05</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>297.3</v>
+        <v>305</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-1.75</v>
+        <v>7.7</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>-0.59</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2168</v>
+        <v>2194.8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2180</v>
+        <v>2176.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2194.8</v>
+        <v>2176.2</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2158.4</v>
+        <v>2109.8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2194.8</v>
+        <v>2153.5</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>26.8</v>
+        <v>-41.3</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1.24</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8967</v>
+        <v>8900</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>9000</v>
+        <v>8806</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>9024</v>
+        <v>8950</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8875</v>
+        <v>8806</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8900</v>
+        <v>8836</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-67</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.75</v>
+        <v>-64</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>422.25</v>
+        <v>419.55</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>423.6</v>
+        <v>413.95</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>423.65</v>
+        <v>419.45</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>416.4</v>
+        <v>410</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>419.55</v>
+        <v>417.65</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-0.64</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>167</v>
+        <v>166.12</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>166.5</v>
+        <v>163.8</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>167.04</v>
+        <v>165.04</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>164.71</v>
+        <v>160</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>166.12</v>
+        <v>163.75</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>-0.53</v>
+        <v>-2.37</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2489</v>
+        <v>2498.1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2485.1</v>
+        <v>2453.2</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2498.1</v>
+        <v>2472.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2468.6</v>
+        <v>2442.8</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2498.1</v>
+        <v>2472.5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>9.1</v>
+        <v>-25.6</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.37</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1474.8</v>
+        <v>1459</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1468.2</v>
+        <v>1452</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1474.8</v>
+        <v>1456</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1451.7</v>
+        <v>1402.5</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1459</v>
+        <v>1411.4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>-1.07</v>
+        <v>-47.6</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>612.3</v>
+        <v>602.7</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>613.5</v>
+        <v>599.5</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>616</v>
+        <v>601.45</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>600.25</v>
+        <v>592.5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>602.7</v>
+        <v>594.8</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>-1.57</v>
+        <v>-7.9</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6221.5</v>
+        <v>6356</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6221.5</v>
+        <v>6327</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6395</v>
+        <v>6327</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6209.5</v>
+        <v>6156.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6356</v>
+        <v>6244.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>134.5</v>
+        <v>-111.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2.16</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1060.5</v>
+        <v>1054.7</v>
       </c>
       <c r="E22" s="12" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1061.2</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>1033.2</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>1058.9</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>1047.2</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>1054.7</v>
-      </c>
       <c r="I22" s="12" t="n">
-        <v>-5.8</v>
+        <v>4.2</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-0.55</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1698.9</v>
+        <v>1668.4</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1693.4</v>
+        <v>1666.7</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1693.4</v>
+        <v>1681.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1655</v>
+        <v>1655.5</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1668.4</v>
+        <v>1679.8</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-30.5</v>
+        <v>11.4</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>-1.8</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1238.5</v>
+        <v>1246</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1242.1</v>
+        <v>1237.9</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1255.2</v>
+        <v>1252.8</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1240.4</v>
+        <v>1229.8</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>1246</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>0.61</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11771</v>
+        <v>11624</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11820</v>
+        <v>11723</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11673</v>
+        <v>11529</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11768</v>
+        <v>11678</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>-0.19</v>
+        <v>-90</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1927</v>
+        <v>1940.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1932.9</v>
+        <v>1912.1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1942.7</v>
+        <v>1926</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1921.1</v>
+        <v>1895</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1940.5</v>
+        <v>1913.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>13.5</v>
+        <v>-27</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.7</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1039.3</v>
+        <v>1043.5</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1042.5</v>
+        <v>1031</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1048.7</v>
+        <v>1035</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1036.5</v>
+        <v>1015.1</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1043.5</v>
+        <v>1034.5</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>4.2</v>
+        <v>-9</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.4</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2208.6</v>
+        <v>2193</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2210</v>
+        <v>2180.2</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2234.8</v>
+        <v>2190.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2188</v>
+        <v>2156.4</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2193</v>
+        <v>2164.6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-0.71</v>
+        <v>-28.4</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>700.05</v>
+        <v>705.15</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>703</v>
+        <v>697.4</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>693.3</v>
+        <v>687</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>705.15</v>
+        <v>691.4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>5.1</v>
+        <v>-13.75</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.73</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>171.7</v>
+        <v>174</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>171.9</v>
+        <v>171.75</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>174.01</v>
+        <v>178.54</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>169.41</v>
+        <v>170.85</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>174</v>
+        <v>176.52</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>1.34</v>
+        <v>2.52</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>234.1</v>
+        <v>237.62</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>235</v>
+        <v>235.35</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>239.46</v>
+        <v>238.13</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>234.84</v>
+        <v>234.3</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>237.62</v>
+        <v>238.13</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>407</v>
+        <v>402.6</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>407.2</v>
+        <v>405.4</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>402</v>
+        <v>399.25</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>405</v>
+        <v>404.35</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>-0.25</v>
+        <v>-0.65</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>470.8</v>
+        <v>463.8</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>471</v>
+        <v>460.75</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>473.95</v>
+        <v>465.75</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>460.95</v>
+        <v>457</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>463.8</v>
+        <v>458.05</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>-1.49</v>
+        <v>-5.75</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1814.7</v>
+        <v>1839</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1815.1</v>
+        <v>1832</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1814</v>
+        <v>1830.5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1839</v>
+        <v>1831.1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>24.3</v>
+        <v>-7.9</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.34</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>433.7</v>
+        <v>429.5</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>434.2</v>
+        <v>427</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>435.45</v>
+        <v>433</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>427.05</v>
+        <v>418.2</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>429.5</v>
+        <v>431</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>-0.97</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>395</v>
+        <v>391.65</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>397</v>
+        <v>391.55</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>397.95</v>
+        <v>396.85</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>388.45</v>
+        <v>384.65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>391.65</v>
+        <v>390.65</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-3.35</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>-0.85</v>
+        <v>-1</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>49100</v>
+        <v>48775</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48865</v>
+        <v>48480</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>49080</v>
+        <v>48960</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>48480</v>
+        <v>48080</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48775</v>
+        <v>48385</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-325</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>-0.66</v>
+        <v>-390</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>303.55</v>
+        <v>303</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>302.95</v>
+        <v>299.4</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>306.1</v>
+        <v>306.45</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>301.75</v>
+        <v>296</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>303</v>
+        <v>304.5</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-0.55</v>
+        <v>1.5</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>-0.18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5090</v>
+        <v>5009</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5108</v>
+        <v>4996</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5108</v>
+        <v>5012.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4997</v>
+        <v>4945</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5009</v>
+        <v>4962</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-81</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>-1.59</v>
+        <v>-47</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>277.2</v>
+        <v>275.8</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>279</v>
+        <v>280.75</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>282.7</v>
+        <v>284.8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>275</v>
+        <v>274.2</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>275.8</v>
+        <v>281.65</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-1.4</v>
+        <v>5.85</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>-0.51</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124.08</v>
+        <v>124.6</v>
       </c>
       <c r="E41" s="9" t="n">
         <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>127.6</v>
+        <v>124.06</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>123.7</v>
+        <v>122.65</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124.6</v>
+        <v>124</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.42</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>786.9</v>
+        <v>782.2</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>788.9</v>
+        <v>781.3</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>791.75</v>
+        <v>782.4</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>780.3</v>
+        <v>768.05</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>782.2</v>
+        <v>779.75</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>-0.6</v>
+        <v>-2.45</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>415.6</v>
+        <v>417.75</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>415.5</v>
+        <v>415</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>423.15</v>
+        <v>420</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>415.3</v>
+        <v>411.45</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>417.75</v>
+        <v>418.8</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1829</v>
+        <v>1859</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1827.1</v>
+        <v>1834.1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1868.2</v>
+        <v>1850.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1804.2</v>
+        <v>1795.1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1859</v>
+        <v>1845.9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>30</v>
+        <v>-13.1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1.64</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1363.1</v>
+        <v>1373.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1366.8</v>
+        <v>1373</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1363.1</v>
+        <v>1347.7</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1373.3</v>
+        <v>1366</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>10.2</v>
+        <v>-7.3</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.75</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>436.3</v>
+        <v>434.3</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>430</v>
+        <v>424.2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>432</v>
+        <v>426.4</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>1</v>
+        <v>-5.6</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.23</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1845</v>
+        <v>1833.1</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1842</v>
+        <v>1807.3</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1878</v>
+        <v>1858.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1821</v>
+        <v>1807.3</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1833.1</v>
+        <v>1846.5</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-11.9</v>
+        <v>13.4</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>-0.64</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1800</v>
+        <v>1808.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1804.5</v>
+        <v>1799</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1810</v>
+        <v>1799.9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1796.9</v>
+        <v>1782.1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1808.5</v>
+        <v>1797.4</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>8.5</v>
+        <v>-11.1</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.47</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>510</v>
+        <v>504.15</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>509.95</v>
+        <v>503.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>503.7</v>
+        <v>494.15</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>504.15</v>
+        <v>499.25</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-1.15</v>
+        <v>-4.9</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1962.7</v>
+        <v>1961.9</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1948.8</v>
+        <v>1950.8</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1972</v>
+        <v>1950.8</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1947</v>
+        <v>1916.4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1961.9</v>
+        <v>1929</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>-0.04</v>
+        <v>-32.9</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>232.96</v>
+        <v>230</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>234</v>
+        <v>231.69</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>229.74</v>
+        <v>226.63</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-2.96</v>
+        <v>1</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>-1.27</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>231.67</v>
+        <v>226.45</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>232</v>
+        <v>225.9</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>232.99</v>
+        <v>231.85</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>224.95</v>
+        <v>223.69</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>226.45</v>
+        <v>227.32</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-5.22</v>
+        <v>0.87</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>-2.25</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5170.5</v>
+        <v>5155</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5170.5</v>
+        <v>5117</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5237</v>
+        <v>5152</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5069.5</v>
+        <v>5020.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5155</v>
+        <v>5070</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>-0.3</v>
+        <v>-85</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>371.55</v>
+        <v>376.45</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>370.45</v>
+        <v>372.35</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>377.75</v>
+        <v>377</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>369</v>
+        <v>372.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>376.45</v>
+        <v>376</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>4.9</v>
+        <v>-0.45</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>1.32</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1733.6</v>
+        <v>1745.3</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1730</v>
+        <v>1745</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1762.2</v>
+        <v>1755</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1745.3</v>
+        <v>1746.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>0.67</v>
+        <v>1.3</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1641.9</v>
+        <v>1645.8</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1664.8</v>
+        <v>1635.1</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1633.5</v>
+        <v>1583.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1645.8</v>
+        <v>1587.8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>3.9</v>
+        <v>-58</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.24</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>55.25</v>
+        <v>54.34</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>55.01</v>
+        <v>54</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>55.59</v>
+        <v>55.4</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>54.2</v>
+        <v>53.1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>54.34</v>
+        <v>54.15</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>-1.65</v>
+        <v>-0.19</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9488</v>
+        <v>9438.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9600.5</v>
+        <v>9370</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9604</v>
+        <v>9415</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9386.5</v>
+        <v>9310.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9438.5</v>
+        <v>9322</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-49.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>-0.52</v>
+        <v>-116.5</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13845</v>
+        <v>13500</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13845</v>
+        <v>13300</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13867</v>
+        <v>13490</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13355</v>
+        <v>12980</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13500</v>
+        <v>13425</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-345</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>-2.49</v>
+        <v>-75</v>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>655.1</v>
+        <v>655.85</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>653.6</v>
+        <v>650</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>662.4</v>
+        <v>651.4</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>651.9</v>
+        <v>630</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>655.85</v>
+        <v>644.5</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>0.75</v>
+        <v>-11.35</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.11</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1147.2</v>
+        <v>1182</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1134.9</v>
+        <v>1130</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1143</v>
+        <v>1165.5</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-2</v>
+        <v>22.5</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>-0.17</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7734.5</v>
+        <v>7697</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7713</v>
+        <v>7600</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7746</v>
+        <v>7633</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7637.5</v>
+        <v>7530</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7697</v>
+        <v>7530</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-37.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-0.48</v>
+        <v>-167</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2989.2</v>
+        <v>2958.4</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2989.2</v>
+        <v>2930</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3002.2</v>
+        <v>2949.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2951</v>
+        <v>2884.9</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2958.4</v>
+        <v>2899.7</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>-1.03</v>
+        <v>-58.7</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>410.75</v>
+        <v>420.85</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>411</v>
+        <v>418.25</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>424</v>
+        <v>418.45</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>411</v>
+        <v>411.45</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>420.85</v>
+        <v>412.65</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>10.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2.46</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>343.85</v>
+        <v>343</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>347.05</v>
+        <v>345.3</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>343.75</v>
+        <v>341.15</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>346</v>
+        <v>344.5</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.29</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>174.9</v>
+        <v>174.49</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>174</v>
+        <v>173.5</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>176.5</v>
+        <v>175.18</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>173.25</v>
+        <v>173.01</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>174.49</v>
+        <v>173.62</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>-0.23</v>
+        <v>-0.87</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2435</v>
+        <v>2415</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2445.9</v>
+        <v>2411.2</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2449.9</v>
+        <v>2431.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2403.1</v>
+        <v>2384.1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2415</v>
+        <v>2419.2</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-20</v>
+        <v>4.2</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>-0.82</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>574.6</v>
+        <v>570.75</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>572</v>
+        <v>564.5</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>575</v>
+        <v>565.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>564.45</v>
+        <v>559.75</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>570.75</v>
+        <v>562.4</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>-0.67</v>
+        <v>-8.35</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>863.8</v>
+        <v>869.9</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>863.8</v>
+        <v>860</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>872.8</v>
+        <v>872.6</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>859</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>869.9</v>
+        <v>865</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>6.1</v>
+        <v>-4.9</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.71</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1857.1</v>
+        <v>1872</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1850</v>
+        <v>1855</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1874.8</v>
+        <v>1855</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1836</v>
+        <v>1719</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1872</v>
+        <v>1748</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>14.9</v>
+        <v>-124</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.8</v>
+        <v>-6.62</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>884.8</v>
+        <v>899.25</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>870.1</v>
+        <v>895.95</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>905.85</v>
+        <v>914.85</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>870.1</v>
+        <v>881.25</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>899.25</v>
+        <v>909.3</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>1.63</v>
+        <v>10.05</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3300</v>
+        <v>3319</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3290</v>
+        <v>3302.4</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3324.4</v>
+        <v>3302.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3279.9</v>
+        <v>3267</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3319</v>
+        <v>3281.9</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>19</v>
+        <v>-37.1</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.58</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="74">
@@ -3264,7 +3264,7 @@
       <c r="I74" s="12" t="n">
         <v/>
       </c>
-      <c r="J74" s="13" t="n">
+      <c r="J74" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>5000.5</v>
+        <v>4950</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>5015</v>
+        <v>4930</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>5052.4</v>
+        <v>4930</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4914.6</v>
+        <v>4875</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4950</v>
+        <v>4905</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-50.5</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>-1.01</v>
+        <v>-45</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1120.4</v>
+        <v>1116</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1121</v>
+        <v>1107.9</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1126</v>
+        <v>1114.7</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1105.5</v>
+        <v>1096.2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>-0.39</v>
+        <v>-5</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1229.8</v>
+        <v>1207</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1224.8</v>
+        <v>1196</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1237</v>
+        <v>1223.4</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1196.9</v>
+        <v>1195.7</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1207</v>
+        <v>1206.1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-1.85</v>
+        <v>-0.9</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2440</v>
+        <v>2433.8</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2430</v>
+        <v>2405</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2448.1</v>
+        <v>2424.6</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2401</v>
+        <v>2366.1</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2433.8</v>
+        <v>2403.9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>-0.25</v>
+        <v>-29.9</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>687.1</v>
+        <v>693.8</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>687.1</v>
+        <v>683.9</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>694.5</v>
+        <v>709</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>686.2</v>
+        <v>681.9</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>693.8</v>
+        <v>708.25</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>0.98</v>
+        <v>14.45</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>514</v>
+        <v>526.15</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>515.15</v>
+        <v>522</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>526.15</v>
+        <v>531.5</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>508.7</v>
+        <v>518.2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>526.15</v>
+        <v>530</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>2.36</v>
+        <v>3.85</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
+        <v>5280</v>
+      </c>
+      <c r="E81" s="9" t="n">
         <v>5218</v>
       </c>
-      <c r="E81" s="9" t="n">
-        <v>5235</v>
-      </c>
       <c r="F81" s="9" t="n">
-        <v>5280</v>
+        <v>5243</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5169</v>
+        <v>5186</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5280</v>
+        <v>5221.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>62</v>
+        <v>-58.5</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1.19</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1026.9</v>
+        <v>1014</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1027.5</v>
+        <v>990</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1029.5</v>
+        <v>992.8</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1007.8</v>
+        <v>973.1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>-1.26</v>
+        <v>-32.5</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>-3.21</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>532.3</v>
+        <v>527.3</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>539.15</v>
+        <v>510</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>543</v>
+        <v>516.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>525.7</v>
+        <v>505</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>527.3</v>
+        <v>514.5</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-12.8</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>348.9</v>
+        <v>352.65</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>347</v>
+        <v>346.5</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>353.85</v>
+        <v>354.9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>346.95</v>
+        <v>340.1</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>352.65</v>
+        <v>352</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>3.75</v>
+        <v>-0.65</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>1.07</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1945</v>
+        <v>1942.3</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1940</v>
+        <v>1930.5</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1950</v>
+        <v>1946.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1936</v>
+        <v>1926.2</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1942.3</v>
+        <v>1927</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-0.14</v>
+        <v>-15.3</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34180</v>
+        <v>34150</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34370</v>
+        <v>34000</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34400</v>
+        <v>34700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33875</v>
+        <v>33800</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34150</v>
+        <v>34580</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-30</v>
+        <v>430</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>-0.09</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86</v>
+        <v>86.84</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86</v>
+        <v>86.2</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>87.40000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.81999999999999</v>
+        <v>85.41</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.84</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.84</v>
+        <v>-0.63</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.98</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>117.95</v>
+        <v>116.63</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>117.95</v>
+        <v>115.88</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>118.63</v>
+        <v>115.91</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>116.06</v>
+        <v>113</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>116.63</v>
+        <v>113.88</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-1.12</v>
+        <v>-2.75</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>152.92</v>
+        <v>153.46</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>152.35</v>
+        <v>152.23</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>154.45</v>
+        <v>152.5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>152</v>
+        <v>151.02</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>153.46</v>
+        <v>151.98</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.54</v>
+        <v>-1.48</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.35</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>722.75</v>
+        <v>715.75</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>718.4</v>
+        <v>712.75</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>720.6</v>
+        <v>720.75</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>712.55</v>
+        <v>708.6</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>715.75</v>
+        <v>718.5</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-7</v>
+        <v>2.75</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>-0.97</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1671.9</v>
+        <v>1637.7</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1672.3</v>
+        <v>1637.7</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1683.2</v>
+        <v>1716.4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1626</v>
+        <v>1624.1</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1637.7</v>
+        <v>1695</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-34.2</v>
+        <v>57.3</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-2.05</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4975</v>
+        <v>4945</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4964.5</v>
+        <v>4875</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4966</v>
+        <v>4973</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4877</v>
+        <v>4822</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4945</v>
+        <v>4973</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-30</v>
+        <v>28</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>-0.6</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1004</v>
+        <v>993.3</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>1001.9</v>
+        <v>988.7</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>1002.7</v>
+        <v>988.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>986.7</v>
+        <v>972.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>993.3</v>
+        <v>978.2</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-1.07</v>
+        <v>-15.1</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>373.7</v>
+        <v>372</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>376.2</v>
+        <v>372</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>376.2</v>
+        <v>390.85</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>368.7</v>
+        <v>372</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-1.7</v>
+        <v>16</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>-0.45</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1035</v>
+        <v>1036.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1039.6</v>
+        <v>1032</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1046.6</v>
+        <v>1047.3</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1027.3</v>
+        <v>1029.7</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1036.5</v>
+        <v>1037.7</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>0.14</v>
+        <v>1.2</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>135.6</v>
+        <v>134.94</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>134.31</v>
+        <v>134</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>136.15</v>
+        <v>136.16</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>134.31</v>
+        <v>133.25</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>134.94</v>
+        <v>135.11</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.66</v>
+        <v>0.17</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1963.6</v>
+        <v>1970.9</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1954.6</v>
+        <v>1975.8</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1979.9</v>
+        <v>1995</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1953.1</v>
+        <v>1958.4</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1970.9</v>
+        <v>1968.5</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>7.3</v>
+        <v>-2.4</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.37</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>469.5</v>
+        <v>467.75</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>470.85</v>
+        <v>467</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>476.4</v>
+        <v>467.15</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>467</v>
+        <v>462.15</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>467.75</v>
+        <v>462.9</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-0.37</v>
+        <v>-4.85</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>260.8</v>
+        <v>259.3</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>263.9</v>
+        <v>261.65</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>259.1</v>
+        <v>257.7</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>259.3</v>
+        <v>259.85</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-1.5</v>
+        <v>0.55</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>-0.58</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1146.5</v>
+        <v>1137</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1149.7</v>
+        <v>1111</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1151.7</v>
+        <v>1122</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1131</v>
+        <v>1058</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1137</v>
+        <v>1120.5</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>-0.83</v>
+        <v>-16.5</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4990.5</v>
+        <v>4915.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>4991.5</v>
+        <v>4900</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5004.5</v>
+        <v>4909.5</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4887</v>
+        <v>4813</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>4915.5</v>
+        <v>4843.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>-1.5</v>
+        <v>-72</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>783.3</v>
+        <v>762.15</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>785</v>
+        <v>754.55</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>790.5</v>
+        <v>766.5</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>760.1</v>
+        <v>741</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>762.15</v>
+        <v>756.1</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-21.15</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>-2.7</v>
+        <v>-6.05</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>534.8</v>
+        <v>530.45</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>529.9</v>
+        <v>527</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>534.05</v>
+        <v>527</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>527.5</v>
+        <v>522.75</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>530.45</v>
+        <v>526.45</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-4.35</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1301</v>
+        <v>1281</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1311.3</v>
+        <v>1286.9</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1292.7</v>
+        <v>1265</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>-0.46</v>
+        <v>-39</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>475.95</v>
+        <v>473.8</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>474.95</v>
+        <v>470.6</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>480.9</v>
+        <v>472.85</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>467.95</v>
+        <v>465.65</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>473.8</v>
+        <v>470.25</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>-0.45</v>
+        <v>-3.55</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1239.2</v>
+        <v>1243.9</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1239.2</v>
+        <v>1245</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1254.2</v>
+        <v>1245</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1224.5</v>
+        <v>1215.3</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>4.7</v>
+        <v>-17.5</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.38</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>414</v>
+        <v>416.55</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>413.7</v>
+        <v>412.6</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>416.55</v>
+        <v>420</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>412.8</v>
+        <v>409.25</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>416.55</v>
+        <v>419</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>0.62</v>
+        <v>2.45</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>553.1</v>
+        <v>550.95</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>554.5</v>
+        <v>550.9</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>559.5</v>
+        <v>555.95</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>548.75</v>
+        <v>545.6</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>550.95</v>
+        <v>553.75</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-2.15</v>
+        <v>2.8</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>-0.39</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1919.7</v>
+        <v>1916.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1917.2</v>
+        <v>1900</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1927</v>
+        <v>1924.6</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1880.9</v>
+        <v>1893.9</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1916.7</v>
+        <v>1909</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>-0.16</v>
+        <v>-7.7</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1932.6</v>
+        <v>1943</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1950.5</v>
+        <v>1981.8</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1920.9</v>
+        <v>1918.1</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>0.41</v>
+        <v>24</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>555</v>
+        <v>552.3</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>558</v>
+        <v>572.35</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>543.8</v>
+        <v>546</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>552.3</v>
+        <v>562.9</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-2.7</v>
+        <v>10.6</v>
       </c>
       <c r="J111" s="13" t="n">
-        <v>-0.49</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3949.4</v>
+        <v>3926</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3965.5</v>
+        <v>3948</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3910</v>
+        <v>3880.7</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>32.4</v>
+        <v>-24.3</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.83</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>309.05</v>
+        <v>307.15</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>311.4</v>
+        <v>311.55</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>306.3</v>
+        <v>302.7</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>311.3</v>
+        <v>309.1</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.29</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3364</v>
+        <v>3377.9</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3364</v>
+        <v>3370</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3411.2</v>
+        <v>3370.1</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3352.5</v>
+        <v>3322.1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>13.9</v>
+        <v>-40.5</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.41</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2100</v>
+        <v>2077.8</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2090</v>
+        <v>2064</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2098.2</v>
+        <v>2108.5</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2060.3</v>
+        <v>2058</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2077.8</v>
+        <v>2095</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-22.2</v>
+        <v>17.2</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>-1.06</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3150</v>
+        <v>3123.8</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3141.7</v>
+        <v>3110</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3146.9</v>
+        <v>3124.2</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3097.7</v>
+        <v>3069.1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3123.8</v>
+        <v>3107</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-0.83</v>
+        <v>-16.8</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>320</v>
+        <v>330.8</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>319.4</v>
+        <v>324.75</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>335.1</v>
+        <v>329.1</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>318.25</v>
+        <v>323.1</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>330.8</v>
+        <v>329</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>10.8</v>
+        <v>-1.8</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>3.38</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>813.9</v>
+        <v>803</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>813.9</v>
+        <v>797</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>813.9</v>
+        <v>810</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>799.55</v>
+        <v>795.7</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>803</v>
+        <v>802.1</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>-1.34</v>
+        <v>-0.9</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12618</v>
+        <v>12590</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12679</v>
+        <v>12520</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12693</v>
+        <v>12541</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12517</v>
+        <v>12381</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12590</v>
+        <v>12400</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-0.22</v>
+        <v>-190</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3311.9</v>
+        <v>3326</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3335.5</v>
+        <v>3389</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3285</v>
+        <v>3247.2</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3300</v>
+        <v>3276</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-50</v>
-      </c>
-      <c r="J122" s="13" t="n">
-        <v>-1.49</v>
+        <v>-24</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>602.1</v>
+        <v>595.65</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>605.15</v>
+        <v>598.1</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>607.5</v>
+        <v>598.1</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>590.6</v>
+        <v>583</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>595.65</v>
+        <v>585.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>-1.07</v>
+        <v>-10.15</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1468.5</v>
+        <v>1479.9</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1465.8</v>
+        <v>1468</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1483.7</v>
+        <v>1488</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1452</v>
+        <v>1453.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1479.9</v>
+        <v>1477</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>11.4</v>
+        <v>-2.9</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.78</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
+        <v>1100.8</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>1099.9</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>1080.4</v>
+      </c>
+      <c r="H125" s="9" t="n">
         <v>1084.3</v>
       </c>
-      <c r="E125" s="9" t="n">
-        <v>1081.5</v>
-      </c>
-      <c r="F125" s="9" t="n">
-        <v>1107</v>
-      </c>
-      <c r="G125" s="9" t="n">
-        <v>1081.5</v>
-      </c>
-      <c r="H125" s="9" t="n">
-        <v>1100.8</v>
-      </c>
       <c r="I125" s="9" t="n">
-        <v>16.5</v>
+        <v>-16.5</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>1.52</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>163.7</v>
+        <v>163.2</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>163.7</v>
+        <v>161.44</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>164.7</v>
+        <v>165.58</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>162.33</v>
+        <v>160.71</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>163.2</v>
+        <v>164.45</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-0.5</v>
+        <v>1.25</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>-0.31</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2307.5</v>
+        <v>2291.7</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2320</v>
+        <v>2275</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2329</v>
+        <v>2309.2</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2290.2</v>
+        <v>2273.3</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2291.7</v>
+        <v>2295</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-15.8</v>
+        <v>3.3</v>
       </c>
       <c r="J127" s="13" t="n">
-        <v>-0.68</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128315</v>
+        <v>128270</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>128400</v>
+        <v>128105</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>129245</v>
+        <v>128765</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128000</v>
+        <v>127015</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128270</v>
+        <v>128290</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-45</v>
+        <v>20</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2815</v>
+        <v>2841.5</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2815.4</v>
+        <v>2790</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2853.9</v>
+        <v>2820</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2807.4</v>
+        <v>2728.6</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2841.5</v>
+        <v>2792.1</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>26.5</v>
+        <v>-49.4</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>377.6</v>
+        <v>373.35</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>371.05</v>
+        <v>352.35</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>373.35</v>
+        <v>361</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>-1.13</v>
+        <v>-12.35</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1266.9</v>
+        <v>1250</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1277.9</v>
+        <v>1262.1</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1246.9</v>
+        <v>1244.8</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1265</v>
+        <v>1250.8</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>-0.16</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8775.5</v>
+        <v>8700.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8748</v>
+        <v>8671</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8771.5</v>
+        <v>8699.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8622</v>
+        <v>8486.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8700.5</v>
+        <v>8543.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>-0.85</v>
+        <v>-157</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1393</v>
+        <v>1386.2</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1396.8</v>
+        <v>1376.7</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1402.8</v>
+        <v>1401.2</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1377.7</v>
+        <v>1373.5</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1386.2</v>
+        <v>1383.3</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>-0.49</v>
+        <v>-2.9</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>85.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>86</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>86.12</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>84.17</v>
+        <v>82.25</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>84.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>-1.4</v>
+        <v>-2.2</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>334.5</v>
+        <v>335</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>335.65</v>
+        <v>333</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>335.7</v>
+        <v>336.25</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>333.1</v>
+        <v>331.6</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>335</v>
+        <v>333.4</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>0.5</v>
+        <v>-1.6</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.15</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1799.8</v>
+        <v>1775.7</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1806.4</v>
+        <v>1780</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1777.5</v>
+        <v>1714.8</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1792</v>
+        <v>1741.1</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>-0.44</v>
+        <v>-50.9</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11630</v>
+        <v>11725</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11680</v>
+        <v>11599</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11814</v>
+        <v>11830</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11627</v>
+        <v>11595</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11725</v>
+        <v>11763</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>0.82</v>
+        <v>38</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>234.02</v>
+        <v>237.27</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>236.1</v>
+        <v>239.9</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>239.8</v>
+        <v>243.16</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>235.6</v>
+        <v>232.5</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>237.27</v>
+        <v>232.5</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>3.25</v>
+        <v>-4.77</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>1.39</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35395</v>
+        <v>35750</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35300</v>
+        <v>35405</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35900</v>
+        <v>35410</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34960</v>
+        <v>35080</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35750</v>
+        <v>35365</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>355</v>
+        <v>-385</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>1</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5419</v>
+        <v>5509.5</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5404.5</v>
+        <v>5469</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5560</v>
+        <v>5545.5</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5370.5</v>
+        <v>5444.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5509.5</v>
+        <v>5516</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>1.67</v>
+        <v>6.5</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>285.9</v>
+        <v>288.7</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>284</v>
+        <v>285.65</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>290.7</v>
+        <v>287.2</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>283.05</v>
+        <v>283.85</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>288.7</v>
+        <v>287.2</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>2.8</v>
+        <v>-1.5</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>0.98</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>351.4</v>
+        <v>352.8</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>354.75</v>
+        <v>353.45</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>349.3</v>
+        <v>348</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>352.8</v>
+        <v>353.45</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1572</v>
+        <v>1550</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1577.9</v>
+        <v>1567.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1553.5</v>
+        <v>1540.4</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1569</v>
+        <v>1566.9</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J144" s="13" t="n">
-        <v>-0.19</v>
+        <v>-2.1</v>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2394</v>
+        <v>2365</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2386.9</v>
+        <v>2350</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2397.6</v>
+        <v>2365</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2352</v>
+        <v>2191</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2365</v>
+        <v>2259</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>-1.21</v>
+        <v>-106</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>-4.48</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>115.61</v>
+        <v>116.85</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>115.5</v>
+        <v>116</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.2</v>
+        <v>117.79</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>115.47</v>
+        <v>114.52</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116.85</v>
+        <v>116.75</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>1.24</v>
+        <v>-0.1</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>1.07</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8354</v>
+        <v>8358</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8330.5</v>
+        <v>8319</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8387.5</v>
+        <v>8319</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8272.5</v>
+        <v>8118</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8358</v>
+        <v>8241</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>4</v>
+        <v>-117</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.05</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>265.85</v>
+        <v>271.75</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>265.85</v>
+        <v>269.95</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>271.75</v>
+        <v>274.05</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>265.3</v>
+        <v>268.35</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>271.75</v>
+        <v>269.1</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>5.9</v>
+        <v>-2.65</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>2.22</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1169.2</v>
+        <v>1221.3</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1175</v>
+        <v>1228</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1159.9</v>
+        <v>1212.1</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1221.3</v>
+        <v>1237.1</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="J149" s="10" t="n">
-        <v>4.46</v>
+        <v>15.8</v>
+      </c>
+      <c r="J149" s="13" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>416</v>
+        <v>410.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>417.2</v>
+        <v>416.5</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>409.05</v>
+        <v>406</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>410.8</v>
+        <v>412.55</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-5.2</v>
+        <v>1.75</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>-1.25</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>314.5</v>
+        <v>313.8</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>313.9</v>
+        <v>312</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>316.9</v>
+        <v>315.05</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>312.65</v>
+        <v>311.25</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>313.8</v>
+        <v>312.7</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>-0.22</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1278.5</v>
+        <v>1267</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1285.3</v>
+        <v>1267.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1266.3</v>
+        <v>1253</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>-0.39</v>
+        <v>-16.5</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>186.4</v>
+        <v>183.75</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>186.51</v>
+        <v>182.43</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>187.03</v>
+        <v>182.43</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>183.1</v>
+        <v>178.65</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>183.75</v>
+        <v>179</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-2.65</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>-1.42</v>
+        <v>-4.75</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>668.4</v>
+        <v>666.3</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>671</v>
+        <v>665.15</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>660.55</v>
+        <v>650.05</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>666.3</v>
+        <v>655.2</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-0.31</v>
+        <v>-11.1</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1684</v>
+        <v>1700.6</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1706.2</v>
+        <v>1697.7</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1674.5</v>
+        <v>1671</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1700.6</v>
+        <v>1684.7</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>16.6</v>
+        <v>-15.9</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.99</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1000.5</v>
+        <v>1009.7</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1011.9</v>
+        <v>1001.9</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1009.7</v>
+        <v>995.7</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>9.199999999999999</v>
+        <v>-14</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>0.92</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22950</v>
+        <v>22785</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22910</v>
+        <v>22660</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22990</v>
+        <v>22680</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22700</v>
+        <v>22370</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22785</v>
+        <v>22570</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-165</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-0.72</v>
+        <v>-215</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1039</v>
+        <v>1034.5</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1020.9</v>
+        <v>1013.2</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1038</v>
+        <v>1028.6</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>9</v>
+        <v>-9.4</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>0.87</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3949.1</v>
+        <v>3954.4</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3949</v>
+        <v>3912.1</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3987.9</v>
+        <v>3957</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3905.2</v>
+        <v>3858.4</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3954.4</v>
+        <v>3957</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>0.13</v>
+        <v>2.6</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2517</v>
+        <v>2508</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2551.7</v>
+        <v>2508</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2504</v>
+        <v>2460</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2519</v>
+        <v>2482.4</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>-0.04</v>
+        <v>-36.6</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1864.9</v>
+        <v>1861</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1865.9</v>
+        <v>1845</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1875.3</v>
+        <v>1854.5</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1840.5</v>
+        <v>1834</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1861</v>
+        <v>1840</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>-0.21</v>
+        <v>-21</v>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>449.3</v>
+        <v>455.55</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>451</v>
+        <v>450.55</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>459.8</v>
+        <v>485.5</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>450.3</v>
+        <v>450</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>455.55</v>
+        <v>476</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>1.39</v>
+        <v>20.45</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>386.8</v>
+        <v>384</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>390</v>
+        <v>383.25</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>390</v>
+        <v>383.6</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>383</v>
+        <v>375.55</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>384</v>
+        <v>382.65</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v>-0.72</v>
+        <v>-1.35</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>603.05</v>
+        <v>610.55</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>603.05</v>
+        <v>608.25</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>617.05</v>
+        <v>616.25</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>603.05</v>
+        <v>600</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>610.55</v>
+        <v>612.45</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1772.8</v>
+        <v>1764.4</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1760</v>
+        <v>1756.2</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1753.7</v>
+        <v>1747.8</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1764.4</v>
+        <v>1761.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>-0.47</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1005.6</v>
+        <v>1000</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>992.5</v>
+        <v>988</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-0.14</v>
+        <v>-8.6</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>369.7</v>
+        <v>364.8</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>369.7</v>
+        <v>367.4</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>363.95</v>
+        <v>362.95</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>367</v>
+        <v>364.65</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.35</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>188.75</v>
+        <v>186.78</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>189</v>
+        <v>184.24</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>185</v>
+        <v>180.79</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>186.78</v>
+        <v>183</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>-1.04</v>
+        <v>-3.78</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2208</v>
+        <v>2204.1</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2199</v>
+        <v>2185.5</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2232</v>
+        <v>2232.6</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2190.6</v>
+        <v>2185.5</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2204.1</v>
+        <v>2200.8</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-0.18</v>
+        <v>-3.3</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1508</v>
+        <v>1525.8</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1511.9</v>
+        <v>1519.3</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1544.7</v>
+        <v>1557.3</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1498.1</v>
+        <v>1518.6</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1525.8</v>
+        <v>1541</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>1.18</v>
+        <v>15.2</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2678.3</v>
+        <v>2652</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2670</v>
+        <v>2637</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2674.5</v>
+        <v>2637.1</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2632.5</v>
+        <v>2580.1</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2652</v>
+        <v>2606.1</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-26.3</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>-0.98</v>
+        <v>-45.9</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5005</v>
+        <v>5021</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>5000.5</v>
+        <v>4964</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5021</v>
+        <v>5015</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4974.5</v>
+        <v>4943</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>5021</v>
+        <v>5009.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>16</v>
+        <v>-11.5</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>0.32</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="174">
@@ -6650,22 +6650,22 @@
         <v>4930</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>5000</v>
+        <v>4929</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>5000</v>
+        <v>4988</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4921</v>
+        <v>4894</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4930</v>
+        <v>4965.5</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>0</v>
+        <v>35.5</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1305.7</v>
+        <v>1296.3</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1305.7</v>
+        <v>1281.7</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1309.3</v>
+        <v>1300.4</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1287.8</v>
+        <v>1278.3</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1296.3</v>
+        <v>1297.6</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-0.72</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2820</v>
+        <v>2818.7</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2811</v>
+        <v>2789</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2835</v>
+        <v>2816</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2800</v>
+        <v>2757.5</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2818.7</v>
+        <v>2802.4</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>-0.05</v>
+        <v>-16.3</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4151.1</v>
+        <v>4121.5</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4151.1</v>
+        <v>4081</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4184.8</v>
+        <v>4151.9</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4098.7</v>
+        <v>4062.8</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4121.5</v>
+        <v>4125</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-29.6</v>
+        <v>3.5</v>
       </c>
       <c r="J177" s="13" t="n">
-        <v>-0.71</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1266.7</v>
+        <v>1256.7</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1260.4</v>
+        <v>1254.5</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1274</v>
+        <v>1263.5</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1253.6</v>
+        <v>1240.2</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1256.7</v>
+        <v>1256.1</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>-0.79</v>
+        <v>-0.6</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>10900</v>
+        <v>10979</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10896</v>
+        <v>10859</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>10979</v>
+        <v>11060</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10858</v>
+        <v>10790</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>10979</v>
+        <v>11000</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>0.72</v>
+        <v>21</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>183.89</v>
+        <v>179.2</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>182.69</v>
+        <v>177.1</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>184.44</v>
+        <v>179.65</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>177.62</v>
+        <v>175.53</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>179.2</v>
+        <v>178.1</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-4.69</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>-2.55</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>575.7</v>
+        <v>575.3</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>578</v>
+        <v>571.8</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>578.6</v>
+        <v>577.65</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>572.5</v>
+        <v>567.55</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>575.3</v>
+        <v>572.95</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.35</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>272.5</v>
+        <v>269.05</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>273.75</v>
+        <v>264</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>275.1</v>
+        <v>264.85</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>268.8</v>
+        <v>256.5</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>269.05</v>
+        <v>263.7</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>-1.27</v>
+        <v>-5.35</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1143.8</v>
+        <v>1158.5</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1142.5</v>
+        <v>1149</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1158.9</v>
+        <v>1169</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1131.4</v>
+        <v>1138</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1158.5</v>
+        <v>1165</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>1.29</v>
+        <v>6.5</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>167</v>
+        <v>166.3</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>167.9</v>
+        <v>165.2</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>169.19</v>
+        <v>167.75</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>166</v>
+        <v>165.16</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>166.3</v>
+        <v>167.4</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-0.42</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1127.4</v>
+        <v>1117.8</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1130</v>
+        <v>1114</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1136.3</v>
+        <v>1135.5</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1108.1</v>
+        <v>1104.6</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1117.8</v>
+        <v>1119.1</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-9.6</v>
+        <v>1.3</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>-0.85</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  10-Sep-2026 04:54 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  11-Sep-2026 04:55 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-Sep-2026 04:54 PM</t>
+          <t>11-Sep-2026 04:55 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 11-Sep-2026 04:55 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 14-Sep-2026 06:21 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>11-Sep-2026 04:55 PM</t>
+          <t>14-Sep-2026 06:21 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  11-Sep-2026 04:55 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  14-Sep-2026 06:21 PM</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  11-Sep-2026 04:55 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  14-Sep-2026 06:21 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-Sep-2026 04:55 PM</t>
+          <t>14-Sep-2026 06:21 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 14-Sep-2026 06:21 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 15-Sep-2026 05:29 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>14-Sep-2026 06:21 PM</t>
+          <t>15-Sep-2026 05:29 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  14-Sep-2026 06:21 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  15-Sep-2026 05:29 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>503.05</v>
+        <v>492.7</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>503</v>
+        <v>492.7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>503</v>
+        <v>494.5</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>490.05</v>
+        <v>466.1</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>492.7</v>
+        <v>468.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-10.35</v>
+        <v>-24</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-2.06</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7329</v>
+        <v>7274</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7294</v>
+        <v>7268</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7324</v>
+        <v>7268</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7173</v>
+        <v>7005</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7274</v>
+        <v>7005</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-55</v>
+        <v>-269</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>-0.75</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25260</v>
+        <v>25550</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25260</v>
+        <v>25690</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25635</v>
+        <v>26245</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25135</v>
+        <v>25550</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25550</v>
+        <v>26125</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>290</v>
+        <v>575</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>1.15</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>395</v>
+        <v>395.15</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>396.2</v>
+        <v>396.8</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>391</v>
+        <v>378.8</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>395</v>
+        <v>378.8</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-5</v>
+        <v>-16.2</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-1.25</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.89</v>
+        <v>50.44</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.5</v>
+        <v>50.35</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.65</v>
+        <v>50.68</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>49.4</v>
+        <v>48.71</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>50.44</v>
+        <v>49.02</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.45</v>
+        <v>-1.42</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-0.88</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1254.3</v>
+        <v>1246.5</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1251.4</v>
+        <v>1234.9</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1251.7</v>
+        <v>1280.3</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1230.6</v>
+        <v>1219.6</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1246.5</v>
+        <v>1225.2</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-7.8</v>
+        <v>-21.3</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>-0.62</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3040</v>
+        <v>3080</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3065</v>
+        <v>3083.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2999</v>
+        <v>2921.3</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-17.2</v>
+        <v>-131.4</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1768</v>
+        <v>1764.6</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1755</v>
+        <v>1791.4</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1771.9</v>
+        <v>1791.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1750.8</v>
+        <v>1713.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-3.4</v>
+        <v>-50.8</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-0.19</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5138</v>
+        <v>5087.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5122</v>
+        <v>5170</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5128</v>
+        <v>5290</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5051</v>
+        <v>5140.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5087.5</v>
+        <v>5161</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-50.5</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-0.98</v>
+        <v>73.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>395.6</v>
+        <v>391.85</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>393</v>
+        <v>392.6</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>393.55</v>
+        <v>393.85</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>387.65</v>
+        <v>380.1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>391.85</v>
+        <v>381.75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-3.75</v>
+        <v>-10.1</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-0.95</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
+        <v>305</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>306.45</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>310</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>297.3</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>295</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>307.4</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>289.05</v>
-      </c>
       <c r="H13" s="9" t="n">
-        <v>305</v>
+        <v>297.5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>2.59</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2194.8</v>
+        <v>2153.5</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2176.2</v>
+        <v>2157</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2176.2</v>
+        <v>2160</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2109.8</v>
+        <v>2107.7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2153.5</v>
+        <v>2119.3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-41.3</v>
+        <v>-34.2</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-1.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8900</v>
+        <v>8836</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8806</v>
+        <v>8937</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8950</v>
+        <v>8950.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8806</v>
+        <v>8714</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8836</v>
+        <v>8714</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-64</v>
+        <v>-122</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>-0.72</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>419.55</v>
+        <v>417.65</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>413.95</v>
+        <v>415</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>419.45</v>
+        <v>417.75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>410</v>
+        <v>405.05</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>417.65</v>
+        <v>406.2</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-1.9</v>
+        <v>-11.45</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-0.45</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>166.12</v>
+        <v>163.75</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>163.8</v>
+        <v>164.5</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>165.04</v>
+        <v>165.36</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>160</v>
+        <v>156.65</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-2.37</v>
+        <v>-7.1</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>-1.43</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2498.1</v>
+        <v>2472.5</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2453.2</v>
+        <v>2472.5</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2472.5</v>
+        <v>2473</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2442.8</v>
+        <v>2402.8</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2472.5</v>
+        <v>2402.8</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-25.6</v>
+        <v>-69.7</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-1.02</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1459</v>
+        <v>1411.4</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1452</v>
+        <v>1410</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1456</v>
+        <v>1414.1</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1402.5</v>
+        <v>1372.8</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1411.4</v>
+        <v>1379.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-47.6</v>
+        <v>-31.8</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>-3.26</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>602.7</v>
+        <v>594.8</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>599.5</v>
+        <v>595</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>601.45</v>
+        <v>602.9</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>592.5</v>
+        <v>576.4</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>594.8</v>
+        <v>580.15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-7.9</v>
+        <v>-14.65</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-1.31</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6356</v>
+        <v>6244.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6327</v>
+        <v>6250</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6327</v>
+        <v>6250</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6156.5</v>
+        <v>6060.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6244.5</v>
+        <v>6081.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-111.5</v>
+        <v>-163</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-1.75</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1054.7</v>
+        <v>1058.9</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1052</v>
+        <v>1061.4</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1061.2</v>
+        <v>1065.7</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1033.2</v>
+        <v>1024.6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1058.9</v>
+        <v>1028</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>0.4</v>
+        <v>-30.9</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1668.4</v>
+        <v>1679.8</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1666.7</v>
+        <v>1688</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1681.4</v>
+        <v>1688</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1655.5</v>
+        <v>1642.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1679.8</v>
+        <v>1660</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>0.68</v>
+        <v>-19.8</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="24">
@@ -1550,22 +1550,22 @@
         <v>1246</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1237.9</v>
+        <v>1254</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1252.8</v>
+        <v>1254</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1229.8</v>
+        <v>1219.9</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1246</v>
+        <v>1222.9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>0</v>
+        <v>-23.1</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11768</v>
+        <v>11678</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11624</v>
+        <v>11693</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11723</v>
+        <v>11709</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11529</v>
+        <v>11416</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-90</v>
+        <v>-254</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-0.76</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1940.5</v>
+        <v>1913.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1912.1</v>
+        <v>1921.4</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1926</v>
+        <v>1930.6</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1895</v>
+        <v>1855.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1913.5</v>
+        <v>1855.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-27</v>
+        <v>-58</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-1.39</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1043.5</v>
+        <v>1034.5</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1035</v>
+        <v>1038.6</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1015.1</v>
+        <v>1005.5</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-9</v>
+        <v>-25.3</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-0.86</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2193</v>
+        <v>2164.6</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2180.2</v>
+        <v>2164.6</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2190.1</v>
+        <v>2176.3</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2156.4</v>
+        <v>2117.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2164.6</v>
+        <v>2129</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-28.4</v>
+        <v>-35.6</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>705.15</v>
+        <v>691.4</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>697.4</v>
+        <v>697.3</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>687</v>
+        <v>667.55</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>691.4</v>
+        <v>677.1</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-13.75</v>
+        <v>-14.3</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-1.95</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>174</v>
+        <v>176.52</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>171.75</v>
+        <v>177</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>178.54</v>
+        <v>179.11</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>170.85</v>
+        <v>172.24</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>176.52</v>
+        <v>172.45</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>1.45</v>
+        <v>-4.07</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>237.62</v>
+        <v>238.13</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>235.35</v>
+        <v>238.13</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>238.13</v>
+        <v>238.51</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>234.3</v>
+        <v>232.44</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>238.13</v>
+        <v>232.7</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>0.21</v>
+        <v>-5.43</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>405</v>
+        <v>404.35</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>402.6</v>
+        <v>402</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>405.4</v>
+        <v>403.65</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>399.25</v>
+        <v>382.9</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>404.35</v>
+        <v>382.9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-0.65</v>
+        <v>-21.45</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-0.16</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>463.8</v>
+        <v>458.05</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>460.75</v>
+        <v>458.05</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>465.75</v>
+        <v>460.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>457</v>
+        <v>445.55</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>458.05</v>
+        <v>447.1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-5.75</v>
+        <v>-10.95</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>-1.24</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1839</v>
+        <v>1831.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1832</v>
+        <v>1844</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1852</v>
+        <v>1844</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1830.5</v>
+        <v>1819.6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1831.1</v>
+        <v>1830.4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-7.9</v>
+        <v>-0.7</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-0.43</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>429.5</v>
+        <v>431</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>427</v>
+        <v>431.25</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>418.2</v>
+        <v>412.85</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>431</v>
+        <v>412.85</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>0.35</v>
+        <v>-18.15</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>-4.21</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>391.65</v>
+        <v>390.65</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>391.55</v>
+        <v>391.95</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>396.85</v>
+        <v>392.05</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>384.65</v>
+        <v>381</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>390.65</v>
+        <v>382</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-1</v>
+        <v>-8.65</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>-0.26</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48775</v>
+        <v>48385</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48480</v>
+        <v>48725</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48960</v>
+        <v>48725</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>48080</v>
+        <v>47070</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48385</v>
+        <v>47070</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-390</v>
+        <v>-1315</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>-0.8</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>303</v>
+        <v>304.5</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>299.4</v>
+        <v>304.2</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>306.45</v>
+        <v>308.15</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>296</v>
+        <v>298.65</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>304.5</v>
+        <v>298.65</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>0.5</v>
+        <v>-5.85</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5009</v>
+        <v>4962</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4996</v>
+        <v>4990</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5012.5</v>
+        <v>5022.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4945</v>
+        <v>4947.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4962</v>
+        <v>4947.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-47</v>
+        <v>-14.5</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>275.8</v>
+        <v>281.65</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>280.75</v>
+        <v>291</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>284.8</v>
+        <v>302.85</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>274.2</v>
+        <v>285.1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>281.65</v>
+        <v>286.45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>5.85</v>
+        <v>4.8</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124.6</v>
+        <v>124</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>124</v>
+        <v>123.25</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>124.06</v>
+        <v>124.48</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>122.65</v>
+        <v>122.05</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124</v>
+        <v>122.37</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.6</v>
+        <v>-1.63</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.48</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>782.2</v>
+        <v>779.75</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>781.3</v>
+        <v>776.2</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>782.4</v>
+        <v>788.75</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>768.05</v>
+        <v>766.85</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>779.75</v>
+        <v>784.8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>-0.31</v>
+        <v>5.05</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>417.75</v>
+        <v>418.8</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>411.45</v>
+        <v>415.45</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>418.8</v>
+        <v>416.65</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>0.25</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1859</v>
+        <v>1845.9</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1834.1</v>
+        <v>1834.8</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1850.2</v>
+        <v>1842</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1795.1</v>
+        <v>1784.2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1845.9</v>
+        <v>1791.6</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-13.1</v>
+        <v>-54.3</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-0.7</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1373.3</v>
+        <v>1366</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1373</v>
+        <v>1355</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1373</v>
+        <v>1362.7</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>1347.7</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1366</v>
+        <v>1351</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-7.3</v>
+        <v>-15</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-0.53</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>432</v>
+        <v>426.4</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>432</v>
+        <v>426.4</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>434.3</v>
+        <v>427</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>424.2</v>
+        <v>418</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>426.4</v>
+        <v>419.25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-5.6</v>
+        <v>-7.15</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1833.1</v>
+        <v>1846.5</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1807.3</v>
+        <v>1887.3</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1858.6</v>
+        <v>1893.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1807.3</v>
+        <v>1765.6</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1846.5</v>
+        <v>1775.5</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>0.73</v>
+        <v>-71</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1808.5</v>
+        <v>1797.4</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1799</v>
+        <v>1797.4</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1799.9</v>
+        <v>1846.6</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1782.1</v>
+        <v>1788.8</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1797.4</v>
+        <v>1820.3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>-0.61</v>
+        <v>22.9</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>504.15</v>
+        <v>499.25</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>500</v>
+        <v>499.95</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>503.5</v>
+        <v>501.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>494.15</v>
+        <v>483.7</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>499.25</v>
+        <v>483.7</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-4.9</v>
+        <v>-15.55</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-0.97</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1961.9</v>
+        <v>1929</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1950.8</v>
+        <v>1928</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1950.8</v>
+        <v>1950</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1916.4</v>
+        <v>1918.9</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1929</v>
+        <v>1939.1</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-32.9</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>-1.68</v>
+        <v>10.1</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>231.69</v>
+        <v>231.6</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>226.63</v>
+        <v>226.11</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>231</v>
+        <v>226.15</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>0.43</v>
+        <v>-4.85</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>226.45</v>
+        <v>227.32</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>225.9</v>
+        <v>227.32</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>231.85</v>
+        <v>231</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>223.69</v>
+        <v>223.25</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>227.32</v>
+        <v>225.78</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>0.38</v>
+        <v>-1.54</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5155</v>
+        <v>5070</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5117</v>
+        <v>5070</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5152</v>
+        <v>5121.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5020.5</v>
+        <v>4874</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5070</v>
+        <v>4874</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-85</v>
+        <v>-196</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-1.65</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>376.45</v>
+        <v>376</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>372.35</v>
+        <v>379</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>377</v>
+        <v>390.95</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>372.1</v>
+        <v>376.75</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>376</v>
+        <v>384.9</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>-0.12</v>
+        <v>8.9</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1745.3</v>
+        <v>1746.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1745</v>
+        <v>1746.6</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1708</v>
+        <v>1682</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1746.6</v>
+        <v>1687.4</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-59.2</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1645.8</v>
+        <v>1587.8</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1634</v>
+        <v>1588.9</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1635.1</v>
+        <v>1597.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1583.2</v>
+        <v>1556.1</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1587.8</v>
+        <v>1561.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-58</v>
+        <v>-26.5</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-3.52</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>54.34</v>
+        <v>54.15</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>54</v>
+        <v>54.14</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>55.4</v>
+        <v>54.53</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>53.1</v>
+        <v>52.82</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>54.15</v>
+        <v>53.79</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>-0.35</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9438.5</v>
+        <v>9322</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9370</v>
+        <v>9367.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9415</v>
+        <v>9397.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9310.5</v>
+        <v>9118.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9322</v>
+        <v>9198</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-116.5</v>
+        <v>-124</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>-1.23</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13500</v>
+        <v>13425</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13300</v>
+        <v>13490</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13490</v>
+        <v>13575</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>12980</v>
+        <v>13093</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13425</v>
+        <v>13180</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-75</v>
+        <v>-245</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>655.85</v>
+        <v>644.5</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>650</v>
+        <v>644.5</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>651.4</v>
+        <v>647.15</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>630</v>
+        <v>620.85</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>644.5</v>
+        <v>620.85</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-11.35</v>
+        <v>-23.65</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-1.73</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1143</v>
+        <v>1165.5</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1130</v>
+        <v>1163.7</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1182</v>
+        <v>1168.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1165.5</v>
+        <v>1145</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>1.97</v>
+        <v>-20.5</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7697</v>
+        <v>7530</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7600</v>
+        <v>7567.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7633</v>
+        <v>7570.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7530</v>
+        <v>7440</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7530</v>
+        <v>7452.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-167</v>
+        <v>-77.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>-2.17</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2958.4</v>
+        <v>2899.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2930</v>
+        <v>2895</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2949.6</v>
+        <v>2899.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2884.9</v>
+        <v>2822.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2899.7</v>
+        <v>2835.8</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-58.7</v>
+        <v>-63.9</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>-1.98</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>420.85</v>
+        <v>412.65</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>418.25</v>
+        <v>412.65</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>418.45</v>
+        <v>417.95</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>411.45</v>
+        <v>405.1</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>412.65</v>
+        <v>409.2</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.45</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-1.95</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>346</v>
+        <v>344.5</v>
       </c>
       <c r="E65" s="9" t="n">
+        <v>344.45</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>339.45</v>
+      </c>
+      <c r="H65" s="9" t="n">
         <v>343</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>345.3</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>341.15</v>
-      </c>
-      <c r="H65" s="9" t="n">
-        <v>344.5</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>-1.5</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>174.49</v>
+        <v>173.62</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.5</v>
+        <v>173.62</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>175.18</v>
+        <v>173.82</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>173.01</v>
+        <v>169.73</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>173.62</v>
+        <v>170.88</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.87</v>
+        <v>-2.74</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-0.5</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2415</v>
+        <v>2419.2</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2411.2</v>
+        <v>2420.8</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2431.9</v>
+        <v>2429.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2384.1</v>
+        <v>2346.6</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2419.2</v>
+        <v>2371.7</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>0.17</v>
+        <v>-47.5</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>570.75</v>
+        <v>562.4</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>564.5</v>
+        <v>564.2</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>565.5</v>
+        <v>564.3</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>559.75</v>
+        <v>540</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>562.4</v>
+        <v>540.6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-8.35</v>
+        <v>-21.8</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>-1.46</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>869.9</v>
+        <v>865</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>872.6</v>
+        <v>877</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>859</v>
+        <v>856.6</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-4.9</v>
+        <v>-8</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1872</v>
+        <v>1748</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1855</v>
+        <v>1754</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1855</v>
+        <v>1759.7</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1719</v>
+        <v>1657.4</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-124</v>
+        <v>-88.7</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-6.62</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>899.25</v>
+        <v>909.3</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>895.95</v>
+        <v>917</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>914.85</v>
+        <v>923.65</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>881.25</v>
+        <v>872.5</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>909.3</v>
+        <v>872.6</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>1.12</v>
+        <v>-36.7</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3319</v>
+        <v>3281.9</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3302.4</v>
+        <v>3263.3</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3302.4</v>
+        <v>3272</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3267</v>
+        <v>3171</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3281.9</v>
+        <v>3171</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-37.1</v>
+        <v>-110.9</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-1.12</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4950</v>
+        <v>4905</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4930</v>
+        <v>4920</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4930</v>
+        <v>4940</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4875</v>
+        <v>4674</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4905</v>
+        <v>4695</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-45</v>
+        <v>-210</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>-0.91</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1107.9</v>
+        <v>1117</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1114.7</v>
+        <v>1117</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1096.2</v>
+        <v>1081.1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1111</v>
+        <v>1087</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-0.45</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1207</v>
+        <v>1206.1</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1196</v>
+        <v>1252</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1223.4</v>
+        <v>1290</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1195.7</v>
+        <v>1250</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1206.1</v>
+        <v>1253.7</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>47.6</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>3.95</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2433.8</v>
+        <v>2403.9</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2405</v>
+        <v>2416.9</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2424.6</v>
+        <v>2423.9</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2366.1</v>
+        <v>2385</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2403.9</v>
+        <v>2409</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-29.9</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>-1.23</v>
+        <v>5.1</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>693.8</v>
+        <v>708.25</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>683.9</v>
+        <v>722.4</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>709</v>
+        <v>730.75</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>681.9</v>
+        <v>715.05</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>14.45</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>526.15</v>
+        <v>530</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>531.5</v>
+        <v>530.65</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>518.2</v>
+        <v>516.1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>0.73</v>
+        <v>-13.9</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5280</v>
+        <v>5221.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5218</v>
+        <v>5287.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5243</v>
+        <v>5327.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5186</v>
+        <v>5166</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5221.5</v>
+        <v>5166</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-58.5</v>
+        <v>-55.5</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>-1.11</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>990</v>
+        <v>980.1</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>992.8</v>
+        <v>981</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>973.1</v>
+        <v>958.7</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>981.5</v>
+        <v>958.7</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-32.5</v>
+        <v>-22.8</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>-3.21</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>527.3</v>
+        <v>514.5</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>510</v>
+        <v>513.95</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>516.5</v>
+        <v>513.95</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>505</v>
+        <v>490.55</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>514.5</v>
+        <v>492.1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-12.8</v>
+        <v>-22.4</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>-2.43</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
+        <v>352</v>
+      </c>
+      <c r="E84" s="12" t="n">
         <v>352.65</v>
       </c>
-      <c r="E84" s="12" t="n">
-        <v>346.5</v>
-      </c>
       <c r="F84" s="12" t="n">
-        <v>354.9</v>
+        <v>355.2</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>340.1</v>
+        <v>344.2</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>352</v>
+        <v>345.3</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-0.65</v>
+        <v>-6.7</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>-0.18</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1942.3</v>
+        <v>1927</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1930.5</v>
+        <v>1944</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1946.6</v>
+        <v>1969.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1926.2</v>
+        <v>1933.8</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1927</v>
+        <v>1938.1</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-15.3</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-0.79</v>
+        <v>11.1</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34150</v>
+        <v>34580</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34000</v>
+        <v>34590</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34700</v>
+        <v>34870</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33800</v>
+        <v>33500</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34580</v>
+        <v>33595</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>430</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>1.26</v>
+        <v>-985</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.84</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86.2</v>
+        <v>86.56</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.73</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.41</v>
+        <v>84.8</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.20999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.63</v>
+        <v>-1.41</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-0.73</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>116.63</v>
+        <v>113.88</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>115.88</v>
+        <v>113.88</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>115.91</v>
+        <v>114.24</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>113</v>
+        <v>111.82</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>113.88</v>
+        <v>112</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-2.75</v>
+        <v>-1.88</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>-2.36</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>153.46</v>
+        <v>151.98</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>152.23</v>
+        <v>151.98</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>152.5</v>
+        <v>152.42</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>151.02</v>
+        <v>149</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>151.98</v>
+        <v>150.03</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.48</v>
+        <v>-1.95</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-0.96</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>715.75</v>
+        <v>718.5</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>712.75</v>
+        <v>724</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>720.75</v>
+        <v>737.75</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>708.6</v>
+        <v>710.85</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>718.5</v>
+        <v>715</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>0.38</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1637.7</v>
+        <v>1695</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1637.7</v>
+        <v>1713.8</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1716.4</v>
+        <v>1713.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1624.1</v>
+        <v>1652</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1695</v>
+        <v>1659.5</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>3.5</v>
+        <v>-35.5</v>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4945</v>
+        <v>4973</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4875</v>
+        <v>4955.5</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4973</v>
+        <v>4963.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4822</v>
+        <v>4773</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4973</v>
+        <v>4776</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>0.57</v>
+        <v>-197</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>993.3</v>
+        <v>978.2</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>988.7</v>
+        <v>978.2</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>988.7</v>
+        <v>984.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>972.3</v>
+        <v>955</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-15.1</v>
+        <v>-21.7</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>-1.52</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>372</v>
+        <v>390.8</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>390.85</v>
+        <v>390.8</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>372</v>
+        <v>378.7</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>4.3</v>
+        <v>-9</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1036.5</v>
+        <v>1037.7</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1032</v>
+        <v>1085</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1047.3</v>
+        <v>1097.7</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1029.7</v>
+        <v>1071.7</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1037.7</v>
+        <v>1077</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1.2</v>
+        <v>39.3</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>0.12</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>134.94</v>
+        <v>135.11</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>134</v>
+        <v>135.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>136.16</v>
+        <v>135.69</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>133.25</v>
+        <v>132.03</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>135.11</v>
+        <v>132.03</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>0.13</v>
+        <v>-3.08</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1970.9</v>
+        <v>1968.5</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1975.8</v>
+        <v>1976.7</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1995</v>
+        <v>1995.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1958.4</v>
+        <v>1924</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1968.5</v>
+        <v>1932.4</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-2.4</v>
+        <v>-36.1</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-0.12</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>467.75</v>
+        <v>462.9</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>467.15</v>
+        <v>466.55</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>462.15</v>
+        <v>457</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>462.9</v>
+        <v>458.55</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-4.85</v>
+        <v>-4.35</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-1.04</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>259.3</v>
+        <v>259.85</v>
       </c>
       <c r="E99" s="9" t="n">
+        <v>261</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>264.2</v>
+      </c>
+      <c r="G99" s="9" t="n">
         <v>258</v>
       </c>
-      <c r="F99" s="9" t="n">
-        <v>261.65</v>
-      </c>
-      <c r="G99" s="9" t="n">
-        <v>257.7</v>
-      </c>
       <c r="H99" s="9" t="n">
-        <v>259.85</v>
+        <v>258</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>0.21</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1137</v>
+        <v>1120.5</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1111</v>
+        <v>1119.7</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1122</v>
+        <v>1119.7</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1058</v>
+        <v>1090.5</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1120.5</v>
+        <v>1095</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-16.5</v>
+        <v>-25.5</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-1.45</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4915.5</v>
+        <v>4843.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>4900</v>
+        <v>4843.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>4909.5</v>
+        <v>4849.5</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4813</v>
+        <v>4701</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>4843.5</v>
+        <v>4712</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-72</v>
+        <v>-131.5</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-1.46</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>762.15</v>
+        <v>756.1</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>754.55</v>
+        <v>755</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>766.5</v>
+        <v>760</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>741</v>
+        <v>721.25</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>756.1</v>
+        <v>723.55</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-6.05</v>
+        <v>-32.55</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>-0.79</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>530.45</v>
+        <v>526.45</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>527</v>
+        <v>526.45</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>527</v>
+        <v>526.45</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>522.75</v>
+        <v>505</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>526.45</v>
+        <v>505</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-4</v>
+        <v>-21.45</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>-0.75</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1286.9</v>
+        <v>1267.7</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-39</v>
+        <v>-35.8</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>-2.99</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>473.8</v>
+        <v>470.25</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>470.6</v>
+        <v>468.95</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>472.85</v>
+        <v>472.95</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>465.65</v>
+        <v>461.6</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>470.25</v>
+        <v>466</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-3.55</v>
+        <v>-4.25</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-0.75</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1245</v>
+        <v>1226.4</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1245</v>
+        <v>1226.7</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1215.3</v>
+        <v>1211</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1226.4</v>
+        <v>1213.6</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-17.5</v>
+        <v>-12.8</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-1.41</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>416.55</v>
+        <v>419</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>412.6</v>
+        <v>420.5</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>420</v>
+        <v>420.5</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>409.25</v>
+        <v>409.8</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>419</v>
+        <v>409.8</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>0.59</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>550.95</v>
+        <v>553.75</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>550.9</v>
+        <v>560</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>555.95</v>
+        <v>580.95</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>545.6</v>
+        <v>560</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>553.75</v>
+        <v>563</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>2.8</v>
+        <v>9.25</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>0.51</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1916.7</v>
+        <v>1909</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1900</v>
+        <v>1907</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1924.6</v>
+        <v>1921</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1893.9</v>
+        <v>1885.5</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1909</v>
+        <v>1906.4</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-7.7</v>
+        <v>-2.6</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1943</v>
+        <v>1975</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1981.8</v>
+        <v>1981</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1918.1</v>
+        <v>1915.6</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1969</v>
+        <v>1926.9</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>1.23</v>
+        <v>-42.1</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>552.3</v>
+        <v>562.9</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>546</v>
+        <v>563.9</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>572.35</v>
+        <v>565.25</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>546</v>
+        <v>538.5</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>562.9</v>
+        <v>542</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>1.92</v>
+        <v>-20.9</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3926</v>
+        <v>3959</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3948</v>
+        <v>3959</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3880.7</v>
+        <v>3835.7</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-24.3</v>
+        <v>-80</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>-0.61</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="F113" s="9" t="n">
         <v>311.3</v>
       </c>
-      <c r="E113" s="9" t="n">
-        <v>307.15</v>
-      </c>
-      <c r="F113" s="9" t="n">
-        <v>311.55</v>
-      </c>
       <c r="G113" s="9" t="n">
-        <v>302.7</v>
+        <v>296.6</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>309.1</v>
+        <v>296.8</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.2</v>
+        <v>-12.3</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>-0.71</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3370</v>
+        <v>3402</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3370.1</v>
+        <v>3441</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3322.1</v>
+        <v>3300.5</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3337.4</v>
+        <v>3312.2</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-40.5</v>
+        <v>-25.2</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-1.2</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2077.8</v>
+        <v>2095</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2064</v>
+        <v>2095</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2108.5</v>
+        <v>2099.5</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2058</v>
+        <v>2049.5</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2095</v>
+        <v>2063.2</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>0.83</v>
+        <v>-31.8</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3123.8</v>
+        <v>3107</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3110</v>
+        <v>3114.6</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3124.2</v>
+        <v>3119.6</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3069.1</v>
+        <v>3029.5</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3107</v>
+        <v>3029.5</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-16.8</v>
+        <v>-77.5</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>-0.54</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>330.8</v>
+        <v>329</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>324.75</v>
+        <v>327.1</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>329.1</v>
+        <v>330.45</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>323.1</v>
+        <v>317.7</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>329</v>
+        <v>318.85</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-1.8</v>
+        <v>-10.15</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-0.54</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>803</v>
+        <v>802.1</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>797</v>
+        <v>809.65</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>810</v>
+        <v>809.8</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>795.7</v>
+        <v>791.25</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>802.1</v>
+        <v>791.25</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-0.9</v>
+        <v>-10.85</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-0.11</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12590</v>
+        <v>12400</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12520</v>
+        <v>12470</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12541</v>
+        <v>12470</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12381</v>
+        <v>12231</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12400</v>
+        <v>12231</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-190</v>
+        <v>-169</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>-1.51</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3300</v>
+        <v>3276</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3326</v>
+        <v>3265</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3389</v>
+        <v>3267.6</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3247.2</v>
+        <v>3156.4</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3276</v>
+        <v>3173.5</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-24</v>
+        <v>-102.5</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>-0.73</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>595.65</v>
+        <v>585.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>598.1</v>
+        <v>586</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>598.1</v>
+        <v>591.5</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>583</v>
+        <v>569.85</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>585.5</v>
+        <v>572.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-10.15</v>
+        <v>-13</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-1.7</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1479.9</v>
+        <v>1477</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1468</v>
+        <v>1478.4</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1488</v>
+        <v>1482</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1453.6</v>
+        <v>1425.9</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1477</v>
+        <v>1425.9</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-2.9</v>
+        <v>-51.1</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>-0.2</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1100.8</v>
+        <v>1084.3</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1099.9</v>
+        <v>1081</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1099.9</v>
+        <v>1092.2</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1080.4</v>
+        <v>1069.1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1084.3</v>
+        <v>1071.7</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-16.5</v>
+        <v>-12.6</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-1.5</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>163.2</v>
+        <v>164.45</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>161.44</v>
+        <v>165</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>165.58</v>
+        <v>165.41</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>160.71</v>
+        <v>158.15</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>164.45</v>
+        <v>158.15</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>0.77</v>
+        <v>-6.3</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>-3.83</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2291.7</v>
+        <v>2295</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2275</v>
+        <v>2353</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2309.2</v>
+        <v>2461.1</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2273.3</v>
+        <v>2353</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2295</v>
+        <v>2378</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>3.3</v>
+        <v>83</v>
       </c>
       <c r="J127" s="13" t="n">
-        <v>0.14</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128270</v>
+        <v>128290</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>128105</v>
+        <v>128800</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>128765</v>
+        <v>129600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>127015</v>
+        <v>125500</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128290</v>
+        <v>125795</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>0.02</v>
+        <v>-2495</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2841.5</v>
+        <v>2792.1</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2790</v>
+        <v>2792.1</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2820</v>
+        <v>2794</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2728.6</v>
+        <v>2722.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2792.1</v>
+        <v>2722.3</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-49.4</v>
+        <v>-69.8</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-1.74</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>373.35</v>
+        <v>361</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>365</v>
+        <v>359.6</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>365</v>
+        <v>360.35</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>352.35</v>
+        <v>350.25</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>361</v>
+        <v>350.55</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-12.35</v>
+        <v>-10.45</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>-3.31</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1265</v>
+        <v>1250.8</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1250</v>
+        <v>1268.1</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1262.1</v>
+        <v>1310</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1244.8</v>
+        <v>1261.5</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1250.8</v>
+        <v>1261.5</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-1.12</v>
+        <v>10.7</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8700.5</v>
+        <v>8543.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8671</v>
+        <v>8586</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8699.5</v>
+        <v>8618.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8486.5</v>
+        <v>8208</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8543.5</v>
+        <v>8228</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-157</v>
+        <v>-315.5</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>-1.8</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1386.2</v>
+        <v>1383.3</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1376.7</v>
+        <v>1383.3</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1401.2</v>
+        <v>1395</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1373.5</v>
+        <v>1362</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1383.3</v>
+        <v>1362</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-2.9</v>
+        <v>-21.3</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>-0.21</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>84.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>83.79000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>83.79000000000001</v>
+        <v>82.89</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>82.25</v>
+        <v>80.5</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>82.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-2.6</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>335</v>
+        <v>333.4</v>
       </c>
       <c r="E135" s="9" t="n">
         <v>333</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>336.25</v>
+        <v>333.3</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>331.6</v>
+        <v>326.4</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>333.4</v>
+        <v>329.5</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-1.6</v>
+        <v>-3.9</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>-0.48</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1792</v>
+        <v>1741.1</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1775.7</v>
+        <v>1746</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1780</v>
+        <v>1749.5</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1714.8</v>
+        <v>1668.5</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1741.1</v>
+        <v>1668.5</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-50.9</v>
+        <v>-72.59999999999999</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-2.84</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11725</v>
+        <v>11763</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11599</v>
+        <v>11910</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11830</v>
+        <v>12099</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11595</v>
+        <v>11692</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11763</v>
+        <v>11803</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J137" s="13" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>237.27</v>
+        <v>232.5</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>239.9</v>
+        <v>234.9</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>243.16</v>
+        <v>236.3</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>232.5</v>
+        <v>233.33</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>232.5</v>
+        <v>235.95</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-4.77</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>-2.01</v>
+        <v>3.45</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35750</v>
+        <v>35365</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35405</v>
+        <v>35465</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35410</v>
+        <v>35510</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35080</v>
+        <v>34580</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35365</v>
+        <v>34580</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-385</v>
+        <v>-785</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>-1.08</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5509.5</v>
+        <v>5516</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5469</v>
+        <v>5654</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5545.5</v>
+        <v>5759</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5444.5</v>
+        <v>5456.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5516</v>
+        <v>5477.5</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>0.12</v>
+        <v>-38.5</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>288.7</v>
+        <v>287.2</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>285.65</v>
+        <v>287.05</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>287.2</v>
+        <v>288.4</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>283.85</v>
+        <v>280.5</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>287.2</v>
+        <v>283.95</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-1.5</v>
+        <v>-3.25</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>-0.52</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>352.8</v>
+        <v>353.45</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>348</v>
+        <v>352.45</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>353.45</v>
+        <v>353.3</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>353.45</v>
+        <v>344</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>0.18</v>
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1569</v>
+        <v>1566.9</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1550</v>
+        <v>1566.9</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1567.9</v>
+        <v>1575.7</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1540.4</v>
+        <v>1521.1</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1566.9</v>
+        <v>1521.1</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-2.1</v>
+        <v>-45.8</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-0.13</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2365</v>
+        <v>2259</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2350</v>
+        <v>2260</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2365</v>
+        <v>2288.3</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2191</v>
+        <v>2240.5</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-106</v>
+        <v>-4</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-4.48</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116.85</v>
+        <v>116.75</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116</v>
+        <v>116.75</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117.79</v>
+        <v>117.23</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>114.52</v>
+        <v>114.7</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116.75</v>
+        <v>114.7</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.1</v>
+        <v>-2.05</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-0.09</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8358</v>
+        <v>8241</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8319</v>
+        <v>8258.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8319</v>
+        <v>8294.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8118</v>
+        <v>8115</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8241</v>
+        <v>8143.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-117</v>
+        <v>-97.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>-1.4</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>271.75</v>
+        <v>269.1</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>269.95</v>
+        <v>267.15</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>274.05</v>
+        <v>268.5</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>268.35</v>
+        <v>262.8</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>269.1</v>
+        <v>262.8</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-2.65</v>
+        <v>-6.3</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>-0.98</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1221.3</v>
+        <v>1237.1</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1228</v>
+        <v>1234.9</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1256</v>
+        <v>1234.9</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1212.1</v>
+        <v>1206.2</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1237.1</v>
+        <v>1221</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J149" s="13" t="n">
-        <v>1.29</v>
+        <v>-16.1</v>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>410.8</v>
+        <v>412.55</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>408</v>
+        <v>412.65</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>416.5</v>
+        <v>414.3</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>406</v>
+        <v>402.15</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>412.55</v>
+        <v>403.6</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>0.43</v>
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>313.8</v>
+        <v>312.7</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>315.05</v>
+        <v>314.8</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>311.25</v>
+        <v>308.5</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>312.7</v>
+        <v>308.5</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-1.1</v>
+        <v>-4.2</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>-0.35</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1267</v>
+        <v>1252.5</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1267.4</v>
+        <v>1259.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1253</v>
+        <v>1235.3</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-16.5</v>
+        <v>-22.2</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>183.75</v>
+        <v>179</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>182.43</v>
+        <v>179.53</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>182.43</v>
+        <v>180</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>178.65</v>
+        <v>172.92</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-4.75</v>
+        <v>-6</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>-2.59</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>666.3</v>
+        <v>655.2</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>665</v>
+        <v>652.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>665.15</v>
+        <v>655.75</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>650.05</v>
+        <v>617.1</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>655.2</v>
+        <v>618.6</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-11.1</v>
+        <v>-36.6</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>-1.67</v>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1700.6</v>
+        <v>1684.7</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1680</v>
+        <v>1672.1</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1697.7</v>
+        <v>1683.1</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1671</v>
+        <v>1652.9</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1684.7</v>
+        <v>1654.1</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-15.9</v>
+        <v>-30.6</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-0.93</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1009.7</v>
+        <v>995.7</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1001.9</v>
+        <v>999.8</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>995.7</v>
+        <v>968</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-14</v>
+        <v>-27.7</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-1.39</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22785</v>
+        <v>22570</v>
       </c>
       <c r="E157" s="9" t="n">
+        <v>22620</v>
+      </c>
+      <c r="F157" s="9" t="n">
         <v>22660</v>
       </c>
-      <c r="F157" s="9" t="n">
-        <v>22680</v>
-      </c>
       <c r="G157" s="9" t="n">
-        <v>22370</v>
+        <v>21905</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22570</v>
+        <v>21905</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-215</v>
+        <v>-665</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1038</v>
+        <v>1028.6</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1021</v>
+        <v>1044.9</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1034.5</v>
+        <v>1044.9</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1013.2</v>
+        <v>979.8</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1028.6</v>
+        <v>979.8</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-9.4</v>
+        <v>-48.8</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>-0.91</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3954.4</v>
+        <v>3957</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3912.1</v>
+        <v>3957.4</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3957</v>
+        <v>3964</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3858.4</v>
+        <v>3770</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3957</v>
+        <v>3770</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-187</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-4.73</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2519</v>
+        <v>2482.4</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2508</v>
+        <v>2482.4</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2508</v>
+        <v>2490.7</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2482.4</v>
+        <v>2455.2</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-36.6</v>
+        <v>-27.2</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>-1.45</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1861</v>
+        <v>1840</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1845</v>
+        <v>1854.6</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1854.5</v>
+        <v>1856.8</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1834</v>
+        <v>1828</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-1.13</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>455.55</v>
+        <v>476</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>450.55</v>
+        <v>476</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>485.5</v>
+        <v>476</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>450</v>
+        <v>461.15</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>476</v>
+        <v>464.25</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>4.49</v>
+        <v>-11.75</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>384</v>
+        <v>382.65</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>383.25</v>
+        <v>382.95</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>383.6</v>
+        <v>383.8</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>375.55</v>
+        <v>377.25</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>382.65</v>
+        <v>378.85</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-1.35</v>
+        <v>-3.8</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-0.35</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>610.55</v>
+        <v>612.45</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>608.25</v>
+        <v>734.9</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>616.25</v>
+        <v>734.9</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>600</v>
+        <v>734.9</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>612.45</v>
+        <v>734.9</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>1.9</v>
+        <v>122.45</v>
       </c>
       <c r="J164" s="13" t="n">
-        <v>0.31</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1764.4</v>
+        <v>1761.6</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1756.2</v>
+        <v>1767.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1785</v>
+        <v>1819.8</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1747.8</v>
+        <v>1742.4</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1761.6</v>
+        <v>1748.2</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-2.8</v>
+        <v>-13.4</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-0.16</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>993</v>
+        <v>990.1</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1000</v>
+        <v>1009.3</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>991</v>
+        <v>986.1</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-8.6</v>
+        <v>-4.9</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>-0.86</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>367</v>
+        <v>364.65</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>364.8</v>
+        <v>375</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>367.4</v>
+        <v>377.65</v>
       </c>
       <c r="G168" s="12" t="n">
         <v>362.95</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>364.65</v>
+        <v>363</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-2.35</v>
+        <v>-1.65</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>-0.64</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>186.78</v>
+        <v>183</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>184</v>
+        <v>186.1</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>184.24</v>
+        <v>186.49</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>180.79</v>
+        <v>182.38</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>183</v>
+        <v>183.65</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>-2.02</v>
+        <v>0.65</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2204.1</v>
+        <v>2200.8</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2185.5</v>
+        <v>2275.5</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2232.6</v>
+        <v>2323</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2185.5</v>
+        <v>2251</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2200.8</v>
+        <v>2251</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>-0.15</v>
+        <v>50.2</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>2.28</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1525.8</v>
+        <v>1541</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1519.3</v>
+        <v>1588</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1557.3</v>
+        <v>1633.2</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1518.6</v>
+        <v>1575.9</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1541</v>
+        <v>1575.9</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>15.2</v>
+        <v>34.9</v>
       </c>
       <c r="J171" s="13" t="n">
-        <v>1</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2652</v>
+        <v>2606.1</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2637</v>
+        <v>2606.1</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2637.1</v>
+        <v>2613.2</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2580.1</v>
+        <v>2521.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2606.1</v>
+        <v>2525</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-45.9</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-1.73</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5021</v>
+        <v>5009.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4964</v>
+        <v>5003</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5015</v>
+        <v>5003</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4943</v>
+        <v>4856</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>5009.5</v>
+        <v>4856</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-11.5</v>
+        <v>-153.5</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-0.23</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4930</v>
+        <v>4965.5</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4929</v>
+        <v>4931</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4988</v>
+        <v>4959.5</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4894</v>
+        <v>4837.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4965.5</v>
+        <v>4850</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>0.72</v>
+        <v>-115.5</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1296.3</v>
+        <v>1297.6</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1281.7</v>
+        <v>1325</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1300.4</v>
+        <v>1326.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1278.3</v>
+        <v>1291.5</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1297.6</v>
+        <v>1300.9</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2818.7</v>
+        <v>2802.4</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2789</v>
+        <v>2802.4</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2816</v>
+        <v>2817.6</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2757.5</v>
+        <v>2730</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2802.4</v>
+        <v>2730</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-16.3</v>
+        <v>-72.40000000000001</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-0.58</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4121.5</v>
+        <v>4125</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4081</v>
+        <v>4150</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4151.9</v>
+        <v>4155</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4062.8</v>
+        <v>4022.1</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4125</v>
+        <v>4050</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>0.08</v>
+        <v>-75</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1256.7</v>
+        <v>1256.1</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1254.5</v>
+        <v>1262.3</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1263.5</v>
+        <v>1268</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1240.2</v>
+        <v>1240</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1256.1</v>
+        <v>1241.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-0.6</v>
+        <v>-14.3</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v>-0.05</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>10979</v>
+        <v>11000</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10859</v>
+        <v>11045</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11060</v>
+        <v>11045</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10790</v>
+        <v>10697</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11000</v>
+        <v>10697</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>0.19</v>
+        <v>-303</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>179.2</v>
+        <v>178.1</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>177.1</v>
+        <v>179.57</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>179.65</v>
+        <v>179.69</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>175.53</v>
+        <v>174.74</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>178.1</v>
+        <v>175</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.1</v>
+        <v>-3.1</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.61</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>575.3</v>
+        <v>572.95</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>571.8</v>
+        <v>573.4</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>577.65</v>
+        <v>575.95</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>567.55</v>
+        <v>558</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>572.95</v>
+        <v>560.8</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-2.35</v>
+        <v>-12.15</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-0.41</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>269.05</v>
+        <v>263.7</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>264</v>
+        <v>263.7</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>264.85</v>
+        <v>264.4</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>256.5</v>
+        <v>253.55</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>263.7</v>
+        <v>257</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-5.35</v>
+        <v>-6.7</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>-1.99</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1158.5</v>
+        <v>1165</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1149</v>
+        <v>1168</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1169</v>
+        <v>1179</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1165</v>
+        <v>1137</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-28</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>166.3</v>
+        <v>167.4</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>165.2</v>
+        <v>172.2</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>167.75</v>
+        <v>173.35</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>165.16</v>
+        <v>169.01</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>167.4</v>
+        <v>170</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>0.66</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1117.8</v>
+        <v>1119.1</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1114</v>
+        <v>1120.1</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1135.5</v>
+        <v>1124.5</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1104.6</v>
+        <v>1099</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1119.1</v>
+        <v>1099</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>0.12</v>
+        <v>-20.1</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>-1.8</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  14-Sep-2026 06:21 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  15-Sep-2026 05:29 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-Sep-2026 06:21 PM</t>
+          <t>15-Sep-2026 05:29 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 15-Sep-2026 05:29 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 16-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>15-Sep-2026 05:29 PM</t>
+          <t>16-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  15-Sep-2026 05:29 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  16-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>492.7</v>
+        <v>468.7</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>492.7</v>
+        <v>470.5</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>494.5</v>
+        <v>474.45</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>466.1</v>
+        <v>459.55</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>468.7</v>
+        <v>472.85</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-24</v>
+        <v>4.15</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-4.87</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7274</v>
+        <v>7005</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7268</v>
+        <v>7005</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7268</v>
+        <v>7051</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7005</v>
+        <v>6905.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7005</v>
+        <v>6980</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-269</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-3.7</v>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25550</v>
+        <v>26125</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25690</v>
+        <v>26195</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26245</v>
+        <v>26450</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25550</v>
+        <v>25500</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>26125</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>575</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>2.25</v>
+        <v>0</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>395</v>
+        <v>378.8</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>395.15</v>
+        <v>378.8</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>396.8</v>
+        <v>384.05</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>378.8</v>
+        <v>378</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>378.8</v>
+        <v>381.3</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-16.2</v>
+        <v>2.5</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-4.1</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.44</v>
+        <v>49.02</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.35</v>
+        <v>49.4</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.68</v>
+        <v>50.45</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>48.71</v>
+        <v>48.91</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>49.02</v>
+        <v>49.74</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.42</v>
+        <v>0.72</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-2.82</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1246.5</v>
+        <v>1225.2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1234.9</v>
+        <v>1233</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1280.3</v>
+        <v>1235</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1219.6</v>
+        <v>1219.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1225.2</v>
+        <v>1226.6</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-21.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>-1.71</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3080</v>
+        <v>2957</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3083.7</v>
+        <v>2972.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2921.3</v>
+        <v>2914.3</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-131.4</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>-4.29</v>
+        <v>-8.6</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1791.4</v>
+        <v>1722.9</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1791.4</v>
+        <v>1737.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1713.8</v>
+        <v>1707</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-50.8</v>
+        <v>10</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-2.88</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5087.5</v>
+        <v>5161</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5170</v>
+        <v>5170.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5290</v>
+        <v>5265.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5140.5</v>
+        <v>5148</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5161</v>
+        <v>5175</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>1.44</v>
+        <v>14</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>391.85</v>
+        <v>381.75</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>392.6</v>
+        <v>382</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>393.85</v>
+        <v>385.45</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>380.1</v>
+        <v>379.55</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>381.75</v>
+        <v>381.05</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>-2.58</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>305</v>
+        <v>297.5</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>306.45</v>
+        <v>295</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>310</v>
+        <v>299.3</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>297.3</v>
+        <v>291.6</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>297.5</v>
+        <v>293.5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-2.46</v>
+        <v>-4</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2153.5</v>
+        <v>2119.3</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2157</v>
+        <v>2115</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2160</v>
+        <v>2132.9</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2107.7</v>
+        <v>2041.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2119.3</v>
+        <v>2120</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-34.2</v>
+        <v>0.7</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-1.59</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8836</v>
+        <v>8714</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8937</v>
+        <v>8756</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8950.5</v>
+        <v>8792.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8714</v>
+        <v>8672.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8714</v>
+        <v>8696.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-122</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>-1.38</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>417.65</v>
+        <v>406.2</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>415</v>
+        <v>410.95</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>417.75</v>
+        <v>429.55</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>405.05</v>
+        <v>402.15</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>406.2</v>
+        <v>411.95</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-11.45</v>
+        <v>5.75</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-2.74</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>164.5</v>
+        <v>157.4</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>165.36</v>
+        <v>158.21</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>156.65</v>
+        <v>154.75</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>156.65</v>
+        <v>156.5</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-4.34</v>
+        <v>-0.15</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2472.5</v>
+        <v>2402.8</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2472.5</v>
+        <v>2405.1</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2473</v>
+        <v>2444.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2402.8</v>
+        <v>2397.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2402.8</v>
+        <v>2416.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-69.7</v>
+        <v>13.8</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-2.82</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1411.4</v>
+        <v>1379.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1410</v>
+        <v>1376</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1414.1</v>
+        <v>1388.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1372.8</v>
+        <v>1357.6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1379.6</v>
+        <v>1382.5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-31.8</v>
+        <v>2.9</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>-2.25</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>594.8</v>
+        <v>580.15</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>602.9</v>
+        <v>597.25</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>576.4</v>
+        <v>580.25</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>580.15</v>
+        <v>586.5</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-14.65</v>
+        <v>6.35</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-2.46</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6244.5</v>
+        <v>6081.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6250</v>
+        <v>6000</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6250</v>
+        <v>6140.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6060.5</v>
+        <v>5995</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6081.5</v>
+        <v>6076</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-163</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>-2.61</v>
+        <v>-5.5</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1058.9</v>
+        <v>1028</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1061.4</v>
+        <v>1030</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1065.7</v>
+        <v>1038.1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1024.6</v>
+        <v>1015.1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1028</v>
+        <v>1033.2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-30.9</v>
+        <v>5.2</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-2.92</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1679.8</v>
+        <v>1660</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1688</v>
+        <v>1657.1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1688</v>
+        <v>1657.1</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1642.1</v>
+        <v>1623</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1660</v>
+        <v>1643</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>-1.18</v>
+        <v>-17</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1246</v>
+        <v>1222.9</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1254</v>
+        <v>1252.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1219.9</v>
+        <v>1223.7</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1222.9</v>
+        <v>1241</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-23.1</v>
+        <v>18.1</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-1.85</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11693</v>
+        <v>11425</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11709</v>
+        <v>11596</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11416</v>
+        <v>11379</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11424</v>
+        <v>11593</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-254</v>
+        <v>169</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-2.18</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1913.5</v>
+        <v>1855.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1921.4</v>
+        <v>1864</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1930.6</v>
+        <v>1874.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1855.5</v>
+        <v>1832.9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1855.5</v>
+        <v>1837</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-58</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-3.03</v>
+        <v>-18.5</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1035</v>
+        <v>1010.5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1038.6</v>
+        <v>1019.3</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1005.5</v>
+        <v>1006.2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-25.3</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>-2.45</v>
+        <v>-3</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2164.6</v>
+        <v>2129</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2164.6</v>
+        <v>2124.5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2176.3</v>
+        <v>2140</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2117.1</v>
+        <v>2100.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2129</v>
+        <v>2124.9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-35.6</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-1.64</v>
+        <v>-4.1</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>691.4</v>
+        <v>677.1</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>697.3</v>
+        <v>674.9</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>667.55</v>
+        <v>657.3</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>677.1</v>
+        <v>682.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-14.3</v>
+        <v>5.5</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-2.07</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>176.52</v>
+        <v>172.45</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>177</v>
+        <v>173.24</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>179.11</v>
+        <v>173.62</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>172.24</v>
+        <v>169.33</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>172.45</v>
+        <v>172.5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-4.07</v>
+        <v>0.05</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>-2.31</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>238.13</v>
+        <v>232.7</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>238.13</v>
+        <v>233.25</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>238.51</v>
+        <v>235.29</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>232.44</v>
+        <v>232.33</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>232.7</v>
+        <v>234.98</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-5.43</v>
+        <v>2.28</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-2.28</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>404.35</v>
+        <v>382.9</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>402</v>
+        <v>384.05</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>403.65</v>
+        <v>390.2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>382.9</v>
+        <v>382.1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>382.9</v>
+        <v>385.75</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-21.45</v>
+        <v>2.85</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-5.3</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>458.05</v>
+        <v>447.1</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>458.05</v>
+        <v>449.1</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>460.95</v>
+        <v>450.7</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>445.55</v>
+        <v>444.15</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>447.1</v>
+        <v>448.15</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-10.95</v>
+        <v>1.05</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>-2.39</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1831.1</v>
+        <v>1830.4</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1844</v>
+        <v>1835.8</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1844</v>
+        <v>1838</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1819.6</v>
+        <v>1818.6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1830.4</v>
+        <v>1835</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>431</v>
+        <v>412.85</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>431.25</v>
+        <v>415.45</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>432</v>
+        <v>417.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>412.85</v>
+        <v>406</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>412.85</v>
+        <v>410.6</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-18.15</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>-4.21</v>
+        <v>-2.25</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>390.65</v>
+        <v>382</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>391.95</v>
+        <v>381</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>392.05</v>
+        <v>383.5</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>381</v>
+        <v>373.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>382</v>
+        <v>374.4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-8.65</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>-2.21</v>
+        <v>-7.6</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48385</v>
+        <v>47070</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48725</v>
+        <v>47100</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48725</v>
+        <v>48325</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47070</v>
+        <v>46850</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47070</v>
+        <v>47555</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-1315</v>
+        <v>485</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>-2.72</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>304.5</v>
+        <v>298.65</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>304.2</v>
+        <v>301</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>308.15</v>
+        <v>304</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>298.65</v>
+        <v>298.1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>298.65</v>
+        <v>303.35</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-5.85</v>
+        <v>4.7</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-1.92</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4962</v>
+        <v>4947.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4990</v>
+        <v>4947.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5022.5</v>
+        <v>5036.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4947.5</v>
+        <v>4933</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4947.5</v>
+        <v>4999.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-14.5</v>
+        <v>52</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>-0.29</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>281.65</v>
+        <v>286.45</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>291</v>
+        <v>286.2</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>302.85</v>
+        <v>287.8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>285.1</v>
+        <v>279.3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>286.45</v>
+        <v>281.25</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>4.8</v>
+        <v>-5.2</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.7</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124</v>
+        <v>122.37</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>123.25</v>
+        <v>122.8</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>124.48</v>
+        <v>123.7</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>122.05</v>
+        <v>121.81</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>122.37</v>
+        <v>123.2</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-1.63</v>
+        <v>0.83</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-1.31</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>779.75</v>
+        <v>784.8</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>776.2</v>
+        <v>790</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>788.75</v>
+        <v>791.95</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>766.85</v>
+        <v>769</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>784.8</v>
+        <v>771.95</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>5.05</v>
+        <v>-12.85</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>0.65</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>418.8</v>
+        <v>416.65</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>421</v>
+        <v>415.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>415.45</v>
+        <v>401.4</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>416.65</v>
+        <v>409.1</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>-0.51</v>
+        <v>-7.55</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1845.9</v>
+        <v>1791.6</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1834.8</v>
+        <v>1800.7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1842</v>
+        <v>1800.7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1784.2</v>
+        <v>1756.3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1791.6</v>
+        <v>1765.6</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-54.3</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>-2.94</v>
+        <v>-26</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1366</v>
+        <v>1351</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1362.7</v>
+        <v>1363.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1347.7</v>
+        <v>1344.3</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-15</v>
+        <v>7</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-1.1</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>426.4</v>
+        <v>419.25</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>426.4</v>
+        <v>419.25</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>427</v>
+        <v>423.45</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>418</v>
+        <v>417.6</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>419.25</v>
+        <v>422.25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-7.15</v>
+        <v>3</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>-1.68</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1846.5</v>
+        <v>1775.5</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1887.3</v>
+        <v>1775</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1893.6</v>
+        <v>1784.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1765.6</v>
+        <v>1717</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1775.5</v>
+        <v>1766.7</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-71</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-3.85</v>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1797.4</v>
+        <v>1820.3</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1797.4</v>
+        <v>1833.9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1846.6</v>
+        <v>1900.1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1788.8</v>
+        <v>1830.1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1820.3</v>
+        <v>1860</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>1.27</v>
+        <v>39.7</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>499.25</v>
+        <v>483.7</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>499.95</v>
+        <v>484</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>501.5</v>
+        <v>491.3</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>483.7</v>
+        <v>480.7</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>483.7</v>
+        <v>488.8</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-15.55</v>
+        <v>5.1</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-3.11</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1929</v>
+        <v>1939.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1928</v>
+        <v>1939.1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1918.9</v>
+        <v>1910</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1939.1</v>
+        <v>1937.8</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>10.1</v>
+        <v>-1.3</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.52</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>231</v>
+        <v>226.15</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>231</v>
+        <v>227.01</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>231.6</v>
+        <v>228.62</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>226.11</v>
+        <v>222.3</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>226.15</v>
+        <v>223.4</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>-2.1</v>
+        <v>-2.75</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>227.32</v>
+        <v>225.78</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>227.32</v>
+        <v>225</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>223.25</v>
+        <v>216.42</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>225.78</v>
+        <v>227.24</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-1.54</v>
+        <v>1.46</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-0.68</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5070</v>
+        <v>4874</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5070</v>
+        <v>4863.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5121.5</v>
+        <v>4985</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4874</v>
+        <v>4844</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4874</v>
+        <v>4940</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-196</v>
+        <v>66</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-3.87</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>376</v>
+        <v>384.9</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>379</v>
+        <v>386.85</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>390.95</v>
+        <v>389.45</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>376.75</v>
+        <v>382</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>384.9</v>
+        <v>382</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>8.9</v>
+        <v>-2.9</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>2.37</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1746.6</v>
+        <v>1687.4</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1746.6</v>
+        <v>1687.8</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1754</v>
+        <v>1704.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1687.4</v>
+        <v>1693.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-59.2</v>
+        <v>6.2</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-3.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1587.8</v>
+        <v>1561.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1588.9</v>
+        <v>1562.8</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1597.9</v>
+        <v>1598</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1556.1</v>
+        <v>1546.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1561.3</v>
+        <v>1590.5</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-26.5</v>
+        <v>29.2</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-1.67</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>54.15</v>
+        <v>53.79</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>54.14</v>
+        <v>53.8</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>54.53</v>
+        <v>57.1</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>52.82</v>
+        <v>51.66</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>53.79</v>
+        <v>55.19</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.36</v>
+        <v>1.4</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>-0.66</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9322</v>
+        <v>9198</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9367.5</v>
+        <v>9168</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9397.5</v>
+        <v>9180</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9118.5</v>
+        <v>8923</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9198</v>
+        <v>9158</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-124</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>-1.33</v>
+        <v>-40</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13425</v>
+        <v>13180</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13490</v>
+        <v>12985</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13575</v>
+        <v>13260</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13093</v>
+        <v>12850</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13180</v>
+        <v>13181</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-245</v>
+        <v>1</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-1.82</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>644.5</v>
+        <v>620.85</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>644.5</v>
+        <v>620.85</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>647.15</v>
+        <v>628.3</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>620.85</v>
+        <v>611.5</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>620.85</v>
+        <v>622.8</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-23.65</v>
+        <v>1.95</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-3.67</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1165.5</v>
+        <v>1145</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1163.7</v>
+        <v>1142</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1168.5</v>
+        <v>1149.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1141</v>
+        <v>1133.9</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-1.76</v>
+        <v>-5</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7530</v>
+        <v>7452.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7567.5</v>
+        <v>7430</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7570.5</v>
+        <v>7524.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7440</v>
+        <v>7406</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7452.5</v>
+        <v>7500</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-77.5</v>
+        <v>47.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>-1.03</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2899.7</v>
+        <v>2835.8</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2895</v>
+        <v>2840</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2899.6</v>
+        <v>2864.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2822.2</v>
+        <v>2791.1</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2835.8</v>
+        <v>2815.6</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-63.9</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>-2.2</v>
+        <v>-20.2</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>412.65</v>
+        <v>409.2</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>412.65</v>
+        <v>407.8</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>417.95</v>
+        <v>419.65</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>405.1</v>
+        <v>407.8</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>409.2</v>
+        <v>415.5</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-3.45</v>
+        <v>6.3</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-0.84</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>344.5</v>
+        <v>343</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>344.45</v>
+        <v>341.8</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>344.5</v>
+        <v>346</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>339.45</v>
+        <v>340.1</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>343</v>
+        <v>341.8</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>-0.44</v>
+        <v>-1.2</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>173.62</v>
+        <v>170.88</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.62</v>
+        <v>170.88</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>173.82</v>
+        <v>171.88</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>169.73</v>
+        <v>168.72</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>170.88</v>
+        <v>170.65</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-2.74</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>-1.58</v>
+        <v>-0.23</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2419.2</v>
+        <v>2371.7</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2420.8</v>
+        <v>2371.7</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2429.8</v>
+        <v>2425.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2346.6</v>
+        <v>2306.3</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2371.7</v>
+        <v>2410</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-47.5</v>
+        <v>38.3</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>-1.96</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>562.4</v>
+        <v>540.6</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>564.2</v>
+        <v>540.6</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>564.3</v>
+        <v>545.6</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>540</v>
+        <v>528.8</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>540.6</v>
+        <v>539.75</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>-3.88</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>877</v>
+        <v>876.85</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>856.6</v>
+        <v>856</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>-0.92</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1754</v>
+        <v>1666.9</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1759.7</v>
+        <v>1703.7</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1657.4</v>
+        <v>1647.6</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1659.3</v>
+        <v>1665.3</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-88.7</v>
+        <v>6</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-5.07</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>909.3</v>
+        <v>872.6</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>917</v>
+        <v>869</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>923.65</v>
+        <v>872</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>872.5</v>
+        <v>829</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>872.6</v>
+        <v>835.6</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-36.7</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>-4.04</v>
+        <v>-37</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3281.9</v>
+        <v>3171</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3263.3</v>
+        <v>3190</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3272</v>
+        <v>3201.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3171</v>
+        <v>3159.1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-110.9</v>
+        <v>16</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-3.38</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74">
@@ -3264,7 +3264,7 @@
       <c r="I74" s="12" t="n">
         <v/>
       </c>
-      <c r="J74" s="10" t="n">
+      <c r="J74" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4905</v>
+        <v>4695</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4920</v>
+        <v>4690</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4940</v>
+        <v>4709.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4674</v>
+        <v>4615.8</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4695</v>
+        <v>4695.6</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-210</v>
+        <v>0.6</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>-4.28</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1111</v>
+        <v>1087</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1117</v>
+        <v>1093</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1117</v>
+        <v>1106.9</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1081.1</v>
+        <v>1084.8</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1087</v>
+        <v>1089.9</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-24</v>
+        <v>2.9</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-2.16</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1206.1</v>
+        <v>1253.7</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1252</v>
+        <v>1262.5</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1290</v>
+        <v>1284.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1250</v>
+        <v>1244.9</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1253.7</v>
+        <v>1253</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>47.6</v>
+        <v>-0.7</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>3.95</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2403.9</v>
+        <v>2409</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2416.9</v>
+        <v>2383.1</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2423.9</v>
+        <v>2408.5</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2385</v>
+        <v>2360</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2409</v>
+        <v>2373.1</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>5.1</v>
+        <v>-35.9</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>0.21</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>722.4</v>
+        <v>714.9</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>730.75</v>
+        <v>725.4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>715.05</v>
+        <v>710.85</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>716.55</v>
+        <v>721.5</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>1.17</v>
+        <v>4.95</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>530.65</v>
+        <v>534</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>516.1</v>
+        <v>517</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-13.9</v>
+        <v>14.1</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>-2.62</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5221.5</v>
+        <v>5166</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5287.5</v>
+        <v>5200</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5327.5</v>
+        <v>5315</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5166</v>
+        <v>5186.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5166</v>
+        <v>5235</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-55.5</v>
+        <v>69</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>-1.06</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>981.5</v>
+        <v>958.7</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>980.1</v>
+        <v>956.4</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>981</v>
+        <v>978.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>958.7</v>
+        <v>956.4</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-22.8</v>
+        <v>14</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>-2.32</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>514.5</v>
+        <v>490.24</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>513.95</v>
+        <v>496</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>513.95</v>
+        <v>496.7</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>490.55</v>
+        <v>477.5</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>492.1</v>
+        <v>481.6</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-22.4</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>-4.35</v>
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>352</v>
+        <v>345.3</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>352.65</v>
+        <v>347</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>355.2</v>
+        <v>352.25</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>344.2</v>
+        <v>343.05</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>345.3</v>
+        <v>350.05</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-6.7</v>
+        <v>4.75</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>-1.9</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1927</v>
+        <v>1938.1</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1944</v>
+        <v>1944.1</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1969.4</v>
+        <v>1977</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1933.8</v>
+        <v>1943.5</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1938.1</v>
+        <v>1962</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>0.58</v>
+        <v>23.9</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34580</v>
+        <v>33595</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34590</v>
+        <v>33600</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34870</v>
+        <v>34170</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33500</v>
+        <v>33510</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33595</v>
+        <v>33895</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-985</v>
+        <v>300</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>-2.85</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.20999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86.56</v>
+        <v>84.61</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.65000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>84.8</v>
+        <v>84.61</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>84.8</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-1.41</v>
+        <v>0.21</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-1.64</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>113.88</v>
+        <v>112</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>113.88</v>
+        <v>112</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>114.24</v>
+        <v>112.41</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>111.82</v>
+        <v>110.35</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>112</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>151.98</v>
+        <v>150.03</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>151.98</v>
+        <v>150</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>152.42</v>
+        <v>150.39</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>149</v>
+        <v>147.27</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>150.03</v>
+        <v>148.77</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>-1.28</v>
+        <v>-1.26</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>718.5</v>
+        <v>715</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>724</v>
+        <v>716.25</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>737.75</v>
+        <v>719.55</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>710.85</v>
+        <v>706.75</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>715</v>
+        <v>713.4</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>-0.49</v>
+        <v>-1.6</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1695</v>
+        <v>1659.5</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1713.8</v>
+        <v>1662</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1713.8</v>
+        <v>1768.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1652</v>
+        <v>1645.2</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1659.5</v>
+        <v>1706.3</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-35.5</v>
+        <v>46.8</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>-2.09</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4973</v>
+        <v>4776</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4955.5</v>
+        <v>4799.5</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4963.5</v>
+        <v>4806</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4773</v>
+        <v>4701.5</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4776</v>
+        <v>4733.5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-197</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-3.96</v>
+        <v>-42.5</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>978.2</v>
+        <v>957.7</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>984.5</v>
+        <v>961.1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>955</v>
+        <v>944.5</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>956.5</v>
+        <v>946.5</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-21.7</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>-2.22</v>
+        <v>-10</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>390.8</v>
+        <v>381</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>390.8</v>
+        <v>381.5</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>378.7</v>
+        <v>375.2</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>379</v>
+        <v>375.6</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>-2.32</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1037.7</v>
+        <v>1077</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1085</v>
+        <v>1082.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1097.7</v>
+        <v>1085.1</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1071.7</v>
+        <v>1053.5</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>39.3</v>
+        <v>-17</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>3.79</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>135.11</v>
+        <v>132.03</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>135.5</v>
+        <v>132.79</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>135.69</v>
+        <v>134.97</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>132.03</v>
+        <v>131.7</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>132.03</v>
+        <v>134.75</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-3.08</v>
+        <v>2.72</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-2.28</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1968.5</v>
+        <v>1932.4</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1976.7</v>
+        <v>1963.3</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1995.9</v>
+        <v>1983</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1924</v>
+        <v>1905</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1932.4</v>
+        <v>1950.7</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-36.1</v>
+        <v>18.3</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-1.83</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>462.9</v>
+        <v>458.55</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>464</v>
+        <v>457.2</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>466.55</v>
+        <v>458</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>457</v>
+        <v>446.5</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>458.55</v>
+        <v>452.95</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-4.35</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-5.6</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>259.85</v>
+        <v>258</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>261</v>
+        <v>259.4</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>264.2</v>
+        <v>264.9</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>258</v>
+        <v>259.3</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>258</v>
+        <v>264.15</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-1.85</v>
+        <v>6.15</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>-0.71</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1120.5</v>
+        <v>1095</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1119.7</v>
+        <v>1088</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1119.7</v>
+        <v>1117</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1090.5</v>
+        <v>1085.4</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-25.5</v>
+        <v>8</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-2.28</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4843.5</v>
+        <v>4712</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>4843.5</v>
+        <v>4716</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>4849.5</v>
+        <v>4872</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4701</v>
+        <v>4676</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>4712</v>
+        <v>4750</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-131.5</v>
+        <v>38</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-2.71</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>756.1</v>
+        <v>723.55</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>755</v>
+        <v>723.55</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>760</v>
+        <v>738.8</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>721.25</v>
+        <v>715</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>723.55</v>
+        <v>730.85</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-32.55</v>
+        <v>7.3</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>-4.3</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>526.45</v>
+        <v>505</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>526.45</v>
+        <v>506.6</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>526.45</v>
+        <v>510.95</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>505</v>
+        <v>503.05</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>505</v>
+        <v>504.7</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-21.45</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>-4.07</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1265</v>
+        <v>1244</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1267.7</v>
+        <v>1250.2</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1229.2</v>
+        <v>1227</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1229.2</v>
+        <v>1248.9</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-35.8</v>
+        <v>19.7</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>-2.83</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>470.25</v>
+        <v>466</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>468.95</v>
+        <v>466</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>472.95</v>
+        <v>472</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>461.6</v>
+        <v>461.65</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-4.25</v>
+        <v>5</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-0.9</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1226.4</v>
+        <v>1213.6</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1226.4</v>
+        <v>1213.6</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1226.7</v>
+        <v>1219.5</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1211</v>
+        <v>1179.1</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1213.6</v>
+        <v>1215.9</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-12.8</v>
+        <v>2.3</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-1.04</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>419</v>
+        <v>409.8</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>420.5</v>
+        <v>413.6</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>420.5</v>
+        <v>417.05</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>409.8</v>
+        <v>409.35</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>409.8</v>
+        <v>415</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-2.2</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>553.75</v>
+        <v>563</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>580.95</v>
+        <v>566.4</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>560</v>
+        <v>553.1</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>9.25</v>
+        <v>-8</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>1.67</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1909</v>
+        <v>1906.4</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1907</v>
+        <v>1921</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1921</v>
+        <v>2038.6</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1885.5</v>
+        <v>1870</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1906.4</v>
+        <v>1895.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-0.14</v>
+        <v>-10.7</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1969</v>
+        <v>1926.9</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1975</v>
+        <v>1924.6</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1981</v>
+        <v>1940.4</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1915.6</v>
+        <v>1863.5</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1926.9</v>
+        <v>1905.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-42.1</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>-2.14</v>
+        <v>-21.4</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>562.9</v>
+        <v>542</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>563.9</v>
+        <v>541.8</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>565.25</v>
+        <v>551.45</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>538.5</v>
+        <v>529.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-20.9</v>
+        <v>1</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>-3.71</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3959</v>
+        <v>3844.2</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3959</v>
+        <v>3867.9</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3835.7</v>
+        <v>3799.9</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3850.7</v>
+        <v>3807.7</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-80</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>-2.04</v>
+        <v>-43</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>309.1</v>
+        <v>296.8</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>310.6</v>
+        <v>296.9</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>311.3</v>
+        <v>300.95</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>296.6</v>
+        <v>293.8</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>296.8</v>
+        <v>295.5</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-3.98</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3337.4</v>
+        <v>3312.2</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3402</v>
+        <v>3340</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3441</v>
+        <v>3366</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3300.5</v>
+        <v>3293</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3312.2</v>
+        <v>3351.5</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-25.2</v>
+        <v>39.3</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.76</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2095</v>
+        <v>2063.2</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2095</v>
+        <v>2056.4</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2099.5</v>
+        <v>2074.1</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2049.5</v>
+        <v>2033.5</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2063.2</v>
+        <v>2045</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>-1.52</v>
+        <v>-18.2</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3107</v>
+        <v>3029.5</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3114.6</v>
+        <v>3044.6</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3119.6</v>
+        <v>3105.9</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3029.5</v>
+        <v>3044.6</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3029.5</v>
+        <v>3070</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-77.5</v>
+        <v>40.5</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>-2.49</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>329</v>
+        <v>318.85</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>327.1</v>
+        <v>321.25</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>330.45</v>
+        <v>324.7</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>317.7</v>
+        <v>317.25</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>318.85</v>
+        <v>319.9</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-10.15</v>
+        <v>1.05</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-3.09</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>802.1</v>
+        <v>791.25</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>809.65</v>
+        <v>795.5</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>809.8</v>
+        <v>819.9</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>791.25</v>
+        <v>792.15</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>791.25</v>
+        <v>810.15</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-10.85</v>
+        <v>18.9</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-1.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12400</v>
+        <v>12231</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12470</v>
+        <v>12231</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12470</v>
+        <v>12367</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12231</v>
+        <v>12159</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12231</v>
+        <v>12166</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-169</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-1.36</v>
+        <v>-65</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3276</v>
+        <v>3173.5</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3265</v>
+        <v>3170.2</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3267.6</v>
+        <v>3224.5</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3156.4</v>
+        <v>3056.6</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3173.5</v>
+        <v>3211.2</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-102.5</v>
+        <v>37.7</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>-3.13</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>585.5</v>
+        <v>572.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>591.5</v>
+        <v>585</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>569.85</v>
+        <v>557.8</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>572.5</v>
+        <v>580.85</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-13</v>
+        <v>8.35</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-2.22</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1477</v>
+        <v>1425.9</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1478.4</v>
+        <v>1425.9</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1482</v>
+        <v>1491.7</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1425.9</v>
+        <v>1423.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1425.9</v>
+        <v>1487.6</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-51.1</v>
+        <v>61.7</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>-3.46</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1084.3</v>
+        <v>1071.7</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1081</v>
+        <v>1071</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1092.2</v>
+        <v>1084.5</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1069.1</v>
+        <v>1047</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1071.7</v>
+        <v>1080.1</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-12.6</v>
+        <v>8.4</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-1.16</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>164.45</v>
+        <v>158.15</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>165</v>
+        <v>157.19</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>165.41</v>
+        <v>160.4</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>158.15</v>
+        <v>156.4</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>158.15</v>
+        <v>158.27</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-6.3</v>
+        <v>0.12</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>-3.83</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2295</v>
+        <v>2378</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2353</v>
+        <v>2379</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2461.1</v>
+        <v>2393.9</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2353</v>
+        <v>2316.7</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2378</v>
+        <v>2316.7</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>83</v>
+        <v>-61.3</v>
       </c>
       <c r="J127" s="13" t="n">
-        <v>3.62</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128290</v>
+        <v>125795</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>128800</v>
+        <v>125880</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>129600</v>
+        <v>127700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>125500</v>
+        <v>124615</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>125795</v>
+        <v>125010</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-2495</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-1.94</v>
+        <v>-785</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2792.1</v>
+        <v>2722.3</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2792.1</v>
+        <v>2726</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2794</v>
+        <v>2804.6</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2722.3</v>
+        <v>2725.2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2722.3</v>
+        <v>2771.4</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-69.8</v>
+        <v>49.1</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>361</v>
+        <v>350.55</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>359.6</v>
+        <v>352</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>360.35</v>
+        <v>357.75</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>350.25</v>
+        <v>350.1</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>350.55</v>
+        <v>356</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-10.45</v>
+        <v>5.45</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>-2.89</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1250.8</v>
+        <v>1261.5</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1268.1</v>
+        <v>1258.5</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1310</v>
+        <v>1274.3</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1261.5</v>
+        <v>1250.9</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1261.5</v>
+        <v>1256</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>10.7</v>
+        <v>-5.5</v>
       </c>
       <c r="J131" s="13" t="n">
-        <v>0.86</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8543.5</v>
+        <v>8228</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8586</v>
+        <v>8212</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8618.5</v>
+        <v>8295</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8208</v>
+        <v>8100</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8228</v>
+        <v>8160.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-315.5</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>-3.69</v>
+        <v>-67.5</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1383.3</v>
+        <v>1362</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1383.3</v>
+        <v>1369.2</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1362</v>
+        <v>1368.7</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1362</v>
+        <v>1384.5</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-21.3</v>
+        <v>22.5</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>-1.54</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>82.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>82.8</v>
+        <v>80.8</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>82.89</v>
+        <v>81.09</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>80.5</v>
+        <v>79.45</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>80.5</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>-2.31</v>
+        <v>-0.18</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>333.4</v>
+        <v>329.5</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>333</v>
+        <v>329.5</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>333.3</v>
+        <v>329.95</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>326.4</v>
+        <v>326.55</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>329.5</v>
+        <v>327</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-1.17</v>
+        <v>-2.5</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1741.1</v>
+        <v>1668.5</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1746</v>
+        <v>1660</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1749.5</v>
+        <v>1717.3</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1668.5</v>
+        <v>1660</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1668.5</v>
+        <v>1706.9</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-72.59999999999999</v>
+        <v>38.4</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-4.17</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11763</v>
+        <v>11803</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11910</v>
+        <v>11840</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>12099</v>
+        <v>11920</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11692</v>
+        <v>11399</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11803</v>
+        <v>11510</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>40</v>
+        <v>-293</v>
       </c>
       <c r="J137" s="13" t="n">
-        <v>0.34</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>232.5</v>
+        <v>235.95</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>234.9</v>
+        <v>236.45</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>236.3</v>
+        <v>236.8</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>233.33</v>
+        <v>233.31</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>235.95</v>
+        <v>236.8</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>1.48</v>
+        <v>0.85</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35365</v>
+        <v>34580</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35465</v>
+        <v>34600</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35510</v>
+        <v>35035</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34580</v>
+        <v>34000</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>34580</v>
+        <v>34275</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-785</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>-2.22</v>
+        <v>-305</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5516</v>
+        <v>5477.5</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5654</v>
+        <v>5522</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5759</v>
+        <v>5529.5</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5456.5</v>
+        <v>5390.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5477.5</v>
+        <v>5440</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-38.5</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-0.7</v>
+        <v>-37.5</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>287.2</v>
+        <v>283.95</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>287.05</v>
+        <v>281.6</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>288.4</v>
+        <v>284.95</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>280.5</v>
+        <v>278.25</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>283.95</v>
+        <v>282.1</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>-1.13</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>353.45</v>
+        <v>344</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>352.45</v>
+        <v>344</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>353.3</v>
+        <v>349.1</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>344</v>
+        <v>343.65</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-9.449999999999999</v>
+        <v>2</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1566.9</v>
+        <v>1521.1</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1566.9</v>
+        <v>1521.2</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1575.7</v>
+        <v>1546.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1521.1</v>
+        <v>1521.2</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1521.1</v>
+        <v>1543.8</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-45.8</v>
+        <v>22.7</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-2.92</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2260</v>
+        <v>2255</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2288.3</v>
+        <v>2287.2</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2240.5</v>
+        <v>2227.2</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-0.18</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116.75</v>
+        <v>114.7</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116.75</v>
+        <v>114.73</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117.23</v>
+        <v>117.48</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>114.7</v>
+        <v>114.63</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>114.7</v>
+        <v>116.8</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-2.05</v>
+        <v>2.1</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-1.76</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8241</v>
+        <v>8143.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8258.5</v>
+        <v>8129.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8294.5</v>
+        <v>8244</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8115</v>
+        <v>8072</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8143.5</v>
+        <v>8121.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-97.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>-1.18</v>
+        <v>-22</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="148">
@@ -5763,13 +5763,13 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>269.1</v>
+        <v>262.8</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>267.15</v>
+        <v>264.1</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>268.5</v>
+        <v>266.35</v>
       </c>
       <c r="G148" s="12" t="n">
         <v>262.8</v>
@@ -5778,10 +5778,10 @@
         <v>262.8</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>-2.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1237.1</v>
+        <v>1221</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1234.9</v>
+        <v>1220</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1234.9</v>
+        <v>1264</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1206.2</v>
+        <v>1217.6</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1221</v>
+        <v>1254.6</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-16.1</v>
+        <v>33.6</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-1.3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>412.55</v>
+        <v>403.6</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>412.65</v>
+        <v>404.8</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>414.3</v>
+        <v>406.7</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>402.15</v>
+        <v>395.95</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>403.6</v>
+        <v>404</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-8.949999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>-2.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>312.7</v>
+        <v>308.5</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>313</v>
+        <v>308.7</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>314.8</v>
+        <v>315.5</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>308.5</v>
+        <v>308.7</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>308.5</v>
+        <v>312.65</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-4.2</v>
+        <v>4.15</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>-1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1252.5</v>
+        <v>1243</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1259.4</v>
+        <v>1255</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-22.2</v>
+        <v>4.7</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>-1.77</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>179.53</v>
+        <v>173.79</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>180</v>
+        <v>174.9</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>172.92</v>
+        <v>170.5</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>173</v>
+        <v>173.55</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-6</v>
+        <v>0.55</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>-3.35</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>655.2</v>
+        <v>618.6</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>652.1</v>
+        <v>619.75</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>655.75</v>
+        <v>629.3</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>617.1</v>
+        <v>612.6</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>618.6</v>
+        <v>618.1</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>-5.59</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1684.7</v>
+        <v>1654.1</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1672.1</v>
+        <v>1656.4</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1683.1</v>
+        <v>1705</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1652.9</v>
+        <v>1656.4</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1654.1</v>
+        <v>1697.9</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-30.6</v>
+        <v>43.8</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-1.82</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>995.7</v>
+        <v>968</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>994</v>
+        <v>976</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>999.8</v>
+        <v>991.4</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>968</v>
+        <v>973.2</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>968</v>
+        <v>991.4</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-27.7</v>
+        <v>23.4</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-2.78</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22570</v>
+        <v>21905</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22620</v>
+        <v>21970</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22660</v>
+        <v>22235</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>21905</v>
+        <v>21665</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>21905</v>
+        <v>21795</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-665</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-2.95</v>
+        <v>-110</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1028.6</v>
+        <v>979.8</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1044.9</v>
+        <v>979</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1044.9</v>
+        <v>990.3</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>979.8</v>
+        <v>972.6</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>979.8</v>
+        <v>979</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-48.8</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-4.74</v>
+        <v>-0.8</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3957</v>
+        <v>3770</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3957.4</v>
+        <v>3764</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3964</v>
+        <v>3799.3</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3770</v>
+        <v>3682.4</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3770</v>
+        <v>3742</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-187</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-4.73</v>
+        <v>-28</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2482.4</v>
+        <v>2455.2</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2482.4</v>
+        <v>2457.5</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2490.7</v>
+        <v>2508.5</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2450</v>
+        <v>2444.5</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2455.2</v>
+        <v>2480.1</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-27.2</v>
+        <v>24.9</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>-1.1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1854.6</v>
+        <v>1843.6</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1856.8</v>
+        <v>1857.4</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1828</v>
+        <v>1837</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1835</v>
+        <v>1853.5</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-5</v>
+        <v>18.5</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-0.27</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>476</v>
+        <v>464.25</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>476</v>
+        <v>466.5</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>461.15</v>
+        <v>460</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>464.25</v>
+        <v>462.45</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-11.75</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>-2.47</v>
+        <v>-1.8</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>382.65</v>
+        <v>378.85</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>382.95</v>
+        <v>376.1</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>383.8</v>
+        <v>382.4</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>377.25</v>
+        <v>374.2</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>378.85</v>
+        <v>380.1</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-3.8</v>
+        <v>1.25</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-0.99</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>612.45</v>
+        <v>734.9</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>734.9</v>
+        <v>715</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>734.9</v>
+        <v>788</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>734.9</v>
+        <v>691.9</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>734.9</v>
+        <v>731.8</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>122.45</v>
+        <v>-3.1</v>
       </c>
       <c r="J164" s="13" t="n">
-        <v>19.99</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1761.6</v>
+        <v>1748.2</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1767.9</v>
+        <v>1754.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1819.8</v>
+        <v>1815.9</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1742.4</v>
+        <v>1740</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1748.2</v>
+        <v>1799.3</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-13.4</v>
+        <v>51.1</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-0.76</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>991</v>
+        <v>986.1</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>990.1</v>
+        <v>990</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1009.3</v>
+        <v>1010.5</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>986</v>
+        <v>988.8</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>986.1</v>
+        <v>1000.1</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-4.9</v>
+        <v>14</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>-0.49</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>364.65</v>
+        <v>363</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>377.65</v>
+        <v>366.1</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>362.95</v>
+        <v>360.4</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>363</v>
+        <v>360.4</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-0.45</v>
+        <v>-2.6</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="E169" s="9" t="n">
+        <v>183.65</v>
+      </c>
+      <c r="F169" s="9" t="n">
+        <v>185.4</v>
+      </c>
+      <c r="G169" s="9" t="n">
+        <v>180.28</v>
+      </c>
+      <c r="H169" s="9" t="n">
         <v>183</v>
       </c>
-      <c r="E169" s="9" t="n">
-        <v>186.1</v>
-      </c>
-      <c r="F169" s="9" t="n">
-        <v>186.49</v>
-      </c>
-      <c r="G169" s="9" t="n">
-        <v>182.38</v>
-      </c>
-      <c r="H169" s="9" t="n">
-        <v>183.65</v>
-      </c>
       <c r="I169" s="9" t="n">
-        <v>0.65</v>
+        <v>-0.65</v>
       </c>
       <c r="J169" s="13" t="n">
-        <v>0.36</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2200.8</v>
+        <v>2251</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2275.5</v>
+        <v>2270</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2323</v>
+        <v>2273.9</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2251</v>
+        <v>2172</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2251</v>
+        <v>2188.8</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>50.2</v>
+        <v>-62.2</v>
       </c>
       <c r="J170" s="13" t="n">
-        <v>2.28</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1541</v>
+        <v>1575.9</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1588</v>
+        <v>1578.2</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1633.2</v>
+        <v>1589.2</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1575.9</v>
+        <v>1548</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1575.9</v>
+        <v>1558</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>34.9</v>
+        <v>-17.9</v>
       </c>
       <c r="J171" s="13" t="n">
-        <v>2.26</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2606.1</v>
+        <v>2525</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2606.1</v>
+        <v>2514</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2613.2</v>
+        <v>2609</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2521.5</v>
+        <v>2482</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2525</v>
+        <v>2566.6</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-81.09999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-3.11</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5009.5</v>
+        <v>4856</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>5003</v>
+        <v>4880</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>5003</v>
+        <v>4921.5</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4856</v>
+        <v>4845</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4856</v>
+        <v>4908.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-153.5</v>
+        <v>52.5</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-3.06</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4965.5</v>
+        <v>4850</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4931</v>
+        <v>4850</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4959.5</v>
+        <v>4870</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4837.5</v>
+        <v>4755.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4850</v>
+        <v>4812.5</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-115.5</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>-2.33</v>
+        <v>-37.5</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1297.6</v>
+        <v>1300.9</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1325</v>
+        <v>1294.2</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1326.9</v>
+        <v>1309.3</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1291.5</v>
+        <v>1267.4</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1300.9</v>
+        <v>1295.3</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>3.3</v>
+        <v>-5.6</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>0.25</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2802.4</v>
+        <v>2730</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2802.4</v>
+        <v>2735.4</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2817.6</v>
+        <v>2799.2</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2730</v>
+        <v>2723.9</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2730</v>
+        <v>2769.7</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-72.40000000000001</v>
+        <v>39.7</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-2.58</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4125</v>
+        <v>4050</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4150</v>
+        <v>4033</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4155</v>
+        <v>4078.5</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4022.1</v>
+        <v>4002</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4050</v>
+        <v>4033</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-1.82</v>
+        <v>-17</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1256.1</v>
+        <v>1241.8</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1262.3</v>
+        <v>1244.1</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1268</v>
+        <v>1251.8</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1240</v>
+        <v>1225.2</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1241.8</v>
+        <v>1227.3</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-1.14</v>
+        <v>-14.5</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11000</v>
+        <v>10697</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11045</v>
+        <v>10777</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11045</v>
+        <v>10880</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10697</v>
+        <v>10639</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-303</v>
+        <v>3</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>-2.75</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>178.1</v>
+        <v>175</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>179.57</v>
+        <v>176.54</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>179.69</v>
+        <v>179.35</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>174.74</v>
+        <v>175.07</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>175</v>
+        <v>178.2</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-1.74</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>572.95</v>
+        <v>560.8</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>573.4</v>
+        <v>560.9</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>575.95</v>
+        <v>563.55</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>558</v>
+        <v>550.6</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>560.8</v>
+        <v>550.6</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-12.15</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>-2.12</v>
+        <v>-10.2</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>263.7</v>
+        <v>257</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>263.7</v>
+        <v>256</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>264.4</v>
+        <v>257.7</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>253.55</v>
+        <v>252.5</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>-2.54</v>
+        <v>-1</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1165</v>
+        <v>1137</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1168</v>
+        <v>1137</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1179</v>
+        <v>1153</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>-2.4</v>
+        <v>-6</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>167.4</v>
+        <v>170</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>172.2</v>
+        <v>170.02</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>173.35</v>
+        <v>170.89</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>169.01</v>
+        <v>166.11</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>170</v>
+        <v>166.89</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>2.6</v>
+        <v>-3.11</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>1.55</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1119.1</v>
+        <v>1099</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1120.1</v>
+        <v>1093.7</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1124.5</v>
+        <v>1113.3</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1099</v>
+        <v>1086</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1099</v>
+        <v>1107.5</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-20.1</v>
+        <v>8.5</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>-1.8</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  15-Sep-2026 05:29 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  16-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-Sep-2026 05:29 PM</t>
+          <t>16-Sep-2026 05:28 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 16-Sep-2026 05:28 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 17-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>16-Sep-2026 05:28 PM</t>
+          <t>17-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  16-Sep-2026 05:28 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  17-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>468.7</v>
+        <v>472.85</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>470.5</v>
+        <v>469.9</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>474.45</v>
+        <v>482.95</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>459.55</v>
+        <v>469.5</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>472.85</v>
+        <v>476.6</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7005</v>
+        <v>6980</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7005</v>
+        <v>6980</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7051</v>
+        <v>7168</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6905.5</v>
+        <v>6975.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6980</v>
+        <v>7130.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>-0.36</v>
+        <v>150.5</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="5">
@@ -904,22 +904,22 @@
         <v>26125</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26195</v>
+        <v>26125</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26450</v>
+        <v>26280</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25500</v>
+        <v>25830</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26125</v>
+        <v>25910</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0</v>
+        <v>-215</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>378.8</v>
+        <v>381.3</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>378.8</v>
+        <v>382</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>384.05</v>
+        <v>391.55</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>378</v>
+        <v>381.45</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>0.66</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.02</v>
+        <v>49.74</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49.4</v>
+        <v>49.54</v>
       </c>
       <c r="F7" s="9" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="H7" s="9" t="n">
         <v>50.45</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>49.74</v>
-      </c>
       <c r="I7" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1225.2</v>
+        <v>1226.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1233</v>
+        <v>1226.8</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1235</v>
+        <v>1240.4</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1219.1</v>
+        <v>1225</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1226.6</v>
+        <v>1232.5</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2957</v>
+        <v>2930.1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2972.9</v>
+        <v>2945</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2914.3</v>
+        <v>2907</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-0.29</v>
+        <v>3.2</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1722.9</v>
+        <v>1731</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1737.9</v>
+        <v>1738.8</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1707</v>
+        <v>1725.1</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5161</v>
+        <v>5175</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5170.5</v>
+        <v>5175</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5265.5</v>
+        <v>5361</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5148</v>
+        <v>5161.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5175</v>
+        <v>5348.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>14</v>
+        <v>173.5</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.27</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>381.75</v>
+        <v>381.05</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>382</v>
+        <v>381.05</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>385.45</v>
+        <v>386.3</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>379.55</v>
+        <v>380.55</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>381.05</v>
+        <v>383.25</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>-0.18</v>
+        <v>2.2</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>297.5</v>
+        <v>293.5</v>
       </c>
       <c r="E13" s="9" t="n">
+        <v>292.9</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>297.95</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>292.15</v>
+      </c>
+      <c r="H13" s="9" t="n">
         <v>295</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>299.3</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>291.6</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>293.5</v>
-      </c>
       <c r="I13" s="9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>-1.34</v>
+        <v>1.5</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2119.3</v>
+        <v>2120</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2132.9</v>
+        <v>2170</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2041.3</v>
+        <v>2110</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2120</v>
+        <v>2148.5</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.7</v>
+        <v>28.5</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.03</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8714</v>
+        <v>8696.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8756</v>
+        <v>8707</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8792.5</v>
+        <v>8799</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8672.5</v>
+        <v>8686.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8696.5</v>
+        <v>8768.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.2</v>
+        <v>72</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>406.2</v>
+        <v>411.95</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>410.95</v>
+        <v>414.25</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>429.55</v>
+        <v>414.3</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>402.15</v>
+        <v>403.25</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>411.95</v>
+        <v>412.15</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>5.75</v>
+        <v>0.2</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1.42</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>156.65</v>
+        <v>156.5</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>157.4</v>
+        <v>156.89</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>158.21</v>
+        <v>159.64</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>154.75</v>
+        <v>156.08</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>156.5</v>
+        <v>158.62</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>-0.1</v>
+        <v>2.12</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2402.8</v>
+        <v>2416.6</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2405.1</v>
+        <v>2424</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2444.5</v>
+        <v>2454</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2397.4</v>
+        <v>2421</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2416.6</v>
+        <v>2454</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>13.8</v>
+        <v>37.4</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.57</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1379.6</v>
+        <v>1382.5</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1376</v>
+        <v>1370.1</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1388.3</v>
+        <v>1401</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1357.6</v>
+        <v>1355</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1382.5</v>
+        <v>1398.9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2.9</v>
+        <v>16.4</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>580.15</v>
+        <v>586.5</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>581</v>
+        <v>589.7</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>597.25</v>
+        <v>589.7</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>580.25</v>
+        <v>582</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>586.5</v>
+        <v>587</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>6.35</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.09</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6081.5</v>
+        <v>6076</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6000</v>
+        <v>6070</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6140.5</v>
+        <v>6156</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>5995</v>
+        <v>6045</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6076</v>
+        <v>6133.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>-0.09</v>
+        <v>57.5</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1028</v>
+        <v>1033.2</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1030</v>
+        <v>1026.2</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1038.1</v>
+        <v>1048</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1015.1</v>
+        <v>1026.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1033.2</v>
+        <v>1039.3</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1660</v>
+        <v>1643</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1657.1</v>
+        <v>1634</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1657.1</v>
+        <v>1692.3</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1623</v>
+        <v>1634</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1643</v>
+        <v>1690</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-17</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>-1.02</v>
+        <v>47</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>2.86</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1222.9</v>
+        <v>1241</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1252.5</v>
+        <v>1257.6</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1223.7</v>
+        <v>1233</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>1.48</v>
+        <v>-1</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11424</v>
+        <v>11593</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11425</v>
+        <v>11568</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11596</v>
+        <v>11576</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11379</v>
+        <v>11435</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11593</v>
+        <v>11500</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>1.48</v>
+        <v>-93</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1855.5</v>
+        <v>1837</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1864</v>
+        <v>1837</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1874.8</v>
+        <v>1863</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1832.9</v>
+        <v>1832.1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1837</v>
+        <v>1859.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>-1</v>
+        <v>22.2</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1010.5</v>
+        <v>1010</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1019.3</v>
+        <v>1027.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1006.2</v>
+        <v>1010</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1006.2</v>
+        <v>1015</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>-0.3</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2129</v>
+        <v>2124.9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2124.5</v>
+        <v>2124.9</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2140</v>
+        <v>2180</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2100.1</v>
+        <v>2120</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2124.9</v>
+        <v>2170.8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-0.19</v>
+        <v>45.9</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>677.1</v>
+        <v>682.6</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>674.9</v>
+        <v>679</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>685</v>
+        <v>687.65</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>657.3</v>
+        <v>671</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>682.6</v>
+        <v>675.7</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>-6.9</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>172.45</v>
+        <v>172.5</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>173.24</v>
+        <v>172</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>173.62</v>
+        <v>175</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>169.33</v>
+        <v>170.98</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>172.5</v>
+        <v>171.5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>0.03</v>
+        <v>-1</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>232.7</v>
+        <v>234.98</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>233.25</v>
+        <v>233.6</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>235.29</v>
+        <v>236.46</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>232.33</v>
+        <v>232.1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>234.98</v>
+        <v>232.3</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>0.98</v>
+        <v>-2.68</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>382.9</v>
+        <v>385.75</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>384.05</v>
+        <v>387</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>390.2</v>
+        <v>395.9</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>382.1</v>
+        <v>387</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>385.75</v>
+        <v>395.45</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>2.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.74</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>447.1</v>
+        <v>448.15</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>449.1</v>
+        <v>449.4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>450.7</v>
+        <v>452.35</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>444.15</v>
+        <v>443.9</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>448.15</v>
+        <v>448.6</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1.05</v>
+        <v>0.45</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1830.4</v>
+        <v>1835</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1835.8</v>
+        <v>1841.8</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1838</v>
+        <v>1845.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1818.6</v>
+        <v>1827.6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>412.85</v>
+        <v>410.6</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>415.45</v>
+        <v>411.55</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>417.4</v>
+        <v>430.75</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>406</v>
+        <v>410.8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>410.6</v>
+        <v>429.2</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>-0.54</v>
+        <v>18.6</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>4.53</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>374</v>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>382</v>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>383.5</v>
-      </c>
       <c r="G36" s="12" t="n">
-        <v>373.5</v>
+        <v>370.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>374.4</v>
+        <v>380</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>-1.99</v>
+        <v>5.6</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47070</v>
+        <v>47555</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47100</v>
+        <v>47740</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48325</v>
+        <v>48160</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>46850</v>
+        <v>47595</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47555</v>
+        <v>47735</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>485</v>
+        <v>180</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.03</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>298.65</v>
+        <v>303.35</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>301</v>
+        <v>304.55</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>298.1</v>
+        <v>303.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>303.35</v>
+        <v>307</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4947.5</v>
+        <v>4999.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4947.5</v>
+        <v>4996</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5036.5</v>
+        <v>5040</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4933</v>
+        <v>4982</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4999.5</v>
+        <v>4982</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>1.05</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>286.45</v>
+        <v>281.25</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>286.2</v>
+        <v>282.4</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>287.8</v>
+        <v>286.95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>279.3</v>
+        <v>281.65</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>281.25</v>
+        <v>283.8</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>-1.82</v>
+        <v>2.55</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>122.37</v>
+        <v>123.2</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>122.8</v>
+        <v>123.15</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>123.7</v>
+        <v>125.14</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>121.81</v>
+        <v>122.48</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>123.2</v>
+        <v>123.9</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>784.8</v>
+        <v>771.95</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>790</v>
+        <v>773.1</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>791.95</v>
+        <v>784.6</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>769</v>
+        <v>770.75</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>771.95</v>
+        <v>774.4</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>-1.64</v>
+        <v>2.45</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>416.65</v>
+        <v>409.1</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>415</v>
+        <v>407.5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>415.5</v>
+        <v>416</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>401.4</v>
+        <v>407.5</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>409.1</v>
+        <v>413.9</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-7.55</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>-1.81</v>
+        <v>4.8</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1791.6</v>
+        <v>1765.6</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1800.7</v>
+        <v>1765.5</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1800.7</v>
+        <v>1793.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1756.3</v>
+        <v>1747.6</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1765.6</v>
+        <v>1764.5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-26</v>
+        <v>-1.1</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>-1.45</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1351</v>
+        <v>1362.5</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1363.7</v>
+        <v>1385</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1344.3</v>
+        <v>1351.6</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1358</v>
+        <v>1376.3</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>7</v>
+        <v>18.3</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>419.25</v>
+        <v>422.25</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>419.25</v>
+        <v>421.1</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>423.45</v>
+        <v>422.8</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>417.6</v>
+        <v>416.55</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>422.25</v>
+        <v>418</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>0.72</v>
+        <v>-4.25</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1775.5</v>
+        <v>1766.7</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1775</v>
+        <v>1766.8</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1784.4</v>
+        <v>1797.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1717</v>
+        <v>1759.4</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1766.7</v>
+        <v>1793</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>-0.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1820.3</v>
+        <v>1860</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1833.9</v>
+        <v>1861</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1900.1</v>
+        <v>1886</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1830.1</v>
+        <v>1840</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1860</v>
+        <v>1840.3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>2.18</v>
+        <v>-19.7</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>483.7</v>
+        <v>488.8</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>491.3</v>
+        <v>494</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>480.7</v>
+        <v>485</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>488.8</v>
+        <v>488.15</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>1.05</v>
+        <v>-0.65</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1939.1</v>
+        <v>1937.8</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1939.1</v>
+        <v>1936</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1945</v>
+        <v>1947.3</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1910</v>
+        <v>1922</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1937.8</v>
+        <v>1929.8</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-1.3</v>
+        <v>-8</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>226.15</v>
+        <v>223.4</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>227.01</v>
+        <v>223.1</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>228.62</v>
+        <v>227.05</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>222.3</v>
+        <v>222.74</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>223.4</v>
+        <v>225.1</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>-1.22</v>
+        <v>1.7</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>225.78</v>
+        <v>227.24</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>216.42</v>
+        <v>227</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>227.24</v>
+        <v>231.82</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1.46</v>
+        <v>4.58</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.65</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4874</v>
+        <v>4940</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>4863.5</v>
+        <v>4940</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>4985</v>
+        <v>5043.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4844</v>
+        <v>4920</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4940</v>
+        <v>5020</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>384.9</v>
+        <v>382</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>386.85</v>
+        <v>382.4</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>389.45</v>
+        <v>386.4</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>382</v>
+        <v>381.3</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>382</v>
+        <v>384.55</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>-0.75</v>
+        <v>2.55</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1687.4</v>
+        <v>1693.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1687.8</v>
+        <v>1680.1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1704.5</v>
+        <v>1700</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1681</v>
+        <v>1676.4</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1693.6</v>
+        <v>1693.3</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>0.37</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1561.3</v>
+        <v>1590.5</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1562.8</v>
+        <v>1595</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1598</v>
+        <v>1611.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1546.2</v>
+        <v>1589.9</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1590.5</v>
+        <v>1604.8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>29.2</v>
+        <v>14.3</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>1.87</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>53.79</v>
+        <v>55.19</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>53.8</v>
+        <v>55.56</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>51.66</v>
+        <v>54.26</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>55.19</v>
+        <v>56.15</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2.6</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9198</v>
+        <v>9158</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9168</v>
+        <v>9158</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9180</v>
+        <v>9371</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>8923</v>
+        <v>9135.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9158</v>
+        <v>9323</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-40</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>-0.43</v>
+        <v>165</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13180</v>
+        <v>13181</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>12985</v>
+        <v>13200</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13260</v>
+        <v>13495</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>12850</v>
+        <v>13176</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13181</v>
+        <v>13290</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.01</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>620.85</v>
+        <v>622.8</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>620.85</v>
+        <v>623.05</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>628.3</v>
+        <v>644.55</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>611.5</v>
+        <v>622</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>622.8</v>
+        <v>640</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>1.95</v>
+        <v>17.2</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.31</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1149.9</v>
+        <v>1189.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1133.9</v>
+        <v>1140</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>-0.44</v>
+        <v>35</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>3.07</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7452.5</v>
+        <v>7500</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7430</v>
+        <v>7495</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7524.5</v>
+        <v>7552.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7406</v>
+        <v>7489</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7500</v>
+        <v>7493.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>0.64</v>
+        <v>-6.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2835.8</v>
+        <v>2815.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2840</v>
+        <v>2815.6</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2864.9</v>
+        <v>2843.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2791.1</v>
+        <v>2809</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2815.6</v>
+        <v>2830</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-20.2</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>-0.71</v>
+        <v>14.4</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>409.2</v>
+        <v>415.5</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>407.8</v>
+        <v>415.35</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>419.65</v>
+        <v>421.95</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>407.8</v>
+        <v>411</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>415.5</v>
+        <v>418.6</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>1.54</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>343</v>
+        <v>341.8</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>341.8</v>
+        <v>342</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>346</v>
+        <v>343.75</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>340.1</v>
+        <v>332.45</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>341.8</v>
+        <v>332.75</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1.2</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>-0.35</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>170.88</v>
+        <v>170.65</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>170.88</v>
+        <v>171.24</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>171.88</v>
+        <v>172.82</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>168.72</v>
+        <v>171.24</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>170.65</v>
+        <v>172</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>-0.13</v>
+        <v>1.35</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2371.7</v>
+        <v>2410</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2371.7</v>
+        <v>2406.8</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2425.8</v>
+        <v>2416.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2306.3</v>
+        <v>2388.4</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2410</v>
+        <v>2416</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>38.3</v>
+        <v>6</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>1.61</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>540.6</v>
+        <v>539.75</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>540.6</v>
+        <v>540</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>545.6</v>
+        <v>599</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>528.8</v>
+        <v>538.2</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>539.75</v>
+        <v>584.85</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>-0.16</v>
+        <v>45.1</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>856</v>
+        <v>866.45</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>876.85</v>
+        <v>876</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>856</v>
+        <v>865.15</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.7</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1659.3</v>
+        <v>1665.3</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1666.9</v>
+        <v>1664</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1703.7</v>
+        <v>1695.3</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1647.6</v>
+        <v>1657.7</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1665.3</v>
+        <v>1678.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>6</v>
+        <v>12.9</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.36</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>872.6</v>
+        <v>835.6</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>869</v>
+        <v>841</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>829</v>
+        <v>838.2</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>835.6</v>
+        <v>870.4</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-37</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>-4.24</v>
+        <v>34.8</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>4.16</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="E73" s="9" t="n">
         <v>3190</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3201.8</v>
+        <v>3205</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3159.1</v>
+        <v>3159</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>0.5</v>
+        <v>-13.9</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4695</v>
+        <v>4695.6</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4690</v>
+        <v>4699</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4709.6</v>
+        <v>4799</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4615.8</v>
+        <v>4687</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4695.6</v>
+        <v>4788</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.01</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1087</v>
+        <v>1089.9</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1093</v>
+        <v>1089.9</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1106.9</v>
+        <v>1095.6</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1084.8</v>
+        <v>1083.5</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1089.9</v>
+        <v>1092</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1253.7</v>
+        <v>1253</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1262.5</v>
+        <v>1242.2</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1284.6</v>
+        <v>1258.3</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1244.9</v>
+        <v>1235.3</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1253</v>
+        <v>1258.3</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.06</v>
+        <v>5.3</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2409</v>
+        <v>2373.1</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2383.1</v>
+        <v>2378.1</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2408.5</v>
+        <v>2415</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2360</v>
+        <v>2378.1</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2373.1</v>
+        <v>2387.7</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-35.9</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>-1.49</v>
+        <v>14.6</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>716.55</v>
+        <v>721.5</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>714.9</v>
+        <v>717.5</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>725.4</v>
+        <v>719.4</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>710.85</v>
+        <v>713</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>721.5</v>
+        <v>713</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>-8.5</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>522</v>
+        <v>532.9</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>534</v>
+        <v>560.95</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>517</v>
+        <v>529.95</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>14.1</v>
+        <v>26.8</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>2.73</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5166</v>
+        <v>5235</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5200</v>
+        <v>5253.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5315</v>
+        <v>5341</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5186.5</v>
+        <v>5243.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5235</v>
+        <v>5325</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>956.4</v>
+        <v>972</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>978.5</v>
+        <v>987.2</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>956.4</v>
+        <v>970.5</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>1.46</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>490.24</v>
+        <v>481.6</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>496.7</v>
+        <v>489.3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>477.5</v>
+        <v>480.7</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>481.6</v>
+        <v>485.5</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>-1.76</v>
+        <v>3.9</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>345.3</v>
+        <v>350.05</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>347</v>
+        <v>352.25</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>352.25</v>
+        <v>353.65</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>343.05</v>
+        <v>350.35</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>350.05</v>
+        <v>350.6</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>4.75</v>
+        <v>0.55</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>1.38</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1938.1</v>
+        <v>1962</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1944.1</v>
+        <v>1962</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1977</v>
+        <v>1968.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1943.5</v>
+        <v>1942.2</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1962</v>
+        <v>1942.2</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>1.23</v>
+        <v>-19.8</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>33595</v>
+        <v>33895</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>33600</v>
+        <v>33730</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34170</v>
+        <v>34140</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33510</v>
+        <v>33730</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33895</v>
+        <v>33915</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.89</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>84.8</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>84.61</v>
+        <v>84.75</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>84.61</v>
+        <v>84.53</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>85.01000000000001</v>
+        <v>86.33</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.21</v>
+        <v>1.32</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.25</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="88">
@@ -3726,22 +3726,22 @@
         <v>112</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>112</v>
+        <v>111.82</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>112.41</v>
+        <v>113.85</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>110.35</v>
+        <v>111.61</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>112</v>
+        <v>113.4</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>150.03</v>
+        <v>148.77</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>150</v>
+        <v>148.66</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>150.39</v>
+        <v>149.67</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>147.27</v>
+        <v>147.9</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>148.77</v>
+        <v>148.67</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.26</v>
+        <v>-0.1</v>
       </c>
       <c r="J89" s="13" t="n">
-        <v>-0.84</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>715</v>
+        <v>713.4</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>716.25</v>
+        <v>713.4</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>719.55</v>
+        <v>729.8</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>706.75</v>
+        <v>712.55</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>713.4</v>
+        <v>726.65</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>-0.22</v>
+        <v>13.25</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1659.5</v>
+        <v>1706.3</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1662</v>
+        <v>1707.9</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1768.8</v>
+        <v>1718.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1645.2</v>
+        <v>1652</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1706.3</v>
+        <v>1662.7</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>2.82</v>
+        <v>-43.6</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4776</v>
+        <v>4733.5</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4799.5</v>
+        <v>4746.5</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4806</v>
+        <v>4855.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4701.5</v>
+        <v>4746.5</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4733.5</v>
+        <v>4845</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>-0.89</v>
+        <v>111.5</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>956.5</v>
+        <v>946.5</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>957.7</v>
+        <v>946</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>961.1</v>
+        <v>970.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>944.5</v>
+        <v>945.2</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>946.5</v>
+        <v>958.2</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-1.05</v>
+        <v>11.7</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>379</v>
+        <v>375.6</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>381</v>
+        <v>377.1</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>381.5</v>
+        <v>384.75</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>375.2</v>
+        <v>377.1</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>375.6</v>
+        <v>381.35</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>-0.9</v>
+        <v>5.75</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1082.5</v>
+        <v>1054.9</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1085.1</v>
+        <v>1063.6</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1053.5</v>
+        <v>1048.6</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1060</v>
+        <v>1058.6</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-17</v>
+        <v>-1.4</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>-1.58</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>132.03</v>
+        <v>134.75</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>132.79</v>
+        <v>134.9</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>134.97</v>
+        <v>135.33</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>131.7</v>
+        <v>134</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>134.75</v>
+        <v>134.27</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>2.06</v>
+        <v>-0.48</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1932.4</v>
+        <v>1950.7</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1963.3</v>
+        <v>1940</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1905</v>
+        <v>1937.9</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1950.7</v>
+        <v>1970.3</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>458.55</v>
+        <v>452.95</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>457.2</v>
+        <v>454</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>458</v>
+        <v>458.4</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>446.5</v>
+        <v>452.15</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>452.95</v>
+        <v>457</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-1.22</v>
+        <v>4.05</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>258</v>
+        <v>264.15</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>259.4</v>
+        <v>264.8</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>264.9</v>
+        <v>268.5</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>259.3</v>
+        <v>264.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>264.15</v>
+        <v>266.2</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>6.15</v>
+        <v>2.05</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>2.38</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1088</v>
+        <v>1104.1</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1117</v>
+        <v>1134.6</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1085.4</v>
+        <v>1104.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1103</v>
+        <v>1128.4</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>8</v>
+        <v>25.4</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.73</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4712</v>
+        <v>4750</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>4716</v>
+        <v>4780</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>4872</v>
+        <v>5055</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4676</v>
+        <v>4745.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>4750</v>
+        <v>5027</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>38</v>
+        <v>277</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>723.55</v>
+        <v>730.85</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>723.55</v>
+        <v>730</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>738.8</v>
+        <v>742.7</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>715</v>
+        <v>721.85</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>730.85</v>
+        <v>724.45</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>1.01</v>
+        <v>-6.4</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
+        <v>504.7</v>
+      </c>
+      <c r="E103" s="9" t="n">
         <v>505</v>
       </c>
-      <c r="E103" s="9" t="n">
-        <v>506.6</v>
-      </c>
       <c r="F103" s="9" t="n">
-        <v>510.95</v>
+        <v>514</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>503.05</v>
+        <v>504.6</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>504.7</v>
+        <v>512</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>-0.06</v>
+        <v>7.3</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1229.2</v>
+        <v>1248.9</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1244</v>
+        <v>1248.9</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1250.2</v>
+        <v>1260</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1227</v>
+        <v>1242.1</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1248.9</v>
+        <v>1253.4</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>19.7</v>
+        <v>4.5</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>1.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>466</v>
+        <v>469.95</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>472</v>
+        <v>486.75</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>461.65</v>
+        <v>467.35</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>471</v>
+        <v>480.2</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1213.6</v>
+        <v>1215.9</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1213.6</v>
+        <v>1215</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1219.5</v>
+        <v>1224.4</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1179.1</v>
+        <v>1210</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1215.9</v>
+        <v>1217.2</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>409.8</v>
+        <v>415</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>413.6</v>
+        <v>415</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>417.05</v>
+        <v>417.6</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>409.35</v>
+        <v>412.5</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>415</v>
+        <v>416.5</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>1.27</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>563</v>
+        <v>556.2</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>566.4</v>
+        <v>560.95</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>553.1</v>
+        <v>552.5</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>555</v>
+        <v>559.3</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-1.42</v>
+        <v>4.3</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1906.4</v>
+        <v>1895.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1921</v>
+        <v>1890.6</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>2038.6</v>
+        <v>1941.1</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1870</v>
+        <v>1888</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1895.7</v>
+        <v>1924.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>29</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1926.9</v>
+        <v>1905.5</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1924.6</v>
+        <v>1898</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1940.4</v>
+        <v>1964.5</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1863.5</v>
+        <v>1894.8</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1905.5</v>
+        <v>1948.1</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>-1.11</v>
+        <v>42.6</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>2.24</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>541.8</v>
+        <v>542.05</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>551.45</v>
+        <v>554.55</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>529.6</v>
+        <v>541.05</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>543</v>
+        <v>545.9</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3850.7</v>
+        <v>3807.7</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3844.2</v>
+        <v>3811</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3867.9</v>
+        <v>3875</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3799.9</v>
+        <v>3811</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3807.7</v>
+        <v>3836.2</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-43</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>-1.12</v>
+        <v>28.5</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>296.8</v>
+        <v>295.5</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>296.9</v>
+        <v>295.3</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>300.95</v>
+        <v>304.05</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>293.8</v>
+        <v>293.5</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>295.5</v>
+        <v>302.3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>-0.44</v>
+        <v>6.8</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3312.2</v>
+        <v>3351.5</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3340</v>
+        <v>3351.5</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3366</v>
+        <v>3377</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3293</v>
+        <v>3307.3</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3351.5</v>
+        <v>3324.3</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>1.19</v>
+        <v>-27.2</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2063.2</v>
+        <v>2045</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2056.4</v>
+        <v>2052.6</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2074.1</v>
+        <v>2098.1</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2033.5</v>
+        <v>2046.3</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2045</v>
+        <v>2098.1</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-0.88</v>
+        <v>53.1</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3029.5</v>
+        <v>3070</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3044.6</v>
+        <v>3047</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3105.9</v>
+        <v>3127.8</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3044.6</v>
+        <v>3047</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3070</v>
+        <v>3076.5</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>40.5</v>
+        <v>6.5</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>1.34</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E118" s="12" t="n">
         <v>318.85</v>
       </c>
-      <c r="E118" s="12" t="n">
-        <v>321.25</v>
-      </c>
       <c r="F118" s="12" t="n">
-        <v>324.7</v>
+        <v>322.15</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>317.25</v>
+        <v>315</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>319.9</v>
+        <v>316.05</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>0.33</v>
+        <v>-3.85</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>791.25</v>
+        <v>810.15</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>795.5</v>
+        <v>810.15</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>819.9</v>
+        <v>826.3</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>792.15</v>
+        <v>810.15</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>810.15</v>
+        <v>817</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>18.9</v>
+        <v>6.85</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>2.39</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12231</v>
+        <v>12166</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12231</v>
+        <v>12165</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12367</v>
+        <v>12409</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12159</v>
+        <v>12127</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12166</v>
+        <v>12338</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-65</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-0.53</v>
+        <v>172</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3173.5</v>
+        <v>3211.2</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3170.2</v>
+        <v>3201.1</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3224.5</v>
+        <v>3304</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3056.6</v>
+        <v>3180.1</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3211.2</v>
+        <v>3265.2</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>37.7</v>
+        <v>54</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>1.19</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>572.5</v>
+        <v>580.85</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>571</v>
+        <v>580.55</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>585</v>
+        <v>590.1</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>557.8</v>
+        <v>577.55</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>580.85</v>
+        <v>586.3</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>8.35</v>
+        <v>5.45</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>1.46</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1425.9</v>
+        <v>1487.6</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1425.9</v>
+        <v>1480.1</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1491.7</v>
+        <v>1569.5</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1423.6</v>
+        <v>1473.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1487.6</v>
+        <v>1554</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>61.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1071.7</v>
+        <v>1080.1</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1071</v>
+        <v>1073.8</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1084.5</v>
+        <v>1079.9</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1047</v>
+        <v>1065</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1080.1</v>
+        <v>1071.2</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>0.78</v>
+        <v>-8.9</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>158.15</v>
+        <v>158.27</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>157.19</v>
+        <v>159.02</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>160.4</v>
+        <v>162.84</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>156.4</v>
+        <v>158.66</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>158.27</v>
+        <v>161.87</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>0.12</v>
+        <v>3.6</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.08</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2378</v>
+        <v>2316.7</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2379</v>
+        <v>2304</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2393.9</v>
+        <v>2325.1</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2316.7</v>
+        <v>2288</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2316.7</v>
+        <v>2320</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-61.3</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-2.58</v>
+        <v>3.3</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>125795</v>
+        <v>125010</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>125880</v>
+        <v>125100</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>127700</v>
+        <v>125850</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124615</v>
+        <v>124300</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>125010</v>
+        <v>124585</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-785</v>
+        <v>-425</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v>-0.62</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2722.3</v>
+        <v>2771.4</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2726</v>
+        <v>2761</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2804.6</v>
+        <v>2790</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2725.2</v>
+        <v>2740</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2771.4</v>
+        <v>2770.2</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>1.8</v>
+        <v>-1.2</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>350.55</v>
+        <v>356</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>357.75</v>
+        <v>360.75</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>350.1</v>
+        <v>354.2</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>356</v>
+        <v>355.7</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>1.55</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1261.5</v>
+        <v>1256</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1258.5</v>
+        <v>1247</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1274.3</v>
+        <v>1283.1</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1250.9</v>
+        <v>1242.8</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>-0.44</v>
+        <v>9</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8228</v>
+        <v>8160.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8212</v>
+        <v>8120</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8295</v>
+        <v>8325</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8100</v>
+        <v>8120</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8160.5</v>
+        <v>8220</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-67.5</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>-0.82</v>
+        <v>59.5</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1362</v>
+        <v>1384.5</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1369.2</v>
+        <v>1384.5</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1397</v>
+        <v>1391.7</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1368.7</v>
+        <v>1370.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1384.5</v>
+        <v>1370.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>1.65</v>
+        <v>-13.9</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>80.5</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="E134" s="12" t="n">
+        <v>80.41</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H134" s="12" t="n">
         <v>80.8</v>
       </c>
-      <c r="F134" s="12" t="n">
-        <v>81.09</v>
-      </c>
-      <c r="G134" s="12" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="H134" s="12" t="n">
-        <v>80.31999999999999</v>
-      </c>
       <c r="I134" s="12" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>-0.22</v>
+        <v>0.48</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>329.5</v>
+        <v>327</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>329.5</v>
+        <v>327.8</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>329.95</v>
+        <v>331.3</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>326.55</v>
+        <v>327.2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>327</v>
+        <v>329.6</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>-0.76</v>
+        <v>2.6</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1668.5</v>
+        <v>1706.9</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1660</v>
+        <v>1705.1</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1717.3</v>
+        <v>1741.9</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1660</v>
+        <v>1695.8</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1706.9</v>
+        <v>1740.7</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>38.4</v>
+        <v>33.8</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11803</v>
+        <v>11510</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11840</v>
+        <v>11500</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11920</v>
+        <v>11666</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11399</v>
+        <v>11356</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11510</v>
+        <v>11620</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-293</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>-2.48</v>
+        <v>110</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>235.95</v>
+        <v>236.8</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>236.45</v>
+        <v>235.1</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>236.8</v>
+        <v>235.65</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>233.31</v>
+        <v>231.25</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>236.8</v>
+        <v>232.43</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>0.36</v>
+        <v>-4.37</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>34580</v>
+        <v>34275</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>34600</v>
+        <v>34300</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35035</v>
+        <v>35290</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34000</v>
+        <v>34300</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>34275</v>
+        <v>35020</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-305</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>-0.88</v>
+        <v>745</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>2.17</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5477.5</v>
+        <v>5440</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5522</v>
+        <v>5410</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5529.5</v>
+        <v>5502</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5390.5</v>
+        <v>5405.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5440</v>
+        <v>5473</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-37.5</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>-0.68</v>
+        <v>33</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>283.95</v>
+        <v>282.1</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>281.6</v>
+        <v>282.05</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>284.95</v>
+        <v>285</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>278.25</v>
+        <v>281.7</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>282.1</v>
+        <v>283.45</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>-0.65</v>
+        <v>1.35</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>344</v>
+        <v>346.1</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>349.1</v>
+        <v>348.5</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>343.65</v>
+        <v>344.75</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>346</v>
+        <v>344.95</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>0.58</v>
+        <v>-1.05</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1521.1</v>
+        <v>1543.8</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1521.2</v>
+        <v>1543</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1546.9</v>
+        <v>1561.1</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1521.2</v>
+        <v>1535</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1543.8</v>
+        <v>1551.5</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>22.7</v>
+        <v>7.7</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>1.49</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2255</v>
+        <v>2260</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2287.2</v>
+        <v>2317</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2227.2</v>
+        <v>2259</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2256</v>
+        <v>2307</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.04</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>114.7</v>
+        <v>116.8</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>114.73</v>
+        <v>116.8</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117.48</v>
+        <v>119.4</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>114.63</v>
+        <v>116.36</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116.8</v>
+        <v>116.47</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>1.83</v>
+        <v>-0.33</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8143.5</v>
+        <v>8121.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8129.5</v>
+        <v>8130</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8244</v>
+        <v>8266</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8072</v>
+        <v>8112.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8121.5</v>
+        <v>8208.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>-0.27</v>
+        <v>87</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="148">
@@ -5766,22 +5766,22 @@
         <v>262.8</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>266.35</v>
+        <v>265.7</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>262.8</v>
+        <v>263.25</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>262.8</v>
+        <v>263.75</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1221</v>
+        <v>1254.6</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1220</v>
+        <v>1248.5</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1264</v>
+        <v>1282</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1217.6</v>
+        <v>1231.2</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1254.6</v>
+        <v>1272.7</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>33.6</v>
+        <v>18.1</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>403.6</v>
+        <v>404</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>404.8</v>
+        <v>403</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>406.7</v>
+        <v>411.65</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>395.95</v>
+        <v>401.95</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>404</v>
+        <v>404.15</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>308.5</v>
+        <v>312.65</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>308.7</v>
+        <v>314</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>315.5</v>
+        <v>315.05</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>308.7</v>
+        <v>310.5</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>312.65</v>
+        <v>310.5</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>1.35</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1243</v>
+        <v>1244.8</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1255</v>
+        <v>1253.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1240</v>
+        <v>1238.5</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
+        <v>173.55</v>
+      </c>
+      <c r="E153" s="9" t="n">
         <v>173</v>
       </c>
-      <c r="E153" s="9" t="n">
-        <v>173.79</v>
-      </c>
       <c r="F153" s="9" t="n">
-        <v>174.9</v>
+        <v>176.25</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>170.5</v>
+        <v>173</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>173.55</v>
+        <v>175.01</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>0.55</v>
+        <v>1.46</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.32</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>618.6</v>
+        <v>618.1</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>619.75</v>
+        <v>616</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>629.3</v>
+        <v>641.55</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>612.6</v>
+        <v>616</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>618.1</v>
+        <v>636.95</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-0.08</v>
+        <v>18.85</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>3.05</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1654.1</v>
+        <v>1697.9</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1656.4</v>
+        <v>1693</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1705</v>
+        <v>1771.1</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1656.4</v>
+        <v>1689</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1697.9</v>
+        <v>1766.9</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>43.8</v>
+        <v>69</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>2.65</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>968</v>
+        <v>991.4</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>976</v>
+        <v>991.2</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>991.4</v>
+        <v>1000.9</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>973.2</v>
+        <v>985.2</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>991.4</v>
+        <v>988.7</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>2.42</v>
+        <v>-2.7</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>21905</v>
+        <v>21795</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>21970</v>
+        <v>21760</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22235</v>
+        <v>22080</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>21665</v>
+        <v>21685</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>21795</v>
+        <v>21960</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-110</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-0.5</v>
+        <v>165</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>979.8</v>
+        <v>979</v>
       </c>
       <c r="E158" s="12" t="n">
         <v>979</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>990.3</v>
+        <v>1005.5</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>972.6</v>
+        <v>978.3</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>-0.08</v>
+        <v>16</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3770</v>
+        <v>3742</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3764</v>
+        <v>3743.1</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3799.3</v>
+        <v>3817.4</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3682.4</v>
+        <v>3742</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3742</v>
+        <v>3763.5</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>-0.74</v>
+        <v>21.5</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2455.2</v>
+        <v>2480.1</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2457.5</v>
+        <v>2505</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2508.5</v>
+        <v>2554</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2444.5</v>
+        <v>2501</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2480.1</v>
+        <v>2536</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>24.9</v>
+        <v>55.9</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>1.01</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1835</v>
+        <v>1853.5</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1843.6</v>
+        <v>1853.5</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1857.4</v>
+        <v>1867.3</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1837</v>
+        <v>1847.4</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1853.5</v>
+        <v>1867.3</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>18.5</v>
+        <v>13.8</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.01</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>464.25</v>
+        <v>462.45</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>466.5</v>
+        <v>463.95</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>460</v>
+        <v>459.15</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>462.45</v>
+        <v>468.4</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>-0.39</v>
+        <v>5.95</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>378.85</v>
+        <v>380.1</v>
       </c>
       <c r="E163" s="9" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="F163" s="9" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="G163" s="9" t="n">
         <v>376.1</v>
       </c>
-      <c r="F163" s="9" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="G163" s="9" t="n">
-        <v>374.2</v>
-      </c>
       <c r="H163" s="9" t="n">
-        <v>380.1</v>
+        <v>380.2</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>1.25</v>
+        <v>0.1</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.33</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>734.9</v>
+        <v>731.8</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>691.9</v>
+        <v>724.75</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>731.8</v>
+        <v>779.3</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-0.42</v>
+        <v>47.5</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>6.49</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1748.2</v>
+        <v>1799.3</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1754.9</v>
+        <v>1810</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1815.9</v>
+        <v>1831.5</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1740</v>
+        <v>1771.2</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1799.3</v>
+        <v>1791.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>2.92</v>
+        <v>-7.7</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>986.1</v>
+        <v>1000.1</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>990</v>
+        <v>1003.1</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1010.5</v>
+        <v>1020.3</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>988.8</v>
+        <v>999</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1000.1</v>
+        <v>1013.7</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>363</v>
+        <v>360.4</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>363</v>
+        <v>360.4</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>366.1</v>
+        <v>370.4</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>360.4</v>
+        <v>360.2</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>360.4</v>
+        <v>369</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>-0.72</v>
+        <v>8.6</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>183.65</v>
+        <v>183</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>183.65</v>
+        <v>183</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>185.4</v>
+        <v>189.49</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>180.28</v>
+        <v>182.87</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>183</v>
+        <v>187.29</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>-0.35</v>
+        <v>4.29</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>2.34</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2251</v>
+        <v>2188.8</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2270</v>
+        <v>2171</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2273.9</v>
+        <v>2263.6</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2172</v>
+        <v>2162.5</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-62.2</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-2.76</v>
+        <v>1.2</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1575.9</v>
+        <v>1558</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1578.2</v>
+        <v>1545.1</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1589.2</v>
+        <v>1569.7</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-17.9</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>-1.14</v>
+        <v>3</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2525</v>
+        <v>2566.6</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2514</v>
+        <v>2566</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2609</v>
+        <v>2626.6</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2482</v>
+        <v>2560.4</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2566.6</v>
+        <v>2598.8</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>41.6</v>
+        <v>32.2</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4856</v>
+        <v>4908.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4880</v>
+        <v>4895</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4921.5</v>
+        <v>4915.5</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4845</v>
+        <v>4838.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>1.08</v>
+        <v>-67.5</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4850</v>
+        <v>4812.5</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4850</v>
+        <v>4810</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4870</v>
+        <v>4899</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4755.5</v>
+        <v>4794.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4812.5</v>
+        <v>4875</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-37.5</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>-0.77</v>
+        <v>62.5</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1300.9</v>
+        <v>1295.3</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1294.2</v>
+        <v>1300</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1309.3</v>
+        <v>1310.6</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1267.4</v>
+        <v>1271</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1295.3</v>
+        <v>1276.4</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-5.6</v>
+        <v>-18.9</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-0.43</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2730</v>
+        <v>2769.7</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2735.4</v>
+        <v>2760</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2799.2</v>
+        <v>2811</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2723.9</v>
+        <v>2760</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>39.7</v>
+        <v>19.3</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
+        <v>4033</v>
+      </c>
+      <c r="E177" s="9" t="n">
         <v>4050</v>
       </c>
-      <c r="E177" s="9" t="n">
-        <v>4033</v>
-      </c>
       <c r="F177" s="9" t="n">
-        <v>4078.5</v>
+        <v>4162.2</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4002</v>
+        <v>4050</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4033</v>
+        <v>4101.7</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-17</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-0.42</v>
+        <v>68.7</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1241.8</v>
+        <v>1227.3</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1244.1</v>
+        <v>1228</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1251.8</v>
+        <v>1239.5</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1225.2</v>
+        <v>1213.5</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1227.3</v>
+        <v>1216.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-14.5</v>
+        <v>-10.5</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-1.17</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10777</v>
+        <v>10740</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>10880</v>
+        <v>10841</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10639</v>
+        <v>10703</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>175</v>
+        <v>178.2</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>176.54</v>
+        <v>177</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>179.35</v>
+        <v>180.62</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>175.07</v>
+        <v>175.83</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>178.2</v>
+        <v>178.09</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>1.83</v>
+        <v>-0.11</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>560.8</v>
+        <v>550.6</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>560.9</v>
+        <v>551</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>563.55</v>
+        <v>558</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>550.6</v>
+        <v>549.8</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>550.6</v>
+        <v>554.75</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>-1.82</v>
+        <v>4.15</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F182" s="12" t="n">
         <v>257.7</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>252.5</v>
+        <v>253.95</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>256</v>
+        <v>257.45</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>-0.39</v>
+        <v>1.45</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1137</v>
+        <v>1131.1</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1153</v>
+        <v>1141.2</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1131</v>
+        <v>1125.1</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>-0.53</v>
+        <v>4</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>170</v>
+        <v>166.89</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>170.02</v>
+        <v>165.75</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>170.89</v>
+        <v>167.6</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>166.11</v>
+        <v>165.02</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>166.89</v>
+        <v>166.4</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-3.11</v>
+        <v>-0.49</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-1.83</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1099</v>
+        <v>1107.5</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1093.7</v>
+        <v>1103.5</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1113.3</v>
+        <v>1139.9</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1086</v>
+        <v>1100.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1107.5</v>
+        <v>1135.1</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>8.5</v>
+        <v>27.6</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>0.77</v>
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  16-Sep-2026 05:28 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  17-Sep-2026 05:28 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16-Sep-2026 05:28 PM</t>
+          <t>17-Sep-2026 05:28 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 17-Sep-2026 05:28 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 18-Sep-2026 04:57 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>17-Sep-2026 05:28 PM</t>
+          <t>18-Sep-2026 04:57 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  17-Sep-2026 05:28 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  18-Sep-2026 04:57 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>472.85</v>
+        <v>476.6</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>469.9</v>
+        <v>476.65</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>482.95</v>
+        <v>493.45</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>469.5</v>
+        <v>476.25</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>476.6</v>
+        <v>491.15</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>3.75</v>
+        <v>14.55</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.79</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>6980</v>
+        <v/>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6980</v>
+        <v>7185.5</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7168</v>
+        <v>7307</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6975.5</v>
+        <v>7151</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7130.5</v>
+        <v>7270.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>2.16</v>
+        <v/>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26125</v>
+        <v/>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26125</v>
+        <v>26035</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26280</v>
+        <v>27490</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25830</v>
+        <v>26035</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25910</v>
+        <v>27270</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-215</v>
+        <v/>
       </c>
       <c r="J5" s="13" t="n">
-        <v>-0.82</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>382</v>
+        <v>390.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>391.55</v>
+        <v>410.05</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>381.45</v>
+        <v>390.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>20.05</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>2.28</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.74</v>
+        <v>50.45</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49.54</v>
+        <v>50.6</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.63</v>
+        <v>50.77</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>49.41</v>
+        <v>49.8</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>50.45</v>
+        <v>50.16</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>1.43</v>
+        <v>-0.29</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1226.6</v>
+        <v>1232.5</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1226.8</v>
+        <v>1236.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1240.4</v>
+        <v>1279.9</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1225</v>
+        <v>1236.6</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1232.5</v>
+        <v>1259.7</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>5.9</v>
+        <v>27.2</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.48</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2930.1</v>
+        <v>2933</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2945</v>
+        <v>3020</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2907</v>
+        <v>2924.6</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>3.2</v>
+        <v>96.8</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.11</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1731</v>
+        <v>1748</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1738.8</v>
+        <v>1824</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1725.1</v>
+        <v>1744</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>14.5</v>
+        <v>85.7</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.84</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5175</v>
+        <v>5348.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5175</v>
+        <v>5378.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5361</v>
+        <v>5466.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5161.5</v>
+        <v>5310.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5348.5</v>
+        <v>5466.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>173.5</v>
+        <v>118</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>3.35</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>381.05</v>
+        <v>383.25</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>381.05</v>
+        <v>384.55</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>386.3</v>
+        <v>396</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>380.55</v>
+        <v>383.9</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>383.25</v>
+        <v>388.3</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>2.2</v>
+        <v>5.05</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.58</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>293.5</v>
+        <v/>
       </c>
       <c r="E13" s="9" t="n">
-        <v>292.9</v>
+        <v>295</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>297.95</v>
+        <v>301.75</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>292.15</v>
+        <v>295</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>295</v>
+        <v>299.1</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.51</v>
+        <v/>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2120</v>
+        <v/>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2110</v>
+        <v>2154.9</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2170</v>
+        <v>2270.1</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2110</v>
+        <v>2146.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2148.5</v>
+        <v>2270.1</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>1.34</v>
+        <v/>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8696.5</v>
+        <v>8768.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8707</v>
+        <v>8800</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8799</v>
+        <v>8944.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8686.5</v>
+        <v>8798</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8768.5</v>
+        <v>8944.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.83</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>411.95</v>
+        <v>412.15</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>414.25</v>
+        <v>414.75</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>414.3</v>
+        <v>418.75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>403.25</v>
+        <v>407.9</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>412.15</v>
+        <v>409.3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>0.05</v>
+        <v>-2.85</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>156.5</v>
+        <v>158.62</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>156.89</v>
+        <v>159.1</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>159.64</v>
+        <v>163.12</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>156.08</v>
+        <v>158.51</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>158.62</v>
+        <v>163</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2.12</v>
+        <v>4.38</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>1.35</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2416.6</v>
+        <v>2454</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2424</v>
+        <v>2455.7</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2454</v>
+        <v>2474</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2421</v>
+        <v>2438</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2454</v>
+        <v>2451.3</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>1.55</v>
+        <v>-2.7</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1382.5</v>
+        <v>1398.9</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1370.1</v>
+        <v>1400</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1401</v>
+        <v>1427.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1355</v>
+        <v>1397.5</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1398.9</v>
+        <v>1427.7</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>16.4</v>
+        <v>28.8</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>586.5</v>
+        <v/>
       </c>
       <c r="E20" s="12" t="n">
-        <v>589.7</v>
+        <v>587.4</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>589.7</v>
+        <v>674.8</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>582</v>
+        <v>587.4</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>587</v>
+        <v>660.7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>0.09</v>
+        <v/>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6076</v>
+        <v/>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6070</v>
+        <v>6133.5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6156</v>
+        <v>6201</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6045</v>
+        <v>6110.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6133.5</v>
+        <v>6170.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>0.95</v>
+        <v/>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1033.2</v>
+        <v/>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1026.2</v>
+        <v>1040.5</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1048</v>
+        <v>1058.6</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1026.2</v>
+        <v>1033.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1039.3</v>
+        <v>1058.6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>0.59</v>
+        <v/>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1643</v>
+        <v/>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1634</v>
+        <v>1683.2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1692.3</v>
+        <v>1734</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1634</v>
+        <v>1676.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1690</v>
+        <v>1734</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>2.86</v>
+        <v/>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1257.6</v>
+        <v>1257</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1233</v>
+        <v>1240.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>-0.08</v>
+        <v>17</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11593</v>
+        <v/>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11568</v>
+        <v>11501</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11576</v>
+        <v>11540</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11435</v>
+        <v>11406</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11500</v>
+        <v>11414</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-93</v>
+        <v/>
       </c>
       <c r="J25" s="13" t="n">
-        <v>-0.8</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1837</v>
+        <v/>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1837</v>
+        <v>1857.2</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1863</v>
+        <v>1872.6</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1832.1</v>
+        <v>1852.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1859.2</v>
+        <v>1852.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>1.21</v>
+        <v/>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1006.2</v>
+        <v/>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1010</v>
+        <v>1025.9</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1027.9</v>
+        <v>1040.3</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1010</v>
+        <v>1019.1</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1015</v>
+        <v>1040.3</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>0.87</v>
+        <v/>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2124.9</v>
+        <v/>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2124.9</v>
+        <v>2170.7</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2180</v>
+        <v>2296</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2120</v>
+        <v>2166</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2170.8</v>
+        <v>2265.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>2.16</v>
+        <v/>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>682.6</v>
+        <v>675.7</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>679</v>
+        <v>676.6</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>687.65</v>
+        <v>679.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>675.7</v>
+        <v>672.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-6.9</v>
+        <v>-3.1</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>-1.01</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
+        <v/>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="G30" s="12" t="n">
         <v>172.5</v>
       </c>
-      <c r="E30" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="F30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>170.98</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>171.5</v>
-      </c>
       <c r="I30" s="12" t="n">
-        <v>-1</v>
+        <v/>
       </c>
       <c r="J30" s="13" t="n">
-        <v>-0.58</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>234.98</v>
+        <v/>
       </c>
       <c r="E31" s="9" t="n">
-        <v>233.6</v>
+        <v>233.56</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>236.46</v>
+        <v>234.94</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>232.1</v>
+        <v>231.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>232.3</v>
+        <v>234.94</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2.68</v>
+        <v/>
       </c>
       <c r="J31" s="13" t="n">
-        <v>-1.14</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>385.75</v>
+        <v>395.45</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>387</v>
+        <v>397.4</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>395.9</v>
+        <v>399.2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>387</v>
+        <v>393.3</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>395.45</v>
+        <v>393.3</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>2.51</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>448.15</v>
+        <v>448.6</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>449.4</v>
+        <v>449.95</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>452.35</v>
+        <v>461.8</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>443.9</v>
+        <v>448.6</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>448.6</v>
+        <v>458.65</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.45</v>
+        <v>10.05</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.1</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1841.8</v>
+        <v>1843</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1845.9</v>
+        <v>1893.3</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1827.6</v>
+        <v>1835.3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1836</v>
+        <v>1893.3</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>1</v>
+        <v>57.3</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.05</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>410.6</v>
+        <v>429.2</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>411.55</v>
+        <v>428.4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>430.75</v>
+        <v>439.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>410.8</v>
+        <v>427.25</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>429.2</v>
+        <v>439.9</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>18.6</v>
+        <v>10.7</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>4.53</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>374.4</v>
+        <v>380</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>374</v>
+        <v>380.05</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>370.5</v>
+        <v>379.3</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47555</v>
+        <v/>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47740</v>
+        <v>47850</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48160</v>
+        <v>48650</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47595</v>
+        <v>47000</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47735</v>
+        <v>47000</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>180</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>0.38</v>
+        <v/>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>303.35</v>
+        <v>307</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>304.55</v>
+        <v>308.55</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>308</v>
+        <v>314.2</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>303.15</v>
+        <v>308.25</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4999.5</v>
+        <v>4982</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4996</v>
+        <v>4982</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5040</v>
+        <v>5026.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4982</v>
+        <v>4968</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4982</v>
+        <v>4998</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>-0.35</v>
+        <v>16</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>281.25</v>
+        <v/>
       </c>
       <c r="E40" s="12" t="n">
-        <v>282.4</v>
+        <v>285</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>286.95</v>
+        <v>285.05</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>281.65</v>
+        <v>278.45</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>283.8</v>
+        <v>280.4</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>0.91</v>
+        <v/>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>123.2</v>
+        <v>123.9</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>123.15</v>
+        <v>123.81</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>125.14</v>
+        <v>123.89</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>122.48</v>
+        <v>123.01</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>123.9</v>
+        <v>123.78</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>0.57</v>
+        <v>-0.12</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>771.95</v>
+        <v/>
       </c>
       <c r="E42" s="12" t="n">
-        <v>773.1</v>
+        <v>777.6</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>784.6</v>
+        <v>787.6</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>770.75</v>
+        <v>769</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>774.4</v>
+        <v>778.5</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>0.32</v>
+        <v/>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>409.1</v>
+        <v>413.9</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>407.5</v>
+        <v>414.7</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>407.5</v>
+        <v>410.9</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>413.9</v>
+        <v>414.9</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1.17</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1765.6</v>
+        <v/>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1765.5</v>
+        <v>1769.3</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1793.2</v>
+        <v>1804.4</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1747.6</v>
+        <v>1766</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1764.5</v>
+        <v>1800</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-1.1</v>
+        <v/>
       </c>
       <c r="J44" s="13" t="n">
-        <v>-0.06</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1358</v>
+        <v/>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1362.5</v>
+        <v>1371.7</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1385</v>
+        <v>1394.5</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1351.6</v>
+        <v>1371.7</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1376.3</v>
+        <v>1394.5</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>1.35</v>
+        <v/>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>422.25</v>
+        <v>418</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>421.1</v>
+        <v>418</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>422.8</v>
+        <v>419.95</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>416.55</v>
+        <v>409.65</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>418</v>
+        <v>409.9</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-4.25</v>
+        <v>-8.1</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>-1.01</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1766.7</v>
+        <v/>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1766.8</v>
+        <v>1793</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1797.4</v>
+        <v>1841</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1759.4</v>
+        <v>1754.2</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1793</v>
+        <v>1841</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>1.49</v>
+        <v/>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1860</v>
+        <v/>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1861</v>
+        <v>1841.5</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1886</v>
+        <v>1917.8</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1840</v>
+        <v>1836.9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1840.3</v>
+        <v>1917.8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-19.7</v>
+        <v/>
       </c>
       <c r="J48" s="13" t="n">
-        <v>-1.06</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>488.8</v>
+        <v>488.15</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>494</v>
+        <v>504.55</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>485</v>
+        <v>485.1</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>488.15</v>
+        <v>504.55</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-0.13</v>
+        <v>16.4</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>3.36</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1937.8</v>
+        <v>1929.8</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1936</v>
+        <v>1929.8</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1947.3</v>
+        <v>2019.9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1922</v>
+        <v>1919.5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1929.8</v>
+        <v>1999.5</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>-0.41</v>
+        <v>69.7</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>3.61</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>223.4</v>
+        <v/>
       </c>
       <c r="E51" s="9" t="n">
-        <v>223.1</v>
+        <v>226</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>227.05</v>
+        <v>227.12</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>222.74</v>
+        <v>225.11</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>225.1</v>
+        <v>227.12</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>0.76</v>
+        <v/>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>227.24</v>
+        <v>231.82</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>227</v>
+        <v>231.6</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>237</v>
+        <v>238.95</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>227</v>
+        <v>231.6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>231.82</v>
+        <v>235.79</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>4.58</v>
+        <v>3.97</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4940</v>
+        <v>5020</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>4940</v>
+        <v>5000</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5043.5</v>
+        <v>5119</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4920</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5020</v>
+        <v>5099.5</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>382</v>
+        <v>384.55</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>382.4</v>
+        <v>384.6</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>386.4</v>
+        <v>395.25</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>381.3</v>
+        <v>382.95</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>384.55</v>
+        <v>395.25</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>2.55</v>
+        <v>10.7</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.67</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1693.6</v>
+        <v/>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1680.1</v>
+        <v>1695</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1700</v>
+        <v>1805</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1676.4</v>
+        <v>1685.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1693.3</v>
+        <v>1761.4</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-0.3</v>
+        <v/>
       </c>
       <c r="J55" s="13" t="n">
-        <v>-0.02</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1590.5</v>
+        <v/>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1595</v>
+        <v>1606.9</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1611.9</v>
+        <v>1623.5</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1589.9</v>
+        <v>1577.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1604.8</v>
+        <v>1586.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>0.9</v>
+        <v/>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>55.19</v>
+        <v>56.15</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>55.56</v>
+        <v>56.5</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>56.8</v>
+        <v>58.85</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>54.26</v>
+        <v>56.03</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>56.15</v>
+        <v>58.34</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>0.96</v>
+        <v>2.19</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9158</v>
+        <v>9323</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9158</v>
+        <v>9346.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9371</v>
+        <v>9445</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9135.5</v>
+        <v>9328.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9323</v>
+        <v>9375</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>1.8</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13181</v>
+        <v/>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13200</v>
+        <v>13290</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13495</v>
+        <v>13383</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13176</v>
+        <v>13005</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13290</v>
+        <v>13005</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>0.83</v>
+        <v/>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>622.8</v>
+        <v>640</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>623.05</v>
+        <v>640</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>644.55</v>
+        <v>653.7</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>640</v>
+        <v>644.35</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>17.2</v>
+        <v>4.35</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>2.76</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1140</v>
+        <v/>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1140</v>
+        <v>1182.6</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1189.8</v>
+        <v>1207.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1140</v>
+        <v>1182.1</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>3.07</v>
+        <v/>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7500</v>
+        <v>7493.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7495</v>
+        <v>7523.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7552.5</v>
+        <v>7569</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7489</v>
+        <v>7477</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7493.5</v>
+        <v>7516</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-0.09</v>
+        <v>22.5</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2815.6</v>
+        <v/>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2815.6</v>
+        <v>2830</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2843.6</v>
+        <v>2836.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2809</v>
+        <v>2769.4</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2830</v>
+        <v>2798.2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>0.51</v>
+        <v/>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>415.5</v>
+        <v>418.6</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>415.35</v>
+        <v>419.35</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>421.95</v>
+        <v>444.7</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>411</v>
+        <v>419.35</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>418.6</v>
+        <v>435.85</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>3.1</v>
+        <v>17.25</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.75</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>341.8</v>
+        <v>332.75</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>342</v>
+        <v>332.8</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>343.75</v>
+        <v>335.4</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>332.45</v>
+        <v>325.4</v>
       </c>
       <c r="H65" s="9" t="n">
         <v>332.75</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>-2.65</v>
+        <v>0</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>170.65</v>
+        <v>172</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>171.24</v>
+        <v>172</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>172.82</v>
+        <v>174.65</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>171.24</v>
+        <v>172</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>172</v>
+        <v>173.9</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2410</v>
+        <v>2416</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2406.8</v>
+        <v>2409.8</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2416.9</v>
+        <v>2447.4</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2388.4</v>
+        <v>2396.8</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2416</v>
+        <v>2447.4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>6</v>
+        <v>31.4</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.25</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>539.75</v>
+        <v>584.85</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>540</v>
+        <v>578.85</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>599</v>
+        <v>594.35</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>538.2</v>
+        <v>574</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>584.85</v>
+        <v>588.9</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>45.1</v>
+        <v>4.05</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>8.359999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>863</v>
+        <v/>
       </c>
       <c r="E70" s="12" t="n">
-        <v>866.45</v>
+        <v>875.3</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>876</v>
+        <v>886</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>865.15</v>
+        <v>870.45</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>1.16</v>
+        <v/>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1665.3</v>
+        <v/>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1664</v>
+        <v>1686.9</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1695.3</v>
+        <v>1721.3</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1657.7</v>
+        <v>1686.6</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1678.2</v>
+        <v>1691.1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>0.77</v>
+        <v/>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>835.6</v>
+        <v>870.4</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>841</v>
+        <v>874</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>874</v>
+        <v>890.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>838.2</v>
+        <v>865.9</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>870.4</v>
+        <v>875.5</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>34.8</v>
+        <v>5.1</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>4.16</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3187</v>
+        <v/>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3190</v>
+        <v>3175</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3205</v>
+        <v>3209.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3159</v>
+        <v>3174.5</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-13.9</v>
+        <v/>
       </c>
       <c r="J73" s="13" t="n">
-        <v>-0.44</v>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4695.6</v>
+        <v>4788</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4699</v>
+        <v>4804.9</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4799</v>
+        <v>4890</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4687</v>
+        <v>4780</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4788</v>
+        <v>4800.3</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>92.40000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.97</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1089.9</v>
+        <v/>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1089.9</v>
+        <v>1086</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1095.6</v>
+        <v>1132.4</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1083.5</v>
+        <v>1086</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1092</v>
+        <v>1132.4</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>0.19</v>
+        <v/>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1253</v>
+        <v>1258.3</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1242.2</v>
+        <v>1258.3</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1258.3</v>
+        <v>1260.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1235.3</v>
+        <v>1235.6</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1258.3</v>
+        <v>1249.3</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>0.42</v>
+        <v>-9</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2373.1</v>
+        <v/>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2378.1</v>
+        <v>2405.6</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2415</v>
+        <v>2439</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2378.1</v>
+        <v>2401.2</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2387.7</v>
+        <v>2425</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>0.62</v>
+        <v/>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>721.5</v>
+        <v>713</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>717.5</v>
+        <v>715.25</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>719.4</v>
+        <v>733.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>713</v>
+        <v>715.25</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>-1.18</v>
+        <v>18</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>2.52</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>532.9</v>
+        <v>557.1</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>560.95</v>
+        <v>564.95</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>529.95</v>
+        <v>550.95</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>557</v>
+        <v>550.95</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>5.05</v>
+        <v>-6.05</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5235</v>
+        <v>5325</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5253.5</v>
+        <v>5325</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5341</v>
+        <v>5362.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5243.5</v>
+        <v>5285.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5325</v>
+        <v>5285.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>1.72</v>
+        <v>-39.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>972.7</v>
+        <v/>
       </c>
       <c r="E82" s="12" t="n">
-        <v>972</v>
+        <v>982.9</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>987.2</v>
+        <v>999.3</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>970.5</v>
+        <v>979.4</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>0.8</v>
+        <v/>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>481.6</v>
+        <v>485.5</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>485</v>
+        <v>490.7</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>489.3</v>
+        <v>499.25</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>480.7</v>
+        <v>487.05</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>485.5</v>
+        <v>497.4</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3.9</v>
+        <v>11.9</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>350.05</v>
+        <v/>
       </c>
       <c r="E84" s="12" t="n">
-        <v>352.25</v>
+        <v>352.4</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>353.65</v>
+        <v>359</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>350.35</v>
+        <v>350.5</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>350.6</v>
+        <v>359</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>0.16</v>
+        <v/>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1962</v>
+        <v>1942.2</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1962</v>
+        <v>1950</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1968.9</v>
+        <v>1959.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1942.2</v>
+        <v>1932</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1942.2</v>
+        <v>1932</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-19.8</v>
+        <v>-10.2</v>
       </c>
       <c r="J85" s="13" t="n">
-        <v>-1.01</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>33895</v>
+        <v/>
       </c>
       <c r="E86" s="12" t="n">
-        <v>33730</v>
+        <v>33915</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34140</v>
+        <v>36485</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33730</v>
+        <v>33885</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33915</v>
+        <v>35445</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>0.06</v>
+        <v/>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>85.01000000000001</v>
+        <v>86.33</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>84.75</v>
+        <v>86</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.48999999999999</v>
+        <v>87.17</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>84.53</v>
+        <v>85.92</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>86.33</v>
+        <v>85.92</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>1.55</v>
+        <v>-0.41</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>112</v>
+        <v>113.4</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>111.82</v>
+        <v>113</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>113.85</v>
+        <v>115.46</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>111.61</v>
+        <v>113</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>113.4</v>
+        <v>115.46</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="89">
@@ -3757,22 +3757,22 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>148.77</v>
+        <v>148.67</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>148.66</v>
+        <v>148.5</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>149.67</v>
+        <v>151.79</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>147.9</v>
+        <v>148.1</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>148.67</v>
+        <v>148.56</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="J89" s="13" t="n">
         <v>-0.07000000000000001</v>
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>713.4</v>
+        <v>726.65</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>713.4</v>
+        <v>725.85</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>729.8</v>
+        <v>743</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>712.55</v>
+        <v>722.6</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>13.25</v>
+        <v>6.1</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.86</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1706.3</v>
+        <v>1662.7</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1707.9</v>
+        <v>1651.4</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1718.8</v>
+        <v>1667</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1652</v>
+        <v>1622.4</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1662.7</v>
+        <v>1646.3</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-43.6</v>
+        <v>-16.4</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-2.56</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4733.5</v>
+        <v>4845</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4746.5</v>
+        <v>4925</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4855.5</v>
+        <v>4970</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4746.5</v>
+        <v>4881</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4845</v>
+        <v>4920</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>111.5</v>
+        <v>75</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>946.5</v>
+        <v>958.2</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>946</v>
+        <v>963.8</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>970.7</v>
+        <v>969.3</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>945.2</v>
+        <v>955.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>958.2</v>
+        <v>966.3</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>11.7</v>
+        <v>8.1</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>1.24</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>375.6</v>
+        <v/>
       </c>
       <c r="E94" s="12" t="n">
-        <v>377.1</v>
+        <v>380.9</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>384.75</v>
+        <v>382.5</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>377.1</v>
+        <v>375.9</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>381.35</v>
+        <v>375.9</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>1.53</v>
+        <v/>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1060</v>
+        <v>1058.6</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1054.9</v>
+        <v>1061.9</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1063.6</v>
+        <v>1061.9</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1048.6</v>
+        <v>1038</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1058.6</v>
+        <v>1051.4</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-1.4</v>
+        <v>-7.2</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>-0.13</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>134.75</v>
+        <v>134.27</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>134.9</v>
+        <v>135.02</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>135.33</v>
+        <v>137</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>134</v>
+        <v>134.6</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>134.27</v>
+        <v>137</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>-0.36</v>
+        <v>2.73</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1950.7</v>
+        <v>1970.3</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1940</v>
+        <v>1972.3</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2014</v>
+        <v>2038</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1937.9</v>
+        <v>1964</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1970.3</v>
+        <v>2009.6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>19.6</v>
+        <v>39.3</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>1</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>452.95</v>
+        <v>457</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>458.4</v>
+        <v>480</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>452.15</v>
+        <v>457.15</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>457</v>
+        <v>476.75</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>4.05</v>
+        <v>19.75</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.89</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>264.15</v>
+        <v>266.2</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>264.8</v>
+        <v>266.6</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>268.5</v>
+        <v>266.6</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>264.1</v>
+        <v>262.3</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>266.2</v>
+        <v>262.3</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>0.78</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1103</v>
+        <v/>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1104.1</v>
+        <v>1128.9</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1134.6</v>
+        <v>1140.2</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1104.1</v>
+        <v>1119.5</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1128.4</v>
+        <v>1119.5</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>2.3</v>
+        <v/>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4750</v>
+        <v>5027</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>4780</v>
+        <v>5010</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5055</v>
+        <v>5139</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4745.5</v>
+        <v>4990</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5027</v>
+        <v>5064.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>277</v>
+        <v>37.5</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5.83</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>730.85</v>
+        <v/>
       </c>
       <c r="E102" s="12" t="n">
-        <v>730</v>
+        <v>724.5</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>742.7</v>
+        <v>754.95</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>721.85</v>
+        <v>724.5</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>724.45</v>
+        <v>750.95</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-6.4</v>
+        <v/>
       </c>
       <c r="J102" s="13" t="n">
-        <v>-0.88</v>
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>504.7</v>
+        <v>512</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>504.6</v>
+        <v>509</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>7.3</v>
+        <v>14</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>1.45</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1248.9</v>
+        <v/>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1248.9</v>
+        <v>1270.1</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1260</v>
+        <v>1278.7</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1242.1</v>
+        <v>1262.7</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1253.4</v>
+        <v>1275.6</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>0.36</v>
+        <v/>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>471</v>
+        <v>480.2</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>469.95</v>
+        <v>483.95</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>486.75</v>
+        <v>502</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>467.35</v>
+        <v>480.3</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>480.2</v>
+        <v>500</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1.95</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1215.9</v>
+        <v/>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1215</v>
+        <v>1211.1</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1224.4</v>
+        <v>1216.9</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1210</v>
+        <v>1197</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1217.2</v>
+        <v>1202.7</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>0.11</v>
+        <v/>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>415</v>
+        <v>416.5</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>415</v>
+        <v>415.5</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>417.6</v>
+        <v>419.2</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>412.5</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>0.36</v>
+        <v>-4</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>555</v>
+        <v>559.3</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>556.2</v>
+        <v>559.3</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>560.95</v>
+        <v>559.5</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>552.5</v>
+        <v>532</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>559.3</v>
+        <v>532</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>0.77</v>
+        <v>-27.3</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-4.88</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1895.7</v>
+        <v/>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1890.6</v>
+        <v>1930.1</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1941.1</v>
+        <v>1959.4</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1888</v>
+        <v>1885</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1924.7</v>
+        <v>1896.9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>1.53</v>
+        <v/>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1905.5</v>
+        <v/>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1898</v>
+        <v>1962</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1964.5</v>
+        <v>1982</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1894.8</v>
+        <v>1954</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1948.1</v>
+        <v>1954</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>2.24</v>
+        <v/>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>543</v>
+        <v/>
       </c>
       <c r="E111" s="9" t="n">
-        <v>542.05</v>
+        <v>548.6</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>554.55</v>
+        <v>552</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>541.05</v>
+        <v>543.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>545.9</v>
+        <v>548.15</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>0.53</v>
+        <v/>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3807.7</v>
+        <v>3836.2</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3811</v>
+        <v>3846</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3875</v>
+        <v>3898</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3811</v>
+        <v>3846</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3836.2</v>
+        <v>3885</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>28.5</v>
+        <v>48.8</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.75</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>295.5</v>
+        <v/>
       </c>
       <c r="E113" s="9" t="n">
-        <v>295.3</v>
+        <v>303</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>304.05</v>
+        <v>314.3</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>293.5</v>
+        <v>302.5</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>302.3</v>
+        <v>312.8</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>2.3</v>
+        <v/>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3351.5</v>
+        <v/>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3351.5</v>
+        <v>3340.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3377</v>
+        <v>3367.9</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3307.3</v>
+        <v>3286.8</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3324.3</v>
+        <v>3347.5</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-27.2</v>
+        <v/>
       </c>
       <c r="J115" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2045</v>
+        <v>2098.1</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2052.6</v>
+        <v>2088.1</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2098.1</v>
+        <v>2114.7</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2046.3</v>
+        <v>2075</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2098.1</v>
+        <v>2083</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>2.6</v>
+        <v>-15.1</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3070</v>
+        <v>3076.5</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3047</v>
+        <v>3082</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3127.8</v>
+        <v>3098.2</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3047</v>
+        <v>3052</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3076.5</v>
+        <v>3052</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>0.21</v>
+        <v>-24.5</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
+        <v/>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>319</v>
+      </c>
+      <c r="F118" s="12" t="n">
         <v>319.9</v>
       </c>
-      <c r="E118" s="12" t="n">
-        <v>318.85</v>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>322.15</v>
-      </c>
       <c r="G118" s="12" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>316.05</v>
+        <v>319.15</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-3.85</v>
+        <v/>
       </c>
       <c r="J118" s="13" t="n">
-        <v>-1.2</v>
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>810.15</v>
+        <v/>
       </c>
       <c r="E119" s="9" t="n">
-        <v>810.15</v>
+        <v>820.05</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>826.3</v>
+        <v>822.45</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>810.15</v>
+        <v>803.9</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>817</v>
+        <v>803.9</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>0.85</v>
+        <v/>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12166</v>
+        <v>12338</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12165</v>
+        <v>12350</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12409</v>
+        <v>12458</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12127</v>
+        <v>12103</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12338</v>
+        <v>12103</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>1.41</v>
+        <v>-235</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3211.2</v>
+        <v/>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3201.1</v>
+        <v>3257.5</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3304</v>
+        <v>3314.9</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3180.1</v>
+        <v>3230.1</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3265.2</v>
+        <v>3260</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>1.68</v>
+        <v/>
+      </c>
+      <c r="J122" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>580.85</v>
+        <v>586.3</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>580.55</v>
+        <v>589.9</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>590.1</v>
+        <v>602.05</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>577.55</v>
+        <v>582</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>586.3</v>
+        <v>597.45</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>5.45</v>
+        <v>11.15</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1487.6</v>
+        <v/>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1480.1</v>
+        <v>1538.6</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1569.5</v>
+        <v>1573.6</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1473.6</v>
+        <v>1538</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>4.46</v>
+        <v/>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1080.1</v>
+        <v>1071.2</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1073.8</v>
+        <v>1067.1</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1079.9</v>
+        <v>1087.5</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1065</v>
+        <v>1066.2</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1071.2</v>
+        <v>1081.7</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-0.82</v>
+        <v>10.5</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>158.27</v>
+        <v>161.87</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>159.02</v>
+        <v>161.87</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>162.84</v>
+        <v>165.37</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>158.66</v>
+        <v>161.84</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>161.87</v>
+        <v>162.57</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>2.27</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2316.7</v>
+        <v/>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2304</v>
+        <v>2322.9</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2325.1</v>
+        <v>2327.9</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2288</v>
+        <v>2275</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2320</v>
+        <v>2300.4</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>0.14</v>
+        <v/>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>125010</v>
+        <v/>
       </c>
       <c r="E128" s="12" t="n">
-        <v>125100</v>
+        <v>124900</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>125850</v>
+        <v>126500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124300</v>
+        <v>123815</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>124585</v>
+        <v>125670</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-425</v>
+        <v/>
       </c>
       <c r="J128" s="13" t="n">
-        <v>-0.34</v>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2771.4</v>
+        <v/>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2761</v>
+        <v>2796.6</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2790</v>
+        <v>2852</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2740</v>
+        <v>2784.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2770.2</v>
+        <v>2841.1</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-1.2</v>
+        <v/>
       </c>
       <c r="J129" s="13" t="n">
-        <v>-0.04</v>
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>356</v>
+        <v>355.7</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>356</v>
+        <v>359.8</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>360.75</v>
+        <v>363.2</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>354.2</v>
+        <v>350.5</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>355.7</v>
+        <v>350.5</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-0.3</v>
+        <v>-5.2</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>-0.08</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1256</v>
+        <v/>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1283.1</v>
+        <v>1284</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1242.8</v>
+        <v>1251.2</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1265</v>
+        <v>1251.2</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>0.72</v>
+        <v/>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8160.5</v>
+        <v>8220</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8120</v>
+        <v>8257</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8325</v>
+        <v>8682.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8120</v>
+        <v>8231.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8220</v>
+        <v>8590</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>59.5</v>
+        <v>370</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.73</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1384.5</v>
+        <v/>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1384.5</v>
+        <v>1372.1</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1391.7</v>
+        <v>1390</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1370.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1370.6</v>
+        <v>1372.4</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-13.9</v>
+        <v/>
       </c>
       <c r="J133" s="13" t="n">
-        <v>-1</v>
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>80.31999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>80.41</v>
+        <v>81.38</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>81.34999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>80.40000000000001</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>80.8</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>0.6</v>
+        <v>-1.65</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>327</v>
+        <v>329.6</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>327.8</v>
+        <v>329.8</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>331.3</v>
+        <v>330.85</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>327.2</v>
+        <v>323.65</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>329.6</v>
+        <v>323.65</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>0.8</v>
+        <v>-5.95</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1706.9</v>
+        <v/>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1705.1</v>
+        <v>1730.1</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1741.9</v>
+        <v>1785</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1695.8</v>
+        <v>1721</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1740.7</v>
+        <v>1785</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>1.98</v>
+        <v/>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11510</v>
+        <v>11620</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11500</v>
+        <v>11648</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11666</v>
+        <v>11896</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11356</v>
+        <v>11515</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11620</v>
+        <v>11896</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>110</v>
+        <v>276</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.96</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>236.8</v>
+        <v>232.43</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>235.1</v>
+        <v>232.43</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>235.65</v>
+        <v>234.32</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>231.25</v>
+        <v>231.75</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>232.43</v>
+        <v>232.8</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-4.37</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>-1.85</v>
+        <v>0.37</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>34275</v>
+        <v>35020</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>34300</v>
+        <v>34990</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35290</v>
+        <v>36400</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34300</v>
+        <v>34900</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35020</v>
+        <v>36400</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>745</v>
+        <v>1380</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>2.17</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5440</v>
+        <v/>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5410</v>
+        <v>5476</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5502</v>
+        <v>5500</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5405.5</v>
+        <v>5389</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5473</v>
+        <v>5416</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>0.61</v>
+        <v/>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>282.1</v>
+        <v>283.45</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>282.05</v>
+        <v>284.85</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>285</v>
+        <v>292.6</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>281.7</v>
+        <v>284.1</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>283.45</v>
+        <v>292.6</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>1.35</v>
+        <v>9.15</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>0.48</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>346</v>
+        <v/>
       </c>
       <c r="E143" s="9" t="n">
-        <v>346.1</v>
+        <v>345</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>348.5</v>
+        <v>347.1</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>344.75</v>
+        <v>342.55</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>344.95</v>
+        <v>342.55</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-1.05</v>
+        <v/>
       </c>
       <c r="J143" s="13" t="n">
-        <v>-0.3</v>
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1543.8</v>
+        <v>1551.5</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1543</v>
+        <v>1559.9</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1561.1</v>
+        <v>1598.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1535</v>
+        <v>1559.9</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1551.5</v>
+        <v>1572.1</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>7.7</v>
+        <v>20.6</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2256</v>
+        <v>2307</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2260</v>
+        <v>2307</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2317</v>
+        <v>2366.8</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2259</v>
+        <v>2302.5</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2307</v>
+        <v>2366.8</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>51</v>
+        <v>59.8</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116.8</v>
+        <v>116.47</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116.8</v>
+        <v>117</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>119.4</v>
+        <v>117.5</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.36</v>
+        <v>116.5</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116.47</v>
+        <v>117.27</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>-0.28</v>
+        <v>0.8</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8121.5</v>
+        <v>8208.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8130</v>
+        <v>8256</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8266</v>
+        <v>8400</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8112.5</v>
+        <v>8235</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8208.5</v>
+        <v>8400</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>87</v>
+        <v>191.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>1.07</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>262.8</v>
+        <v/>
       </c>
       <c r="E148" s="12" t="n">
-        <v>263.5</v>
+        <v>264.6</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>265.7</v>
+        <v>270.3</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>263.25</v>
+        <v>263.4</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>263.75</v>
+        <v>270.3</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>0.36</v>
+        <v/>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1254.6</v>
+        <v>1272.7</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1248.5</v>
+        <v>1277.5</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1282</v>
+        <v>1339.8</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1231.2</v>
+        <v>1270</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1272.7</v>
+        <v>1324.7</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>18.1</v>
+        <v>52</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>1.44</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>404</v>
+        <v>404.15</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>403</v>
+        <v>406.15</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>411.65</v>
+        <v>415.9</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>401.95</v>
+        <v>405</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>404.15</v>
+        <v>415.9</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>0.15</v>
+        <v>11.75</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.04</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>312.65</v>
+        <v/>
       </c>
       <c r="E151" s="9" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>315.05</v>
+        <v>313.4</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>310.5</v>
+        <v>309.05</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>310.5</v>
+        <v>312</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-2.15</v>
+        <v/>
       </c>
       <c r="J151" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1244.8</v>
+        <v>1245</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1253.4</v>
+        <v>1247.3</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1238.5</v>
+        <v>1226.4</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>0.31</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>173.55</v>
+        <v>175.01</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>173</v>
+        <v>176.5</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>176.25</v>
+        <v>179.8</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>173</v>
+        <v>176.03</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>175.01</v>
+        <v>177.33</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1.46</v>
+        <v>2.32</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>618.1</v>
+        <v>636.95</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>616</v>
+        <v>635.95</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>641.55</v>
+        <v>651.15</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>616</v>
+        <v>630.7</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>636.95</v>
+        <v>651.15</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>18.85</v>
+        <v>14.2</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1697.9</v>
+        <v>1766.9</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1693</v>
+        <v>1751.3</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1771.1</v>
+        <v>1770</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1689</v>
+        <v>1731</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1766.9</v>
+        <v>1731</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>69</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>4.06</v>
+        <v>-35.9</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>991.4</v>
+        <v>988.7</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>991.2</v>
+        <v>992</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1000.9</v>
+        <v>996.2</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>985.2</v>
+        <v>985.1</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>988.7</v>
+        <v>996.2</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>-0.27</v>
+        <v>7.5</v>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>21795</v>
+        <v>21960</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>21760</v>
+        <v>22200</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22080</v>
+        <v>23000</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>21685</v>
+        <v>22100</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>21960</v>
+        <v>22600</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>165</v>
+        <v>640</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>0.76</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>979</v>
+        <v>1004.9</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1005.5</v>
+        <v>1019</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>978.3</v>
+        <v>1000.5</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3742</v>
+        <v/>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3743.1</v>
+        <v>3781.4</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3817.4</v>
+        <v>3913.9</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3742</v>
+        <v>3770</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3763.5</v>
+        <v>3913.9</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>0.57</v>
+        <v/>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2480.1</v>
+        <v>2536</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2505</v>
+        <v>2536.6</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2554</v>
+        <v>2569.9</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2501</v>
+        <v>2512</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2536</v>
+        <v>2512</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>2.25</v>
+        <v>-24</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1853.5</v>
+        <v>1867.3</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1853.5</v>
+        <v>1866.1</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1867.3</v>
+        <v>1877.2</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1847.4</v>
+        <v>1837.3</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1867.3</v>
+        <v>1837.3</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>0.74</v>
+        <v>-30</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>462.45</v>
+        <v/>
       </c>
       <c r="E162" s="12" t="n">
-        <v>463.95</v>
+        <v>469.8</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>471</v>
+        <v>470.4</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>459.15</v>
+        <v>449.05</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>468.4</v>
+        <v>451.7</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>1.29</v>
+        <v/>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>380.1</v>
+        <v/>
       </c>
       <c r="E163" s="9" t="n">
-        <v>380.1</v>
+        <v>379.1</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>381.5</v>
+        <v>384</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>376.1</v>
+        <v>366.65</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>380.2</v>
+        <v>369.05</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>0.03</v>
+        <v/>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>731.8</v>
+        <v>779.3</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>832</v>
+        <v>741.35</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>724.75</v>
+        <v>687.1</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>779.3</v>
+        <v>693.25</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>6.49</v>
+        <v>-86.05</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>-11.04</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1799.3</v>
+        <v/>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1810</v>
+        <v>1794.8</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1831.5</v>
+        <v>1805</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1771.2</v>
+        <v>1743.3</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1791.6</v>
+        <v>1780.1</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-7.7</v>
+        <v/>
       </c>
       <c r="J165" s="13" t="n">
-        <v>-0.43</v>
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1000.1</v>
+        <v>1013.7</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1003.1</v>
+        <v>1016.2</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1020.3</v>
+        <v>1018.7</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1013.7</v>
+        <v>996</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>1.36</v>
+        <v>-17.7</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>360.4</v>
+        <v>369</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>360.4</v>
+        <v>364.8</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>370.4</v>
+        <v>374.8</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>360.2</v>
+        <v>360.9</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>369</v>
+        <v>374.8</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>2.39</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>183</v>
+        <v>187.29</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>183</v>
+        <v>186.4</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>189.49</v>
+        <v>187.96</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>182.87</v>
+        <v>185.54</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>187.29</v>
+        <v>185.54</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>2.34</v>
+        <v>-1.75</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2171</v>
+        <v>2177.2</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2263.6</v>
+        <v>2177.3</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2162.5</v>
+        <v>2101.2</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2190</v>
+        <v>2105</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>0.05</v>
+        <v>-85</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-3.88</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1558</v>
+        <v/>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1545.1</v>
+        <v>1558.3</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1569.7</v>
+        <v>1561.2</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1538</v>
+        <v>1523.1</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1561</v>
+        <v>1537.1</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>0.19</v>
+        <v/>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2566.6</v>
+        <v>2598.8</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2566</v>
+        <v>2598.9</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2626.6</v>
+        <v>2637.8</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2560.4</v>
+        <v>2571.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2598.8</v>
+        <v>2600</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>32.2</v>
+        <v>1.2</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>1.25</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4895</v>
+        <v>4851</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4915.5</v>
+        <v>4864.5</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4838.5</v>
+        <v>4772</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4841</v>
+        <v>4798.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-67.5</v>
+        <v>-42.5</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>-1.38</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4812.5</v>
+        <v/>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4810</v>
+        <v>4874.5</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4899</v>
+        <v>4928</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4794.5</v>
+        <v>4827</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4875</v>
+        <v>4840</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>1.3</v>
+        <v/>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1295.3</v>
+        <v>1276.4</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1300</v>
+        <v>1277</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1310.6</v>
+        <v>1285.7</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1271</v>
+        <v>1232</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1276.4</v>
+        <v>1258.8</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-18.9</v>
+        <v>-17.6</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-1.46</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2760</v>
+        <v>2789.3</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2811</v>
+        <v>2824</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2760</v>
+        <v>2776.1</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2789</v>
+        <v>2824</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>19.3</v>
+        <v>35</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>0.7</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="177">
@@ -6749,22 +6749,22 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4033</v>
+        <v>4101.7</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4050</v>
+        <v>4125</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4162.2</v>
+        <v>4195</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4050</v>
+        <v>4122.1</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4101.7</v>
+        <v>4171.3</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J177" s="10" t="n">
         <v>1.7</v>
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1227.3</v>
+        <v/>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1228</v>
+        <v>1219.9</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1239.5</v>
+        <v>1258</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1213.5</v>
+        <v>1219.9</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1216.8</v>
+        <v>1251.5</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-10.5</v>
+        <v/>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-0.86</v>
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10740</v>
+        <v>10890</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>10841</v>
+        <v>11060</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10703</v>
+        <v>10819</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>0.6</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>178.2</v>
+        <v>178.09</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>180.62</v>
+        <v>178.92</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>175.83</v>
+        <v>176.56</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>178.09</v>
+        <v>176.56</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-0.11</v>
+        <v>-1.53</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-0.06</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>550.6</v>
+        <v>554.75</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>549.8</v>
+        <v>553.4</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>554.75</v>
+        <v>580</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>4.15</v>
+        <v>25.25</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>0.75</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>256</v>
+        <v>257.45</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>257.7</v>
+        <v>267.6</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>253.95</v>
+        <v>258</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>257.45</v>
+        <v>267.6</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>1.45</v>
+        <v>10.15</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>0.57</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1131.1</v>
+        <v>1136</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1141.2</v>
+        <v>1145.3</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1125.1</v>
+        <v>1110.9</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1135</v>
+        <v>1110.9</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>0.35</v>
+        <v>-24.1</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>166.89</v>
+        <v>166.4</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>165.75</v>
+        <v>166.9</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>167.6</v>
+        <v>166.9</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>165.02</v>
+        <v>163.3</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>166.4</v>
+        <v>166.83</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>-0.29</v>
+        <v>0.43</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1107.5</v>
+        <v>1135.1</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1103.5</v>
+        <v>1150.7</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1139.9</v>
+        <v>1167.3</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1100.1</v>
+        <v>1147.7</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1135.1</v>
+        <v>1160</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>27.6</v>
+        <v>24.9</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  17-Sep-2026 05:28 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  18-Sep-2026 04:57 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-Sep-2026 05:28 PM</t>
+          <t>18-Sep-2026 04:57 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 18-Sep-2026 04:57 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 21-Sep-2026 06:29 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>18-Sep-2026 04:57 PM</t>
+          <t>21-Sep-2026 06:29 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  18-Sep-2026 04:57 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  21-Sep-2026 06:29 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>476.6</v>
+        <v>491.15</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>476.65</v>
+        <v>483</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>493.45</v>
+        <v>502</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>476.25</v>
+        <v>481.05</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>491.15</v>
+        <v>499.8</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>14.55</v>
+        <v>8.65</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v/>
+        <v>7270.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7185.5</v>
+        <v>7240</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7307</v>
+        <v>7330</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7151</v>
+        <v>7221</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7270.5</v>
+        <v>7271</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v/>
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v/>
+        <v>27270</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26035</v>
+        <v>27200</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27490</v>
+        <v>27300</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26035</v>
+        <v>26815</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>27270</v>
+        <v>26960</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v/>
+        <v>-310</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v/>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>390.5</v>
+        <v>405.1</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>410.05</v>
+        <v>405.45</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>390.5</v>
+        <v>400.95</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>410.05</v>
+        <v>403.4</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>5.14</v>
+        <v>-6.65</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.45</v>
+        <v>50.16</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.6</v>
+        <v>50.15</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.77</v>
+        <v>50.56</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>50.16</v>
+        <v>49.85</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>-0.57</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1232.5</v>
+        <v>1259.7</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1236.6</v>
+        <v>1260</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1279.9</v>
+        <v>1272</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1236.6</v>
+        <v>1251</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1259.7</v>
+        <v>1256.3</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>2.21</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2933</v>
+        <v>2995.6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3020</v>
+        <v>3015.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2924.6</v>
+        <v>2973</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3020</v>
+        <v>2975</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>3.31</v>
+        <v>-45</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1748</v>
+        <v>1793.7</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1824</v>
+        <v>1796.8</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1744</v>
+        <v>1766.7</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1824</v>
+        <v>1787.1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>4.93</v>
+        <v>-36.9</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5348.5</v>
+        <v>5466.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5378.5</v>
+        <v>5395</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5466.5</v>
+        <v>5411</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5310.5</v>
+        <v>5316.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5466.5</v>
+        <v>5364</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>2.21</v>
+        <v>-102.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>383.25</v>
+        <v>388.3</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>384.55</v>
+        <v>389.1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>396</v>
+        <v>395.95</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>383.9</v>
+        <v>389.1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>388.3</v>
+        <v>390.75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>5.05</v>
+        <v>2.45</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.32</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v/>
+        <v>299.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>295</v>
+        <v>299.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>301.75</v>
+        <v>302</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>295</v>
+        <v>295.2</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>299.1</v>
+        <v>296.15</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v/>
+        <v>-2.95</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v/>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v/>
+        <v>2270.1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2154.9</v>
+        <v>2224.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2270.1</v>
+        <v>2229</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2146.3</v>
+        <v>2178.7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2270.1</v>
+        <v>2181.1</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v/>
+        <v>-89</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v/>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8768.5</v>
+        <v>8944.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8800</v>
+        <v>8889</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8944.5</v>
+        <v>8974.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8798</v>
+        <v>8826.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8944.5</v>
+        <v>8912</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>176</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>2.01</v>
+        <v>-32.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>412.15</v>
+        <v>409.3</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>414.75</v>
+        <v>410</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>418.75</v>
+        <v>413.8</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>407.9</v>
+        <v>408.35</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>409.3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>158.62</v>
+        <v>163</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>159.1</v>
+        <v>163</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>163.12</v>
+        <v>163.19</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>158.51</v>
+        <v>160.87</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>163</v>
+        <v>161.75</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>2.76</v>
+        <v>-1.25</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2454</v>
+        <v>2451.3</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2455.7</v>
+        <v>2450</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2474</v>
+        <v>2463.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2438</v>
+        <v>2440.3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2451.3</v>
+        <v>2440.3</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-2.7</v>
+        <v>-11</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-0.11</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1398.9</v>
+        <v>1427.7</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1400</v>
+        <v>1421.8</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1427.7</v>
+        <v>1426.1</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1397.5</v>
+        <v>1400.9</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1427.7</v>
+        <v>1400.9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>2.06</v>
+        <v>-26.8</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v/>
+        <v>660.7</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>587.4</v>
+        <v>657.65</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>674.8</v>
+        <v>659.05</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>587.4</v>
+        <v>629.15</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>660.7</v>
+        <v>638.4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v/>
+        <v>-22.3</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v/>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v/>
+        <v>6170.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6133.5</v>
+        <v>6120</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6201</v>
+        <v>6150</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6110.5</v>
+        <v>6058.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6170.5</v>
+        <v>6086</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v/>
+        <v>-84.5</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v/>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v/>
+        <v>1058.6</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1040.5</v>
+        <v>1046.8</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1058.6</v>
+        <v>1046.8</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1033.3</v>
+        <v>1037.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1058.6</v>
+        <v>1038</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v/>
+        <v>-20.6</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v/>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v/>
+        <v>1734</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1683.2</v>
+        <v>1709.8</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1734</v>
+        <v>1738.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1676.1</v>
+        <v>1706.4</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1734</v>
+        <v>1713.4</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v/>
+        <v>-20.6</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v/>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1257</v>
+        <v>1254.3</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1240.5</v>
+        <v>1242</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>1.37</v>
+        <v>-7</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v/>
+        <v>11414</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11501</v>
+        <v>11470</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11540</v>
+        <v>11533</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11406</v>
+        <v>11450</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11414</v>
+        <v>11460</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v/>
+        <v>46</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v/>
+        <v>1852.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1857.2</v>
+        <v>1860.2</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1872.6</v>
+        <v>1864</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1852.5</v>
+        <v>1849.2</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1852.5</v>
+        <v>1849.8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v/>
+        <v>-2.7</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v/>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v/>
+        <v>1040.3</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1025.9</v>
+        <v>1035</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1040.3</v>
+        <v>1037.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1019.1</v>
+        <v>1021.3</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1040.3</v>
+        <v>1021.3</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v/>
+        <v>-19</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v/>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v/>
+        <v>2265.3</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2170.7</v>
+        <v>2259</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2296</v>
+        <v>2259</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2166</v>
+        <v>2200.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2265.3</v>
+        <v>2216.8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v/>
+        <v>-48.5</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v/>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>675.7</v>
+        <v>672.6</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>676.6</v>
+        <v>672.6</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>679.9</v>
+        <v>678</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>662</v>
+        <v>661.1</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>672.6</v>
+        <v>663.65</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-3.1</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>-0.46</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v/>
+        <v>175</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>178.3</v>
+        <v>181.26</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>172.5</v>
+        <v>175.63</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v/>
+        <v>234.94</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>233.56</v>
+        <v>234</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>234.94</v>
+        <v>234.51</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>231.92</v>
+        <v>232.52</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>234.94</v>
+        <v>233.64</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v/>
+        <v>-1.3</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>395.45</v>
+        <v>393.3</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>397.4</v>
+        <v>394.35</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>399.2</v>
+        <v>399.15</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>393.3</v>
+        <v>393.1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>393.3</v>
+        <v>398.5</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>-0.54</v>
+        <v>5.2</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>448.6</v>
+        <v>458.65</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>449.95</v>
+        <v>460.8</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>461.8</v>
+        <v>463</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>448.6</v>
+        <v>448.1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>458.65</v>
+        <v>450.6</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>2.24</v>
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1836</v>
+        <v>1893.3</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1843</v>
+        <v>1854.8</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1893.3</v>
+        <v>1854.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1835.3</v>
+        <v>1822</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1893.3</v>
+        <v>1830.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>3.12</v>
+        <v>-63.1</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>429.2</v>
+        <v>439.9</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>428.4</v>
+        <v>433</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>439.9</v>
+        <v>438.3</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>427.25</v>
+        <v>430.2</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>439.9</v>
+        <v>433.4</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>2.49</v>
+        <v>-6.5</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>380.05</v>
+        <v>388.3</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>388</v>
+        <v>396.15</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>379.3</v>
+        <v>387.6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.32</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v/>
+        <v>47000</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47850</v>
+        <v>47460</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48650</v>
+        <v>48180</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47000</v>
+        <v>47460</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47000</v>
+        <v>47565</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v/>
+        <v>565</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>308.55</v>
+        <v>313</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>314.2</v>
+        <v>315.95</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>308.25</v>
+        <v>310.85</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>314</v>
+        <v>312.75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>2.28</v>
+        <v>-1.25</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4982</v>
+        <v>4998</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4982</v>
+        <v>5001.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5026.5</v>
+        <v>5030.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4968</v>
+        <v>4991.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4998</v>
+        <v>5023</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.32</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v/>
+        <v>280.4</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>285</v>
+        <v>280.4</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>285.05</v>
+        <v>284.9</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>278.45</v>
+        <v>278</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>280.4</v>
+        <v>284.15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v/>
+        <v>3.75</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>123.9</v>
+        <v>123.78</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>123.81</v>
+        <v>123.23</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>123.89</v>
+        <v>123.99</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>123.01</v>
+        <v>122.95</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>123.78</v>
+        <v>123.7</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-0.1</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v/>
+        <v>778.5</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>777.6</v>
+        <v>781</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>787.6</v>
+        <v>783</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>769</v>
+        <v>766.05</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>778.5</v>
+        <v>769.9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v/>
+        <v>-8.6</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v/>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>413.9</v>
+        <v>414.9</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>414.7</v>
+        <v>415</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>420</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>410.9</v>
+        <v>413.25</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>414.9</v>
+        <v>417.2</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v/>
+        <v>1800</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1769.3</v>
+        <v>1806</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1804.4</v>
+        <v>1806</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1766</v>
+        <v>1763.5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1800</v>
+        <v>1764</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v/>
+        <v>-36</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v/>
+        <v>-2</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v/>
+        <v>1394.5</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1371.7</v>
+        <v>1383.2</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1394.5</v>
+        <v>1405.2</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1371.7</v>
+        <v>1378.3</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1394.5</v>
+        <v>1386.1</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v/>
+        <v>-8.4</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v/>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>418</v>
+        <v>409.9</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>418</v>
+        <v>411.7</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>419.95</v>
+        <v>415.4</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>409.65</v>
+        <v>410.45</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>409.9</v>
+        <v>414.7</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>-1.94</v>
+        <v>4.8</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v/>
+        <v>1841</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1793</v>
+        <v>1809</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1841</v>
+        <v>1819.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1754.2</v>
+        <v>1791</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1841</v>
+        <v>1814</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v/>
+        <v>-27</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v/>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v/>
+        <v>1917.8</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1841.5</v>
+        <v>1892.3</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1917.8</v>
+        <v>1903</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1836.9</v>
+        <v>1879.4</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1917.8</v>
+        <v>1892</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v/>
+        <v>-25.8</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v/>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>488.15</v>
+        <v>503.55</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>489</v>
+        <v>498.6</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>504.55</v>
+        <v>501.95</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>485.1</v>
+        <v>487.05</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>504.55</v>
+        <v>487.05</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>3.36</v>
+        <v>-16.5</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1929.8</v>
+        <v>1999.5</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1929.8</v>
+        <v>1976.2</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2019.9</v>
+        <v>1990</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1919.5</v>
+        <v>1936.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1999.5</v>
+        <v>1940.8</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>3.61</v>
+        <v>-58.7</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v/>
+        <v>227.12</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>226</v>
+        <v>226.53</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>227.12</v>
+        <v>226.69</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>225.11</v>
+        <v>225.05</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>227.12</v>
+        <v>225.05</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v/>
+        <v>-2.07</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v/>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>231.82</v>
+        <v>235.79</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>231.6</v>
+        <v>236</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>238.95</v>
+        <v>237.74</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>231.6</v>
+        <v>233.1</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>235.79</v>
+        <v>234.94</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>1.71</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5020</v>
+        <v>5099.5</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5119</v>
+        <v>5135</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5000</v>
+        <v>5050</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5099.5</v>
+        <v>5067</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>1.58</v>
+        <v>-32.5</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>384.55</v>
+        <v>395.25</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>384.6</v>
+        <v>390</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>395.25</v>
+        <v>392.8</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>382.95</v>
+        <v>386.8</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>395.25</v>
+        <v>386.8</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>2.78</v>
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v/>
+        <v>1761.4</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1695</v>
+        <v>1765</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1805</v>
+        <v>1814.4</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1685.1</v>
+        <v>1757.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1761.4</v>
+        <v>1764.4</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v/>
+        <v>1586.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1606.9</v>
+        <v>1586.3</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1623.5</v>
+        <v>1602</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1577.2</v>
+        <v>1570.1</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>1586.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>56.15</v>
+        <v>58.34</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>58.85</v>
+        <v>64</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>56.03</v>
+        <v>58.36</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>58.34</v>
+        <v>61.59</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>3.9</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9323</v>
+        <v>9375</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9346.5</v>
+        <v>9418</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9445</v>
+        <v>9461.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9328.5</v>
+        <v>9375.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9375</v>
+        <v>9410.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>52</v>
+        <v>35.5</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v/>
+        <v>12995</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13290</v>
+        <v>13128</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13383</v>
+        <v>13415</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13005</v>
+        <v>13125</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13005</v>
+        <v>13350</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v/>
+        <v>355</v>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>640</v>
+        <v>644.35</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>640</v>
+        <v>645.1</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>653.7</v>
+        <v>660.95</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>644.35</v>
+        <v>660.25</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>4.35</v>
+        <v>15.9</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.68</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v/>
+        <v>1185</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1182.6</v>
+        <v>1185</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1207.5</v>
+        <v>1211.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1182.1</v>
+        <v>1185</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1185</v>
+        <v>1198.3</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v/>
+        <v>13.3</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7493.5</v>
+        <v>7516</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7523.5</v>
+        <v>7550</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7569</v>
+        <v>7569.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7477</v>
+        <v>7490</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7516</v>
+        <v>7512.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>0.3</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v/>
+        <v>2798.2</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2830</v>
+        <v>2798</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2836.8</v>
+        <v>2859.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2769.4</v>
+        <v>2797.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2798.2</v>
+        <v>2819.8</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v/>
+        <v>21.6</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>418.6</v>
+        <v>435.85</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>419.35</v>
+        <v>434.75</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>444.7</v>
+        <v>437.3</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>419.35</v>
+        <v>430.7</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>435.85</v>
+        <v>434.5</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>4.12</v>
+        <v>-1.35</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="65">
@@ -2944,22 +2944,22 @@
         <v>332.75</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>332.8</v>
+        <v>333.1</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>335.4</v>
+        <v>335.35</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>325.4</v>
+        <v>328.8</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>332.75</v>
+        <v>332</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>0</v>
+        <v>-0.75</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>172</v>
+        <v>173.9</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>172</v>
+        <v>173.6</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>174.65</v>
+        <v>174.38</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>172</v>
+        <v>172.61</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>173.9</v>
+        <v>172.61</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>1.1</v>
+        <v>-1.29</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2416</v>
+        <v>2447.4</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2409.8</v>
+        <v>2425</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2447.4</v>
+        <v>2473.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2396.8</v>
+        <v>2424</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2447.4</v>
+        <v>2450</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>31.4</v>
+        <v>2.6</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>1.3</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>584.85</v>
+        <v>588.9</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>578.85</v>
+        <v>588.9</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>594.35</v>
+        <v>598.85</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>574</v>
+        <v>582.75</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>588.9</v>
+        <v>589.9</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>4.05</v>
+        <v>1</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v/>
+        <v>880</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>875.3</v>
+        <v>879</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>870.45</v>
+        <v>866.1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>880</v>
+        <v>867.5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v/>
+        <v>-12.5</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v/>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v/>
+        <v>1691.1</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1686.9</v>
+        <v>1704</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1721.3</v>
+        <v>1720.9</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1686.6</v>
+        <v>1696</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1691.1</v>
+        <v>1696.9</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>870.4</v>
+        <v>875.5</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>874</v>
+        <v>879.25</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>890.4</v>
+        <v>890.3</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>865.9</v>
+        <v>871</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>875.5</v>
+        <v>875.15</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>0.59</v>
+        <v>-0.35</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v/>
+        <v>3209.2</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3175</v>
+        <v>3204.9</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3209.2</v>
+        <v>3217.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3174.5</v>
+        <v>3166</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v/>
+        <v>-43.2</v>
       </c>
       <c r="J73" s="13" t="n">
-        <v/>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4788</v>
+        <v>4800.3</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4804.9</v>
+        <v>4850</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4890</v>
+        <v>4888.9</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4780</v>
+        <v>4825</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4800.3</v>
+        <v>4826</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>12.3</v>
+        <v>25.7</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.26</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v/>
+        <v>1132.4</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1086</v>
+        <v>1108.6</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1132.4</v>
+        <v>1113.4</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1086</v>
+        <v>1100.5</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1132.4</v>
+        <v>1103.1</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v/>
+        <v>-29.3</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v/>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1258.3</v>
+        <v>1249.3</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1258.3</v>
+        <v>1242.3</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1260.8</v>
+        <v>1284.9</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1235.6</v>
+        <v>1237.3</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1249.3</v>
+        <v>1281</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.72</v>
+        <v>31.7</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v/>
+        <v>2425</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2405.6</v>
+        <v>2434.9</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2439</v>
+        <v>2456.2</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2401.2</v>
+        <v>2412.4</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2425</v>
+        <v>2440</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v/>
+        <v>15</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>715.25</v>
+        <v>731</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>733.8</v>
+        <v>742.65</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>715.25</v>
+        <v>729.05</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>731</v>
+        <v>739.5</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>2.52</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>557</v>
+        <v>550.95</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>557.1</v>
+        <v>551.65</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>564.95</v>
+        <v>565.9</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>550.95</v>
+        <v>551.65</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>550.95</v>
+        <v>559.4</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-6.05</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>-1.09</v>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5325</v>
+        <v>5285.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5325</v>
+        <v>5308</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5362.5</v>
+        <v>5425</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5285.5</v>
+        <v>5308</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5285.5</v>
+        <v>5419</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-39.5</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>-0.74</v>
+        <v>133.5</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v/>
+        <v>986.5</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>982.9</v>
+        <v>987</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>999.3</v>
+        <v>993.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>979.4</v>
+        <v>976</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v/>
+        <v>-5.3</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v/>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>485.5</v>
+        <v>497.4</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>490.7</v>
+        <v>504.5</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>499.25</v>
+        <v>507</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>487.05</v>
+        <v>497.2</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>497.4</v>
+        <v>503.95</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>11.9</v>
+        <v>6.55</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>2.45</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v/>
+        <v>359</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>352.4</v>
+        <v>356.85</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>359</v>
+        <v>359.85</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>350.5</v>
+        <v>355.5</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>359</v>
+        <v>357.6</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v/>
+        <v>-1.4</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v/>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1942.2</v>
+        <v>1932</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1950</v>
+        <v>1940</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1959.6</v>
+        <v>1966.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1932</v>
+        <v>1939</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-0.53</v>
+        <v>15</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v/>
+        <v>35445</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>33915</v>
+        <v>35350</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>36485</v>
+        <v>35430</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33885</v>
+        <v>34455</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>35445</v>
+        <v>34685</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v/>
+        <v>-760</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v/>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>86.33</v>
+        <v>85.92</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>86</v>
+        <v>85.92</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>87.17</v>
+        <v>86.55</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.92</v>
+        <v>85.2</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>85.92</v>
+        <v>85.8</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.41</v>
+        <v>-0.12</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>-0.47</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>113.4</v>
+        <v>115.46</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>113</v>
+        <v>115.46</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>115.46</v>
+        <v>115.56</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>113</v>
+        <v>113.7</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>115.46</v>
+        <v>113.82</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>1.82</v>
+        <v>-1.64</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>148.67</v>
+        <v>148.56</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>148.5</v>
+        <v>148.56</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>151.79</v>
+        <v>149.42</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>148.1</v>
+        <v>147.8</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>148.56</v>
+        <v>148.85</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.29</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>725.85</v>
+        <v>748.05</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>722.6</v>
+        <v>741</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>732.75</v>
+        <v>745</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>6.1</v>
+        <v>12.25</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>0.84</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1662.7</v>
+        <v>1646.3</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1651.4</v>
+        <v>1650</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1667</v>
+        <v>1656</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1622.4</v>
+        <v>1630</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1646.3</v>
+        <v>1631.4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-16.4</v>
+        <v>-14.9</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-0.99</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4845</v>
+        <v>4920</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>4925</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4970</v>
+        <v>5030.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4881</v>
+        <v>4925</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4920</v>
+        <v>4941</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>1.55</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>958.2</v>
+        <v>966.3</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>963.8</v>
+        <v>961</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>969.3</v>
+        <v>966</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>955.3</v>
+        <v>956</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>966.3</v>
+        <v>956</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>0.85</v>
+        <v>-10.3</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v/>
+        <v>375.9</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>380.9</v>
+        <v>376</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>382.5</v>
+        <v>380.7</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>375.9</v>
+        <v>374.25</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>375.9</v>
+        <v>377.65</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v/>
+        <v>1.75</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1058.6</v>
+        <v>1051.4</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1061.9</v>
+        <v>1041.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1061.9</v>
+        <v>1044.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1038</v>
+        <v>1030.3</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1051.4</v>
+        <v>1038.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-7.2</v>
+        <v>-12.9</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>-0.68</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>134.27</v>
+        <v>137</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>135.02</v>
+        <v>136.9</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137</v>
+        <v>137.71</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>134.6</v>
+        <v>136.34</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>137</v>
+        <v>136.53</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>2.03</v>
+        <v>-0.47</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1970.3</v>
+        <v>2009.6</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1972.3</v>
+        <v>2012</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2038</v>
+        <v>2033.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1964</v>
+        <v>2000.8</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>2009.6</v>
+        <v>2008.2</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>1.99</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>457</v>
+        <v>476.75</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>480</v>
+        <v>479.85</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>457.15</v>
+        <v>470</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>476.75</v>
+        <v>470.7</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>4.32</v>
+        <v>-6.05</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>266.2</v>
+        <v>262.3</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>266.6</v>
+        <v>263.55</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>266.6</v>
+        <v>267.95</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>262.3</v>
+        <v>263.55</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>262.3</v>
+        <v>267</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>-1.47</v>
+        <v>4.7</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v/>
+        <v>1119.5</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1128.9</v>
+        <v>1138</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1140.2</v>
+        <v>1143.5</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1119.5</v>
+        <v>1127.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1119.5</v>
+        <v>1130.6</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v/>
+        <v>11.1</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5027</v>
+        <v>5064.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5010</v>
+        <v>5064.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5139</v>
+        <v>5108</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4990</v>
+        <v>5001.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5064.5</v>
+        <v>5087</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.75</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v/>
+        <v>750.95</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>724.5</v>
+        <v>745</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>754.95</v>
+        <v>754.35</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>724.5</v>
+        <v>739.5</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>750.95</v>
+        <v>751.45</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v/>
+        <v>0.5</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>526</v>
+        <v>522.15</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>509</v>
+        <v>514.55</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>2.73</v>
+        <v>-9</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v/>
+        <v>1275.6</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1270.1</v>
+        <v>1281.3</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1278.7</v>
+        <v>1287</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1262.7</v>
+        <v>1268.6</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1275.6</v>
+        <v>1268.6</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v/>
+        <v>-7</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>480.2</v>
+        <v>500</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>483.95</v>
+        <v>498</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>502</v>
+        <v>503.6</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>480.3</v>
+        <v>485.7</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>500</v>
+        <v>487.05</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>4.12</v>
+        <v>-12.95</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v/>
+        <v>1196.7</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1211.1</v>
+        <v>1196.5</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1216.9</v>
+        <v>1205.9</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1197</v>
+        <v>1190.1</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1202.7</v>
+        <v>1200.5</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v/>
+        <v>3.8</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>415.5</v>
+        <v>415.2</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>419.2</v>
+        <v>420.6</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>412.5</v>
+        <v>414.55</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>412.5</v>
+        <v>414.8</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>-0.96</v>
+        <v>2.3</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>559.3</v>
+        <v>532</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>559.3</v>
+        <v>536</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>559.5</v>
+        <v>538.1</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>532</v>
+        <v>526.95</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>532</v>
+        <v>536.8</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-27.3</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-4.88</v>
+        <v>4.8</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v/>
+        <v>1896.9</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1930.1</v>
+        <v>1896.9</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1959.4</v>
+        <v>1935</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1885</v>
+        <v>1896.9</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1896.9</v>
+        <v>1920.4</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v/>
+        <v>23.5</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v/>
+        <v>1954</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1962</v>
+        <v>1966.6</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1982</v>
+        <v>2023.5</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1954</v>
+        <v>1963.8</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1954</v>
+        <v>2017.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v/>
+        <v>63.5</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v/>
+        <v>548.15</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>548.6</v>
+        <v>548.3</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>552</v>
+        <v>574.15</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>543.6</v>
+        <v>543.65</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>548.15</v>
+        <v>568</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v/>
+        <v>19.85</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>3.62</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3836.2</v>
+        <v>3885</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3846</v>
+        <v>3885</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3898</v>
+        <v>3908.7</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3846</v>
+        <v>3883</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3885</v>
+        <v>3904.8</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>48.8</v>
+        <v>19.8</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>1.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v/>
+        <v>312.8</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>314.3</v>
+        <v>311.25</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>302.5</v>
+        <v>306.3</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>312.8</v>
+        <v>307.8</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v/>
+        <v>-5</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v/>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v/>
+        <v>3347.5</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3340.9</v>
+        <v>3347.5</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3367.9</v>
+        <v>3348.2</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3286.8</v>
+        <v>3294.2</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3347.5</v>
+        <v>3307</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v/>
+        <v>-40.5</v>
       </c>
       <c r="J115" s="13" t="n">
-        <v/>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2098.1</v>
+        <v>2083</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2088.1</v>
+        <v>2084</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2114.7</v>
+        <v>2129</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2075</v>
+        <v>2080</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2083</v>
+        <v>2124.5</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-0.72</v>
+        <v>41.5</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3076.5</v>
+        <v>3052</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3082</v>
+        <v>3065</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3098.2</v>
+        <v>3088</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3052</v>
+        <v>3055.3</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3052</v>
+        <v>3055.3</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-24.5</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-0.8</v>
+        <v>3.3</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v/>
+        <v>319.15</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>319</v>
+        <v>319.15</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>319.9</v>
+        <v>320</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>310</v>
+        <v>313.8</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>319.15</v>
+        <v>315.1</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v/>
+        <v>-4.05</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v/>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v/>
+        <v>803.9</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>820.05</v>
+        <v>807</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>822.45</v>
+        <v>829.75</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>803.9</v>
+        <v>804.25</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>803.9</v>
+        <v>824.4</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v/>
+        <v>20.5</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12338</v>
+        <v>12103</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12350</v>
+        <v>12129</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12458</v>
+        <v>12229</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12103</v>
+        <v>12129</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12103</v>
+        <v>12153</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-235</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-1.9</v>
+        <v>50</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v/>
+        <v>3260</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3257.5</v>
+        <v>3250</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3314.9</v>
+        <v>3268</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3230.1</v>
+        <v>3155.5</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3260</v>
+        <v>3209</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v/>
+        <v>-51</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v/>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>586.3</v>
+        <v>597.45</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>589.9</v>
+        <v>602.4</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>602.05</v>
+        <v>607.85</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>597.45</v>
+        <v>593.4</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>1.9</v>
+        <v>-4.05</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v/>
+        <v>1559</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1538.6</v>
+        <v>1551.3</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1573.6</v>
+        <v>1591.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1538</v>
+        <v>1545.7</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v/>
+        <v>10</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1071.2</v>
+        <v>1081.7</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1067.1</v>
+        <v>1079.5</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1087.5</v>
+        <v>1083.9</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1066.2</v>
+        <v>1070.5</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1081.7</v>
+        <v>1077.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>0.98</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>161.87</v>
+        <v>162.57</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>161.87</v>
+        <v>163.12</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>165.37</v>
+        <v>163.88</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>161.84</v>
+        <v>160.5</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>162.57</v>
+        <v>162.91</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v/>
+        <v>2300.4</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2322.9</v>
+        <v>2300.4</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2327.9</v>
+        <v>2313.7</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2275</v>
+        <v>2257.1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2300.4</v>
+        <v>2296.2</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v/>
+        <v>-4.2</v>
       </c>
       <c r="J127" s="13" t="n">
-        <v/>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v/>
+        <v>125670</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>124900</v>
+        <v>125780</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>126500</v>
+        <v>125780</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>123815</v>
+        <v>124700</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>125670</v>
+        <v>124855</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v/>
+        <v>-815</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v/>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v/>
+        <v>2841.1</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2796.6</v>
+        <v>2826</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2852</v>
+        <v>2874.2</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2784.3</v>
+        <v>2814</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2841.1</v>
+        <v>2854.2</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v/>
+        <v>13.1</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>355.7</v>
+        <v>350.5</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>359.8</v>
+        <v>355.3</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>363.2</v>
+        <v>357.4</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>350.5</v>
+        <v>351.55</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>350.5</v>
+        <v>352.5</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>-1.46</v>
+        <v>2</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v/>
+        <v>1251.2</v>
       </c>
       <c r="E131" s="9" t="n">
         <v>1265</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1284</v>
+        <v>1305.3</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1251.2</v>
+        <v>1251.4</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1251.2</v>
+        <v>1296.4</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v/>
+        <v>45.2</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>3.61</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8220</v>
+        <v>8590</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8257</v>
+        <v>8590</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8682.5</v>
+        <v>8594</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8231.5</v>
+        <v>8405</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8590</v>
+        <v>8486.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>370</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>4.5</v>
+        <v>-103.5</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v/>
+        <v>1372.4</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1372.1</v>
+        <v>1360</v>
       </c>
       <c r="F133" s="9" t="n">
         <v>1390</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1332.8</v>
+        <v>1360</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1372.4</v>
+        <v>1385</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v/>
+        <v>12.6</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>80.8</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>81.38</v>
+        <v>80.09</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>81.7</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>79.15000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>79.15000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>-2.04</v>
+        <v>0.65</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>329.6</v>
+        <v>323.65</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>329.8</v>
+        <v>325</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>330.85</v>
+        <v>328.75</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>323.65</v>
+        <v>324.85</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>323.65</v>
+        <v>326.4</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-5.95</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>-1.81</v>
+        <v>2.75</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v/>
+        <v>1785</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1730.1</v>
+        <v>1765</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1785</v>
+        <v>1827.7</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1721</v>
+        <v>1754.3</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1785</v>
+        <v>1821</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v/>
+        <v>36</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11620</v>
+        <v>11896</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11648</v>
+        <v>11787</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11896</v>
+        <v>11787</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>11515</v>
+        <v>10900</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>11896</v>
+        <v>10911</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>276</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>2.38</v>
+        <v>-985</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>232.43</v>
+        <v>232.8</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>232.43</v>
+        <v>232.8</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>234.32</v>
+        <v>236</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>231.75</v>
+        <v>232.32</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>232.8</v>
+        <v>235.63</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>0.37</v>
+        <v>2.83</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>0.16</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35020</v>
+        <v>36400</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>34990</v>
+        <v>35975</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>36400</v>
+        <v>36300</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34900</v>
+        <v>35495</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36400</v>
+        <v>35950</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>1380</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>3.94</v>
+        <v>-450</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v/>
+        <v>5416</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5476</v>
+        <v>5416</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5500</v>
+        <v>5458</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5389</v>
+        <v>5380.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5416</v>
+        <v>5449</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v/>
+        <v>33</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>283.45</v>
+        <v>292.6</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>284.85</v>
+        <v>287</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>292.6</v>
+        <v>289.65</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>284.1</v>
+        <v>286.6</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>292.6</v>
+        <v>287.5</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>3.23</v>
+        <v>-5.1</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>345</v>
+        <v>342.6</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>347.1</v>
+        <v>348.05</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>342.55</v>
+        <v>342.6</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>342.55</v>
+        <v>344.75</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1551.5</v>
+        <v>1572.1</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1559.9</v>
+        <v>1598</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1598.9</v>
+        <v>1598</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1559.9</v>
+        <v>1573.2</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1572.1</v>
+        <v>1573.2</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>20.6</v>
+        <v>1.1</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>1.33</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2307</v>
+        <v>2366.8</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2307</v>
+        <v>2324</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2366.8</v>
+        <v>2342.7</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2302.5</v>
+        <v>2315.7</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2366.8</v>
+        <v>2321.8</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>2.59</v>
+        <v>-45</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>116.47</v>
+        <v>117.27</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>117</v>
+        <v>117.23</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>117.5</v>
+        <v>118.58</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.5</v>
+        <v>116.64</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>117.27</v>
+        <v>118</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8208.5</v>
+        <v>8400</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8256</v>
+        <v>8352.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8400</v>
+        <v>8429</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8235</v>
+        <v>8331</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8400</v>
+        <v>8369.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>2.33</v>
+        <v>-30.5</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v/>
+        <v>270.3</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>264.6</v>
+        <v>267.75</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>270.3</v>
+        <v>269.05</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>263.4</v>
+        <v>266.1</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>270.3</v>
+        <v>266.1</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v/>
+        <v>-4.2</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v/>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1272.7</v>
+        <v>1324.7</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1277.5</v>
+        <v>1328.7</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1339.8</v>
+        <v>1357.8</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1270</v>
+        <v>1322.6</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1324.7</v>
+        <v>1349.3</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>52</v>
+        <v>24.6</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>4.09</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>404.15</v>
+        <v>415.9</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>406.15</v>
+        <v>408</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>415.9</v>
+        <v>409.9</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>405</v>
+        <v>401.1</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>415.9</v>
+        <v>402.4</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>2.91</v>
+        <v>-13.5</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v/>
+        <v>312</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>313.4</v>
+        <v>313.45</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>309.05</v>
+        <v>310.2</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>312</v>
+        <v>310.2</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v/>
+        <v>-1.8</v>
       </c>
       <c r="J151" s="13" t="n">
-        <v/>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1245</v>
+        <v>1234.1</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1247.3</v>
+        <v>1249.1</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1226.4</v>
+        <v>1232.5</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1226.4</v>
+        <v>1247.4</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>-1.41</v>
+        <v>21</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>175.01</v>
+        <v>177.33</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="F153" s="9" t="n">
         <v>179.8</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>176.03</v>
+        <v>175.1</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>177.33</v>
+        <v>177.3</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>1.33</v>
+        <v>-0.03</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>636.95</v>
+        <v>651.15</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>635.95</v>
+        <v>642.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>651.15</v>
+        <v>643.65</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>630.7</v>
+        <v>636.2</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>651.15</v>
+        <v>637</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>2.23</v>
+        <v>-14.15</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1766.9</v>
+        <v>1731</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1751.3</v>
+        <v>1744</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1770</v>
+        <v>1774.4</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1731</v>
+        <v>1734.3</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1731</v>
+        <v>1756</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-35.9</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>-2.03</v>
+        <v>25</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>988.7</v>
+        <v>996.2</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>992</v>
+        <v>993.6</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>996.2</v>
+        <v>997.5</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>985.1</v>
+        <v>989.1</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>996.2</v>
+        <v>996</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>0.76</v>
+        <v>-0.2</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>21960</v>
+        <v>22600</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22200</v>
+        <v>22450</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>23000</v>
+        <v>22700</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22100</v>
+        <v>22355</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22600</v>
+        <v>22550</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>640</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>2.91</v>
+        <v>-50</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1004.9</v>
+        <v>1019</v>
       </c>
       <c r="F158" s="12" t="n">
         <v>1019</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1000.5</v>
+        <v>1005.3</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1010</v>
+        <v>1011.8</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.51</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v/>
+        <v>3913.9</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3781.4</v>
+        <v>3880</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3913.9</v>
+        <v>3919</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3770</v>
+        <v>3851.5</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3913.9</v>
+        <v>3887</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v/>
+        <v>-26.9</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v/>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2536</v>
+        <v>2512</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2536.6</v>
+        <v>2530.9</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2569.9</v>
+        <v>2563</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2512</v>
+        <v>2530.9</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2512</v>
+        <v>2540</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-24</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>-0.95</v>
+        <v>28</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1867.3</v>
+        <v>1837.3</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1866.1</v>
+        <v>1832.2</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1877.2</v>
+        <v>1891.5</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1837.3</v>
+        <v>1832.2</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1837.3</v>
+        <v>1868.9</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>-1.61</v>
+        <v>31.6</v>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>1.72</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v/>
+        <v>451.7</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>469.8</v>
+        <v>451.7</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>470.4</v>
+        <v>460.75</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>449.05</v>
+        <v>447.2</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>451.7</v>
+        <v>457.55</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v/>
+        <v>5.85</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v/>
+        <v>369.05</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>379.1</v>
+        <v>369.95</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>384</v>
+        <v>387.05</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>366.65</v>
+        <v>360.4</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>369.05</v>
+        <v>385.15</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v/>
+        <v>16.1</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>4.36</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>779.3</v>
+        <v>693.25</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>729</v>
+        <v>687.6</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>741.35</v>
+        <v>698.5</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>687.1</v>
+        <v>668.6</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>693.25</v>
+        <v>694.7</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-86.05</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-11.04</v>
+        <v>1.45</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v/>
+        <v>1780.1</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1794.8</v>
+        <v>1771</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1805</v>
+        <v>1789.6</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1743.3</v>
+        <v>1725</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1780.1</v>
+        <v>1732.7</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v/>
+        <v>-47.4</v>
       </c>
       <c r="J165" s="13" t="n">
-        <v/>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1013.7</v>
+        <v>996</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1016.2</v>
+        <v>998.9</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1018.7</v>
+        <v>1015.5</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>996</v>
+        <v>997.2</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>996</v>
+        <v>1000.6</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-1.75</v>
+        <v>4.6</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>369</v>
+        <v>374.8</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>364.8</v>
+        <v>367.3</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>374.8</v>
+        <v>369.6</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>360.9</v>
+        <v>365.65</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>374.8</v>
+        <v>367.15</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>1.57</v>
+        <v>-7.65</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>187.29</v>
+        <v>185.54</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>186.4</v>
+        <v>184.55</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>187.96</v>
+        <v>186.87</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>185.54</v>
+        <v>183.34</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>185.54</v>
+        <v>183.4</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-1.75</v>
+        <v>-2.14</v>
       </c>
       <c r="J169" s="13" t="n">
-        <v>-0.93</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2190</v>
+        <v>2105</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2177.2</v>
+        <v>2090</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2177.3</v>
+        <v>2145</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2101.2</v>
+        <v>2075.3</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2105</v>
+        <v>2128.7</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-85</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-3.88</v>
+        <v>23.7</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v/>
+        <v>1537.1</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1558.3</v>
+        <v>1529</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1561.2</v>
+        <v>1560.6</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1523.1</v>
+        <v>1525.1</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1537.1</v>
+        <v>1558.5</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v/>
+        <v>21.4</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>1.39</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2598.8</v>
+        <v>2600</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2598.9</v>
+        <v>2601</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2637.8</v>
+        <v>2614.2</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2571.5</v>
+        <v>2569.1</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2600</v>
+        <v>2588</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v>0.05</v>
+        <v>-12</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4841</v>
+        <v>4798.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4851</v>
+        <v>4816.5</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4864.5</v>
+        <v>4880</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4772</v>
+        <v>4780</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4798.5</v>
+        <v>4875</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>-0.88</v>
+        <v>76.5</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v/>
+        <v>4840</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4874.5</v>
+        <v>4860</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4928</v>
+        <v>4986.5</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4827</v>
+        <v>4848.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4840</v>
+        <v>4970</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v/>
+        <v>130</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1276.4</v>
+        <v>1258.8</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1277</v>
+        <v>1250</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1285.7</v>
+        <v>1269.8</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1258.8</v>
+        <v>1262</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>-1.38</v>
+        <v>3.2</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2789</v>
+        <v>2824</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2789.3</v>
+        <v>2813.9</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2824</v>
+        <v>2836.9</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2776.1</v>
+        <v>2801</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2824</v>
+        <v>2815.5</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>1.25</v>
+        <v>-8.5</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4101.7</v>
+        <v>4171.3</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4125</v>
+        <v>4173.1</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4195</v>
+        <v>4208.1</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4122.1</v>
+        <v>4155</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4171.3</v>
+        <v>4155</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>1.7</v>
+        <v>-16.3</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v/>
+        <v>1251.5</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1219.9</v>
+        <v>1251.5</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1219.9</v>
+        <v>1225</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1251.5</v>
+        <v>1227.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v/>
+        <v>-23.7</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v/>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>10890</v>
+        <v>11014</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11060</v>
+        <v>11146</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10819</v>
+        <v>10983</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>250</v>
+        <v>86</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>2.32</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
+        <v>176.56</v>
+      </c>
+      <c r="E180" s="12" t="n">
+        <v>177.11</v>
+      </c>
+      <c r="F180" s="12" t="n">
+        <v>178.87</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>177.03</v>
+      </c>
+      <c r="H180" s="12" t="n">
         <v>178.09</v>
       </c>
-      <c r="E180" s="12" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="F180" s="12" t="n">
-        <v>178.92</v>
-      </c>
-      <c r="G180" s="12" t="n">
-        <v>176.56</v>
-      </c>
-      <c r="H180" s="12" t="n">
-        <v>176.56</v>
-      </c>
       <c r="I180" s="12" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>-0.86</v>
+        <v>1.53</v>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>554.75</v>
+        <v>580</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>554</v>
+        <v>564.2</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>580</v>
+        <v>569.2</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>553.4</v>
+        <v>559.9</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>580</v>
+        <v>559.9</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>4.55</v>
+        <v>-20.1</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>257.45</v>
+        <v>267.6</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>258</v>
+        <v>264.5</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>267.6</v>
+        <v>264.5</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>267.6</v>
+        <v>260.5</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>3.94</v>
+        <v>-7.1</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1135</v>
+        <v>1110.9</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1136</v>
+        <v>1125</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1145.3</v>
+        <v>1158.8</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1110.9</v>
+        <v>1125</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1110.9</v>
+        <v>1142.1</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>-2.12</v>
+        <v>31.2</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>166.4</v>
+        <v>166.83</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>166.9</v>
+        <v>165.24</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>166.9</v>
+        <v>165.5</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>163.3</v>
+        <v>163.34</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>166.83</v>
+        <v>164.55</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>0.26</v>
+        <v>-2.28</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1135.1</v>
+        <v>1160</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1150.7</v>
+        <v>1155</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1167.3</v>
+        <v>1173.5</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1147.7</v>
+        <v>1152.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>24.9</v>
+        <v>1</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>2.19</v>
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  18-Sep-2026 04:57 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  21-Sep-2026 06:29 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-Sep-2026 04:57 PM</t>
+          <t>21-Sep-2026 06:29 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 21-Sep-2026 06:29 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 22-Sep-2026 05:31 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>21-Sep-2026 06:29 PM</t>
+          <t>22-Sep-2026 05:31 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  21-Sep-2026 06:29 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  22-Sep-2026 05:31 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>491.15</v>
+        <v>499.8</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>483</v>
+        <v>500.35</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>502</v>
+        <v>504.8</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>481.05</v>
+        <v>492.05</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>499.8</v>
+        <v>496</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>8.65</v>
+        <v>-3.8</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1.76</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7270.5</v>
+        <v>7271</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7240</v>
+        <v>7261.5</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7330</v>
+        <v>7405.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7221</v>
+        <v>7117.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7271</v>
+        <v>7120.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>0.5</v>
+        <v>-150.5</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.01</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>27270</v>
+        <v>26960</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>27200</v>
+        <v>26960</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27300</v>
+        <v>27295</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26815</v>
+        <v>26960</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26960</v>
+        <v>27225</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-310</v>
+        <v>265</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>-1.14</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>410.05</v>
+        <v>403.4</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>405.1</v>
+        <v>401</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>405.45</v>
+        <v>405</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>400.95</v>
+        <v>394.65</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>403.4</v>
+        <v>397</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-1.62</v>
+        <v>-6.4</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.16</v>
+        <v>49.85</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.15</v>
+        <v>49.97</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.56</v>
+        <v>50.24</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>49.7</v>
+        <v>49.01</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1259.7</v>
+        <v>1256.3</v>
       </c>
       <c r="E8" s="12" t="n">
+        <v>1256.5</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>1260</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>1272</v>
-      </c>
       <c r="G8" s="12" t="n">
-        <v>1251</v>
+        <v>1234.8</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1256.3</v>
+        <v>1238.2</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>-0.27</v>
+        <v>-18.1</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3020</v>
+        <v>2975</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2995.6</v>
+        <v>2995</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3015.9</v>
+        <v>3026.1</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2973</v>
+        <v>2979.6</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2975</v>
+        <v>2997</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-45</v>
+        <v>22</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>-1.49</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1824</v>
+        <v>1787.1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1793.7</v>
+        <v>1796</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1796.8</v>
+        <v>1812.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1766.7</v>
+        <v>1786.1</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1787.1</v>
+        <v>1795</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-36.9</v>
+        <v>7.9</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>-2.02</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5466.5</v>
+        <v>5364</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5395</v>
+        <v>5365</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5411</v>
+        <v>5419.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5316.5</v>
+        <v>5308.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5364</v>
+        <v>5331.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-102.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>-1.88</v>
+        <v>-32.5</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>388.3</v>
+        <v>390.75</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>389.1</v>
+        <v>391.1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>395.95</v>
+        <v>394</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>389.1</v>
+        <v>385.15</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>390.75</v>
+        <v>386.9</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>2.45</v>
+        <v>-3.85</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.63</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>299.1</v>
+        <v>296.15</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>299.2</v>
+        <v>296.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>302</v>
+        <v>298.65</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>295.2</v>
+        <v>293.2</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>296.15</v>
+        <v>295.1</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>-0.99</v>
+        <v>-1.05</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2270.1</v>
+        <v>2181.1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2224.2</v>
+        <v>2180.9</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2229</v>
+        <v>2199.3</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2178.7</v>
+        <v>2159.9</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2181.1</v>
+        <v>2195</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-89</v>
+        <v>13.9</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-3.92</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8944.5</v>
+        <v>8912</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8889</v>
+        <v>8960</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8974.5</v>
+        <v>9000</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8826.5</v>
+        <v>8822.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8912</v>
+        <v>8835.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-32.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.36</v>
+        <v>-76.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="16">
@@ -1278,22 +1278,22 @@
         <v>409.3</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>410</v>
+        <v>409.3</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>413.8</v>
+        <v>411.35</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>408.35</v>
+        <v>401</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>409.3</v>
+        <v>402.55</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0</v>
+        <v>-6.75</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>163</v>
+        <v>161.75</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>163</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>163.19</v>
+        <v>164.2</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>160.87</v>
+        <v>159.8</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>161.75</v>
+        <v>160.75</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>-0.77</v>
+        <v>-1</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2451.3</v>
+        <v>2440.3</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2450</v>
+        <v>2475.1</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2463.8</v>
+        <v>2475.1</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2440.3</v>
+        <v>2435.6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2440.3</v>
+        <v>2448.5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-0.45</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1427.7</v>
+        <v>1400.9</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1421.8</v>
+        <v>1401</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1426.1</v>
+        <v>1407.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1400.9</v>
+        <v>1381.6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1400.9</v>
+        <v>1381.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-26.8</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>-1.88</v>
+        <v>-19.3</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>660.7</v>
+        <v>638.4</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>657.65</v>
+        <v>640</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>659.05</v>
+        <v>642.95</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>629.15</v>
+        <v>622.2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>638.4</v>
+        <v>626.25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-22.3</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>-3.38</v>
+        <v>-12.15</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6170.5</v>
+        <v>6086</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6120</v>
+        <v>6128</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6150</v>
+        <v>6234</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6058.5</v>
+        <v>6096</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6086</v>
+        <v>6176.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-84.5</v>
+        <v>90.5</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>-1.37</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1058.6</v>
+        <v>1038</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1046.8</v>
+        <v>1037.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1046.8</v>
+        <v>1043.5</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1037.2</v>
+        <v>1027.6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1038</v>
+        <v>1036.4</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>-1.95</v>
+        <v>-1.6</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1734</v>
+        <v>1713.4</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1709.8</v>
+        <v>1718.3</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1738.9</v>
+        <v>1719</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1706.4</v>
+        <v>1689.3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1713.4</v>
+        <v>1700</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>-1.19</v>
+        <v>-13.4</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1248</v>
+        <v>1245.2</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1254.3</v>
+        <v>1255.6</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1242</v>
+        <v>1240.1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1250</v>
+        <v>1242.7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-7.3</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11414</v>
+        <v>11460</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11470</v>
+        <v>11460</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11533</v>
+        <v>11515</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11450</v>
+        <v>11281</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11460</v>
+        <v>11363</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>46</v>
+        <v>-97</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.4</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1852.5</v>
+        <v>1849.8</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1860.2</v>
+        <v>1862.7</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1849.2</v>
+        <v>1823.4</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1849.8</v>
+        <v>1823.4</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>-0.15</v>
+        <v>-26.4</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1040.3</v>
+        <v>1021.3</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1035</v>
+        <v>1025.3</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1037.7</v>
+        <v>1029.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1021.3</v>
+        <v>1005</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1021.3</v>
+        <v>1008.8</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>-1.83</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2265.3</v>
+        <v>2216.8</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2259</v>
+        <v>2224</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2259</v>
+        <v>2231</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2200.5</v>
+        <v>2202.3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2216.8</v>
+        <v>2216.9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-48.5</v>
+        <v>0.1</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>-2.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>672.6</v>
+        <v>663.65</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>672.6</v>
+        <v>661</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>678</v>
+        <v>668.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>661.1</v>
+        <v>651.3</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>663.65</v>
+        <v>661.05</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>-1.33</v>
+        <v>-2.6</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>181.26</v>
+        <v>185.11</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>175.63</v>
+        <v>179.9</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>179</v>
+        <v>184.7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>2.29</v>
+        <v>5.7</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>3.18</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>234.94</v>
+        <v>233.64</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>234</v>
+        <v>233.64</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>234.51</v>
+        <v>234.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>232.52</v>
+        <v>232.71</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>233.64</v>
+        <v>234.35</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-1.3</v>
+        <v>0.71</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>-0.55</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>393.3</v>
+        <v>398.5</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>394.35</v>
+        <v>398.5</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>399.15</v>
+        <v>400.65</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>393.1</v>
+        <v>395.8</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>398.5</v>
+        <v>397.9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>5.2</v>
+        <v>-0.6</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1.32</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>458.65</v>
+        <v>450.6</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>460.8</v>
+        <v>453</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>463</v>
+        <v>456.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>448.1</v>
+        <v>448</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>450.6</v>
+        <v>452.6</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-8.050000000000001</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>-1.76</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1893.3</v>
+        <v>1830.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1854.8</v>
+        <v>1833.9</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1854.8</v>
+        <v>1836.3</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1822</v>
+        <v>1813</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1830.2</v>
+        <v>1817.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-63.1</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>-3.33</v>
+        <v>-13</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>439.9</v>
+        <v>433.4</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>433</v>
+        <v>435.2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>438.3</v>
+        <v>439.7</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>430.2</v>
+        <v>424.65</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>433.4</v>
+        <v>425.8</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>-1.48</v>
+        <v>-7.6</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>388.3</v>
+        <v>394.3</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>396.15</v>
+        <v>396.25</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>387.6</v>
+        <v>389</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>2.6</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47000</v>
+        <v>47565</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47460</v>
+        <v>47795</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48180</v>
+        <v>48290</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47460</v>
+        <v>47530</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47565</v>
+        <v>48290</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>565</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>1.2</v>
+        <v>725</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>314</v>
+        <v>312.75</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>315.95</v>
+        <v>318.2</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>310.85</v>
+        <v>308.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>312.75</v>
+        <v>313.6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-1.25</v>
+        <v>0.85</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>-0.4</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4998</v>
+        <v>5023</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5001.5</v>
+        <v>5030</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5030.5</v>
+        <v>5030</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4991.5</v>
+        <v>4915</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5023</v>
+        <v>4918</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>25</v>
+        <v>-105</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.5</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>280.4</v>
+        <v>284.15</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>280.4</v>
+        <v>284.15</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>284.9</v>
+        <v>284.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>278</v>
+        <v>280.75</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>284.15</v>
+        <v>281.15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>3.75</v>
+        <v>-3</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1.34</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>123.78</v>
+        <v>123.7</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>123.23</v>
+        <v>124.02</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>123.99</v>
+        <v>124.69</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>122.95</v>
+        <v>122.8</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>123.7</v>
+        <v>122.9</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>-0.06</v>
+        <v>-0.8</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>778.5</v>
+        <v>769.9</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>783</v>
+        <v>775.55</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>766.05</v>
+        <v>755.3</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>769.9</v>
+        <v>759.55</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>-1.1</v>
+        <v>-10.35</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>414.9</v>
+        <v>417.2</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>415</v>
+        <v>417.95</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>420</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>413.25</v>
+        <v>414.3</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>417.2</v>
+        <v>418.5</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>0.55</v>
+        <v>1.3</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1800</v>
+        <v>1764</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1806</v>
+        <v>1769.9</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1806</v>
+        <v>1779.4</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1763.5</v>
+        <v>1756.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1764</v>
+        <v>1759.1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-36</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>-2</v>
+        <v>-4.9</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1394.5</v>
+        <v>1386.1</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1383.2</v>
+        <v>1386.3</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1405.2</v>
+        <v>1388.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1378.3</v>
+        <v>1364.5</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1386.1</v>
+        <v>1384.1</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>409.9</v>
+        <v>414.7</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>411.7</v>
+        <v>424.7</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>415.4</v>
+        <v>428.75</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>410.45</v>
+        <v>419.65</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>414.7</v>
+        <v>428</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>1.17</v>
+        <v>13.3</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>3.21</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1841</v>
+        <v>1814</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1819.4</v>
+        <v>1818</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1791</v>
+        <v>1784.4</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1814</v>
+        <v>1803</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-27</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>-1.47</v>
+        <v>-11</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1917.8</v>
+        <v>1892</v>
       </c>
       <c r="E48" s="12" t="n">
+        <v>1892.1</v>
+      </c>
+      <c r="F48" s="12" t="n">
         <v>1892.3</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>1903</v>
-      </c>
       <c r="G48" s="12" t="n">
-        <v>1879.4</v>
+        <v>1863</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1892</v>
+        <v>1869</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-25.8</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>-1.35</v>
+        <v>-23</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>503.55</v>
+        <v>487.05</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>498.6</v>
+        <v>489.5</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>501.95</v>
+        <v>489.5</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>487.05</v>
+        <v>466.7</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>487.05</v>
+        <v>467</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-3.28</v>
+        <v>-20.05</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1999.5</v>
+        <v>1940.8</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1976.2</v>
+        <v>1935</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1990</v>
+        <v>1953.4</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1936.1</v>
+        <v>1935</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1940.8</v>
+        <v>1944.9</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-58.7</v>
+        <v>4.1</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>-2.94</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>227.12</v>
+        <v>225.05</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>226.53</v>
+        <v>224.75</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>226.69</v>
+        <v>225.71</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>225.05</v>
+        <v>221.76</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>225.05</v>
+        <v>222</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>-0.91</v>
+        <v>-3.05</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>235.79</v>
+        <v>234.94</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>236</v>
+        <v>234.9</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>237.74</v>
+        <v>235.78</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>233.1</v>
+        <v>226</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>234.94</v>
+        <v>227.21</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>-0.36</v>
+        <v>-7.73</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5099.5</v>
+        <v>5067</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5100</v>
+        <v>5090</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5135</v>
+        <v>5128.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5050</v>
+        <v>4962.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5067</v>
+        <v>4962.5</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-32.5</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>-0.64</v>
+        <v>-104.5</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>395.25</v>
+        <v>386.8</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>390</v>
+        <v>388.3</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>392.8</v>
+        <v>390.1</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>386.8</v>
+        <v>385.2</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>386.8</v>
+        <v>388.1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-8.449999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>-2.14</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1761.4</v>
+        <v>1764.4</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1814.4</v>
+        <v>1785.4</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1757.1</v>
+        <v>1736.3</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1764.4</v>
+        <v>1741.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>3</v>
+        <v>-22.8</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.17</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="56">
@@ -2638,22 +2638,22 @@
         <v>1586.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1586.3</v>
+        <v>1605.1</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1602</v>
+        <v>1623.8</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1570.1</v>
+        <v>1593.4</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1586.3</v>
+        <v>1613.2</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>0</v>
+        <v>26.9</v>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>58.34</v>
+        <v>61.59</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>58.5</v>
+        <v>61.99</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>64</v>
+        <v>63.55</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>58.36</v>
+        <v>61.02</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>61.59</v>
+        <v>61.77</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>5.57</v>
+        <v>0.18</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9375</v>
+        <v>9410.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9418</v>
+        <v>9444</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9461.5</v>
+        <v>9444</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9375.5</v>
+        <v>9315.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9410.5</v>
+        <v>9352</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>35.5</v>
+        <v>-58.5</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.38</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>12995</v>
+        <v>13350</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13128</v>
+        <v>13364</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13415</v>
+        <v>13434</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13125</v>
+        <v>12996</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13350</v>
+        <v>13084</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>355</v>
+        <v>-266</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>2.73</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>644.35</v>
+        <v>660.25</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>645.1</v>
+        <v>662</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>660.95</v>
+        <v>671.9</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>644</v>
+        <v>659.05</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>660.25</v>
+        <v>669.5</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>2.47</v>
+        <v>9.25</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1185</v>
+        <v>1198.3</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1185</v>
+        <v>1207</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1211.9</v>
+        <v>1222</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1185</v>
+        <v>1201.2</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1198.3</v>
+        <v>1211</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>1.12</v>
+        <v>12.7</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7516</v>
+        <v>7512.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7550</v>
+        <v>7519</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7569.5</v>
+        <v>7555</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7490</v>
+        <v>7427</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7512.5</v>
+        <v>7427</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-0.05</v>
+        <v>-85.5</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2798.2</v>
+        <v>2819.8</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2798</v>
+        <v>2833.9</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2859.3</v>
+        <v>2848.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2797.2</v>
+        <v>2787</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2819.8</v>
+        <v>2793.6</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>21.6</v>
+        <v>-26.2</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.77</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>435.85</v>
+        <v>434.5</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>434.75</v>
+        <v>434.5</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>437.3</v>
+        <v>438.5</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>430.7</v>
+        <v>427.5</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>434.5</v>
+        <v>429.7</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>-0.31</v>
+        <v>-4.8</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>332.75</v>
+        <v>332</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>333.1</v>
+        <v>332.3</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>335.35</v>
+        <v>334.85</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>328.8</v>
+        <v>325.5</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>-0.23</v>
+        <v>-5</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>173.9</v>
+        <v>172.61</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.6</v>
+        <v>173.08</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>174.38</v>
+        <v>174.3</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>172.61</v>
+        <v>171.35</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>172.61</v>
+        <v>171.84</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2447.4</v>
+        <v>2450</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2425</v>
+        <v>2460.4</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2473.6</v>
+        <v>2472</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2424</v>
+        <v>2443</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2450</v>
+        <v>2461.4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>0.11</v>
+        <v>11.4</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>588.9</v>
+        <v>589.9</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>588.9</v>
+        <v>592.1</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>598.85</v>
+        <v>615.85</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>582.75</v>
+        <v>589.3</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>589.9</v>
+        <v>598.7</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>0.17</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>880</v>
+        <v>867.5</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>879</v>
+        <v>869.8</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>891</v>
+        <v>878.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>866.1</v>
+        <v>864.2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>867.5</v>
+        <v>873.6</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-12.5</v>
+        <v>6.1</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>-1.42</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1691.1</v>
+        <v>1696.9</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1704</v>
+        <v>1710</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1720.9</v>
+        <v>1732</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1696</v>
+        <v>1690.2</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1696.9</v>
+        <v>1699.5</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>0.34</v>
+        <v>2.6</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>875.5</v>
+        <v>875.15</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>879.25</v>
+        <v>876</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>890.3</v>
+        <v>876.6</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>871</v>
+        <v>853.9</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>875.15</v>
+        <v>864.05</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>-0.04</v>
+        <v>-11.1</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3204.9</v>
+        <v>3171</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3217.3</v>
+        <v>3180.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3166</v>
+        <v>3125</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-43.2</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>-1.35</v>
+        <v>-37.8</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="74">
@@ -3264,7 +3264,7 @@
       <c r="I74" s="12" t="n">
         <v/>
       </c>
-      <c r="J74" s="13" t="n">
+      <c r="J74" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4800.3</v>
+        <v>4826</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4850</v>
+        <v>4834.8</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4888.9</v>
+        <v>4879.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4825</v>
+        <v>4776.2</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4826</v>
+        <v>4800</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>25.7</v>
+        <v>-26</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1132.4</v>
+        <v>1103.1</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1108.6</v>
+        <v>1103.6</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1113.4</v>
+        <v>1109.4</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1100.5</v>
+        <v>1086</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1103.1</v>
+        <v>1088.9</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-29.3</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>-2.59</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1249.3</v>
+        <v>1281</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1242.3</v>
+        <v>1280</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1284.9</v>
+        <v>1286.1</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1237.3</v>
+        <v>1240.3</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1281</v>
+        <v>1270.4</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>31.7</v>
+        <v>-10.6</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>2.54</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2425</v>
+        <v>2440</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2434.9</v>
+        <v>2438.2</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2456.2</v>
+        <v>2451.8</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2412.4</v>
+        <v>2414.1</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.62</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>731</v>
+        <v>739.5</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>731</v>
+        <v>738.85</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>742.65</v>
+        <v>749.3</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>729.05</v>
+        <v>738.6</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>739.5</v>
+        <v>738.6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>8.5</v>
+        <v>-0.9</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>1.16</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>550.95</v>
+        <v>559.4</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>551.65</v>
+        <v>560.55</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>565.9</v>
+        <v>567.4</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>551.65</v>
+        <v>559.05</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>559.4</v>
+        <v>559.2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>8.449999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>1.53</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5285.5</v>
+        <v>5419</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5308</v>
+        <v>5424</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5425</v>
+        <v>5443</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5308</v>
+        <v>5368</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5419</v>
+        <v>5373</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>133.5</v>
+        <v>-46</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>2.53</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>987</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>993.5</v>
+        <v>987.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>976</v>
+        <v>967.1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>981.2</v>
+        <v>973</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>-0.54</v>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>497.4</v>
+        <v>503.95</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>504.5</v>
+        <v>510.05</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>507</v>
+        <v>521.7</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>497.2</v>
+        <v>507.1</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>503.95</v>
+        <v>508.2</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>1.32</v>
+        <v>4.25</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>359</v>
+        <v>357.6</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>356.85</v>
+        <v>359.2</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>359.85</v>
+        <v>365.2</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>355.5</v>
+        <v>354.7</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>357.6</v>
+        <v>360.7</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>-0.39</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1940</v>
+        <v>1952</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1966.6</v>
+        <v>1956.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1939</v>
+        <v>1933.8</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1947</v>
+        <v>1933.8</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>15</v>
+        <v>-13.2</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.78</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>35445</v>
+        <v>34685</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>35350</v>
+        <v>34685</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>35430</v>
+        <v>34890</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>34455</v>
+        <v>33950</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34685</v>
+        <v>34025</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-760</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>-2.14</v>
+        <v>-660</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>85.92</v>
+        <v>85.8</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>85.92</v>
+        <v>85.64</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.55</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>85.8</v>
+        <v>85.37</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>-0.14</v>
+        <v>-0.43</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>115.46</v>
+        <v>113.82</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>115.46</v>
+        <v>113.82</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>115.56</v>
+        <v>114.12</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>113.7</v>
+        <v>112.12</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>113.82</v>
+        <v>112.9</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-1.42</v>
+        <v>-0.92</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>148.56</v>
+        <v>148.85</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>148.56</v>
+        <v>148.71</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>149.42</v>
+        <v>148.99</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>147.8</v>
+        <v>145.5</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>148.85</v>
+        <v>146.68</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.29</v>
+        <v>-2.17</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.2</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>732.75</v>
+        <v>745</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>748.05</v>
+        <v>749.4</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>755</v>
+        <v>749.4</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>741</v>
+        <v>735.75</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>745</v>
+        <v>736.25</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>12.25</v>
+        <v>-8.75</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.67</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1646.3</v>
+        <v>1631.4</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1650</v>
+        <v>1635</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1656</v>
+        <v>1645</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>1630</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1631.4</v>
+        <v>1635.2</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-14.9</v>
+        <v>3.8</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-0.91</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4920</v>
+        <v>4941</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4925</v>
+        <v>5000</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5030.5</v>
+        <v>5064</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4925</v>
+        <v>4943</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4941</v>
+        <v>5030</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>0.43</v>
+        <v>89</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>966.3</v>
+        <v>956</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>966</v>
+        <v>963.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>956</v>
+        <v>949.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-1.07</v>
+        <v>-1</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>375.9</v>
+        <v>377.65</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>380.7</v>
+        <v>382.1</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>374.25</v>
+        <v>373.65</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>377.65</v>
+        <v>382.1</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>0.47</v>
+        <v>4.45</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1051.4</v>
+        <v>1038.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1041.5</v>
+        <v>1037.7</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1044.5</v>
+        <v>1041</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1030.3</v>
+        <v>1019.2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1038.5</v>
+        <v>1029.4</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-1.23</v>
+        <v>-9.1</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>137</v>
+        <v>136.53</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>136.9</v>
+        <v>137.53</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137.71</v>
+        <v>139.3</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>136.34</v>
+        <v>136.8</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>136.53</v>
+        <v>137.8</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.47</v>
+        <v>1.27</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>-0.34</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2009.6</v>
+        <v>2008.2</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>2012</v>
+        <v>2015.5</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2033.9</v>
+        <v>2037</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>2000.8</v>
+        <v>1980</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>2008.2</v>
+        <v>1992.4</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-15.8</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>476.75</v>
+        <v>470.2</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>479.85</v>
+        <v>474.6</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>470</v>
+        <v>466.35</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>470.7</v>
+        <v>469.65</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-6.05</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-1.27</v>
+        <v>-0.55</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>262.3</v>
+        <v>267</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>263.55</v>
+        <v>267.9</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>267.95</v>
+        <v>268.25</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>263.55</v>
+        <v>264.75</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>267</v>
+        <v>265.8</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>4.7</v>
+        <v>-1.2</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>1.79</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1119.5</v>
+        <v>1130.6</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1143.5</v>
+        <v>1147.5</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1127.1</v>
+        <v>1131</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1130.6</v>
+        <v>1141</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>0.99</v>
+        <v>10.4</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5064.5</v>
+        <v>5087</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5064.5</v>
+        <v>5090.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5108</v>
+        <v>5175</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5001.5</v>
+        <v>5050</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5087</v>
+        <v>5104</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>0.44</v>
+        <v>17</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>750.95</v>
+        <v>751.45</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>754.35</v>
+        <v>750.1</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>739.5</v>
+        <v>738.5</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>751.45</v>
+        <v>743.45</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>0.5</v>
+        <v>-8</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>522.15</v>
+        <v>522.05</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>514.55</v>
+        <v>515.35</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>-1.71</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1275.6</v>
+        <v>1268.6</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1281.3</v>
+        <v>1274.7</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1287</v>
+        <v>1277.5</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1268.6</v>
+        <v>1264.4</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1268.6</v>
+        <v>1267</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>-0.55</v>
+        <v>-1.6</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>500</v>
+        <v>487.05</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>498</v>
+        <v>487.65</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>503.6</v>
+        <v>495.9</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>485.7</v>
+        <v>487</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>487.05</v>
+        <v>491.1</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-12.95</v>
+        <v>4.05</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>-2.59</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1196.7</v>
+        <v>1200.5</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1196.5</v>
+        <v>1203.9</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1205.9</v>
+        <v>1205.3</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1190.1</v>
+        <v>1176.6</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1200.5</v>
+        <v>1183.6</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>3.8</v>
+        <v>-16.9</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.32</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>412.5</v>
+        <v>414.8</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>415.2</v>
+        <v>416.5</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>420.6</v>
+        <v>417.8</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>414.55</v>
+        <v>412.55</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>414.8</v>
+        <v>412.65</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>2.3</v>
+        <v>-2.15</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>532</v>
+        <v>536.8</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>536</v>
+        <v>539.9</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>538.1</v>
+        <v>539.9</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>526.95</v>
+        <v>524</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>536.8</v>
+        <v>529.05</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>4.8</v>
+        <v>-7.75</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.9</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1896.9</v>
+        <v>1920.4</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1896.9</v>
+        <v>1920.4</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1935</v>
+        <v>1944</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1896.9</v>
+        <v>1903.1</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1920.4</v>
+        <v>1909.8</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>23.5</v>
+        <v>-10.6</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>1.24</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1954</v>
+        <v>2017.5</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1966.6</v>
+        <v>2018</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2023.5</v>
+        <v>2032.8</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1963.8</v>
+        <v>2002.2</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>2017.5</v>
+        <v>2006.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>63.5</v>
+        <v>-11</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>3.25</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>548.15</v>
+        <v>568</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>548.3</v>
+        <v>569</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>574.15</v>
+        <v>573.95</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>543.65</v>
+        <v>563.2</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>19.85</v>
+        <v>-3</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>3.62</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3885</v>
+        <v>3904.8</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3885</v>
+        <v>3919.6</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3908.7</v>
+        <v>3930.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3883</v>
+        <v>3866</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3904.8</v>
+        <v>3866.4</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>19.8</v>
+        <v>-38.4</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.51</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>312.8</v>
+        <v>307.8</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>311</v>
+        <v>308.15</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>311.25</v>
+        <v>309.25</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>306.3</v>
+        <v>302.05</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>307.8</v>
+        <v>304.9</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>-1.6</v>
+        <v>-2.9</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3347.5</v>
+        <v>3307</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3347.5</v>
+        <v>3317.1</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3348.2</v>
+        <v>3330.5</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3294.2</v>
+        <v>3271</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3307</v>
+        <v>3293.6</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-40.5</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>-1.21</v>
+        <v>-13.4</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2083</v>
+        <v>2124.5</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2084</v>
+        <v>2123.6</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2129</v>
+        <v>2135</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2080</v>
+        <v>2109</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2124.5</v>
+        <v>2135</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>1.99</v>
+        <v>10.5</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3052</v>
+        <v>3055.3</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3088</v>
+        <v>3093.7</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3055.3</v>
+        <v>3035</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3055.3</v>
+        <v>3044.5</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>3.3</v>
+        <v>-10.8</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.11</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>319.15</v>
+        <v>315.1</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>319.15</v>
+        <v>315.9</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>320</v>
+        <v>320.2</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>313.8</v>
+        <v>315.9</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>315.1</v>
+        <v>319.3</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-4.05</v>
+        <v>4.2</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>-1.27</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>803.9</v>
+        <v>824.4</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>807</v>
+        <v>824.55</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>829.75</v>
+        <v>830.5</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>804.25</v>
+        <v>824.55</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>824.4</v>
+        <v>830</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>2.55</v>
+        <v>5.6</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12103</v>
+        <v>12153</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12129</v>
+        <v>12155</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12229</v>
+        <v>12275</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12129</v>
+        <v>12142</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12153</v>
+        <v>12190</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>0.41</v>
+        <v>37</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3260</v>
+        <v>3209</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3250</v>
+        <v>3220</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3268</v>
+        <v>3289.8</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3155.5</v>
+        <v>3212.8</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3209</v>
+        <v>3262.6</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-51</v>
+        <v>53.6</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>-1.56</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>597.45</v>
+        <v>593.4</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>602.4</v>
+        <v>593.5</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>607.85</v>
+        <v>599</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>591</v>
+        <v>590.35</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>593.4</v>
+        <v>592.4</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>-0.68</v>
+        <v>-1</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1551.3</v>
+        <v>1574.9</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1591.8</v>
+        <v>1581.1</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1545.7</v>
+        <v>1549.2</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1569</v>
+        <v>1554.2</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>10</v>
+        <v>-14.8</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1081.7</v>
+        <v>1077.8</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1079.5</v>
+        <v>1075.5</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1083.9</v>
+        <v>1079.8</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1070.5</v>
+        <v>1059</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1077.8</v>
+        <v>1067.3</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-0.36</v>
+        <v>-10.5</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>162.57</v>
+        <v>162.91</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>163.12</v>
+        <v>162.75</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>163.88</v>
+        <v>163.9</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>160.5</v>
+        <v>161.21</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>162.91</v>
+        <v>161.77</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>0.34</v>
+        <v>-1.14</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.21</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2300.4</v>
+        <v>2296.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2300.4</v>
+        <v>2298.4</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2313.7</v>
+        <v>2306.5</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2257.1</v>
+        <v>2254.5</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2296.2</v>
+        <v>2265</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-0.18</v>
+        <v>-31.2</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>125670</v>
+        <v>124855</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>125780</v>
+        <v>125490</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>125780</v>
+        <v>125755</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124700</v>
+        <v>124635</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>124855</v>
+        <v>124770</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-815</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>-0.65</v>
+        <v>-85</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2841.1</v>
+        <v>2854.2</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2826</v>
+        <v>2855</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2874.2</v>
+        <v>2874</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2814</v>
+        <v>2822</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2854.2</v>
+        <v>2831.5</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>13.1</v>
+        <v>-22.7</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.46</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>350.5</v>
+        <v>352.5</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>355.3</v>
+        <v>352.95</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>357.4</v>
+        <v>353.2</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>351.55</v>
+        <v>348.1</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>352.5</v>
+        <v>352.2</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>2</v>
+        <v>-0.3</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>0.57</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1251.2</v>
+        <v>1296.4</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1305.3</v>
+        <v>1316.9</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1251.4</v>
+        <v>1291.9</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1296.4</v>
+        <v>1304</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>3.61</v>
+        <v>7.6</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8590</v>
+        <v>8486.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8590</v>
+        <v>8500</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8594</v>
+        <v>8650</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8405</v>
+        <v>8411</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8486.5</v>
+        <v>8438</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-103.5</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>-1.2</v>
+        <v>-48.5</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1372.4</v>
+        <v>1385</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1360</v>
+        <v>1382.2</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1390</v>
+        <v>1392.9</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1360</v>
+        <v>1363.9</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1385</v>
+        <v>1363.9</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>12.6</v>
+        <v>-21.1</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.92</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>79.15000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="E134" s="12" t="n">
         <v>80.09</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>80.84999999999999</v>
+        <v>80.31</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>79.8</v>
+        <v>79.34</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>79.8</v>
+        <v>80.2</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>0.82</v>
+        <v>0.4</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>323.65</v>
+        <v>326.4</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>325</v>
+        <v>326.5</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>328.75</v>
+        <v>329</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>324.85</v>
+        <v>325.55</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>326.4</v>
+        <v>327.8</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>0.85</v>
+        <v>1.4</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1785</v>
+        <v>1821</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1765</v>
+        <v>1823.9</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1827.7</v>
+        <v>1853</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1754.3</v>
+        <v>1802.6</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1821</v>
+        <v>1845.6</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>2.02</v>
+        <v>24.6</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>11896</v>
+        <v>10911</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>11787</v>
+        <v>10962</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11787</v>
+        <v>11111</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>10900</v>
+        <v>10835</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>10911</v>
+        <v>10989</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-985</v>
+        <v>78</v>
       </c>
       <c r="J137" s="13" t="n">
-        <v>-8.279999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>232.8</v>
+        <v>235.63</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>232.8</v>
+        <v>235.51</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>236</v>
+        <v>236.37</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>232.32</v>
+        <v>233.75</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>235.63</v>
+        <v>236.13</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>1.22</v>
+        <v>0.5</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36400</v>
+        <v>35950</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35975</v>
+        <v>36130</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>36300</v>
+        <v>37345</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>35495</v>
+        <v>36075</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35950</v>
+        <v>37150</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-450</v>
+        <v>1200</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>-1.24</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5416</v>
+        <v>5449</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5416</v>
+        <v>5454.5</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5458</v>
+        <v>5463</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5380.5</v>
+        <v>5359</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5449</v>
+        <v>5366</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>33</v>
+        <v>-83</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>0.61</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>292.6</v>
+        <v>287.5</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>287</v>
+        <v>287.6</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>289.65</v>
+        <v>288.25</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>286.6</v>
+        <v>280.3</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>287.5</v>
+        <v>281.75</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>-1.74</v>
+        <v>-5.75</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>342.55</v>
+        <v>344.75</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>342.6</v>
+        <v>345.2</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>348.05</v>
+        <v>346.5</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>342.6</v>
+        <v>343.1</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>344.75</v>
+        <v>345.8</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>0.64</v>
+        <v>1.05</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1572.1</v>
+        <v>1573.2</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1598</v>
+        <v>1576.3</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1598</v>
+        <v>1587</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1573.2</v>
+        <v>1562.7</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1573.2</v>
+        <v>1572.7</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2366.8</v>
+        <v>2321.8</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2324</v>
+        <v>2364.9</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2342.7</v>
+        <v>2428.7</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2315.7</v>
+        <v>2350</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2321.8</v>
+        <v>2410</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-45</v>
+        <v>88.2</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>-1.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>117.27</v>
+        <v>118</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>117.23</v>
+        <v>118.45</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.58</v>
+        <v>118.74</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.64</v>
+        <v>116.7</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.73</v>
+        <v>-1</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.62</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
+        <v>8369.5</v>
+      </c>
+      <c r="E147" s="9" t="n">
         <v>8400</v>
       </c>
-      <c r="E147" s="9" t="n">
-        <v>8352.5</v>
-      </c>
       <c r="F147" s="9" t="n">
-        <v>8429</v>
+        <v>8442</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8331</v>
+        <v>8345</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8369.5</v>
+        <v>8350</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>-0.36</v>
+        <v>-19.5</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>270.3</v>
+        <v>266.1</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>267.75</v>
+        <v>267</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>269.05</v>
+        <v>268.3</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>266.1</v>
+        <v>265.95</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>266.1</v>
+        <v>265.95</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-1.55</v>
+        <v>-0.15</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1324.7</v>
+        <v>1349.3</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1328.7</v>
+        <v>1350</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1357.8</v>
+        <v>1352.8</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1322.6</v>
+        <v>1306</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1349.3</v>
+        <v>1334.8</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>24.6</v>
+        <v>-14.5</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>1.86</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>415.9</v>
+        <v>402.4</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>408</v>
+        <v>404.3</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>409.9</v>
+        <v>424.4</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>401.1</v>
+        <v>402.85</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>402.4</v>
+        <v>423.2</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-13.5</v>
+        <v>20.8</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>-3.25</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>312</v>
+        <v>310.2</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>312</v>
+        <v>310.3</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>313.45</v>
+        <v>311</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>310.2</v>
+        <v>307.1</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>310.2</v>
+        <v>307.1</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>-0.58</v>
+        <v>-3.1</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1226.4</v>
+        <v>1247.4</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1234.1</v>
+        <v>1247.6</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1249.1</v>
+        <v>1251.9</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1232.5</v>
+        <v>1237.4</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>21</v>
+        <v>-7</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>177.33</v>
+        <v>177.3</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>178</v>
+        <v>177.1</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>179.8</v>
+        <v>178.29</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>175.1</v>
+        <v>174</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>177.3</v>
+        <v>174.01</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>-0.02</v>
+        <v>-3.29</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>651.15</v>
+        <v>637</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>642.1</v>
+        <v>637.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>643.65</v>
+        <v>642.65</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>636.2</v>
+        <v>630.65</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>637</v>
+        <v>634.95</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-14.15</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-2.17</v>
+        <v>-2.05</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1731</v>
+        <v>1756</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1744</v>
+        <v>1761.1</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1774.4</v>
+        <v>1772.7</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1734.3</v>
+        <v>1740</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1756</v>
+        <v>1756.3</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>1.44</v>
+        <v>0.3</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>996.2</v>
+        <v>996</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>993.6</v>
+        <v>999.1</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>997.5</v>
+        <v>1000.1</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>989.1</v>
+        <v>981.3</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>-0.02</v>
+        <v>-9</v>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22600</v>
+        <v>22550</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22450</v>
+        <v>22540</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22700</v>
+        <v>22650</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22355</v>
+        <v>22165</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22550</v>
+        <v>22200</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-50</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-0.22</v>
+        <v>-350</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1010</v>
+        <v>1011.8</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1019</v>
+        <v>1011.8</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1019</v>
+        <v>1016.6</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1005.3</v>
+        <v>995.5</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1011.8</v>
+        <v>1006</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>1.8</v>
+        <v>-5.8</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>0.18</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3913.9</v>
+        <v>3887</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3880</v>
+        <v>3890</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3919</v>
+        <v>3954.3</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3851.5</v>
+        <v>3850.1</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3887</v>
+        <v>3858</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-26.9</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-29</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2512</v>
+        <v>2540</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2530.9</v>
+        <v>2540</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2563</v>
+        <v>2554.3</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2530.9</v>
+        <v>2526.4</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2540</v>
+        <v>2538.3</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>28</v>
+        <v>-1.7</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>1.11</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1837.3</v>
+        <v>1868.9</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1832.2</v>
+        <v>1869</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1891.5</v>
+        <v>1876.4</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1832.2</v>
+        <v>1842.3</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1868.9</v>
+        <v>1846.4</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>31.6</v>
+        <v>-22.5</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.72</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>451.7</v>
+        <v>457.55</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>451.7</v>
+        <v>458</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>460.75</v>
+        <v>494.2</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>447.2</v>
+        <v>454</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>457.55</v>
+        <v>490.1</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>1.3</v>
+        <v>32.55</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>7.11</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>369.05</v>
+        <v>385.15</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>369.95</v>
+        <v>385.15</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>387.05</v>
+        <v>385.85</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>360.4</v>
+        <v>373.6</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>385.15</v>
+        <v>377.5</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>16.1</v>
+        <v>-7.65</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>4.36</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>693.25</v>
+        <v>694.7</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>687.6</v>
+        <v>695</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>698.5</v>
+        <v>697.05</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>668.6</v>
+        <v>673</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>694.7</v>
+        <v>674</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>1.45</v>
+        <v>-20.7</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>0.21</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1780.1</v>
+        <v>1732.7</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1771</v>
+        <v>1733</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1789.6</v>
+        <v>1741</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1725</v>
+        <v>1682.1</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1732.7</v>
+        <v>1692.4</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-47.4</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>-2.66</v>
+        <v>-40.3</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>996</v>
+        <v>1000.6</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>998.9</v>
+        <v>1002.9</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1015.5</v>
+        <v>1006</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>997.2</v>
+        <v>984.1</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1000.6</v>
+        <v>984.1</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>4.6</v>
+        <v>-16.5</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>0.46</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>374.8</v>
+        <v>367.15</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>367.3</v>
+        <v>367</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>369.6</v>
+        <v>370</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>365.65</v>
+        <v>365.9</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>367.15</v>
+        <v>367</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-7.65</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>-2.04</v>
+        <v>-0.15</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>185.54</v>
+        <v>183.4</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>184.55</v>
+        <v>183.6</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>186.87</v>
+        <v>185.49</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>183.34</v>
+        <v>183.1</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>183.4</v>
+        <v>184.97</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-2.14</v>
+        <v>1.57</v>
       </c>
       <c r="J169" s="13" t="n">
-        <v>-1.15</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
+        <v>2128.7</v>
+      </c>
+      <c r="E170" s="12" t="n">
+        <v>2135.1</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>2135.2</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>2098.2</v>
+      </c>
+      <c r="H170" s="12" t="n">
         <v>2105</v>
       </c>
-      <c r="E170" s="12" t="n">
-        <v>2090</v>
-      </c>
-      <c r="F170" s="12" t="n">
-        <v>2145</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>2075.3</v>
-      </c>
-      <c r="H170" s="12" t="n">
-        <v>2128.7</v>
-      </c>
       <c r="I170" s="12" t="n">
-        <v>23.7</v>
+        <v>-23.7</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>1.13</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1537.1</v>
+        <v>1558.5</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1529</v>
+        <v>1553.7</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1560.6</v>
+        <v>1558.7</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1525.1</v>
+        <v>1530.9</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1558.5</v>
+        <v>1551.6</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>21.4</v>
+        <v>-6.9</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>1.39</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2600</v>
+        <v>2588</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2614.2</v>
+        <v>2617.4</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2569.1</v>
+        <v>2558.4</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2588</v>
+        <v>2574</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-12</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>-0.46</v>
+        <v>-14</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4798.5</v>
+        <v>4875</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4816.5</v>
+        <v>4876</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4880</v>
+        <v>4982</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4780</v>
+        <v>4862.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4875</v>
+        <v>4928.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>1.59</v>
+        <v>53.5</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4840</v>
+        <v>4970</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4860</v>
+        <v>4984</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4986.5</v>
+        <v>4984</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4848.5</v>
+        <v>4910</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4970</v>
+        <v>4935</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>130</v>
+        <v>-35</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>2.69</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1258.8</v>
+        <v>1262</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1269.8</v>
+        <v>1268.4</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1262</v>
+        <v>1246.3</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>3.2</v>
+        <v>-15.7</v>
       </c>
       <c r="J175" s="10" t="n">
-        <v>0.25</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2824</v>
+        <v>2815.5</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2813.9</v>
+        <v>2838.7</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2836.9</v>
+        <v>2847.9</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2801</v>
+        <v>2754.2</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2815.5</v>
+        <v>2782.9</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>-0.3</v>
+        <v>-32.6</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4171.3</v>
+        <v>4155</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4173.1</v>
+        <v>4155</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4208.1</v>
+        <v>4188.1</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4155</v>
+        <v>4134</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4155</v>
+        <v>4140</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-16.3</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-0.39</v>
+        <v>-15</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1251.5</v>
+        <v>1227.8</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1251.5</v>
+        <v>1234</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1260</v>
+        <v>1234.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1225</v>
+        <v>1210.4</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1227.8</v>
+        <v>1215.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-23.7</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>-1.89</v>
+        <v>-12.6</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11146</v>
+        <v>11142</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>10983</v>
+        <v>11000</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>86</v>
+        <v>-100</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>0.78</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>176.56</v>
+        <v>178.09</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>177.11</v>
+        <v>178</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>178.87</v>
+        <v>178.8</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>177.03</v>
+        <v>175.86</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>178.09</v>
+        <v>178</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>1.53</v>
+        <v>-0.09</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>0.87</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>580</v>
+        <v>559.9</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>564.2</v>
+        <v>559.25</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>569.2</v>
+        <v>562.55</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>559.9</v>
+        <v>555</v>
       </c>
       <c r="H181" s="9" t="n">
         <v>559.9</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-20.1</v>
+        <v>0</v>
       </c>
       <c r="J181" s="13" t="n">
-        <v>-3.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>267.6</v>
+        <v>260.5</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>264.5</v>
+        <v>261</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>264.5</v>
+        <v>263.85</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>259</v>
+        <v>260.2</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>260.5</v>
+        <v>263</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J182" s="13" t="n">
-        <v>-2.65</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1110.9</v>
+        <v>1142.1</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1125</v>
+        <v>1143</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1158.8</v>
+        <v>1143.1</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1142.1</v>
+        <v>1100.8</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>31.2</v>
+        <v>-41.3</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>2.81</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>166.83</v>
+        <v>164.55</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>165.24</v>
+        <v>164.81</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>165.5</v>
+        <v>166</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>163.34</v>
+        <v>163.21</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>164.55</v>
+        <v>166</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-2.28</v>
+        <v>1.45</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-1.37</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E186" s="12" t="n">
+        <v>1161</v>
+      </c>
+      <c r="F186" s="12" t="n">
+        <v>1178</v>
+      </c>
+      <c r="G186" s="12" t="n">
         <v>1160</v>
       </c>
-      <c r="E186" s="12" t="n">
-        <v>1155</v>
-      </c>
-      <c r="F186" s="12" t="n">
-        <v>1173.5</v>
-      </c>
-      <c r="G186" s="12" t="n">
-        <v>1152.1</v>
-      </c>
       <c r="H186" s="12" t="n">
-        <v>1161</v>
+        <v>1162.3</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>0.09</v>
+        <v>1.3</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  21-Sep-2026 06:29 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  22-Sep-2026 05:31 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-Sep-2026 06:29 PM</t>
+          <t>22-Sep-2026 05:31 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 22-Sep-2026 05:31 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 23-Sep-2026 05:43 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>22-Sep-2026 05:31 PM</t>
+          <t>23-Sep-2026 05:43 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  22-Sep-2026 05:31 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  23-Sep-2026 05:43 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>499.8</v>
+        <v>496</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>500.35</v>
+        <v>493</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>504.8</v>
+        <v>504.25</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>492.05</v>
+        <v>489.2</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>496</v>
+        <v>491.35</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-3.8</v>
+        <v>-4.65</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.76</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7271</v>
+        <v>7120.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7261.5</v>
+        <v>7141.5</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7405.5</v>
+        <v>7185</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7117.5</v>
+        <v>7077</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7120.5</v>
+        <v>7120</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-150.5</v>
+        <v>-0.5</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>-2.07</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26960</v>
+        <v>27225</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26960</v>
+        <v>27225</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27295</v>
+        <v>27490</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26960</v>
+        <v>26905</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>27225</v>
+        <v>26935</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>265</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>0.98</v>
+        <v>-290</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>403.4</v>
+        <v>397</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>401</v>
+        <v>398.85</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>405</v>
+        <v>402.75</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>394.65</v>
+        <v>397.6</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>397</v>
+        <v>402.45</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>-1.59</v>
+        <v>5.45</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49.97</v>
+        <v>49.29</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>50.24</v>
+        <v>49.59</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>49.01</v>
+        <v>48.9</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>49.22</v>
+        <v>49.09</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.63</v>
+        <v>-0.13</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-1.26</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1256.3</v>
+        <v>1238.2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1256.5</v>
+        <v>1242.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1260</v>
+        <v>1254.6</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1234.8</v>
+        <v>1240.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1238.2</v>
+        <v>1251.4</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>-1.44</v>
+        <v>13.2</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2975</v>
+        <v>2997</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2995</v>
+        <v>3015.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3026.1</v>
+        <v>3023.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2979.6</v>
+        <v>2978.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2997</v>
+        <v>2993.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>0.74</v>
+        <v>-3.8</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1787.1</v>
+        <v>1795</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1812.7</v>
+        <v>1810.1</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1786.1</v>
+        <v>1790.5</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1795</v>
+        <v>1807.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>7.9</v>
+        <v>12.3</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5364</v>
+        <v>5331.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5365</v>
+        <v>5344</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5419.5</v>
+        <v>5445</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5308.5</v>
+        <v>5316</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5331.5</v>
+        <v>5417.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-32.5</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-0.61</v>
+        <v>86</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>390.75</v>
+        <v>386.9</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>391.1</v>
+        <v>387.3</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>394</v>
+        <v>392.85</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>385.15</v>
+        <v>387.3</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>386.9</v>
+        <v>392.75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>-0.99</v>
+        <v>5.85</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>296.15</v>
+        <v>295.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>296.2</v>
+        <v>295.25</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>298.65</v>
+        <v>301.1</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>293.2</v>
+        <v>295.25</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>295.1</v>
+        <v>300</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-0.35</v>
+        <v>4.9</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2181.1</v>
+        <v>2195</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2180.9</v>
+        <v>2199</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2199.3</v>
+        <v>2204</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2159.9</v>
+        <v>2178</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>2195</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8912</v>
+        <v>8835.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8960</v>
+        <v>8875</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>9000</v>
+        <v>9070.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8822.5</v>
+        <v>8865</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8835.5</v>
+        <v>9069</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-76.5</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>-0.86</v>
+        <v>233.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>2.64</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>409.3</v>
+        <v>402.55</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>409.3</v>
+        <v>403.1</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>411.35</v>
+        <v>406.8</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>401</v>
+        <v>401.35</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>402.55</v>
+        <v>405.7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-1.65</v>
+        <v>3.15</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>161.75</v>
+        <v>160.75</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>163</v>
+        <v>160.99</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>164.2</v>
+        <v>163.13</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>159.8</v>
+        <v>160.85</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>160.75</v>
+        <v>162.89</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-0.62</v>
+        <v>2.14</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2440.3</v>
+        <v>2448.5</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2475.1</v>
+        <v>2469</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2475.1</v>
+        <v>2471.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2435.6</v>
+        <v>2448.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2448.5</v>
+        <v>2455</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1400.9</v>
+        <v>1381.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1401</v>
+        <v>1388.9</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1407.9</v>
+        <v>1404</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1381.6</v>
+        <v>1383</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1381.6</v>
+        <v>1394.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-1.38</v>
+        <v>13.2</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>638.4</v>
+        <v>626.25</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>642.95</v>
+        <v>633.25</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>622.2</v>
+        <v>623.05</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>626.25</v>
+        <v>625.25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-12.15</v>
+        <v>-1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-1.9</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6086</v>
+        <v>6176.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6128</v>
+        <v>6199</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6234</v>
+        <v>6199</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6096</v>
+        <v>6095</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6176.5</v>
+        <v>6118</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>1.49</v>
+        <v>-58.5</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1038</v>
+        <v>1036.4</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1037.9</v>
+        <v>1034</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1043.5</v>
+        <v>1055.8</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1027.6</v>
+        <v>1032.6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1036.4</v>
+        <v>1053</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>-0.15</v>
+        <v>16.6</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1713.4</v>
+        <v>1700</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1718.3</v>
+        <v>1700</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1719</v>
+        <v>1724.7</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1689.3</v>
+        <v>1692.6</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1700</v>
+        <v>1721.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>-0.78</v>
+        <v>21.5</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1250</v>
+        <v>1242.7</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1245.2</v>
+        <v>1242.2</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1255.6</v>
+        <v>1252</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1240.1</v>
+        <v>1238.9</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1242.7</v>
+        <v>1243.2</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>-0.58</v>
+        <v>0.5</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11460</v>
+        <v>11363</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11460</v>
+        <v>11363</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11515</v>
+        <v>11425</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11281</v>
+        <v>11293</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11363</v>
+        <v>11400</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-97</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-0.85</v>
+        <v>37</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1849.8</v>
+        <v>1823.4</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1862.7</v>
+        <v>1825</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1863</v>
+        <v>1864.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1823.4</v>
+        <v>1825</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1823.4</v>
+        <v>1846.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-26.4</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-1.43</v>
+        <v>23.1</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1021.3</v>
+        <v>1008.8</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1025.3</v>
+        <v>1034.7</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1029.2</v>
+        <v>1043.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1005</v>
+        <v>1022</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1008.8</v>
+        <v>1043.2</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>-1.22</v>
+        <v>34.4</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>3.41</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2216.8</v>
+        <v>2216.9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2224</v>
+        <v>2205</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2231</v>
+        <v>2225.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2202.3</v>
+        <v>2190</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2216.9</v>
+        <v>2199.6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>0</v>
+        <v>-17.3</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>663.65</v>
+        <v>661.05</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>661</v>
+        <v>661.05</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>668.4</v>
+        <v>682.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>651.3</v>
+        <v>658.85</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>661.05</v>
+        <v>676.4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>-0.39</v>
+        <v>15.35</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>2.32</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>179</v>
+        <v>184.7</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>180</v>
+        <v>185.95</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>185.11</v>
+        <v>193</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>179.9</v>
+        <v>185.7</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>184.7</v>
+        <v>191.38</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>5.7</v>
+        <v>6.68</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>233.64</v>
+        <v>234.35</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>233.64</v>
+        <v>233.2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>234.9</v>
+        <v>237.7</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>232.71</v>
+        <v>233.2</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>234.35</v>
+        <v>236.87</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.71</v>
+        <v>2.52</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>398.5</v>
+        <v>397.9</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>398.5</v>
+        <v>397.9</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>400.65</v>
+        <v>399.5</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>395.8</v>
+        <v>395.6</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>397.9</v>
+        <v>396.05</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-0.6</v>
+        <v>-1.85</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-0.15</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>450.6</v>
+        <v>452.6</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>453</v>
+        <v>459.7</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>456.9</v>
+        <v>462</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>448</v>
+        <v>455.3</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>452.6</v>
+        <v>459.75</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2</v>
+        <v>7.15</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0.44</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1830.2</v>
+        <v>1817.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1833.9</v>
+        <v>1818.1</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1836.3</v>
+        <v>1836.7</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1817.2</v>
+        <v>1833.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-13</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>-0.71</v>
+        <v>16</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>433.4</v>
+        <v>425.8</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>435.2</v>
+        <v>427.25</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>439.7</v>
+        <v>430</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>424.65</v>
+        <v>419.05</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>425.8</v>
+        <v>423.1</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-7.6</v>
+        <v>-2.7</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>-1.75</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
+        <v>390</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>389</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>395</v>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>394.3</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>396.25</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>389</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>390</v>
-      </c>
       <c r="I36" s="12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>-1.27</v>
+        <v>5</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47565</v>
+        <v>48290</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47795</v>
+        <v>48290</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48290</v>
+        <v>48330</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47530</v>
+        <v>47585</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48290</v>
+        <v>47955</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>725</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>1.52</v>
+        <v>-335</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>312.75</v>
+        <v>313.6</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>315</v>
+        <v>314.65</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>318.2</v>
+        <v>315.9</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>308.15</v>
+        <v>312.55</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>313.6</v>
+        <v>315.75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0.85</v>
+        <v>2.15</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5023</v>
+        <v>4918</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5030</v>
+        <v>4927.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5030</v>
+        <v>4965</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4915</v>
+        <v>4905</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4918</v>
+        <v>4929</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-105</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>-2.09</v>
+        <v>11</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>284.15</v>
+        <v>281.15</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>284.15</v>
+        <v>281.1</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>284.5</v>
+        <v>282.8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>280.75</v>
+        <v>280</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>281.15</v>
+        <v>281.1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-3</v>
+        <v>-0.05</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-1.06</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>123.7</v>
+        <v>122.9</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>124.02</v>
+        <v>123.2</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>124.69</v>
+        <v>126.3</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>122.8</v>
+        <v>123.17</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>122.9</v>
+        <v>126</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>-0.65</v>
+        <v>3.1</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>2.52</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>769.9</v>
+        <v>759.55</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>775.55</v>
+        <v>767.4</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>755.3</v>
+        <v>753.75</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>759.55</v>
+        <v>757.95</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-10.35</v>
+        <v>-1.6</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-1.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>417.2</v>
+        <v>418.5</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>417.95</v>
+        <v>418.5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>420</v>
+        <v>421.65</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>414.3</v>
+        <v>417.75</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>418.5</v>
+        <v>419.6</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1764</v>
+        <v>1759.1</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1769.9</v>
+        <v>1760</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1779.4</v>
+        <v>1784</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1756.8</v>
+        <v>1758.7</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1759.1</v>
+        <v>1774</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>-0.28</v>
+        <v>14.9</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1386.1</v>
+        <v>1384.1</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1386.3</v>
+        <v>1382.4</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1388.7</v>
+        <v>1387</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1364.5</v>
+        <v>1371.8</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1384.1</v>
+        <v>1383</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-2</v>
+        <v>-1.1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>414.7</v>
+        <v>428</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>424.7</v>
+        <v>428.25</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>428.75</v>
+        <v>429.4</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>419.65</v>
+        <v>421.55</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>428</v>
+        <v>424.55</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>3.21</v>
+        <v>-3.45</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1814</v>
+        <v>1803</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1818</v>
+        <v>1817.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1784.4</v>
+        <v>1774.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1803</v>
+        <v>1782.4</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-11</v>
+        <v>-20.6</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>-0.61</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1892</v>
+        <v>1869</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1892.1</v>
+        <v>1869</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1892.3</v>
+        <v>1901.3</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1863</v>
+        <v>1863.3</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1869</v>
+        <v>1886.7</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-23</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>-1.22</v>
+        <v>17.7</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>487.05</v>
+        <v>467</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>489.5</v>
+        <v>469</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>489.5</v>
+        <v>473.65</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>466.7</v>
+        <v>463.15</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>467</v>
+        <v>464.65</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-20.05</v>
+        <v>-2.35</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-4.12</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1940.8</v>
+        <v>1944.9</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1935</v>
+        <v>1944.2</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1953.4</v>
+        <v>1989</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1935</v>
+        <v>1936.2</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1944.9</v>
+        <v>1956</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>4.1</v>
+        <v>11.1</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>225.05</v>
+        <v>222</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>224.75</v>
+        <v>223.3</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>225.71</v>
+        <v>226.76</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>221.76</v>
+        <v>222.6</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>222</v>
+        <v>223.43</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>-1.36</v>
+        <v>1.43</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>234.94</v>
+        <v>227.21</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>234.9</v>
+        <v>227</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>235.78</v>
+        <v>230.79</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>226</v>
+        <v>224.71</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>227.21</v>
+        <v>225.34</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-7.73</v>
+        <v>-1.87</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-3.29</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5067</v>
+        <v>4962.5</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5090</v>
+        <v>5000</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5128.5</v>
+        <v>5053.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4962.5</v>
+        <v>4928</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4962.5</v>
+        <v>5010</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-104.5</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>-2.06</v>
+        <v>47.5</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>386.8</v>
+        <v>388.1</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>388.3</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>390.1</v>
+        <v>395.45</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>385.2</v>
+        <v>387.4</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>388.1</v>
+        <v>387.4</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>0.34</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1764.4</v>
+        <v>1741.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1764</v>
+        <v>1741.1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1785.4</v>
+        <v>1749.9</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1736.3</v>
+        <v>1729.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1741.6</v>
+        <v>1744</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-22.8</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>-1.29</v>
+        <v>2.4</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1586.3</v>
+        <v>1613.2</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1605.1</v>
+        <v>1614</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1623.8</v>
+        <v>1639</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1593.4</v>
+        <v>1605.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1613.2</v>
+        <v>1635.8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>26.9</v>
+        <v>22.6</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>61.59</v>
+        <v>61.77</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>61.99</v>
+        <v>62.3</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>63.55</v>
+        <v>69</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>61.02</v>
+        <v>61.77</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>61.77</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>0.18</v>
+        <v>6.88</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>0.29</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9410.5</v>
+        <v>9352</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9444</v>
+        <v>9330</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9444</v>
+        <v>9624</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9315.5</v>
+        <v>9312.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9352</v>
+        <v>9624</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-58.5</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>-0.62</v>
+        <v>272</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13350</v>
+        <v>13084</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13364</v>
+        <v>13084</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13434</v>
+        <v>13250</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>12996</v>
+        <v>13055</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13084</v>
+        <v>13200</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-266</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>-1.99</v>
+        <v>116</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>660.25</v>
+        <v>669.5</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>671.9</v>
+        <v>681</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>659.05</v>
+        <v>668</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>669.5</v>
+        <v>675</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>9.25</v>
+        <v>5.5</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>1.4</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1198.3</v>
+        <v>1211</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1222</v>
+        <v>1220.5</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1201.2</v>
+        <v>1205.9</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1211</v>
+        <v>1211.2</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>12.7</v>
+        <v>0.2</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>1.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7512.5</v>
+        <v>7427</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7519</v>
+        <v>7468.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7555</v>
+        <v>7485</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7427</v>
+        <v>7414</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7427</v>
+        <v>7470</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-85.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-1.14</v>
+        <v>43</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2819.8</v>
+        <v>2793.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2833.9</v>
+        <v>2803.9</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2848.3</v>
+        <v>2829</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2787</v>
+        <v>2784.9</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2793.6</v>
+        <v>2796.9</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>-0.93</v>
+        <v>3.3</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>434.5</v>
+        <v>429.7</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>434.5</v>
+        <v>430.05</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>438.5</v>
+        <v>432.2</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>427.5</v>
+        <v>423.65</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>429.7</v>
+        <v>425.95</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-4.8</v>
+        <v>-3.75</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-1.1</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>332.3</v>
+        <v>328.45</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>334.85</v>
+        <v>331.3</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>325.5</v>
+        <v>325.25</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>327</v>
+        <v>331.3</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>-1.51</v>
+        <v>4.3</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>1.31</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>172.61</v>
+        <v>171.84</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.08</v>
+        <v>172.48</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>174.3</v>
+        <v>173.79</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>171.35</v>
+        <v>172</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>171.84</v>
+        <v>172.95</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>-0.45</v>
+        <v>1.11</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2450</v>
+        <v>2461.4</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2460.4</v>
+        <v>2472</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2472</v>
+        <v>2482.6</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2443</v>
+        <v>2453.6</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2461.4</v>
+        <v>2475</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>589.9</v>
+        <v>598.7</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>592.1</v>
+        <v>601</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>615.85</v>
+        <v>628.1</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>589.3</v>
+        <v>594.55</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>598.7</v>
+        <v>623.05</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>24.35</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>1.49</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="70">
@@ -3111,22 +3111,22 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>867.5</v>
+        <v>873.6</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>869.8</v>
+        <v>871.5</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>878.8</v>
+        <v>883.65</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>864.2</v>
+        <v>871.5</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>873.6</v>
+        <v>879.75</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="J70" s="13" t="n">
         <v>0.7</v>
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1696.9</v>
+        <v>1699.5</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1710</v>
+        <v>1700.9</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1732</v>
+        <v>1720</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1690.2</v>
+        <v>1700.9</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1699.5</v>
+        <v>1707.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>2.6</v>
+        <v>8.1</v>
       </c>
       <c r="J71" s="13" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>875.15</v>
+        <v>864.05</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>876</v>
+        <v>861.95</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>876.6</v>
+        <v>873.95</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>853.9</v>
+        <v>857.35</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>864.05</v>
+        <v>860.25</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-11.1</v>
+        <v>-3.8</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>-1.27</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3171</v>
+        <v>3138</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3180.8</v>
+        <v>3190</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3125</v>
+        <v>3127.1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3128.2</v>
+        <v>3188.5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-37.8</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>-1.19</v>
+        <v>60.3</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>1.93</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4826</v>
+        <v>4800</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4834.8</v>
+        <v>4810</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4879.5</v>
+        <v>4849</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4776.2</v>
+        <v>4802</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4800</v>
+        <v>4836</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-26</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>-0.54</v>
+        <v>36</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1103.1</v>
+        <v>1088.9</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1103.6</v>
+        <v>1091.1</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1109.4</v>
+        <v>1098</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1086</v>
+        <v>1086.1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1088.9</v>
+        <v>1096.5</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>-1.29</v>
+        <v>7.6</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1281</v>
+        <v>1270.4</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1280</v>
+        <v>1270</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1286.1</v>
+        <v>1279.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1240.3</v>
+        <v>1250</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1270.4</v>
+        <v>1256.7</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-10.6</v>
+        <v>-13.7</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>-0.83</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2438.2</v>
+        <v>2426.4</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2451.8</v>
+        <v>2454</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2414.1</v>
+        <v>2426</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2430</v>
+        <v>2448.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>-0.41</v>
+        <v>18.3</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>739.5</v>
+        <v>738.6</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>738.85</v>
+        <v>735.65</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>749.3</v>
+        <v>742.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>738.6</v>
+        <v>734</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>738.6</v>
+        <v>737.25</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-0.9</v>
+        <v>-1.35</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-0.12</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>559.4</v>
+        <v>559.2</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>560.55</v>
+        <v>561.9</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>567.4</v>
+        <v>565.5</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>559.05</v>
+        <v>556.4</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>559.2</v>
+        <v>561.5</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>-0.04</v>
+        <v>2.3</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5419</v>
+        <v>5373</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5424</v>
+        <v>5395</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5443</v>
+        <v>5448.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5368</v>
+        <v>5365</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5373</v>
+        <v>5394</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-46</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-0.85</v>
+        <v>21</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>981.2</v>
+        <v>973</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>987</v>
+        <v>979.5</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>987.5</v>
+        <v>1003.8</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>967.1</v>
+        <v>978.2</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>973</v>
+        <v>1003.8</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>-0.84</v>
+        <v>30.8</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>3.17</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>503.95</v>
+        <v>508.2</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>510.05</v>
+        <v>513</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>521.7</v>
+        <v>521.3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>507.1</v>
+        <v>509.4</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>508.2</v>
+        <v>513</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>357.6</v>
+        <v>360.7</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>359.2</v>
+        <v>362.5</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>365.2</v>
+        <v>364.65</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>354.7</v>
+        <v>358</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>360.7</v>
+        <v>360</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>0.87</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1947</v>
+        <v>1933.8</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1952</v>
+        <v>1938</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1956.8</v>
+        <v>1954</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1933.8</v>
+        <v>1936</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1933.8</v>
+        <v>1950</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-0.68</v>
+        <v>16.2</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34685</v>
+        <v>34025</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34685</v>
+        <v>34050</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34890</v>
+        <v>34500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33950</v>
+        <v>33700</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34025</v>
+        <v>34275</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-660</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-1.9</v>
+        <v>250</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>85.8</v>
+        <v>85.37</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>85.64</v>
+        <v>85.98</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>86.09999999999999</v>
+        <v>89.61</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>85.37</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>-0.5</v>
+        <v>2.53</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>2.96</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>113.82</v>
+        <v>112.9</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>113.82</v>
+        <v>112.9</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>114.12</v>
+        <v>113.9</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>112.12</v>
+        <v>112.75</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>112.9</v>
+        <v>113.16</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>148.85</v>
+        <v>146.68</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>148.71</v>
+        <v>147.41</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>148.99</v>
+        <v>148.65</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>145.5</v>
+        <v>146.23</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>146.68</v>
+        <v>147.09</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>-1.46</v>
+        <v>0.41</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>745</v>
+        <v>736.25</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>749.4</v>
+        <v>738.25</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>749.4</v>
+        <v>744</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>735.75</v>
+        <v>736.15</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-8.75</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>-1.17</v>
+        <v>7.45</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1631.4</v>
+        <v>1635.2</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1635</v>
+        <v>1644.7</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1645</v>
+        <v>1657</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1635.2</v>
+        <v>1652.4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3.8</v>
+        <v>17.2</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>0.23</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4941</v>
+        <v>5030</v>
       </c>
       <c r="E92" s="12" t="n">
+        <v>5026</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>5061</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="F92" s="12" t="n">
-        <v>5064</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>4943</v>
-      </c>
       <c r="H92" s="12" t="n">
-        <v>5030</v>
+        <v>5028.5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>1.8</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>959</v>
+        <v>951.8</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>963.5</v>
+        <v>970.8</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>949.3</v>
+        <v>951.8</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>955</v>
+        <v>959.3</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>-0.1</v>
+        <v>4.3</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>377.65</v>
+        <v>382.1</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>377.65</v>
+        <v>382.15</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>382.1</v>
+        <v>388.55</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>373.65</v>
+        <v>381.2</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>382.1</v>
+        <v>384.8</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>4.45</v>
+        <v>2.7</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>1.18</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1038.5</v>
+        <v>1029.4</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1037.7</v>
+        <v>1021.8</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1041</v>
+        <v>1029.4</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1019.2</v>
+        <v>1015.1</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1029.4</v>
+        <v>1020.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-9.1</v>
+        <v>-8.9</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>136.53</v>
+        <v>137.8</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>137.53</v>
+        <v>138.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>139.3</v>
+        <v>138.75</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>136.8</v>
+        <v>137.1</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>137.8</v>
+        <v>138.15</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>1.27</v>
+        <v>0.35</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>0.93</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2008.2</v>
+        <v>1992.4</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>2015.5</v>
+        <v>1993</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2037</v>
+        <v>1999.4</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1980</v>
+        <v>1948.5</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1992.4</v>
+        <v>1962.6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-15.8</v>
+        <v>-29.8</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-0.79</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>470.2</v>
+        <v>469.65</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>472</v>
+        <v>469.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>474.6</v>
+        <v>472.1</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>466.35</v>
+        <v>461</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>469.65</v>
+        <v>463.8</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-0.55</v>
+        <v>-5.85</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-0.12</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>267</v>
+        <v>265.8</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>267.9</v>
+        <v>265.85</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>268.25</v>
+        <v>271.05</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>264.75</v>
+        <v>265.15</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>265.8</v>
+        <v>270.15</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-0.45</v>
+        <v>4.35</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1130.6</v>
+        <v>1141</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1135</v>
+        <v>1138.2</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1147.5</v>
+        <v>1187.4</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1131</v>
+        <v>1138.2</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1141</v>
+        <v>1175.3</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>10.4</v>
+        <v>34.3</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>0.92</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5087</v>
+        <v>5104</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5090.5</v>
+        <v>5104</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5175</v>
+        <v>5160</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5050</v>
+        <v>5005</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5104</v>
+        <v>5085</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>0.33</v>
+        <v>-19</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>751.45</v>
+        <v>743.45</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>749</v>
+        <v>748.95</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>750.1</v>
+        <v>766.85</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>738.5</v>
+        <v>744.1</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>743.45</v>
+        <v>758.55</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>-1.06</v>
+        <v>15.1</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>517</v>
+        <v>517.2</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>522.05</v>
+        <v>525.85</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>515.35</v>
+        <v>516</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1268.6</v>
+        <v>1267</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1274.7</v>
+        <v>1273</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1277.5</v>
+        <v>1304</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1264.4</v>
+        <v>1270.8</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1267</v>
+        <v>1297.8</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>-0.13</v>
+        <v>30.8</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>2.43</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>487.05</v>
+        <v>491.1</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>487.65</v>
+        <v>491.65</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>495.9</v>
+        <v>493.7</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>487</v>
+        <v>483.3</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>491.1</v>
+        <v>483.3</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>0.83</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1200.5</v>
+        <v>1183.6</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1203.9</v>
+        <v>1186.1</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1205.3</v>
+        <v>1224</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1176.6</v>
+        <v>1175.7</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1183.6</v>
+        <v>1216.4</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>-1.41</v>
+        <v>32.8</v>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>414.8</v>
+        <v>412.65</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>416.5</v>
+        <v>414.65</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>417.8</v>
+        <v>417.25</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>412.55</v>
+        <v>411.35</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>412.65</v>
+        <v>413.25</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>-0.52</v>
+        <v>0.6</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>536.8</v>
+        <v>529.05</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>539.9</v>
+        <v>532</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>539.9</v>
+        <v>533.35</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>529.05</v>
+        <v>527</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-7.75</v>
+        <v>-2.05</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>-1.44</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1920.4</v>
+        <v>1909.8</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1920.4</v>
+        <v>1903</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1944</v>
+        <v>1930</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1903.1</v>
+        <v>1890</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1909.8</v>
+        <v>1924.3</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-0.55</v>
+        <v>14.5</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>2017.5</v>
+        <v>2006.5</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>2018</v>
+        <v>2009.5</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2032.8</v>
+        <v>2037.2</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>2002.2</v>
+        <v>1999.7</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>2006.5</v>
+        <v>2034</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-11</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>-0.55</v>
+        <v>27.5</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>569</v>
+        <v>565.1</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>573.95</v>
+        <v>576.7</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>563.2</v>
+        <v>564.05</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>565</v>
+        <v>572.5</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>-0.53</v>
+        <v>7.5</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3904.8</v>
+        <v>3866.4</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3919.6</v>
+        <v>3870</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3930.5</v>
+        <v>3945</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3866</v>
+        <v>3870</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-38.4</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>-0.98</v>
+        <v>63.5</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>307.8</v>
+        <v>304.9</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>308.15</v>
+        <v>308.9</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>309.25</v>
+        <v>312.7</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>302.05</v>
+        <v>307.75</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>5.1</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3307</v>
+        <v>3293.6</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3317.1</v>
+        <v>3285</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3330.5</v>
+        <v>3300</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3271</v>
+        <v>3198.2</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3293.6</v>
+        <v>3231.3</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-13.4</v>
+        <v>-62.3</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.41</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2124.5</v>
+        <v>2135</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2123.6</v>
+        <v>2125</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2135</v>
+        <v>2125</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2109</v>
+        <v>2090.1</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2135</v>
+        <v>2102.8</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>0.49</v>
+        <v>-32.2</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3055.3</v>
+        <v>3044.5</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3066</v>
+        <v>3048.4</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3093.7</v>
+        <v>3052</v>
       </c>
       <c r="G117" s="9" t="n">
+        <v>3022.4</v>
+      </c>
+      <c r="H117" s="9" t="n">
         <v>3035</v>
       </c>
-      <c r="H117" s="9" t="n">
-        <v>3044.5</v>
-      </c>
       <c r="I117" s="9" t="n">
-        <v>-10.8</v>
+        <v>-9.5</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>315.1</v>
+        <v>319.3</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>315.9</v>
+        <v>320</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>320.2</v>
+        <v>323</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>315.9</v>
+        <v>317.5</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>319.3</v>
+        <v>320.4</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>1.33</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>824.4</v>
+        <v>830</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>824.55</v>
+        <v>830.5</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>830.5</v>
+        <v>833.2</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>824.55</v>
+        <v>828</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>830</v>
+        <v>832.3</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="J119" s="13" t="n">
-        <v>0.68</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12153</v>
+        <v>12190</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12155</v>
+        <v>12240</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12275</v>
+        <v>12255</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12142</v>
+        <v>12106</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12190</v>
+        <v>12230</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J120" s="13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3209</v>
+        <v>3262.6</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3220</v>
+        <v>3269</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3289.8</v>
+        <v>3374</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3212.8</v>
+        <v>3237.5</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3262.6</v>
+        <v>3374</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>53.6</v>
+        <v>111.4</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>1.67</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>593.4</v>
+        <v>592.4</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>593.5</v>
+        <v>591.3</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>599</v>
+        <v>595.45</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>590.35</v>
+        <v>581</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>592.4</v>
+        <v>585.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-1</v>
+        <v>-6.9</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-0.17</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1569</v>
+        <v>1554.2</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1574.9</v>
+        <v>1562.4</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1581.1</v>
+        <v>1563.5</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1549.2</v>
+        <v>1548.1</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1554.2</v>
+        <v>1562.9</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1077.8</v>
+        <v>1067.3</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1075.5</v>
+        <v>1068</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1079.8</v>
+        <v>1112</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1067.3</v>
+        <v>1092.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>-0.97</v>
+        <v>25.5</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>162.91</v>
+        <v>161.77</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>162.75</v>
+        <v>162.99</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>163.9</v>
+        <v>165.2</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>161.21</v>
+        <v>162.33</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>161.77</v>
+        <v>164.4</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>-0.7</v>
+        <v>2.63</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2296.2</v>
+        <v>2265</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2298.4</v>
+        <v>2265</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2306.5</v>
+        <v>2274.3</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2254.5</v>
+        <v>2229.9</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2265</v>
+        <v>2259</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-31.2</v>
+        <v>-6</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-1.36</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>124855</v>
+        <v>124770</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>125490</v>
+        <v>124940</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>125755</v>
+        <v>125250</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124635</v>
+        <v>124415</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>124770</v>
+        <v>124580</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-85</v>
+        <v>-190</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2854.2</v>
+        <v>2831.5</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2855</v>
+        <v>2831</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2874</v>
+        <v>2856.5</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2822</v>
+        <v>2814.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2831.5</v>
+        <v>2856.5</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-22.7</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>-0.8</v>
+        <v>25</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="E130" s="12" t="n">
         <v>352.5</v>
       </c>
-      <c r="E130" s="12" t="n">
-        <v>352.95</v>
-      </c>
       <c r="F130" s="12" t="n">
-        <v>353.2</v>
+        <v>363.95</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>348.1</v>
+        <v>352.5</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>352.2</v>
+        <v>363.45</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>-0.09</v>
+        <v>11.25</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>3.19</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1296.4</v>
+        <v>1304</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1296</v>
+        <v>1295.6</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1316.9</v>
+        <v>1322.7</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1291.9</v>
+        <v>1291.1</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>0.59</v>
+        <v>-7</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8486.5</v>
+        <v>8438</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8500</v>
+        <v>8490</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8650</v>
+        <v>8495</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8411</v>
+        <v>8360</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8438</v>
+        <v>8457.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>-0.57</v>
+        <v>19.5</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1385</v>
+        <v>1363.9</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1382.2</v>
+        <v>1370</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1392.9</v>
+        <v>1387.2</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1363.9</v>
+        <v>1361.6</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1363.9</v>
+        <v>1387.2</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-21.1</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>-1.52</v>
+        <v>23.3</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>79.8</v>
+        <v>80.2</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>80.09</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>80.31</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>79.34</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>80.2</v>
+        <v>82</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J134" s="13" t="n">
-        <v>0.5</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>326.4</v>
+        <v>327.8</v>
       </c>
       <c r="E135" s="9" t="n">
         <v>326.5</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>329</v>
+        <v>329.4</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>325.55</v>
+        <v>325</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>327.8</v>
+        <v>326</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>0.43</v>
+        <v>-1.8</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1821</v>
+        <v>1845.6</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1823.9</v>
+        <v>1842.1</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1853</v>
+        <v>1878.1</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1802.6</v>
+        <v>1831</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1845.6</v>
+        <v>1850</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>24.6</v>
+        <v>4.4</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>1.35</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>10911</v>
+        <v>10989</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>10962</v>
+        <v>10989</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11111</v>
+        <v>11072</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>10835</v>
+        <v>10801</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>10989</v>
+        <v>10849</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>0.71</v>
+        <v>-140</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>235.63</v>
+        <v>236.13</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>235.51</v>
+        <v>235.5</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>236.37</v>
+        <v>236.9</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>233.75</v>
+        <v>234.2</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>236.13</v>
+        <v>236.9</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="J138" s="13" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35950</v>
+        <v>37150</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>36130</v>
+        <v>37480</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37345</v>
+        <v>37545</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36075</v>
+        <v>37055</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37150</v>
+        <v>37340</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>1200</v>
+        <v>190</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>3.34</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5449</v>
+        <v>5366</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5454.5</v>
+        <v>5400</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5463</v>
+        <v>5413</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5359</v>
+        <v>5213.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5366</v>
+        <v>5240</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-83</v>
+        <v>-126</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>-1.52</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>287.5</v>
+        <v>281.75</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>287.6</v>
+        <v>282.05</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>288.25</v>
+        <v>286.9</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>280.3</v>
+        <v>282.05</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>281.75</v>
+        <v>285.85</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>-2</v>
+        <v>4.1</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>344.75</v>
+        <v>345.8</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>345.2</v>
+        <v>345.55</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>346.5</v>
+        <v>349.95</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>343.1</v>
+        <v>344.55</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>345.8</v>
+        <v>346</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>1.05</v>
+        <v>0.2</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1573.2</v>
+        <v>1572.7</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1576.3</v>
+        <v>1575.1</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1587</v>
+        <v>1591.7</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1562.7</v>
+        <v>1575.1</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1572.7</v>
+        <v>1588.1</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>-0.03</v>
+        <v>15.4</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2321.8</v>
+        <v>2410</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2364.9</v>
+        <v>2407.2</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2428.7</v>
+        <v>2417.1</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2350</v>
+        <v>2381</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2410</v>
+        <v>2386</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>3.8</v>
+        <v>-24</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>118.45</v>
+        <v>116.61</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.74</v>
+        <v>118.9</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.7</v>
+        <v>116.61</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>117</v>
+        <v>118.3</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>-0.85</v>
+        <v>1.3</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8369.5</v>
+        <v>8350</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8400</v>
+        <v>8398.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8442</v>
+        <v>8454</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8345</v>
+        <v>8367</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8350</v>
+        <v>8417</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>-0.23</v>
+        <v>67</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>266.1</v>
+        <v>265.95</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>267</v>
+        <v>265.95</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>268.3</v>
+        <v>270.85</v>
       </c>
       <c r="G148" s="12" t="n">
         <v>265.95</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>265.95</v>
+        <v>270.2</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>-0.06</v>
+        <v>4.25</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1349.3</v>
+        <v>1334.8</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1350</v>
+        <v>1329.3</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1352.8</v>
+        <v>1329.3</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1306</v>
+        <v>1292.4</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1334.8</v>
+        <v>1317.5</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-14.5</v>
+        <v>-17.3</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-1.07</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>402.4</v>
+        <v>423.2</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>404.3</v>
+        <v>423.2</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>424.4</v>
+        <v>429.6</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>402.85</v>
+        <v>422.05</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>423.2</v>
+        <v>428</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>20.8</v>
+        <v>4.8</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>5.17</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>310.2</v>
+        <v>307.1</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>310.3</v>
+        <v>308</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>311</v>
+        <v>313.4</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>307.1</v>
+        <v>307.65</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>307.1</v>
+        <v>311.5</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-1</v>
+        <v>4.4</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1247.6</v>
+        <v>1242</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1251.9</v>
+        <v>1252.8</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1237.4</v>
+        <v>1238.9</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>7.6</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>177.3</v>
+        <v>174.01</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>177.1</v>
+        <v>174.5</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>178.29</v>
+        <v>185.7</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>174</v>
+        <v>174.5</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>174.01</v>
+        <v>185.44</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>-1.86</v>
+        <v>11.43</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>6.57</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>637</v>
+        <v>634.95</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>637.1</v>
+        <v>636</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>642.65</v>
+        <v>639.85</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>630.65</v>
+        <v>633.35</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>634.95</v>
+        <v>635</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>-0.32</v>
+        <v>0.05</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1756</v>
+        <v>1756.3</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1761.1</v>
+        <v>1758</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1772.7</v>
+        <v>1770.1</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1740</v>
+        <v>1744.4</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1756.3</v>
+        <v>1760</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J155" s="13" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>999.1</v>
+        <v>987</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1000.1</v>
+        <v>996.4</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>981.3</v>
+        <v>986.4</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>987</v>
+        <v>994.1</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>-0.9</v>
+        <v>7.1</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22550</v>
+        <v>22200</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22540</v>
+        <v>22210</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22650</v>
+        <v>22500</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22165</v>
+        <v>22210</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22200</v>
+        <v>22500</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-350</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-1.55</v>
+        <v>300</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1011.8</v>
+        <v>1006</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1011.8</v>
+        <v>1012</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1016.6</v>
+        <v>1018</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>995.5</v>
+        <v>1005.5</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1006</v>
+        <v>1010.8</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-0.57</v>
+        <v>4.8</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3887</v>
+        <v>3858</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3890</v>
+        <v>3878.3</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3954.3</v>
+        <v>3903</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3850.1</v>
+        <v>3828</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3858</v>
+        <v>3886</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-0.75</v>
+        <v>28</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
+        <v>2538.3</v>
+      </c>
+      <c r="E160" s="12" t="n">
+        <v>2545</v>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>2562</v>
+      </c>
+      <c r="G160" s="12" t="n">
         <v>2540</v>
       </c>
-      <c r="E160" s="12" t="n">
-        <v>2540</v>
-      </c>
-      <c r="F160" s="12" t="n">
-        <v>2554.3</v>
-      </c>
-      <c r="G160" s="12" t="n">
-        <v>2526.4</v>
-      </c>
       <c r="H160" s="12" t="n">
-        <v>2538.3</v>
+        <v>2550</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>11.7</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1868.9</v>
+        <v>1846.4</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1869</v>
+        <v>1846.4</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1876.4</v>
+        <v>1869.6</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1842.3</v>
+        <v>1844</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1846.4</v>
+        <v>1865</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-22.5</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>-1.2</v>
+        <v>18.6</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>457.55</v>
+        <v>490.1</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>458</v>
+        <v>490.1</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>494.2</v>
+        <v>503.3</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>454</v>
+        <v>485.6</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>490.1</v>
+        <v>490.2</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>32.55</v>
+        <v>0.1</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>7.11</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>385.15</v>
+        <v>377.5</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>385.15</v>
+        <v>379.4</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>385.85</v>
+        <v>386.85</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>373.6</v>
+        <v>375.15</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>377.5</v>
+        <v>381.85</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-7.65</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>-1.99</v>
+        <v>4.35</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>694.7</v>
+        <v>674</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>697.05</v>
+        <v>677.9</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>673</v>
+        <v>667.1</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>674</v>
+        <v>669.9</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-20.7</v>
+        <v>-4.1</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-2.98</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1732.7</v>
+        <v>1692.4</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1733</v>
+        <v>1692.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1741</v>
+        <v>1708.7</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1682.1</v>
+        <v>1681.2</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1692.4</v>
+        <v>1700.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-40.3</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>-2.33</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1000.6</v>
+        <v>984.1</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1002.9</v>
+        <v>988.4</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1006</v>
+        <v>997.1</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>984.1</v>
+        <v>985</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>984.1</v>
+        <v>994.3</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>-1.65</v>
+        <v>10.2</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>367.15</v>
+        <v>367</v>
       </c>
       <c r="E168" s="12" t="n">
         <v>367</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>370</v>
+        <v>369.9</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>365.9</v>
+        <v>367</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-0.04</v>
+        <v>2</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>183.4</v>
+        <v>184.97</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>183.6</v>
+        <v>184.88</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>185.49</v>
+        <v>191.5</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>183.1</v>
+        <v>184.87</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>184.97</v>
+        <v>190.82</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>1.57</v>
+        <v>5.85</v>
       </c>
       <c r="J169" s="13" t="n">
-        <v>0.86</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2128.7</v>
+        <v>2105</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2135.1</v>
+        <v>2099</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2135.2</v>
+        <v>2104.2</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2098.2</v>
+        <v>2077.6</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2105</v>
+        <v>2089.6</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-23.7</v>
+        <v>-15.4</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-1.11</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1558.5</v>
+        <v>1551.6</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1553.7</v>
+        <v>1540</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1558.7</v>
+        <v>1558</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1530.9</v>
+        <v>1539.3</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1551.6</v>
+        <v>1557</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>-0.44</v>
+        <v>5.4</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2588</v>
+        <v>2574</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2602</v>
+        <v>2574</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2617.4</v>
+        <v>2603</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2558.4</v>
+        <v>2565</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2574</v>
+        <v>2578.6</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-14</v>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v>-0.54</v>
+        <v>4.6</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4875</v>
+        <v>4928.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4876</v>
+        <v>4928.5</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4982</v>
+        <v>4951</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4862.5</v>
+        <v>4852.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>1.1</v>
+        <v>-48.5</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4970</v>
+        <v>4935</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4984</v>
+        <v>4924</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4984</v>
+        <v>4992</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4910</v>
+        <v>4884</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4935</v>
+        <v>4985</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-35</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>-0.7</v>
+        <v>50</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1262</v>
+        <v>1246.3</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1261</v>
+        <v>1247.1</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1268.4</v>
+        <v>1268</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1242</v>
+        <v>1247.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1246.3</v>
+        <v>1259.4</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>-1.24</v>
+        <v>13.1</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2815.5</v>
+        <v>2782.9</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2838.7</v>
+        <v>2782.9</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2847.9</v>
+        <v>2794.4</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2754.2</v>
+        <v>2764.5</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-32.6</v>
+        <v>-8.9</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-1.16</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4155</v>
+        <v>4140</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4155</v>
+        <v>4130.2</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4188.1</v>
+        <v>4164.8</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4134</v>
+        <v>4100.4</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4140</v>
+        <v>4135</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>-0.36</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1227.8</v>
+        <v>1215.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1234</v>
+        <v>1215</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1234.9</v>
+        <v>1248.1</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1210.4</v>
+        <v>1215</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1215.2</v>
+        <v>1242.3</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-1.03</v>
+        <v>27.1</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11100</v>
+        <v>11050</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11142</v>
+        <v>11198</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11000</v>
+        <v>11044</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11000</v>
+        <v>11155</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>-0.9</v>
+        <v>155</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>178.09</v>
+        <v>178</v>
       </c>
       <c r="E180" s="12" t="n">
         <v>178</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>178.8</v>
+        <v>180.55</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>175.86</v>
+        <v>178</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>-0.05</v>
+        <v>2</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="181">
@@ -6888,22 +6888,22 @@
         <v>559.9</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>559.25</v>
+        <v>557.6</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>562.55</v>
+        <v>560.45</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>555</v>
+        <v>550.1</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>559.9</v>
+        <v>553.15</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>0</v>
+        <v>-6.75</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>260.5</v>
+        <v>263</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>261</v>
+        <v>262.8</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>263.85</v>
+        <v>271.35</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>260.2</v>
+        <v>262.2</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="J182" s="13" t="n">
-        <v>0.96</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1142.1</v>
+        <v>1100.8</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1143</v>
+        <v>1092.9</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1143.1</v>
+        <v>1131.4</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1100</v>
+        <v>1090.8</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1100.8</v>
+        <v>1130</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-41.3</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>-3.62</v>
+        <v>29.2</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>2.65</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>164.55</v>
+        <v>166</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>164.81</v>
+        <v>164.7</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>166</v>
+        <v>165.7</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>163.21</v>
+        <v>164.1</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>166</v>
+        <v>164.9</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>0.88</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1161</v>
+        <v>1162.3</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1162.3</v>
+        <v>1170.1</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>0.11</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  22-Sep-2026 05:31 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  23-Sep-2026 05:43 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-Sep-2026 05:31 PM</t>
+          <t>23-Sep-2026 05:43 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 23-Sep-2026 05:43 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 24-Sep-2026 05:44 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>23-Sep-2026 05:43 PM</t>
+          <t>24-Sep-2026 05:44 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  23-Sep-2026 05:43 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  24-Sep-2026 05:44 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>496</v>
+        <v>491.35</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>493</v>
+        <v>487.65</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>504.25</v>
+        <v>492.2</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>489.2</v>
+        <v>484.05</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>491.35</v>
+        <v>489.45</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-4.65</v>
+        <v>-1.9</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7120.5</v>
+        <v>7120</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7141.5</v>
+        <v>7080</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7185</v>
+        <v>7144.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7077</v>
+        <v>7062.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7120</v>
+        <v>7129</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-0.01</v>
+        <v>9</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
+        <v>26935</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>26910</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>27225</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>27225</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>27490</v>
-      </c>
       <c r="G5" s="9" t="n">
-        <v>26905</v>
+        <v>26780</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26935</v>
+        <v>26860</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-290</v>
+        <v>-75</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>-1.07</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>397</v>
+        <v>402.45</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>398.85</v>
+        <v>394.6</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>402.75</v>
+        <v>401.7</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>397.6</v>
+        <v>388.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>402.45</v>
+        <v>390.1</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>1.37</v>
+        <v>-12.35</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.22</v>
+        <v>49.09</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49.29</v>
+        <v>49</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>49.59</v>
+        <v>49</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>48.9</v>
+        <v>47.94</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>49.09</v>
+        <v>48.06</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.13</v>
+        <v>-1.03</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-0.26</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1238.2</v>
+        <v>1251.4</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1242.6</v>
+        <v>1247</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1254.6</v>
+        <v>1247.1</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1240.5</v>
+        <v>1230.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1251.4</v>
+        <v>1236.1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>1.07</v>
+        <v>-15.3</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2997</v>
+        <v>2993.2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3015.5</v>
+        <v>2978</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>3023.9</v>
+        <v>2978</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2978.2</v>
+        <v>2898.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2993.2</v>
+        <v>2900</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-3.8</v>
+        <v>-93.2</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-0.13</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1795</v>
+        <v>1807.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1799</v>
+        <v>1802.4</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1810.1</v>
+        <v>1802.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1790.5</v>
+        <v>1775</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1807.3</v>
+        <v>1785.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>-22</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5331.5</v>
+        <v>5417.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5344</v>
+        <v>5372</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5445</v>
+        <v>5447</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5316</v>
+        <v>5261.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5417.5</v>
+        <v>5326</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>1.61</v>
+        <v>-91.5</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>386.9</v>
+        <v>392.75</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>387.3</v>
+        <v>390</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>392.85</v>
+        <v>390.9</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>387.3</v>
+        <v>382.65</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>392.75</v>
+        <v>384.1</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>1.51</v>
+        <v>-8.65</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>295.1</v>
+        <v>300</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>295.25</v>
+        <v>296</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>301.1</v>
+        <v>297.75</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>295.25</v>
+        <v>289.8</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>300</v>
+        <v>290.7</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>1.66</v>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="14">
@@ -1210,22 +1210,22 @@
         <v>2195</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2199</v>
+        <v>2177</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2204</v>
+        <v>2204.9</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2178</v>
+        <v>2158.2</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2195</v>
+        <v>2184.8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>0</v>
+        <v>-10.2</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8835.5</v>
+        <v>9069</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8875</v>
+        <v>9069</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>9070.5</v>
+        <v>9069</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8865</v>
+        <v>8888.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>9069</v>
+        <v>8888.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>233.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>2.64</v>
+        <v>-180.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>402.55</v>
+        <v>405.7</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>403.1</v>
+        <v>405.5</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>406.8</v>
+        <v>405.5</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>401.35</v>
+        <v>396.2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>405.7</v>
+        <v>397.95</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>0.78</v>
+        <v>-7.75</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>160.75</v>
+        <v>162.89</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>160.99</v>
+        <v>160</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>163.13</v>
+        <v>160.6</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>160.85</v>
+        <v>157</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>162.89</v>
+        <v>157.3</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>1.33</v>
+        <v>-5.59</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-3.43</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2448.5</v>
+        <v>2455</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2469</v>
+        <v>2430</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2471.9</v>
+        <v>2437.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2448.2</v>
+        <v>2391</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2455</v>
+        <v>2392.7</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>0.27</v>
+        <v>-62.3</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1381.6</v>
+        <v>1394.8</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1388.9</v>
+        <v>1387.8</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1404</v>
+        <v>1402.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1394.8</v>
+        <v>1392</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>0.96</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>626.25</v>
+        <v>625.25</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>630</v>
+        <v>623.9</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>633.25</v>
+        <v>623.9</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>623.05</v>
+        <v>611.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>625.25</v>
+        <v>612.4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-1</v>
+        <v>-12.85</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-0.16</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6176.5</v>
+        <v>6118</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6199</v>
+        <v>6100</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6199</v>
+        <v>6208.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6095</v>
+        <v>6098.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6118</v>
+        <v>6135.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-58.5</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>-0.95</v>
+        <v>17.5</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1036.4</v>
+        <v>1053</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1034</v>
+        <v>1034.1</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1055.8</v>
+        <v>1034.1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1032.6</v>
+        <v>999.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1053</v>
+        <v>1000.1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>1.6</v>
+        <v>-52.9</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-5.02</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1700</v>
+        <v>1721.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1700</v>
+        <v>1719.7</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1724.7</v>
+        <v>1740</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1692.6</v>
+        <v>1710</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1721.5</v>
+        <v>1716</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>1.26</v>
+        <v>-5.5</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1242.7</v>
+        <v>1243.2</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1242.2</v>
+        <v>1225.2</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1252</v>
+        <v>1225.2</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1238.9</v>
+        <v>1175</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1243.2</v>
+        <v>1186.5</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>0.04</v>
+        <v>-56.7</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-4.56</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11363</v>
+        <v>11400</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11363</v>
+        <v>11341</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11425</v>
+        <v>11383</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11293</v>
+        <v>11201</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11400</v>
+        <v>11208</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>0.33</v>
+        <v>-192</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1823.4</v>
+        <v>1846.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1825</v>
+        <v>1818</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1864.8</v>
+        <v>1818</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1825</v>
+        <v>1760.9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1846.5</v>
+        <v>1762.3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>1.27</v>
+        <v>-84.2</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>-4.56</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1008.8</v>
+        <v>1043.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1034.7</v>
+        <v>1005</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1043.2</v>
+        <v>1015</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1022</v>
+        <v>974</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>1043.2</v>
+        <v>982</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>3.41</v>
+        <v>-61.2</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-5.87</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2216.9</v>
+        <v>2199.6</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2205</v>
+        <v>2185</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2225.9</v>
+        <v>2201.7</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2190</v>
+        <v>2161.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2199.6</v>
+        <v>2167.8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-17.3</v>
+        <v>-31.8</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>-0.78</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>661.05</v>
+        <v>676.4</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>661.05</v>
+        <v>674.8</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>682.9</v>
+        <v>677.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>658.85</v>
+        <v>657</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>676.4</v>
+        <v>659.4</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>2.32</v>
+        <v>-17</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>184.7</v>
+        <v>191.38</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>185.95</v>
+        <v>186</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>193</v>
+        <v>189.28</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>185.7</v>
+        <v>182.62</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>191.38</v>
+        <v>182.9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>3.62</v>
+        <v>-8.48</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>234.35</v>
+        <v>236.87</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>233.2</v>
+        <v>234.5</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>237.7</v>
+        <v>236.22</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>233.2</v>
+        <v>233.77</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>236.87</v>
+        <v>234.3</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>1.08</v>
+        <v>-2.57</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>397.9</v>
+        <v>396.05</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>397.9</v>
+        <v>394</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>399.5</v>
+        <v>398.05</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>395.6</v>
+        <v>392</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>396.05</v>
+        <v>392</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-1.85</v>
+        <v>-4.05</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-0.46</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>452.6</v>
+        <v>459.75</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>459.7</v>
+        <v>457.85</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>462</v>
+        <v>457.85</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>455.3</v>
+        <v>444.35</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>459.75</v>
+        <v>449.4</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>1.58</v>
+        <v>-10.35</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1817.2</v>
+        <v>1833.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1818.1</v>
+        <v>1829.7</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1836.7</v>
+        <v>1829.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1818</v>
+        <v>1795.8</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1833.2</v>
+        <v>1795.8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>0.88</v>
+        <v>-37.4</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>425.8</v>
+        <v>423.1</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>427.25</v>
+        <v>421.4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>430</v>
+        <v>422.65</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>419.05</v>
+        <v>415.35</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>423.1</v>
+        <v>415.35</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-2.7</v>
+        <v>-7.75</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>-0.63</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>389</v>
+        <v>390.9</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>397.2</v>
+        <v>394.8</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>388.6</v>
+        <v>384.9</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>1.28</v>
+        <v>-8</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48290</v>
+        <v>47955</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>48290</v>
+        <v>47890</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48330</v>
+        <v>48080</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47585</v>
+        <v>47145</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47955</v>
+        <v>47750</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-335</v>
+        <v>-205</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>313.6</v>
+        <v>315.75</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>314.65</v>
+        <v>312.4</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>315.9</v>
+        <v>313.95</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>312.55</v>
+        <v>306.7</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>315.75</v>
+        <v>307.1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>-8.65</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4918</v>
+        <v>4929</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4927.5</v>
+        <v>4935</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>4965</v>
+        <v>4959.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4905</v>
+        <v>4885</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4929</v>
+        <v>4895</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>0.22</v>
+        <v>-34</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>281.15</v>
+        <v>281.1</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>281.1</v>
+        <v>280</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>282.8</v>
+        <v>280.35</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>281.1</v>
+        <v>277.7</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-0.05</v>
+        <v>-3.4</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-0.02</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>122.9</v>
+        <v>126</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>123.2</v>
+        <v>124.95</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>126.3</v>
+        <v>126.2</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>123.17</v>
+        <v>124.57</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>126</v>
+        <v>125.9</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>2.52</v>
+        <v>-0.1</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>759.55</v>
+        <v>757.95</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>761</v>
+        <v>757.95</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>767.4</v>
+        <v>759.9</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>753.75</v>
+        <v>740.05</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>757.95</v>
+        <v>743.15</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-1.6</v>
+        <v>-14.8</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-0.21</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>418.5</v>
+        <v>419.6</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>418.5</v>
+        <v>419.6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>421.65</v>
+        <v>421.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>417.75</v>
+        <v>415.45</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>419.6</v>
+        <v>418.2</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>0.26</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1759.1</v>
+        <v>1774</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1760</v>
+        <v>1630</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1784</v>
+        <v>1712</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1758.7</v>
+        <v>1629.9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1774</v>
+        <v>1681.7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>0.85</v>
+        <v>-92.3</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>-5.2</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1384.1</v>
+        <v>1383</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1382.4</v>
+        <v>1375</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1387</v>
+        <v>1419</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1371.8</v>
+        <v>1364.6</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1383</v>
+        <v>1399</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>-0.08</v>
+        <v>16</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>428</v>
+        <v>424.55</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>428.25</v>
+        <v>422</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>429.4</v>
+        <v>423.85</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>421.55</v>
+        <v>418.8</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>424.55</v>
+        <v>422</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-3.45</v>
+        <v>-2.55</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1803</v>
+        <v>1782.4</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1812</v>
+        <v>1762</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1817.4</v>
+        <v>1803.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1774.1</v>
+        <v>1758.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1782.4</v>
+        <v>1785.9</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-20.6</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-1.14</v>
+        <v>3.5</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1869</v>
+        <v>1886.7</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1901.3</v>
+        <v>1885.7</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1863.3</v>
+        <v>1852.2</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1886.7</v>
+        <v>1854.8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>0.95</v>
+        <v>-31.9</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>467</v>
+        <v>464.65</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>469</v>
+        <v>462.9</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>473.65</v>
+        <v>472.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>463.15</v>
+        <v>457.55</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>464.65</v>
+        <v>466.3</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>-0.5</v>
+        <v>1.65</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1944.9</v>
+        <v>1956</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1944.2</v>
+        <v>1943</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1989</v>
+        <v>1957.4</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1936.2</v>
+        <v>1922.2</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1956</v>
+        <v>1942.5</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>0.57</v>
+        <v>-13.5</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>222</v>
+        <v>223.43</v>
       </c>
       <c r="E51" s="9" t="n">
+        <v>222.78</v>
+      </c>
+      <c r="F51" s="9" t="n">
         <v>223.3</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>226.76</v>
-      </c>
       <c r="G51" s="9" t="n">
-        <v>222.6</v>
+        <v>218.65</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>223.43</v>
+        <v>219.8</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>0.64</v>
+        <v>-3.63</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>227.21</v>
+        <v>225.34</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>230.79</v>
+        <v>228.37</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>224.71</v>
+        <v>218.95</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>225.34</v>
+        <v>220.52</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-1.87</v>
+        <v>-4.82</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-0.82</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4962.5</v>
+        <v>5010</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5000</v>
+        <v>5003.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5053.5</v>
+        <v>5011.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4928</v>
+        <v>4958</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5010</v>
+        <v>4973</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>0.96</v>
+        <v>-37</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>388.1</v>
+        <v>387.4</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>388.3</v>
+        <v>387.2</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>395.45</v>
+        <v>388.9</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>387.4</v>
+        <v>383.45</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>387.4</v>
+        <v>385.7</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-0.7</v>
+        <v>-1.7</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-0.18</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1741.6</v>
+        <v>1744</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1741.1</v>
+        <v>1748</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1749.9</v>
+        <v>1750</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1729.1</v>
+        <v>1711.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1744</v>
+        <v>1721.2</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>0.14</v>
+        <v>-22.8</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1613.2</v>
+        <v>1635.8</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1614</v>
+        <v>1634</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1605.2</v>
+        <v>1596.1</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1635.8</v>
+        <v>1600.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v>1.4</v>
+        <v>-34.9</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>61.77</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>62.3</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>69</v>
+        <v>74.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>61.77</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>68.65000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>6.88</v>
+        <v>4.03</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>11.14</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9352</v>
+        <v>9624</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9330</v>
+        <v>9540.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9624</v>
+        <v>9740</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9312.5</v>
+        <v>9540</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9624</v>
+        <v>9602</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>272</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>2.91</v>
+        <v>-22</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13084</v>
+        <v>13200</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13084</v>
+        <v>13100</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13250</v>
+        <v>13315</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13055</v>
+        <v>13091</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13200</v>
+        <v>13299</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>669.5</v>
+        <v>675</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>669</v>
+        <v>666.75</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>681</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>668</v>
+        <v>666.55</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>675</v>
+        <v>670.4</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>0.82</v>
+        <v>-4.6</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1211</v>
+        <v>1211.2</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1210</v>
+        <v>1210.9</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1220.5</v>
+        <v>1213.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1205.9</v>
+        <v>1197</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1211.2</v>
+        <v>1200.4</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>0.02</v>
+        <v>-10.8</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7427</v>
+        <v>7470</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7468.5</v>
+        <v>7437</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7485</v>
+        <v>7460</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7414</v>
+        <v>7333</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7470</v>
+        <v>7338.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>0.58</v>
+        <v>-131.5</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2793.6</v>
+        <v>2796.9</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2803.9</v>
+        <v>2804</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2829</v>
+        <v>2861.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2784.9</v>
+        <v>2789.1</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2796.9</v>
+        <v>2822.9</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>3.3</v>
+        <v>26</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>429.7</v>
+        <v>425.95</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>430.05</v>
+        <v>426</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>432.2</v>
+        <v>436.8</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>423.65</v>
+        <v>421.9</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>425.95</v>
+        <v>426.55</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>-0.87</v>
+        <v>0.6</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>327</v>
+        <v>331.3</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>328.45</v>
+        <v>328</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>331.3</v>
+        <v>332.7</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>325.25</v>
+        <v>325.95</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>331.3</v>
+        <v>329.5</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>1.31</v>
+        <v>-1.8</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
+        <v>172.95</v>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>173.85</v>
+      </c>
+      <c r="G66" s="12" t="n">
         <v>171.84</v>
       </c>
-      <c r="E66" s="12" t="n">
-        <v>172.48</v>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>173.79</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>172</v>
-      </c>
       <c r="H66" s="12" t="n">
-        <v>172.95</v>
+        <v>173.85</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2461.4</v>
+        <v>2475</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2472</v>
+        <v>2460</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2482.6</v>
+        <v>2470</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2453.6</v>
+        <v>2422</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2475</v>
+        <v>2430.4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>0.55</v>
+        <v>-44.6</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>598.7</v>
+        <v>623.05</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>628.1</v>
+        <v>635</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>594.55</v>
+        <v>616</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>623.05</v>
+        <v>625.1</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>24.35</v>
+        <v>2.05</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>4.07</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>873.6</v>
+        <v>879.75</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>871.5</v>
+        <v>875.5</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>883.65</v>
+        <v>884.7</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>871.5</v>
+        <v>871.2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>879.75</v>
+        <v>875</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>0.7</v>
+        <v>-4.75</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1699.5</v>
+        <v>1707.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1700.9</v>
+        <v>1680</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1720</v>
+        <v>1707.9</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1700.9</v>
+        <v>1665.7</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1707.6</v>
+        <v>1671.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>0.48</v>
+        <v>-36.4</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>864.05</v>
+        <v>860.25</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>861.95</v>
+        <v>857</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>873.95</v>
+        <v>867</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>857.35</v>
+        <v>850.55</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>860.25</v>
+        <v>853</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-3.8</v>
+        <v>-7.25</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>-0.44</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3128.2</v>
+        <v>3188.5</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3138</v>
+        <v>3151</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3190</v>
+        <v>3203.7</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3127.1</v>
+        <v>3150.6</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3188.5</v>
+        <v>3166.5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>1.93</v>
+        <v>-22</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4800</v>
+        <v>4836</v>
       </c>
       <c r="E75" s="9" t="n">
         <v>4810</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4849</v>
+        <v>4846.7</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4802</v>
+        <v>4770</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4836</v>
+        <v>4774.2</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>0.75</v>
+        <v>-61.8</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1088.9</v>
+        <v>1096.5</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1091.1</v>
+        <v>1092</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1098</v>
+        <v>1102.9</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1086.1</v>
+        <v>1087</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1096.5</v>
+        <v>1090</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>0.7</v>
+        <v>-6.5</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1270.4</v>
+        <v>1256.7</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1270</v>
+        <v>1251</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1279.8</v>
+        <v>1263.3</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1250</v>
+        <v>1242.8</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1256.7</v>
+        <v>1243.6</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-13.7</v>
+        <v>-13.1</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>-1.08</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2430</v>
+        <v>2448.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2426.4</v>
+        <v>2427.8</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2454</v>
+        <v>2432</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2426</v>
+        <v>2380.3</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2448.3</v>
+        <v>2380.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>0.75</v>
+        <v>-68</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>738.6</v>
+        <v>737.25</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>735.65</v>
+        <v>725</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>742.8</v>
+        <v>734.85</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>734</v>
+        <v>722.7</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>737.25</v>
+        <v>728.9</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-1.35</v>
+        <v>-8.35</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-0.18</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>559.2</v>
+        <v>561.5</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>561.9</v>
+        <v>531</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>565.5</v>
+        <v>535.35</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>556.4</v>
+        <v>514</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>561.5</v>
+        <v>526.9</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>0.41</v>
+        <v>-34.6</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>-6.16</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5373</v>
+        <v>5394</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5395</v>
+        <v>5331.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5448.5</v>
+        <v>5368</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5365</v>
+        <v>5294</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5394</v>
+        <v>5296</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>0.39</v>
+        <v>-98</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>973</v>
+        <v>1003.8</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>979.5</v>
+        <v>983.5</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1003.8</v>
+        <v>991.9</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>978.2</v>
+        <v>976.5</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1003.8</v>
+        <v>982</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>3.17</v>
+        <v>-21.8</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>508.2</v>
+        <v>513</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>513</v>
+        <v>504.1</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>521.3</v>
+        <v>507.4</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>509.4</v>
+        <v>493.6</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>513</v>
+        <v>495.7</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>-17.3</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>360.7</v>
+        <v>360</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>362.5</v>
+        <v>356.05</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>364.65</v>
+        <v>358</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>358</v>
+        <v>349.3</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>360</v>
+        <v>350.4</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-0.7</v>
+        <v>-9.6</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>-0.19</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1933.8</v>
+        <v>1950</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1936</v>
+        <v>1925.5</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1950</v>
+        <v>1933.5</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>0.84</v>
+        <v>-16.5</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34025</v>
+        <v>34275</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34050</v>
+        <v>34275</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34500</v>
+        <v>34275</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33700</v>
+        <v>33200</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>34275</v>
+        <v>33625</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>0.73</v>
+        <v>-650</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>85.37</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>85.98</v>
+        <v>84.5</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>89.61</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>85.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>2.96</v>
+        <v>-4.14</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>112.9</v>
+        <v>113.16</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>112.9</v>
+        <v>112.32</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>113.9</v>
+        <v>112.5</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>112.75</v>
+        <v>111.04</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>113.16</v>
+        <v>111.2</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>0.23</v>
+        <v>-1.96</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>146.68</v>
+        <v>147.09</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>147.41</v>
+        <v>146.5</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>148.65</v>
+        <v>146.62</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>146.23</v>
+        <v>145.1</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>147.09</v>
+        <v>145.74</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>0.28</v>
+        <v>-1.35</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>738.25</v>
+        <v>739</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>744</v>
+        <v>740.1</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>736.15</v>
+        <v>727.4</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>1.01</v>
+        <v>-14.9</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1635.2</v>
+        <v>1652.4</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1644.7</v>
+        <v>1657.5</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1657</v>
+        <v>1657.5</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1636</v>
+        <v>1619</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1652.4</v>
+        <v>1635.9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>1.05</v>
+        <v>-16.5</v>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>5030</v>
+        <v>5028.5</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>5026</v>
+        <v>4975</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>5061</v>
+        <v>4975</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>5000</v>
+        <v>4874.5</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>5028.5</v>
+        <v>4890</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-1.5</v>
+        <v>-138.5</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>-0.03</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>955</v>
+        <v>959.3</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>951.8</v>
+        <v>918</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>970.8</v>
+        <v>928.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>951.8</v>
+        <v>909.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>959.3</v>
+        <v>919.5</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>0.45</v>
+        <v>-39.8</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-4.15</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>382.1</v>
+        <v>384.8</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>382.15</v>
+        <v>382</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>388.55</v>
+        <v>384.85</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>381.2</v>
+        <v>376.55</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>384.8</v>
+        <v>379.85</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>0.71</v>
+        <v>-4.95</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1029.4</v>
+        <v>1020.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1021.8</v>
+        <v>1015</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1029.4</v>
+        <v>1022.8</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1015.1</v>
+        <v>1005.2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-8.9</v>
+        <v>-6</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-0.86</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>137.8</v>
+        <v>138.15</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>138.5</v>
+        <v>136.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>138.75</v>
+        <v>137.5</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>137.1</v>
+        <v>135.51</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>138.15</v>
+        <v>136.27</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>0.25</v>
+        <v>-1.88</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1992.4</v>
+        <v>1962.6</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1993</v>
+        <v>1968.9</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1999.4</v>
+        <v>2006.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1948.5</v>
+        <v>1962.6</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1962.6</v>
+        <v>1997.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-29.8</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>-1.5</v>
+        <v>34.5</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>1.76</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>469.65</v>
+        <v>463.8</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>469.5</v>
+        <v>463.8</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>472.1</v>
+        <v>464.55</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>461</v>
+        <v>460.05</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>463.8</v>
+        <v>461.2</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-5.85</v>
+        <v>-2.6</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-1.25</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>265.8</v>
+        <v>270.15</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>265.85</v>
+        <v>268.7</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>271.05</v>
+        <v>270.3</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>265.15</v>
+        <v>266.7</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>270.15</v>
+        <v>268</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>1.64</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1141</v>
+        <v>1175.3</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1138.2</v>
+        <v>1157.3</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1187.4</v>
+        <v>1174.7</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1138.2</v>
+        <v>1152.3</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1175.3</v>
+        <v>1157.8</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>3.01</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5104</v>
+        <v>5085</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5104</v>
+        <v>5025</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5160</v>
+        <v>5229</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5005</v>
+        <v>4981</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5085</v>
+        <v>5184.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-19</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>-0.37</v>
+        <v>99.5</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>1.96</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>743.45</v>
+        <v>758.55</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>748.95</v>
+        <v>752</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>766.85</v>
+        <v>763.85</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>744.1</v>
+        <v>737</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>758.55</v>
+        <v>738.95</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>2.03</v>
+        <v>-19.6</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>517.2</v>
+        <v>520</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>525.85</v>
+        <v>520</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>516</v>
+        <v>508.1</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>0.58</v>
+        <v>-11</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1267</v>
+        <v>1297.8</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1273</v>
+        <v>1289</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1304</v>
+        <v>1298.4</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1270.8</v>
+        <v>1272.2</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1297.8</v>
+        <v>1273.2</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>2.43</v>
+        <v>-24.6</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>491.1</v>
+        <v>483.3</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>491.65</v>
+        <v>484.65</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>493.7</v>
+        <v>484.75</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>483.3</v>
+        <v>476.05</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>483.3</v>
+        <v>478.9</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-7.8</v>
+        <v>-4.4</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-1.59</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1183.6</v>
+        <v>1216.4</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1186.1</v>
+        <v>1214</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1224</v>
+        <v>1239.1</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1175.7</v>
+        <v>1204</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1216.4</v>
+        <v>1221.8</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>32.8</v>
+        <v>5.4</v>
       </c>
       <c r="J106" s="13" t="n">
-        <v>2.77</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>412.65</v>
+        <v>413.25</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>414.65</v>
+        <v>407</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>417.25</v>
+        <v>410</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>411.35</v>
+        <v>404.3</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>413.25</v>
+        <v>405</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>0.15</v>
+        <v>-8.25</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>529.05</v>
+        <v>527</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>533.35</v>
+        <v>527.8</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>527</v>
+        <v>516.85</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-2.05</v>
+        <v>-10.15</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>-0.39</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1909.8</v>
+        <v>1924.3</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1903</v>
+        <v>1940</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1930</v>
+        <v>1976.2</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1890</v>
+        <v>1911.7</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1924.3</v>
+        <v>1961.3</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>14.5</v>
+        <v>37</v>
       </c>
       <c r="J109" s="13" t="n">
-        <v>0.76</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>2006.5</v>
+        <v>2034</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>2009.5</v>
+        <v>2021.1</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2037.2</v>
+        <v>2055.3</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1999.7</v>
+        <v>2020</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>2034</v>
+        <v>2026.2</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>1.37</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>565</v>
+        <v>572.5</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>565.1</v>
+        <v>569.8</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>576.7</v>
+        <v>571.9</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>564.05</v>
+        <v>563.8</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>572.5</v>
+        <v>564.25</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>1.33</v>
+        <v>-8.25</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3870</v>
+        <v>3887.3</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3945</v>
+        <v>3907</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3870</v>
+        <v>3849</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3929.9</v>
+        <v>3858.4</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>1.64</v>
+        <v>-71.5</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>308.9</v>
+        <v>279</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>312.7</v>
+        <v>290.6</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>307.75</v>
+        <v>279</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>1.67</v>
+        <v>-28</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3293.6</v>
+        <v>3231.3</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3285</v>
+        <v>3233.7</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3300</v>
+        <v>3238.8</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3198.2</v>
+        <v>3190</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3231.3</v>
+        <v>3209.1</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-62.3</v>
+        <v>-22.2</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-1.89</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2135</v>
+        <v>2102.8</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2125</v>
+        <v>2099.9</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2125</v>
+        <v>2114.8</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2090.1</v>
+        <v>2084.5</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2102.8</v>
+        <v>2100.7</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-32.2</v>
+        <v>-2.1</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-1.51</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3044.5</v>
+        <v>3035</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3048.4</v>
+        <v>3028.8</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3052</v>
+        <v>3039</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3022.4</v>
+        <v>2982.7</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3035</v>
+        <v>2982.7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-9.5</v>
+        <v>-52.3</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>-0.31</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>319.3</v>
+        <v>320.4</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>320</v>
+        <v>314.4</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>317.5</v>
+        <v>313.15</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>320.4</v>
+        <v>324.95</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>1.1</v>
+        <v>4.55</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>0.34</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
+        <v>832.3</v>
+      </c>
+      <c r="E119" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="E119" s="9" t="n">
-        <v>830.5</v>
-      </c>
       <c r="F119" s="9" t="n">
-        <v>833.2</v>
+        <v>831.65</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>828</v>
+        <v>820.05</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>832.3</v>
+        <v>824.55</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>0.28</v>
+        <v>-7.75</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12190</v>
+        <v>12230</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12240</v>
+        <v>12180</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12255</v>
+        <v>12184</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12106</v>
+        <v>11975</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12230</v>
+        <v>11990</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>0.33</v>
+        <v>-240</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3262.6</v>
+        <v>3374</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3269</v>
+        <v>3365</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3374</v>
+        <v>3477</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3237.5</v>
+        <v>3351.1</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3374</v>
+        <v>3427.7</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>111.4</v>
+        <v>53.7</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>3.41</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>592.4</v>
+        <v>585.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>591.3</v>
+        <v>583.95</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>595.45</v>
+        <v>589.9</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>581</v>
+        <v>578.45</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>585.5</v>
+        <v>582.95</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-6.9</v>
+        <v>-2.55</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-1.16</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1554.2</v>
+        <v>1562.9</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1562.4</v>
+        <v>1406.7</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1563.5</v>
+        <v>1429.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1548.1</v>
+        <v>1360.1</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1562.9</v>
+        <v>1410</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-152.9</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1067.3</v>
+        <v>1092.8</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1068</v>
+        <v>1083.7</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1112</v>
+        <v>1092</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1068</v>
+        <v>1077.4</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1092.8</v>
+        <v>1079.6</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>2.39</v>
+        <v>-13.2</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>161.77</v>
+        <v>164.4</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>162.99</v>
+        <v>163.75</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>165.2</v>
+        <v>164.8</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>162.33</v>
+        <v>162.5</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>164.4</v>
+        <v>162.5</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>1.63</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2265</v>
+        <v>2259</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2265</v>
+        <v>2230</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2274.3</v>
+        <v>2277</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2229.9</v>
+        <v>2230</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2259</v>
+        <v>2248.2</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-6</v>
+        <v>-10.8</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-0.26</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>124770</v>
+        <v>124580</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>124940</v>
+        <v>124300</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>125250</v>
+        <v>124480</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124415</v>
+        <v>123520</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>124580</v>
+        <v>123985</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-190</v>
+        <v>-595</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>-0.15</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2831.5</v>
+        <v>2856.5</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2831</v>
+        <v>2825</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2856.5</v>
+        <v>2855</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2814.1</v>
+        <v>2808.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2856.5</v>
+        <v>2825.3</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>0.88</v>
+        <v>-31.2</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>352.2</v>
+        <v>363.45</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>352.5</v>
+        <v>355.95</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>363.95</v>
+        <v>361.65</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>352.5</v>
+        <v>354.4</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>363.45</v>
+        <v>358.4</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>3.19</v>
+        <v>-5.05</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1295.6</v>
+        <v>1232</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1322.7</v>
+        <v>1257.6</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1291.1</v>
+        <v>1202.3</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1297</v>
+        <v>1224</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-7</v>
+        <v>-73</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>-0.54</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8438</v>
+        <v>8457.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8490</v>
+        <v>8400</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8495</v>
+        <v>8559.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8360</v>
+        <v>8400</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8457.5</v>
+        <v>8461</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1363.9</v>
+        <v>1387.2</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1370</v>
+        <v>1355.7</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1387.2</v>
+        <v>1386</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1361.6</v>
+        <v>1350.2</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1387.2</v>
+        <v>1351</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>1.71</v>
+        <v>-36.2</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>80.2</v>
+        <v>82</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>80.06999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>82.31999999999999</v>
+        <v>82.09</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>80.06999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>82</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>2.24</v>
+        <v>-1.18</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>327.8</v>
+        <v>326</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>326.5</v>
+        <v>326.95</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>329.4</v>
+        <v>327.7</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>325</v>
+        <v>324.4</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>326</v>
+        <v>326.6</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-0.55</v>
+        <v>0.6</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1845.6</v>
+        <v>1850</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1842.1</v>
+        <v>1815</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1878.1</v>
+        <v>1874.7</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1831</v>
+        <v>1815</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1850</v>
+        <v>1837.5</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>0.24</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>10989</v>
+        <v>10849</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>10989</v>
+        <v>10600</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>11072</v>
+        <v>10995</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>10801</v>
+        <v>10600</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>10849</v>
+        <v>10925</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-140</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>-1.27</v>
+        <v>76</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>236.13</v>
+        <v>236.9</v>
       </c>
       <c r="E138" s="12" t="n">
         <v>235.5</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>236.9</v>
+        <v>239</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>234.2</v>
+        <v>235.23</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>236.9</v>
+        <v>239</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>0.77</v>
+        <v>2.1</v>
       </c>
       <c r="J138" s="13" t="n">
-        <v>0.33</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37150</v>
+        <v>37340</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37480</v>
+        <v>37015</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37545</v>
+        <v>37705</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37055</v>
+        <v>37010</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37340</v>
+        <v>37500</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5366</v>
+        <v>5240</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5400</v>
+        <v>5188</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5413</v>
+        <v>5345</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5213.5</v>
+        <v>5188</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5240</v>
+        <v>5277</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-126</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-2.35</v>
+        <v>37</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>281.75</v>
+        <v>285.85</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>282.05</v>
+        <v>285</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>286.9</v>
+        <v>288.1</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>282.05</v>
+        <v>283.3</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>285.85</v>
+        <v>286.6</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>4.1</v>
+        <v>0.75</v>
       </c>
       <c r="J142" s="13" t="n">
-        <v>1.46</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>345.8</v>
+        <v>346</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>345.55</v>
+        <v>343.85</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>349.95</v>
+        <v>345.1</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>344.55</v>
+        <v>338</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>346</v>
+        <v>339.35</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>0.06</v>
+        <v>-6.65</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1572.7</v>
+        <v>1588.1</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1575.1</v>
+        <v>1561</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1591.7</v>
+        <v>1579</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1575.1</v>
+        <v>1517.5</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1588.1</v>
+        <v>1522</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J144" s="13" t="n">
-        <v>0.98</v>
+        <v>-66.09999999999999</v>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>-4.16</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
+        <v>2386</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>2386</v>
+      </c>
+      <c r="F145" s="9" t="n">
         <v>2410</v>
       </c>
-      <c r="E145" s="9" t="n">
-        <v>2407.2</v>
-      </c>
-      <c r="F145" s="9" t="n">
-        <v>2417.1</v>
-      </c>
       <c r="G145" s="9" t="n">
-        <v>2381</v>
+        <v>2365.3</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2386</v>
+        <v>2393.5</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-24</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>-1</v>
+        <v>7.5</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>117</v>
+        <v>118.3</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>116.61</v>
+        <v>117.25</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.9</v>
+        <v>118.67</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.61</v>
+        <v>117.06</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>118.3</v>
+        <v>117.12</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>1.11</v>
+        <v>-1.18</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8350</v>
+        <v>8417</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8398.5</v>
+        <v>8371</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8454</v>
+        <v>8420</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8367</v>
+        <v>8324</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8417</v>
+        <v>8366.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>0.8</v>
+        <v>-50.5</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>265.95</v>
+        <v>270.2</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>265.95</v>
+        <v>270.4</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>270.85</v>
+        <v>270.9</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>265.95</v>
+        <v>265.75</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>270.2</v>
+        <v>266.4</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>1.6</v>
+        <v>-3.8</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1334.8</v>
+        <v>1317.5</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1329.3</v>
+        <v>1295.1</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1329.3</v>
+        <v>1310</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1292.4</v>
+        <v>1251</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1317.5</v>
+        <v>1256.7</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-17.3</v>
+        <v>-60.8</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-1.3</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
+        <v>428</v>
+      </c>
+      <c r="E150" s="12" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="F150" s="12" t="n">
         <v>423.2</v>
       </c>
-      <c r="E150" s="12" t="n">
-        <v>423.2</v>
-      </c>
-      <c r="F150" s="12" t="n">
-        <v>429.6</v>
-      </c>
       <c r="G150" s="12" t="n">
-        <v>422.05</v>
+        <v>409.1</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>428</v>
+        <v>412.75</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>1.13</v>
+        <v>-15.25</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>307.1</v>
+        <v>311.5</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>308</v>
+        <v>309.85</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>313.4</v>
+        <v>310.85</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>307.65</v>
+        <v>307.2</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>311.5</v>
+        <v>308.25</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>1.43</v>
+        <v>-3.25</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1242</v>
+        <v>1236.6</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1252.8</v>
+        <v>1241.6</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1238.9</v>
+        <v>1219.2</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1248</v>
+        <v>1219.2</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>0.61</v>
+        <v>-28.8</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>174.01</v>
+        <v>185.44</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>174.5</v>
+        <v>182.7</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>185.7</v>
+        <v>191.36</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>174.5</v>
+        <v>182.15</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>185.44</v>
+        <v>184</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>6.57</v>
+        <v>-1.44</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>634.95</v>
+        <v>635</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>639.85</v>
+        <v>642.3</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>633.35</v>
+        <v>616.2</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>635</v>
+        <v>618.4</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>0.01</v>
+        <v>-16.6</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1756.3</v>
+        <v>1760</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1758</v>
+        <v>1710</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1770.1</v>
+        <v>1791.4</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1744.4</v>
+        <v>1699.9</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>0.21</v>
+        <v>-5</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>987</v>
+        <v>994.1</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>987</v>
+        <v>982.3</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>996.4</v>
+        <v>992</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>986.4</v>
+        <v>975.8</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>994.1</v>
+        <v>978.5</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>0.72</v>
+        <v>-15.6</v>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22200</v>
+        <v>22500</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22210</v>
+        <v>22300</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22500</v>
+        <v>22725</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22210</v>
+        <v>22170</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22500</v>
+        <v>22350</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>300</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>1.35</v>
+        <v>-150</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1006</v>
+        <v>1010.8</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1012</v>
+        <v>999</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1018</v>
+        <v>1008.6</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1005.5</v>
+        <v>983.4</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1010.8</v>
+        <v>990</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>0.48</v>
+        <v>-20.8</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3858</v>
+        <v>3886</v>
       </c>
       <c r="E159" s="9" t="n">
+        <v>3852</v>
+      </c>
+      <c r="F159" s="9" t="n">
         <v>3878.3</v>
       </c>
-      <c r="F159" s="9" t="n">
-        <v>3903</v>
-      </c>
       <c r="G159" s="9" t="n">
-        <v>3828</v>
+        <v>3825</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3886</v>
+        <v>3841.8</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>0.73</v>
+        <v>-44.2</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2538.3</v>
+        <v>2550</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2562</v>
+        <v>2558.8</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2540</v>
+        <v>2515.2</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2550</v>
+        <v>2533.8</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>0.46</v>
+        <v>-16.2</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1846.4</v>
+        <v>1865</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1846.4</v>
+        <v>1859</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1869.6</v>
+        <v>1880</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1844</v>
+        <v>1848.4</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1865</v>
+        <v>1849.9</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>1.01</v>
+        <v>-15.1</v>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>490.1</v>
+        <v>490.2</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>490.1</v>
+        <v>485</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>503.3</v>
+        <v>522</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>485.6</v>
+        <v>483</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>490.2</v>
+        <v>512.7</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>0.1</v>
+        <v>22.5</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>0.02</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>377.5</v>
+        <v>381.85</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>379.4</v>
+        <v>380</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>386.85</v>
+        <v>384.9</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>375.15</v>
+        <v>378.1</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>381.85</v>
+        <v>380.35</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v>1.15</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>674</v>
+        <v>669.9</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>677</v>
+        <v>669.9</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>677.9</v>
+        <v>670</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>667.1</v>
+        <v>649.95</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>669.9</v>
+        <v>652.2</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-4.1</v>
+        <v>-17.7</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-0.61</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1692.4</v>
+        <v>1700.6</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1692.9</v>
+        <v>1696</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1708.7</v>
+        <v>1701</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1681.2</v>
+        <v>1666.6</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1700.6</v>
+        <v>1670</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>0.48</v>
+        <v>-30.6</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>984.1</v>
+        <v>994.3</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>988.4</v>
+        <v>989</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>997.1</v>
+        <v>992</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>994.3</v>
+        <v>986.3</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>1.04</v>
+        <v>-8</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>367</v>
+        <v>366.5</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>369.9</v>
+        <v>367.5</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>367</v>
+        <v>362.95</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>369</v>
+        <v>363.45</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>0.54</v>
+        <v>-5.55</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>184.97</v>
+        <v>190.82</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>184.88</v>
+        <v>188.21</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>191.5</v>
+        <v>191.8</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>184.87</v>
+        <v>187.72</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>190.82</v>
+        <v>188.02</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>3.16</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2105</v>
+        <v>2089.6</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2099</v>
+        <v>2076</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2104.2</v>
+        <v>2096.9</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2077.6</v>
+        <v>2067.1</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2089.6</v>
+        <v>2087</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-15.4</v>
+        <v>-2.6</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1551.6</v>
+        <v>1557</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1540</v>
+        <v>1549.9</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1558</v>
+        <v>1576.2</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1539.3</v>
+        <v>1543</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>0.35</v>
+        <v>-14</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2574</v>
+        <v>2578.6</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2574</v>
+        <v>2558</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2603</v>
+        <v>2585.5</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2565</v>
+        <v>2540.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2578.6</v>
+        <v>2540.5</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>0.18</v>
+        <v>-38.1</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4928.5</v>
+        <v>4868</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4951</v>
+        <v>4912</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4852.5</v>
+        <v>4830</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4880</v>
+        <v>4832.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-48.5</v>
+        <v>-47.5</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4935</v>
+        <v>4985</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4924</v>
+        <v>4976</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4992</v>
+        <v>5010</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4884</v>
+        <v>4902</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4985</v>
+        <v>4928.5</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>1.01</v>
+        <v>-56.5</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1246.3</v>
+        <v>1259.4</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1247.1</v>
+        <v>1238</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1268</v>
+        <v>1254</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1247.1</v>
+        <v>1235.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1259.4</v>
+        <v>1244.2</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>1.05</v>
+        <v>-15.2</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2782.9</v>
+        <v>2765</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2794.4</v>
+        <v>2767.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2764.5</v>
+        <v>2699.9</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2774</v>
+        <v>2700</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-8.9</v>
+        <v>-74</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-0.32</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4140</v>
+        <v>4135</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4130.2</v>
+        <v>4093.4</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4164.8</v>
+        <v>4123</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4100.4</v>
+        <v>4057</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4135</v>
+        <v>4091</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-5</v>
+        <v>-44</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>-0.12</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1215.2</v>
+        <v>1242.3</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1215</v>
+        <v>1240</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1248.1</v>
+        <v>1289.7</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1215</v>
+        <v>1227.1</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1242.3</v>
+        <v>1270.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11000</v>
+        <v>11155</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11050</v>
+        <v>11098</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11198</v>
+        <v>11192</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11044</v>
+        <v>11056</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11155</v>
+        <v>11056</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>155</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>1.41</v>
+        <v>-99</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>178</v>
+        <v>178.9</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>180.55</v>
+        <v>180.2</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>178</v>
+        <v>175.86</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>180</v>
+        <v>179.45</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>1.12</v>
+        <v>-0.55</v>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>559.9</v>
+        <v>553.15</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>557.6</v>
+        <v>550.7</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>560.45</v>
+        <v>553.65</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>550.1</v>
+        <v>546.5</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>553.15</v>
+        <v>549.6</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-6.75</v>
+        <v>-3.55</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-1.21</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>262.8</v>
+        <v>267.9</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>271.35</v>
+        <v>269.4</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>262.2</v>
+        <v>264.2</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>271</v>
+        <v>267.5</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>3.04</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1100.8</v>
+        <v>1130</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1092.9</v>
+        <v>1119.1</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1131.4</v>
+        <v>1126.4</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1090.8</v>
+        <v>1106.9</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1130</v>
+        <v>1113.4</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>2.65</v>
+        <v>-16.6</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>166</v>
+        <v>164.9</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>164.7</v>
+        <v>164.16</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>165.7</v>
+        <v>165.67</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>164.1</v>
+        <v>163.36</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>164.9</v>
+        <v>163.64</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.1</v>
+        <v>-1.26</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>-0.66</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1162.3</v>
+        <v>1170.1</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1156</v>
+        <v>1169.8</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1175</v>
+        <v>1190.6</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1156</v>
+        <v>1161.6</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1170.1</v>
+        <v>1180.3</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  23-Sep-2026 05:43 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  24-Sep-2026 05:44 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-Sep-2026 05:43 PM</t>
+          <t>24-Sep-2026 05:44 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 24-Sep-2026 05:44 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 25-Sep-2026 05:46 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>24-Sep-2026 05:44 PM</t>
+          <t>25-Sep-2026 05:46 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  24-Sep-2026 05:44 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  25-Sep-2026 05:46 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>491.35</v>
+        <v>489.45</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>487.65</v>
+        <v>487.85</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>492.2</v>
+        <v>492.7</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>484.05</v>
+        <v>484.6</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>489.45</v>
+        <v>489.25</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-1.9</v>
+        <v>-0.2</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.39</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7120</v>
+        <v>7129</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7080</v>
+        <v>7111</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7144.5</v>
+        <v>7201.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7062.5</v>
+        <v>7025</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7129</v>
+        <v>7052.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>0.13</v>
+        <v>-76.5</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26935</v>
+        <v>26860</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26910</v>
+        <v>26860</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27225</v>
+        <v>27095</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26780</v>
+        <v>26860</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26860</v>
+        <v>26955</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-75</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>-0.28</v>
+        <v>95</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>402.45</v>
+        <v>390.1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>394.6</v>
+        <v>390.9</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>401.7</v>
+        <v>392.2</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>388.5</v>
+        <v>384.8</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>390.1</v>
+        <v>390</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-12.35</v>
+        <v>-0.1</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-3.07</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.09</v>
+        <v>48.06</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49</v>
+        <v>48.02</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>49</v>
+        <v>49.28</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>47.94</v>
+        <v>47.88</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>48.06</v>
+        <v>49.14</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>-2.1</v>
+        <v>1.08</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1251.4</v>
+        <v>1236.1</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1247</v>
+        <v>1236.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1247.1</v>
+        <v>1239.8</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>1230.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1236.1</v>
+        <v>1236.4</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-15.3</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>-1.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2993.2</v>
+        <v>2900</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2978</v>
+        <v>2920</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2978</v>
+        <v>2939.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2898.2</v>
+        <v>2902.5</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-93.2</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>-3.11</v>
+        <v>16.5</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1807.3</v>
+        <v>1785.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1802.4</v>
+        <v>1791.8</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1802.4</v>
+        <v>1800.6</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>1775</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>-1.22</v>
+        <v>2.7</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5417.5</v>
+        <v>5326</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5372</v>
+        <v>5322.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5447</v>
+        <v>5325</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5261.5</v>
+        <v>5237</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5326</v>
+        <v>5274</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-91.5</v>
+        <v>-52</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>-1.69</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>392.75</v>
+        <v>384.1</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>390</v>
+        <v>382.2</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>390.9</v>
+        <v>387.2</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>382.65</v>
+        <v>381.7</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>384.1</v>
+        <v>383.8</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-8.65</v>
+        <v>-0.3</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-2.2</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>300</v>
+        <v>290.7</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>296</v>
+        <v>290.7</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>297.75</v>
+        <v>292.2</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>289.8</v>
+        <v>286.5</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>290.7</v>
+        <v>288</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-9.300000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-3.1</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2195</v>
+        <v>2184.8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2177</v>
+        <v>2179.1</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2204.9</v>
+        <v>2219</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2158.2</v>
+        <v>2176.5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>-0.46</v>
+        <v>29.9</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>9069</v>
+        <v>8888.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>9069</v>
+        <v>8891</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>9069</v>
+        <v>8934.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8888.5</v>
+        <v>8821.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8888.5</v>
+        <v>8889</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-180.5</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>-1.99</v>
+        <v>0.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>405.7</v>
+        <v>397.95</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>405.5</v>
+        <v>399.5</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>405.5</v>
+        <v>400.95</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>396.2</v>
+        <v>395.5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>397.95</v>
+        <v>400.1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-1.91</v>
+        <v>2.15</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>162.89</v>
+        <v>157.3</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>160</v>
+        <v>157.52</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>160.6</v>
+        <v>159.52</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>157</v>
+        <v>156.1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>157.3</v>
+        <v>159.08</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-3.43</v>
+        <v>1.78</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2455</v>
+        <v>2392.7</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2430</v>
+        <v>2401.9</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2437.8</v>
+        <v>2451</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2391</v>
+        <v>2397</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2392.7</v>
+        <v>2444</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-62.3</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>-2.54</v>
+        <v>51.3</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>2.14</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1394.8</v>
+        <v>1392</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1387.8</v>
+        <v>1389.8</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1402.3</v>
+        <v>1399</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1384</v>
+        <v>1385.6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-0.2</v>
+        <v>7</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>625.25</v>
+        <v>612.4</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>623.9</v>
+        <v>615</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>623.9</v>
+        <v>615</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>611.1</v>
+        <v>605.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>612.4</v>
+        <v>611.65</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-12.85</v>
+        <v>-0.75</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-2.06</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6118</v>
+        <v>6135.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6100</v>
+        <v>6164</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6208.5</v>
+        <v>6164</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6098.5</v>
+        <v>6050</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6135.5</v>
+        <v>6070.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>0.29</v>
+        <v>-65</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1053</v>
+        <v>1000.1</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1034.1</v>
+        <v>1001</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1034.1</v>
+        <v>1021.2</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>999.2</v>
+        <v>997</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1000.1</v>
+        <v>1018</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-52.9</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>-5.02</v>
+        <v>17.9</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1721.5</v>
+        <v>1716</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1719.7</v>
+        <v>1716</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1740</v>
+        <v>1727.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1710</v>
+        <v>1699.5</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-5.5</v>
+        <v>-4</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1243.2</v>
+        <v>1186.5</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1225.2</v>
+        <v>1191.5</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1225.2</v>
+        <v>1225</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1175</v>
+        <v>1191.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1186.5</v>
+        <v>1222.4</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-56.7</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>-4.56</v>
+        <v>35.9</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>3.03</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11400</v>
+        <v>11208</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11341</v>
+        <v>11245</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11383</v>
+        <v>11332</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11201</v>
+        <v>11212</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11208</v>
+        <v>11281</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-192</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-1.68</v>
+        <v>73</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1846.5</v>
+        <v>1762.3</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1818</v>
+        <v>1774</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1818</v>
+        <v>1778.1</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1760.9</v>
+        <v>1755</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1762.3</v>
+        <v>1771</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-84.2</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-4.56</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1043.2</v>
+        <v>982</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1005</v>
+        <v>982</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1015</v>
+        <v>997.2</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>974</v>
+        <v>980.2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>982</v>
+        <v>996.9</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-61.2</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>-5.87</v>
+        <v>14.9</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2199.6</v>
+        <v>2167.8</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2185</v>
+        <v>2166.5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2201.7</v>
+        <v>2192.2</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2161.1</v>
+        <v>2150</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2167.8</v>
+        <v>2185.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-1.45</v>
+        <v>17.5</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>676.4</v>
+        <v>659.4</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>674.8</v>
+        <v>663</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>677.5</v>
+        <v>697</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>657</v>
+        <v>657.85</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>659.4</v>
+        <v>685.8</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-17</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>-2.51</v>
+        <v>26.4</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>191.38</v>
+        <v>182.9</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>186</v>
+        <v>182.91</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>189.28</v>
+        <v>188.23</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>182.62</v>
+        <v>182.91</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>182.9</v>
+        <v>187.7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-8.48</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>-4.43</v>
+        <v>4.8</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>236.87</v>
+        <v>234.3</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>234.5</v>
+        <v>234.55</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>236.22</v>
+        <v>236.03</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>233.77</v>
+        <v>234.12</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>234.3</v>
+        <v>235.26</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2.57</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>-1.08</v>
+        <v>0.96</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>396.05</v>
+        <v>392</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>398.05</v>
+        <v>394.55</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>392</v>
+        <v>388.6</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>392</v>
+        <v>393.55</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>-1.02</v>
+        <v>1.55</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>459.75</v>
+        <v>449.4</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>457.85</v>
+        <v>451.9</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>457.85</v>
+        <v>459</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>444.35</v>
+        <v>449.8</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>449.4</v>
+        <v>458.35</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-10.35</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>-2.25</v>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1833.2</v>
+        <v>1795.8</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1829.7</v>
+        <v>1794</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1829.9</v>
+        <v>1801.7</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1795.8</v>
+        <v>1785</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1795.8</v>
+        <v>1785.4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-37.4</v>
+        <v>-10.4</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-2.04</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>423.1</v>
+        <v>415.35</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>421.4</v>
+        <v>417.75</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>422.65</v>
+        <v>423</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>415.35</v>
+        <v>411.8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>415.35</v>
+        <v>418.95</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>-1.83</v>
+        <v>3.6</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>390.9</v>
+        <v>387.5</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>394.8</v>
+        <v>388.7</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>384.9</v>
+        <v>380.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>387</v>
+        <v>382.15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-8</v>
+        <v>-4.85</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>-2.03</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47955</v>
+        <v>47750</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47890</v>
+        <v>47700</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48080</v>
+        <v>48445</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47145</v>
+        <v>47700</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>47750</v>
+        <v>48250</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-205</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>-0.43</v>
+        <v>500</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>315.75</v>
+        <v>307.1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>312.4</v>
+        <v>308.1</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>313.95</v>
+        <v>309.4</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>306.7</v>
+        <v>305.8</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>307.1</v>
+        <v>308.5</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-8.65</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>-2.74</v>
+        <v>1.4</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4929</v>
+        <v>4895</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4935</v>
+        <v>4900.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>4959.5</v>
+        <v>4939.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4885</v>
+        <v>4883</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4895</v>
+        <v>4937.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-34</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>42.5</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>281.1</v>
+        <v>277.7</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>280</v>
+        <v>277.3</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>280.35</v>
+        <v>278.15</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>276</v>
+        <v>273.3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>277.7</v>
+        <v>274.05</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-3.4</v>
+        <v>-3.65</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-1.21</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>126</v>
+        <v>125.9</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>124.95</v>
+        <v>125.79</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>126.2</v>
+        <v>126.7</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>124.57</v>
+        <v>124.8</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>125.9</v>
+        <v>124.99</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.1</v>
+        <v>-0.91</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>757.95</v>
+        <v>743.15</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>757.95</v>
+        <v>743.4</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>759.9</v>
+        <v>758</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>740.05</v>
+        <v>736.35</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>743.15</v>
+        <v>753.25</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>-1.95</v>
+        <v>10.1</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>419.6</v>
+        <v>418.2</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>419.6</v>
+        <v>418</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>421.5</v>
+        <v>423.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>415.45</v>
+        <v>416</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>418.2</v>
+        <v>417.95</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-1.4</v>
+        <v>-0.25</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>-0.33</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1774</v>
+        <v>1681.7</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1630</v>
+        <v>1678.1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1712</v>
+        <v>1681.9</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1629.9</v>
+        <v>1637.6</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1681.7</v>
+        <v>1662.7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-92.3</v>
+        <v>-19</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-5.2</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1383</v>
+        <v>1399</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1375</v>
+        <v>1402.9</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1364.6</v>
+        <v>1388.4</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1399</v>
+        <v>1399.7</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>16</v>
+        <v>0.7</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>1.16</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>424.55</v>
+        <v>422</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>423.85</v>
+        <v>426.65</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>418.8</v>
+        <v>421.35</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>422</v>
+        <v>426.1</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>-0.6</v>
+        <v>4.1</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1782.4</v>
+        <v>1785.9</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1762</v>
+        <v>1786.9</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1803.4</v>
+        <v>1793.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1758.1</v>
+        <v>1767.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1785.9</v>
+        <v>1784</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>0.2</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1886.7</v>
+        <v>1854.8</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1875</v>
+        <v>1854.8</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1885.7</v>
+        <v>1862.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1852.2</v>
+        <v>1835.4</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1854.8</v>
+        <v>1855.8</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-31.9</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>-1.69</v>
+        <v>1</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>464.65</v>
+        <v>466.3</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>462.9</v>
+        <v>467.8</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>472.9</v>
+        <v>468.15</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>457.55</v>
+        <v>458.55</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>466.3</v>
+        <v>461.5</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>0.36</v>
+        <v>-4.8</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1956</v>
+        <v>1942.5</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1943</v>
+        <v>1942.5</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1957.4</v>
+        <v>1975</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1922.2</v>
+        <v>1934</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1942.5</v>
+        <v>1963.9</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>21.4</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>223.43</v>
+        <v>219.8</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>222.78</v>
+        <v>219.8</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>223.3</v>
+        <v>221.75</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>218.65</v>
+        <v>217.5</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>219.8</v>
+        <v>218.6</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-3.63</v>
+        <v>-1.2</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>-1.62</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>225.34</v>
+        <v>220.52</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>225</v>
+        <v>223.39</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>228.37</v>
+        <v>227.11</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>218.95</v>
+        <v>221.79</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>220.52</v>
+        <v>225.57</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-4.82</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>-2.14</v>
+        <v>5.05</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5010</v>
+        <v>4973</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5003.5</v>
+        <v>4972</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5011.5</v>
+        <v>4991.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4958</v>
+        <v>4922.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4973</v>
+        <v>4945</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-37</v>
+        <v>-28</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.74</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>387.4</v>
+        <v>385.7</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>387.2</v>
+        <v>384.8</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>388.9</v>
+        <v>386</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>383.45</v>
+        <v>381.55</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>385.7</v>
+        <v>385.6</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-1.7</v>
+        <v>-0.1</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-0.44</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1744</v>
+        <v>1721.2</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1748</v>
+        <v>1746.2</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1750</v>
+        <v>1746.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1711.2</v>
+        <v>1680.7</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1721.2</v>
+        <v>1700.2</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-22.8</v>
+        <v>-21</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1635.8</v>
+        <v>1600.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1634</v>
+        <v>1601.1</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1634</v>
+        <v>1608.3</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1596.1</v>
+        <v>1575</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1600.9</v>
+        <v>1587.1</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-34.9</v>
+        <v>-13.8</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-2.13</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>68.65000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>68.84999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>74.8</v>
+        <v>77.89</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>68.84999999999999</v>
+        <v>69.31</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>72.68000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>4.03</v>
+        <v>4.16</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>5.87</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9624</v>
+        <v>9602</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9540.5</v>
+        <v>9602</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9740</v>
+        <v>9668.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9540</v>
+        <v>9530</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9602</v>
+        <v>9619.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>-0.23</v>
+        <v>17.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13200</v>
+        <v>13299</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13100</v>
+        <v>13280</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13315</v>
+        <v>13514</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13091</v>
+        <v>13211</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13299</v>
+        <v>13390</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>675</v>
+        <v>670.4</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>666.75</v>
+        <v>671.2</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>681</v>
+        <v>683.6</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>666.55</v>
+        <v>670.6</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>670.4</v>
+        <v>683</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>-0.68</v>
+        <v>12.6</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>1.88</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1211.2</v>
+        <v>1200.4</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1210.9</v>
+        <v>1204.5</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1213.9</v>
+        <v>1207.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1197</v>
+        <v>1193.4</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1200.4</v>
+        <v>1201</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-10.8</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-0.89</v>
+        <v>0.6</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7470</v>
+        <v>7338.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7437</v>
+        <v>7340.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7460</v>
+        <v>7381</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7333</v>
+        <v>7305</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7338.5</v>
+        <v>7360</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-131.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-1.76</v>
+        <v>21.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2796.9</v>
+        <v>2822.9</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2804</v>
+        <v>2822.9</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2861.9</v>
+        <v>2866.3</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2789.1</v>
+        <v>2817.1</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2822.9</v>
+        <v>2855.7</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>26</v>
+        <v>32.8</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>425.95</v>
+        <v>426.55</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>426</v>
+        <v>426.85</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>436.8</v>
+        <v>431.7</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>421.9</v>
+        <v>419.85</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>426.55</v>
+        <v>423.65</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>0.14</v>
+        <v>-2.9</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>331.3</v>
+        <v>329.5</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>328</v>
+        <v>327.5</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>332.7</v>
+        <v>332.5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>325.95</v>
+        <v>319.5</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>329.5</v>
+        <v>322</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1.8</v>
+        <v>-7.5</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>-0.54</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>172.95</v>
+        <v>173.85</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>172.1</v>
+        <v>173.9</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>173.85</v>
+        <v>173.98</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>171.84</v>
+        <v>171.59</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>173.85</v>
+        <v>172.7</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>0.52</v>
+        <v>-1.15</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2475</v>
+        <v>2430.4</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2460</v>
+        <v>2425</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2470</v>
+        <v>2435.2</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2422</v>
+        <v>2365.7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2430.4</v>
+        <v>2380</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-44.6</v>
+        <v>-50.4</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>-1.8</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>623.05</v>
+        <v>625.1</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>620</v>
+        <v>625.1</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>625.1</v>
+        <v>630.3</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>0.33</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>879.75</v>
+        <v>875</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>875.5</v>
+        <v>873.35</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>884.7</v>
+        <v>880.55</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>871.2</v>
+        <v>871.45</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>-0.54</v>
+        <v>5</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1707.6</v>
+        <v>1671.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1680</v>
+        <v>1666</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1707.9</v>
+        <v>1700.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1665.7</v>
+        <v>1666</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1671.2</v>
+        <v>1700.1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-36.4</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>-2.13</v>
+        <v>28.9</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>860.25</v>
+        <v>853</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>857</v>
+        <v>856.9</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>850.55</v>
+        <v>849.05</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>853</v>
+        <v>868.65</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>-0.84</v>
+        <v>15.65</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3188.5</v>
+        <v>3166.5</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3151</v>
+        <v>3175</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3203.7</v>
+        <v>3212.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3150.6</v>
+        <v>3161</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>24.5</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4836</v>
+        <v>4774.2</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4810</v>
+        <v>4774.2</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4846.7</v>
+        <v>4819.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4770</v>
+        <v>4760.1</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4774.2</v>
+        <v>4800</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>-1.28</v>
+        <v>25.8</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>1085.2</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>1097.3</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>1085.2</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>1096.5</v>
       </c>
-      <c r="E76" s="12" t="n">
-        <v>1092</v>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>1102.9</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>1087</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>1090</v>
-      </c>
       <c r="I76" s="12" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>-0.59</v>
+        <v>6.5</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1256.7</v>
+        <v>1243.6</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1251</v>
+        <v>1241</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1263.3</v>
+        <v>1266.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1242.8</v>
+        <v>1234.6</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1243.6</v>
+        <v>1258</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-13.1</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-1.04</v>
+        <v>14.4</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2448.3</v>
+        <v>2380.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2427.8</v>
+        <v>2390</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2432</v>
+        <v>2395.5</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2380.3</v>
+        <v>2366.5</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2380.3</v>
+        <v>2378</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-68</v>
+        <v>-2.3</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-2.78</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>737.25</v>
+        <v>728.9</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>734.85</v>
+        <v>739.65</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>722.7</v>
+        <v>723</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>728.9</v>
+        <v>735.6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>-1.13</v>
+        <v>6.7</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>561.5</v>
+        <v>526.9</v>
       </c>
       <c r="E80" s="12" t="n">
+        <v>526.9</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>535</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>516.45</v>
+      </c>
+      <c r="H80" s="12" t="n">
         <v>531</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>535.35</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>514</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>526.9</v>
-      </c>
       <c r="I80" s="12" t="n">
-        <v>-34.6</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>-6.16</v>
+        <v>4.1</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5394</v>
+        <v>5296</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5331.5</v>
+        <v>5340</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5368</v>
+        <v>5397</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5294</v>
+        <v>5304</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5296</v>
+        <v>5360</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-98</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-1.82</v>
+        <v>64</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>1.21</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1003.8</v>
+        <v>982</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>983.5</v>
+        <v>979.2</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>991.9</v>
+        <v>983.4</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>976.5</v>
+        <v>971.2</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-21.8</v>
+        <v>-5</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>-2.17</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>513</v>
+        <v>495.7</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>504.1</v>
+        <v>496</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>507.4</v>
+        <v>498.65</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>493.6</v>
+        <v>489.4</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>495.7</v>
+        <v>494.65</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-17.3</v>
+        <v>-1.05</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>-3.37</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>360</v>
+        <v>350.4</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>356.05</v>
+        <v>352.55</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>358</v>
+        <v>353.8</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>349.3</v>
+        <v>348.65</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>350.4</v>
+        <v>351</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>-2.67</v>
+        <v>0.6</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1950</v>
+        <v>1933.5</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1940</v>
+        <v>1933.5</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1953</v>
+        <v>1942.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1925.5</v>
+        <v>1915</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1933.5</v>
+        <v>1942.9</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-0.85</v>
+        <v>9.4</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>34275</v>
+        <v>33625</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>34275</v>
+        <v>33625</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>34275</v>
+        <v>33990</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33200</v>
+        <v>33315</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33625</v>
+        <v>33865</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-650</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-1.9</v>
+        <v>240</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>84.5</v>
+        <v>83.48</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>85.48999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>83.3</v>
+        <v>83.27</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>83.76000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-4.14</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>-4.71</v>
+        <v>0.04</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>113.16</v>
+        <v>111.2</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>112.32</v>
+        <v>111.38</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>112.5</v>
+        <v>112.9</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>111.04</v>
+        <v>110.89</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>111.2</v>
+        <v>112.7</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>-1.73</v>
+        <v>1.5</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>1.35</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>147.09</v>
+        <v>145.74</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>146.5</v>
+        <v>146</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>146.62</v>
+        <v>146.48</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>145.1</v>
+        <v>144.22</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>145.74</v>
+        <v>144.95</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.35</v>
+        <v>-0.79</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-0.92</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>739</v>
+        <v>726.1</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>740.1</v>
+        <v>731.25</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>727.4</v>
+        <v>721.95</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>728.8</v>
+        <v>726.8</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-14.9</v>
+        <v>-2</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>-2</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1652.4</v>
+        <v>1635.9</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1657.5</v>
+        <v>1637.8</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1657.5</v>
+        <v>1645</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1619</v>
+        <v>1625.9</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1635.9</v>
+        <v>1642.1</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>-1</v>
+        <v>6.2</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>5028.5</v>
+        <v>4890</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4975</v>
+        <v>4890</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4975</v>
+        <v>4956</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4874.5</v>
+        <v>4890</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4890</v>
+        <v>4940</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-138.5</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-2.75</v>
+        <v>50</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>959.3</v>
+        <v>919.5</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>918</v>
+        <v>919.5</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>928.9</v>
+        <v>923.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>909.3</v>
+        <v>906.9</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>919.5</v>
+        <v>912.2</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-39.8</v>
+        <v>-7.3</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>-4.15</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>384.8</v>
+        <v>379.85</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>384.85</v>
+        <v>379.25</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>376.55</v>
+        <v>373.2</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>379.85</v>
+        <v>374.65</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-4.95</v>
+        <v>-5.2</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>-1.29</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1015</v>
+        <v>999.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1022.8</v>
+        <v>1004.2</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1005.2</v>
+        <v>991.6</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1014.5</v>
+        <v>1000.2</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-6</v>
+        <v>-14.3</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-0.59</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>138.15</v>
+        <v>136.27</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>136.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137.5</v>
+        <v>137.06</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>135.51</v>
+        <v>135.33</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>136.27</v>
+        <v>135.7</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-1.88</v>
+        <v>-0.57</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-1.36</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1962.6</v>
+        <v>1997.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1968.9</v>
+        <v>2020</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2006.9</v>
+        <v>2020</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1962.6</v>
+        <v>1950</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1997.1</v>
+        <v>1970.8</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>1.76</v>
+        <v>-26.3</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>463.8</v>
+        <v>461.2</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>463.8</v>
+        <v>461.2</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>464.55</v>
+        <v>461.9</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>460.05</v>
+        <v>457.7</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>461.2</v>
+        <v>458.7</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>270.15</v>
+        <v>268</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>268.7</v>
+        <v>268.1</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>270.3</v>
+        <v>269</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>266.7</v>
+        <v>266.3</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-0.8</v>
+        <v>1</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1175.3</v>
+        <v>1157.8</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1157.3</v>
+        <v>1154.4</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1174.7</v>
+        <v>1168.9</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1152.3</v>
+        <v>1137</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1157.8</v>
+        <v>1164.8</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>-1.49</v>
+        <v>7</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5085</v>
+        <v>5184.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5025</v>
+        <v>5165</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5229</v>
+        <v>5165</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4981</v>
+        <v>4985</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5184.5</v>
+        <v>5000</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>1.96</v>
+        <v>-184.5</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>758.55</v>
+        <v>738.95</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>763.85</v>
+        <v>752.85</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>738.95</v>
+        <v>748.25</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>-2.58</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>520</v>
+        <v>513.1</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>508.1</v>
+        <v>503.15</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>510</v>
+        <v>506.55</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-11</v>
+        <v>-3.45</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>-2.11</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1297.8</v>
+        <v>1273.2</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1289</v>
+        <v>1279</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1298.4</v>
+        <v>1288.6</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1272.2</v>
+        <v>1266.3</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1273.2</v>
+        <v>1277</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-24.6</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>-1.9</v>
+        <v>3.8</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>483.3</v>
+        <v>478.9</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>484.65</v>
+        <v>478.5</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>484.75</v>
+        <v>490</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>476.05</v>
+        <v>474.1</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>478.9</v>
+        <v>484.55</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>-0.91</v>
+        <v>5.65</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1216.4</v>
+        <v>1221.8</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1214</v>
+        <v>1214.7</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1239.1</v>
+        <v>1227</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1204</v>
+        <v>1213</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1221.8</v>
+        <v>1218.1</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>0.44</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>413.25</v>
+        <v>405</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>407</v>
+        <v>406.9</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>410</v>
+        <v>407.95</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>404.3</v>
+        <v>399.3</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-8.25</v>
+        <v>-1</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-2</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>527</v>
+        <v>516.85</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>526</v>
+        <v>517.95</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>527.8</v>
+        <v>519.5</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>514</v>
+        <v>507.8</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>516.85</v>
+        <v>519.4</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-10.15</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>-1.93</v>
+        <v>2.55</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1924.3</v>
+        <v>1961.3</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1940</v>
+        <v>1980</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1976.2</v>
+        <v>1986.8</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1911.7</v>
+        <v>1902.7</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1961.3</v>
+        <v>1952.3</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>1.92</v>
+        <v>-9</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>2034</v>
+        <v>2026.2</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>2021.1</v>
+        <v>2026</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2055.3</v>
+        <v>2040</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>2020</v>
+        <v>1979.2</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>2026.2</v>
+        <v>2007</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-7.8</v>
+        <v>-19.2</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>-0.38</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>572.5</v>
+        <v>564.25</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>569.8</v>
+        <v>564.75</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>571.9</v>
+        <v>569.55</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>563.8</v>
+        <v>558.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>-1.44</v>
+        <v>1.75</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3929.9</v>
+        <v>3858.4</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3887.3</v>
+        <v>3865</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3907</v>
+        <v>3887.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3849</v>
+        <v>3842.4</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-71.5</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>-1.82</v>
+        <v>17.8</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>279</v>
+        <v>284.95</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>290.6</v>
+        <v>285.75</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>279</v>
+        <v>280.05</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-9.029999999999999</v>
+        <v>2</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3231.3</v>
+        <v>3209.1</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3233.7</v>
+        <v>3218.6</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3238.8</v>
+        <v>3229</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3190</v>
+        <v>3178</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3209.1</v>
+        <v>3206.1</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-22.2</v>
+        <v>-3</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2102.8</v>
+        <v>2100.7</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2099.9</v>
+        <v>2091.3</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2114.8</v>
+        <v>2095.7</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2084.5</v>
+        <v>2077.5</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2100.7</v>
+        <v>2092</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-2.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
+        <v>2982.7</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>2965</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>3045</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>2965</v>
+      </c>
+      <c r="H117" s="9" t="n">
         <v>3035</v>
       </c>
-      <c r="E117" s="9" t="n">
-        <v>3028.8</v>
-      </c>
-      <c r="F117" s="9" t="n">
-        <v>3039</v>
-      </c>
-      <c r="G117" s="9" t="n">
-        <v>2982.7</v>
-      </c>
-      <c r="H117" s="9" t="n">
-        <v>2982.7</v>
-      </c>
       <c r="I117" s="9" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-1.72</v>
+        <v>52.3</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>320.4</v>
+        <v>324.95</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>314.4</v>
+        <v>324.95</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>327</v>
+        <v>334.25</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>313.15</v>
+        <v>323.25</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>324.95</v>
+        <v>334</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>4.55</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>1.42</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>832.3</v>
+        <v>824.55</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>831.65</v>
+        <v>824</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>820.05</v>
+        <v>807.05</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>824.55</v>
+        <v>819</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-7.75</v>
+        <v>-5.55</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-0.93</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12230</v>
+        <v>11990</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>12180</v>
+        <v>11997</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12184</v>
+        <v>12098</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>11975</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>11990</v>
+        <v>12065</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-240</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-1.96</v>
+        <v>75</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3374</v>
+        <v>3427.7</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3365</v>
+        <v>3463.6</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3477</v>
+        <v>3481.4</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3351.1</v>
+        <v>3310</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3427.7</v>
+        <v>3324.9</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="J122" s="13" t="n">
-        <v>1.59</v>
+        <v>-102.8</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>585.5</v>
+        <v>582.95</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>583.95</v>
+        <v>584.95</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>589.9</v>
+        <v>589.95</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>578.45</v>
+        <v>572.1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>582.95</v>
+        <v>582.6</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-2.55</v>
+        <v>-0.35</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-0.44</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1562.9</v>
+        <v>1410</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1406.7</v>
+        <v>1390</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1429.8</v>
+        <v>1463.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1360.1</v>
+        <v>1390</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1410</v>
+        <v>1458</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-152.9</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>-9.779999999999999</v>
+        <v>48</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1092.8</v>
+        <v>1079.6</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1083.7</v>
+        <v>1076.5</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1077.4</v>
+        <v>1062.9</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1079.6</v>
+        <v>1071.3</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-13.2</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-1.21</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>164.4</v>
+        <v>162.5</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>163.75</v>
+        <v>162.6</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>164.8</v>
+        <v>166.22</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>162.5</v>
+        <v>160.72</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>162.5</v>
+        <v>165.71</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>-1.16</v>
+        <v>3.21</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2259</v>
+        <v>2248.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2230</v>
+        <v>2235</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2277</v>
+        <v>2240</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2230</v>
+        <v>2203.6</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2248.2</v>
+        <v>2234</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-10.8</v>
+        <v>-14.2</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-0.48</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>124580</v>
+        <v>123985</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>124300</v>
+        <v>124480</v>
       </c>
       <c r="F128" s="12" t="n">
         <v>124480</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>123520</v>
+        <v>123440</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>123985</v>
+        <v>124035</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-595</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-0.48</v>
+        <v>50</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2856.5</v>
+        <v>2825.3</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2825</v>
+        <v>2830</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2855</v>
+        <v>2839.6</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2808.1</v>
+        <v>2808</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2825.3</v>
+        <v>2835</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-31.2</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>-1.09</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>363.45</v>
+        <v>358.4</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>355.95</v>
+        <v>360.6</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>361.65</v>
+        <v>362.9</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>354.4</v>
+        <v>357.05</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>358.4</v>
+        <v>358.7</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-5.05</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>-1.39</v>
+        <v>0.3</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1297</v>
+        <v>1224</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1232</v>
+        <v>1216.4</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1257.6</v>
+        <v>1259</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1202.3</v>
+        <v>1215.4</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1224</v>
+        <v>1254.8</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-73</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-5.63</v>
+        <v>30.8</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>2.52</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8457.5</v>
+        <v>8461</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8400</v>
+        <v>8488.5</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8559.5</v>
+        <v>8600</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8400</v>
+        <v>8467</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8461</v>
+        <v>8584.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>3.5</v>
+        <v>123.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>0.04</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1387.2</v>
+        <v>1351</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1355.7</v>
+        <v>1357</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1386</v>
+        <v>1362.6</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1350.2</v>
+        <v>1348.3</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1351</v>
+        <v>1362.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-36.2</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>-2.61</v>
+        <v>11.6</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>82</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>81.09999999999999</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>82.09</v>
+        <v>81.12</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>80.8</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>80.81999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.18</v>
+        <v>-0.92</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-1.44</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>326</v>
+        <v>326.6</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>326.95</v>
+        <v>327.3</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>327.7</v>
+        <v>327.3</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>324.4</v>
+        <v>323.5</v>
       </c>
       <c r="H135" s="9" t="n">
         <v>326.6</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1850</v>
+        <v>1837.5</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1815</v>
+        <v>1837.5</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1874.7</v>
+        <v>1882.9</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1815</v>
+        <v>1837.5</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1837.5</v>
+        <v>1858.5</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>-0.68</v>
+        <v>21</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>10849</v>
+        <v>10925</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>10600</v>
+        <v>10782</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>10995</v>
+        <v>10805</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>10600</v>
+        <v>10332</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>10925</v>
+        <v>10770</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>0.7</v>
+        <v>-155</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>236.9</v>
+        <v>239</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>235.5</v>
+        <v>238</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>235.23</v>
+        <v>234.71</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>239</v>
+        <v>235.86</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>0.89</v>
+        <v>-3.14</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37340</v>
+        <v>37500</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37015</v>
+        <v>37350</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37705</v>
+        <v>37845</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37010</v>
+        <v>37350</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37500</v>
+        <v>37695</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5240</v>
+        <v>5277</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5188</v>
+        <v>5277</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5345</v>
+        <v>5385</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5188</v>
+        <v>5230</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5277</v>
+        <v>5372</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="J141" s="13" t="n">
-        <v>0.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>285.85</v>
+        <v>286.6</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>285</v>
+        <v>285.35</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>288.1</v>
+        <v>286.5</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>283.3</v>
+        <v>283.4</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>286.6</v>
+        <v>286.5</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>346</v>
+        <v>339.35</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>343.85</v>
+        <v>340</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>345.1</v>
+        <v>340.05</v>
       </c>
       <c r="G143" s="9" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="H143" s="9" t="n">
         <v>338</v>
       </c>
-      <c r="H143" s="9" t="n">
-        <v>339.35</v>
-      </c>
       <c r="I143" s="9" t="n">
-        <v>-6.65</v>
+        <v>-1.35</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>-1.92</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1588.1</v>
+        <v>1522</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1561</v>
+        <v>1525</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1579</v>
+        <v>1530</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1517.5</v>
+        <v>1495.7</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1522</v>
+        <v>1517.2</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-66.09999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-4.16</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2386</v>
+        <v>2393.5</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2386</v>
+        <v>2388.6</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2410</v>
+        <v>2405.6</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2365.3</v>
+        <v>2362.6</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2393.5</v>
+        <v>2400</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>118.3</v>
+        <v>117.12</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>117.25</v>
+        <v>117.12</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.67</v>
+        <v>118.01</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>117.06</v>
+        <v>116.23</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.18</v>
+        <v>-0.52</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-1</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8417</v>
+        <v>8366.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8371</v>
+        <v>8394</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8420</v>
+        <v>8463</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8324</v>
+        <v>8350</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8366.5</v>
+        <v>8408.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-50.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>-0.6</v>
+        <v>42</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>270.2</v>
+        <v>266.4</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>270.4</v>
+        <v>268.7</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>270.9</v>
+        <v>269.75</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>265.75</v>
+        <v>266.9</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>266.4</v>
+        <v>269.5</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>-1.41</v>
+        <v>3.1</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1317.5</v>
+        <v>1256.7</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1295.1</v>
+        <v>1264.9</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1310</v>
+        <v>1292</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1256.7</v>
+        <v>1254.6</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-60.8</v>
+        <v>-2.1</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-4.61</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>428</v>
+        <v>412.75</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>416.5</v>
+        <v>412.6</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>423.2</v>
+        <v>416</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>409.1</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>412.75</v>
+        <v>415.05</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-15.25</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>-3.56</v>
+        <v>2.3</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>311.5</v>
+        <v>308.25</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>309.85</v>
+        <v>309.2</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>310.85</v>
+        <v>312.95</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>307.2</v>
+        <v>307.25</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>308.25</v>
+        <v>312.95</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-1.04</v>
+        <v>4.7</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1248</v>
+        <v>1219.2</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1236.6</v>
+        <v>1210.5</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1241.6</v>
+        <v>1227.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1219.2</v>
+        <v>1210.5</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-28.8</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-2.31</v>
+        <v>6.8</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>185.44</v>
+        <v>184</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>182.7</v>
+        <v>184.64</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>191.36</v>
+        <v>186.05</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>182.15</v>
+        <v>182.77</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>-0.78</v>
+        <v>1</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>635</v>
+        <v>618.4</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>632</v>
+        <v>617</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>642.3</v>
+        <v>621.65</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>616.2</v>
+        <v>606.7</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>618.4</v>
+        <v>611.2</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-16.6</v>
+        <v>-7.2</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>-2.61</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1710</v>
+        <v>1755</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1791.4</v>
+        <v>1758.4</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1699.9</v>
+        <v>1732.3</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>994.1</v>
+        <v>978.5</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>982.3</v>
+        <v>980.8</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>992</v>
+        <v>985.7</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>975.8</v>
+        <v>977</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>978.5</v>
+        <v>983</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>-1.57</v>
+        <v>4.5</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22500</v>
+        <v>22350</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22300</v>
+        <v>22350</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22725</v>
+        <v>22520</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22170</v>
+        <v>22225</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22350</v>
+        <v>22520</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-150</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-0.67</v>
+        <v>170</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1010.8</v>
+        <v>990</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1008.6</v>
+        <v>1002</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>983.4</v>
+        <v>986.4</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>990</v>
+        <v>994.1</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-2.06</v>
+        <v>4.1</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3886</v>
+        <v>3841.8</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3852</v>
+        <v>3841.1</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3878.3</v>
+        <v>3881.6</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3825</v>
+        <v>3828.1</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3841.8</v>
+        <v>3877</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-44.2</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-1.14</v>
+        <v>35.2</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2550</v>
+        <v>2533.8</v>
       </c>
       <c r="E160" s="12" t="n">
+        <v>2535</v>
+      </c>
+      <c r="F160" s="12" t="n">
         <v>2540</v>
       </c>
-      <c r="F160" s="12" t="n">
-        <v>2558.8</v>
-      </c>
       <c r="G160" s="12" t="n">
-        <v>2515.2</v>
+        <v>2495.1</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2533.8</v>
+        <v>2540</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-16.2</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>-0.64</v>
+        <v>6.2</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1865</v>
+        <v>1849.9</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1859</v>
+        <v>1858.7</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1880</v>
+        <v>1858.7</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1848.4</v>
+        <v>1841.6</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1849.9</v>
+        <v>1852.2</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.3</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>490.2</v>
+        <v>512.7</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>485</v>
+        <v>511.35</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>522</v>
+        <v>521.75</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>483</v>
+        <v>504.55</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>512.7</v>
+        <v>513.2</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>22.5</v>
+        <v>0.5</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>4.59</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="F163" s="9" t="n">
         <v>381.85</v>
       </c>
-      <c r="E163" s="9" t="n">
-        <v>380</v>
-      </c>
-      <c r="F163" s="9" t="n">
-        <v>384.9</v>
-      </c>
       <c r="G163" s="9" t="n">
-        <v>378.1</v>
+        <v>376.95</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>380.35</v>
+        <v>378.7</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-1.5</v>
+        <v>-1.65</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-0.39</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>669.9</v>
+        <v>652.2</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>669.9</v>
+        <v>654.65</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>670</v>
+        <v>654.65</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>649.95</v>
+        <v>633.6</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>652.2</v>
+        <v>643.75</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-17.7</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-2.64</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1700.6</v>
+        <v>1670</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1696</v>
+        <v>1671.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1701</v>
+        <v>1682</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1666.6</v>
+        <v>1650.1</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1670</v>
+        <v>1666.5</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-30.6</v>
+        <v>-3.5</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-1.8</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>994.3</v>
+        <v>986.3</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>992</v>
+        <v>989.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>983</v>
+        <v>979.2</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>986.3</v>
+        <v>983.2</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-8</v>
+        <v>-3.1</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>-0.8</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>369</v>
+        <v>363.45</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>366.5</v>
+        <v>363</v>
       </c>
       <c r="F168" s="12" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>362.65</v>
+      </c>
+      <c r="H168" s="12" t="n">
         <v>367.5</v>
       </c>
-      <c r="G168" s="12" t="n">
-        <v>362.95</v>
-      </c>
-      <c r="H168" s="12" t="n">
-        <v>363.45</v>
-      </c>
       <c r="I168" s="12" t="n">
-        <v>-5.55</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-1.5</v>
+        <v>4.05</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>190.82</v>
+        <v>188.02</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>188.21</v>
+        <v>188.57</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>191.8</v>
+        <v>190.34</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>187.72</v>
+        <v>187.01</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>188.02</v>
+        <v>187.97</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-2.8</v>
+        <v>-0.05</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>-1.47</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2089.6</v>
+        <v>2087</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2076</v>
+        <v>2054</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2096.9</v>
+        <v>2090.2</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2067.1</v>
+        <v>2038.1</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-2.6</v>
+        <v>-5</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.12</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1549.9</v>
+        <v>1540</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1576.2</v>
+        <v>1554.7</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1543</v>
+        <v>1526.6</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-14</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>-0.9</v>
+        <v>5</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2578.6</v>
+        <v>2540.5</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2558</v>
+        <v>2530</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2585.5</v>
+        <v>2547.8</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2540.5</v>
+        <v>2506.1</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2540.5</v>
+        <v>2511.1</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-38.1</v>
+        <v>-29.4</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-1.48</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4880</v>
+        <v>4832.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4868</v>
+        <v>4855</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4912</v>
+        <v>4884</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4830</v>
+        <v>4821.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-47.5</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>-0.97</v>
+        <v>51.5</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4985</v>
+        <v>4928.5</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4976</v>
+        <v>4911.5</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>5010</v>
+        <v>4990.5</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4902</v>
+        <v>4906.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4928.5</v>
+        <v>4988.5</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-56.5</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>-1.13</v>
+        <v>60</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1259.4</v>
+        <v>1244.2</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1254</v>
+        <v>1264.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1235.1</v>
+        <v>1233.8</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1244.2</v>
+        <v>1254.6</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>-1.21</v>
+        <v>10.4</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2774</v>
+        <v>2700</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2765</v>
+        <v>2720</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2767.5</v>
+        <v>2720</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2699.9</v>
+        <v>2646</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2700</v>
+        <v>2669.3</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-74</v>
+        <v>-30.7</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-2.67</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4135</v>
+        <v>4091</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4093.4</v>
+        <v>4075</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4123</v>
+        <v>4177.9</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4057</v>
+        <v>4075</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4091</v>
+        <v>4157.3</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-44</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-1.06</v>
+        <v>66.3</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1242.3</v>
+        <v>1270.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1240</v>
+        <v>1270.2</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1289.7</v>
+        <v>1271.2</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1227.1</v>
+        <v>1243.2</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1270.2</v>
+        <v>1251.3</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>2.25</v>
+        <v>-18.9</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
+        <v>11056</v>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F179" s="9" t="n">
+        <v>11184</v>
+      </c>
+      <c r="G179" s="9" t="n">
+        <v>11027</v>
+      </c>
+      <c r="H179" s="9" t="n">
         <v>11155</v>
       </c>
-      <c r="E179" s="9" t="n">
-        <v>11098</v>
-      </c>
-      <c r="F179" s="9" t="n">
-        <v>11192</v>
-      </c>
-      <c r="G179" s="9" t="n">
-        <v>11056</v>
-      </c>
-      <c r="H179" s="9" t="n">
-        <v>11056</v>
-      </c>
       <c r="I179" s="9" t="n">
-        <v>-99</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>-0.89</v>
+        <v>99</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>180</v>
+        <v>179.45</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>178.9</v>
+        <v>178.78</v>
       </c>
       <c r="F180" s="12" t="n">
+        <v>180.72</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>178.34</v>
+      </c>
+      <c r="H180" s="12" t="n">
         <v>180.2</v>
       </c>
-      <c r="G180" s="12" t="n">
-        <v>175.86</v>
-      </c>
-      <c r="H180" s="12" t="n">
-        <v>179.45</v>
-      </c>
       <c r="I180" s="12" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>-0.31</v>
+        <v>0.75</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>553.15</v>
+        <v>549.6</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>550.7</v>
+        <v>548</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>553.65</v>
+        <v>552</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>546.5</v>
+        <v>543.6</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>549.6</v>
+        <v>550.05</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>-0.64</v>
+        <v>0.45</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>271</v>
+        <v>267.5</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>267.9</v>
+        <v>266.25</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>269.4</v>
+        <v>267.25</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>264.2</v>
+        <v>264.3</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>267.5</v>
+        <v>266.35</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-3.5</v>
+        <v>-1.15</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>-1.29</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1130</v>
+        <v>1113.4</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1119.1</v>
+        <v>1109.9</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1126.4</v>
+        <v>1122.1</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1106.9</v>
+        <v>1103.9</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1113.4</v>
+        <v>1118.2</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>-1.47</v>
+        <v>4.8</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>164.9</v>
+        <v>163.64</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>164.16</v>
+        <v>163.05</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>165.67</v>
+        <v>164.5</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>163.36</v>
+        <v>161.66</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>163.64</v>
+        <v>164.02</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-0.76</v>
+        <v>0.38</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1170.1</v>
+        <v>1180.3</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1169.8</v>
+        <v>1185.5</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1190.6</v>
+        <v>1208.6</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1161.6</v>
+        <v>1182.4</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1180.3</v>
+        <v>1203.9</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>10.2</v>
+        <v>23.6</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>0.87</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  24-Sep-2026 05:44 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  25-Sep-2026 05:46 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Sep-2026 05:44 PM</t>
+          <t>25-Sep-2026 05:46 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -64,7 +64,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,11 +94,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -161,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,9 +190,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -575,7 +567,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 25-Sep-2026 05:46 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 28-Sep-2026 08:00 PM</t>
         </is>
       </c>
     </row>
@@ -600,7 +592,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +613,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>25-Sep-2026 05:46 PM</t>
+          <t>28-Sep-2026 08:00 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +756,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  25-Sep-2026 05:46 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  28-Sep-2026 08:00 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +825,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>489.45</v>
+        <v>489.25</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>487.85</v>
+        <v/>
       </c>
       <c r="F3" s="9" t="n">
-        <v>492.7</v>
+        <v/>
       </c>
       <c r="G3" s="9" t="n">
-        <v>484.6</v>
+        <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>489.25</v>
+        <v/>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-0.2</v>
+        <v/>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.04</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -867,25 +859,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7129</v>
+        <v>7052.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7111</v>
+        <v/>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7201.5</v>
+        <v/>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7025</v>
+        <v/>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7052.5</v>
+        <v/>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-76.5</v>
+        <v/>
       </c>
       <c r="J4" s="10" t="n">
-        <v>-1.07</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -901,25 +893,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26860</v>
+        <v>26955</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26860</v>
+        <v/>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27095</v>
+        <v/>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26860</v>
+        <v/>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26955</v>
+        <v/>
       </c>
       <c r="I5" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>0.35</v>
+        <v/>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -935,25 +927,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>390.1</v>
+        <v>390</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>390.9</v>
+        <v/>
       </c>
       <c r="F6" s="12" t="n">
-        <v>392.2</v>
+        <v/>
       </c>
       <c r="G6" s="12" t="n">
-        <v>384.8</v>
+        <v/>
       </c>
       <c r="H6" s="12" t="n">
-        <v>390</v>
+        <v/>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-0.1</v>
+        <v/>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-0.03</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -969,25 +961,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>48.06</v>
+        <v>49.14</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>48.02</v>
+        <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>49.28</v>
+        <v/>
       </c>
       <c r="G7" s="9" t="n">
-        <v>47.88</v>
+        <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>49.14</v>
+        <v/>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>2.25</v>
+        <v/>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +995,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1236.1</v>
+        <v>1236.4</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1236.1</v>
+        <v/>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1239.8</v>
+        <v/>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1230.5</v>
+        <v/>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1236.4</v>
+        <v/>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0.02</v>
+        <v/>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1029,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2920</v>
+        <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2939.9</v>
+        <v/>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2902.5</v>
+        <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2916.5</v>
+        <v/>
       </c>
       <c r="I9" s="9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>0.57</v>
+        <v/>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1063,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1791.8</v>
+        <v/>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1800.6</v>
+        <v/>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1775</v>
+        <v/>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1788</v>
+        <v/>
       </c>
       <c r="I10" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0.15</v>
+        <v/>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1097,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5326</v>
+        <v>5274</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5322.5</v>
+        <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5325</v>
+        <v/>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5237</v>
+        <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5274</v>
+        <v/>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-52</v>
+        <v/>
       </c>
       <c r="J11" s="10" t="n">
-        <v>-0.98</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1131,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>384.1</v>
+        <v>383.8</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>382.2</v>
+        <v/>
       </c>
       <c r="F12" s="12" t="n">
-        <v>387.2</v>
+        <v/>
       </c>
       <c r="G12" s="12" t="n">
-        <v>381.7</v>
+        <v/>
       </c>
       <c r="H12" s="12" t="n">
-        <v>383.8</v>
+        <v/>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-0.3</v>
+        <v/>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-0.08</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1165,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>290.7</v>
+        <v>288</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>290.7</v>
+        <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>292.2</v>
+        <v/>
       </c>
       <c r="G13" s="9" t="n">
-        <v>286.5</v>
+        <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>288</v>
+        <v/>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-2.7</v>
+        <v/>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-0.93</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1199,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2184.8</v>
+        <v>2214.7</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2179.1</v>
+        <v/>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2219</v>
+        <v/>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2176.5</v>
+        <v/>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2214.7</v>
+        <v/>
       </c>
       <c r="I14" s="12" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>1.37</v>
+        <v/>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1233,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8888.5</v>
+        <v>8889</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8891</v>
+        <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8934.5</v>
+        <v/>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8821.5</v>
+        <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8889</v>
+        <v/>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>0.01</v>
+        <v/>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1267,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>397.95</v>
+        <v>400.1</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>399.5</v>
+        <v/>
       </c>
       <c r="F16" s="12" t="n">
-        <v>400.95</v>
+        <v/>
       </c>
       <c r="G16" s="12" t="n">
-        <v>395.5</v>
+        <v/>
       </c>
       <c r="H16" s="12" t="n">
-        <v>400.1</v>
+        <v/>
       </c>
       <c r="I16" s="12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>0.54</v>
+        <v/>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1301,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>157.3</v>
+        <v>159.08</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>157.52</v>
+        <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>159.52</v>
+        <v/>
       </c>
       <c r="G17" s="9" t="n">
-        <v>156.1</v>
+        <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>159.08</v>
+        <v/>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>1.13</v>
+        <v/>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1335,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2392.7</v>
+        <v>2444</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2401.9</v>
+        <v/>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2451</v>
+        <v/>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2397</v>
+        <v/>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2444</v>
+        <v/>
       </c>
       <c r="I18" s="12" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>2.14</v>
+        <v/>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1369,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1389.8</v>
+        <v/>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1399</v>
+        <v/>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1385.6</v>
+        <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1399</v>
+        <v/>
       </c>
       <c r="I19" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>0.5</v>
+        <v/>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1403,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>612.4</v>
+        <v>611.65</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>615</v>
+        <v/>
       </c>
       <c r="F20" s="12" t="n">
-        <v>615</v>
+        <v/>
       </c>
       <c r="G20" s="12" t="n">
-        <v>605.1</v>
+        <v/>
       </c>
       <c r="H20" s="12" t="n">
-        <v>611.65</v>
+        <v/>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-0.75</v>
+        <v/>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-0.12</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1437,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6135.5</v>
+        <v>6070.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6164</v>
+        <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6164</v>
+        <v/>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6050</v>
+        <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6070.5</v>
+        <v/>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-65</v>
+        <v/>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-1.06</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1471,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1000.1</v>
+        <v>1018</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1001</v>
+        <v/>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1021.2</v>
+        <v/>
       </c>
       <c r="G22" s="12" t="n">
-        <v>997</v>
+        <v/>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1018</v>
+        <v/>
       </c>
       <c r="I22" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>1.79</v>
+        <v/>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1505,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1716</v>
+        <v/>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1727.9</v>
+        <v/>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1699.5</v>
+        <v/>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1712</v>
+        <v/>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-4</v>
+        <v/>
       </c>
       <c r="J23" s="10" t="n">
-        <v>-0.23</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1539,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1186.5</v>
+        <v>1222.4</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1191.5</v>
+        <v/>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1225</v>
+        <v/>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1191.5</v>
+        <v/>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1222.4</v>
+        <v/>
       </c>
       <c r="I24" s="12" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>3.03</v>
+        <v/>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1573,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11208</v>
+        <v>11281</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>11245</v>
+        <v/>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11332</v>
+        <v/>
       </c>
       <c r="G25" s="9" t="n">
-        <v>11212</v>
+        <v/>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11281</v>
+        <v/>
       </c>
       <c r="I25" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>0.65</v>
+        <v/>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1607,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1762.3</v>
+        <v>1771</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1774</v>
+        <v/>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1778.1</v>
+        <v/>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1755</v>
+        <v/>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1771</v>
+        <v/>
       </c>
       <c r="I26" s="12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>0.49</v>
+        <v/>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1641,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>982</v>
+        <v>996.9</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>982</v>
+        <v/>
       </c>
       <c r="F27" s="9" t="n">
-        <v>997.2</v>
+        <v/>
       </c>
       <c r="G27" s="9" t="n">
-        <v>980.2</v>
+        <v/>
       </c>
       <c r="H27" s="9" t="n">
-        <v>996.9</v>
+        <v/>
       </c>
       <c r="I27" s="9" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>1.52</v>
+        <v/>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1675,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2167.8</v>
+        <v>2185.3</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2166.5</v>
+        <v/>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2192.2</v>
+        <v/>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2150</v>
+        <v/>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2185.3</v>
+        <v/>
       </c>
       <c r="I28" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v/>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1709,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>659.4</v>
+        <v>685.8</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>663</v>
+        <v/>
       </c>
       <c r="F29" s="9" t="n">
-        <v>697</v>
+        <v/>
       </c>
       <c r="G29" s="9" t="n">
-        <v>657.85</v>
+        <v/>
       </c>
       <c r="H29" s="9" t="n">
-        <v>685.8</v>
+        <v/>
       </c>
       <c r="I29" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1743,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>182.9</v>
+        <v>187.7</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>182.91</v>
+        <v/>
       </c>
       <c r="F30" s="12" t="n">
-        <v>188.23</v>
+        <v/>
       </c>
       <c r="G30" s="12" t="n">
-        <v>182.91</v>
+        <v/>
       </c>
       <c r="H30" s="12" t="n">
-        <v>187.7</v>
+        <v/>
       </c>
       <c r="I30" s="12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>2.62</v>
+        <v/>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1777,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>234.3</v>
+        <v>235.26</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>234.55</v>
+        <v/>
       </c>
       <c r="F31" s="9" t="n">
-        <v>236.03</v>
+        <v/>
       </c>
       <c r="G31" s="9" t="n">
-        <v>234.12</v>
+        <v/>
       </c>
       <c r="H31" s="9" t="n">
-        <v>235.26</v>
+        <v/>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>0.41</v>
+        <v/>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1811,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>392</v>
+        <v>393.55</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>392</v>
+        <v/>
       </c>
       <c r="F32" s="12" t="n">
-        <v>394.55</v>
+        <v/>
       </c>
       <c r="G32" s="12" t="n">
-        <v>388.6</v>
+        <v/>
       </c>
       <c r="H32" s="12" t="n">
-        <v>393.55</v>
+        <v/>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>0.4</v>
+        <v/>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1845,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>449.4</v>
+        <v>458.35</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>451.9</v>
+        <v/>
       </c>
       <c r="F33" s="9" t="n">
-        <v>459</v>
+        <v/>
       </c>
       <c r="G33" s="9" t="n">
-        <v>449.8</v>
+        <v/>
       </c>
       <c r="H33" s="9" t="n">
-        <v>458.35</v>
+        <v/>
       </c>
       <c r="I33" s="9" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>1.99</v>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1879,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1795.8</v>
+        <v>1785.4</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1794</v>
+        <v/>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1801.7</v>
+        <v/>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1785</v>
+        <v/>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1785.4</v>
+        <v/>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-10.4</v>
+        <v/>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-0.58</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1913,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>415.35</v>
+        <v>418.95</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>417.75</v>
+        <v/>
       </c>
       <c r="F35" s="9" t="n">
-        <v>423</v>
+        <v/>
       </c>
       <c r="G35" s="9" t="n">
-        <v>411.8</v>
+        <v/>
       </c>
       <c r="H35" s="9" t="n">
-        <v>418.95</v>
+        <v/>
       </c>
       <c r="I35" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>0.87</v>
+        <v/>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1947,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>387</v>
+        <v>382.15</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>387.5</v>
+        <v/>
       </c>
       <c r="F36" s="12" t="n">
-        <v>388.7</v>
+        <v/>
       </c>
       <c r="G36" s="12" t="n">
-        <v>380.5</v>
+        <v/>
       </c>
       <c r="H36" s="12" t="n">
-        <v>382.15</v>
+        <v/>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-4.85</v>
+        <v/>
       </c>
       <c r="J36" s="10" t="n">
-        <v>-1.25</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1981,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>47750</v>
+        <v>48250</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>47700</v>
+        <v/>
       </c>
       <c r="F37" s="9" t="n">
-        <v>48445</v>
+        <v/>
       </c>
       <c r="G37" s="9" t="n">
-        <v>47700</v>
+        <v/>
       </c>
       <c r="H37" s="9" t="n">
-        <v>48250</v>
+        <v/>
       </c>
       <c r="I37" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>1.05</v>
+        <v/>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2015,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>307.1</v>
+        <v>308.5</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>308.1</v>
+        <v/>
       </c>
       <c r="F38" s="12" t="n">
-        <v>309.4</v>
+        <v/>
       </c>
       <c r="G38" s="12" t="n">
-        <v>305.8</v>
+        <v/>
       </c>
       <c r="H38" s="12" t="n">
-        <v>308.5</v>
+        <v/>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>0.46</v>
+        <v/>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2049,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4895</v>
+        <v>4937.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>4900.5</v>
+        <v/>
       </c>
       <c r="F39" s="9" t="n">
-        <v>4939.5</v>
+        <v/>
       </c>
       <c r="G39" s="9" t="n">
-        <v>4883</v>
+        <v/>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4937.5</v>
+        <v/>
       </c>
       <c r="I39" s="9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>0.87</v>
+        <v/>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2083,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>277.7</v>
+        <v>274.05</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>277.3</v>
+        <v/>
       </c>
       <c r="F40" s="12" t="n">
-        <v>278.15</v>
+        <v/>
       </c>
       <c r="G40" s="12" t="n">
-        <v>273.3</v>
+        <v/>
       </c>
       <c r="H40" s="12" t="n">
-        <v>274.05</v>
+        <v/>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-3.65</v>
+        <v/>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-1.31</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2117,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>125.9</v>
+        <v>124.99</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>125.79</v>
+        <v/>
       </c>
       <c r="F41" s="9" t="n">
-        <v>126.7</v>
+        <v/>
       </c>
       <c r="G41" s="9" t="n">
-        <v>124.8</v>
+        <v/>
       </c>
       <c r="H41" s="9" t="n">
-        <v>124.99</v>
+        <v/>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.91</v>
+        <v/>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.72</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2151,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>743.15</v>
+        <v>753.25</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>743.4</v>
+        <v/>
       </c>
       <c r="F42" s="12" t="n">
-        <v>758</v>
+        <v/>
       </c>
       <c r="G42" s="12" t="n">
-        <v>736.35</v>
+        <v/>
       </c>
       <c r="H42" s="12" t="n">
-        <v>753.25</v>
+        <v/>
       </c>
       <c r="I42" s="12" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>1.36</v>
+        <v/>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2185,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>418.2</v>
+        <v>417.95</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>418</v>
+        <v/>
       </c>
       <c r="F43" s="9" t="n">
-        <v>423.5</v>
+        <v/>
       </c>
       <c r="G43" s="9" t="n">
-        <v>416</v>
+        <v/>
       </c>
       <c r="H43" s="9" t="n">
-        <v>417.95</v>
+        <v/>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-0.25</v>
+        <v/>
       </c>
       <c r="J43" s="10" t="n">
-        <v>-0.06</v>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2219,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1681.7</v>
+        <v>1662.7</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1678.1</v>
+        <v/>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1681.9</v>
+        <v/>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1637.6</v>
+        <v/>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1662.7</v>
+        <v/>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-19</v>
+        <v/>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-1.13</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2253,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1399</v>
+        <v>1399.7</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1402.9</v>
+        <v/>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1421</v>
+        <v/>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1388.4</v>
+        <v/>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1399.7</v>
+        <v/>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>0.05</v>
+        <v/>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2287,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>422</v>
+        <v>426.1</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>424</v>
+        <v/>
       </c>
       <c r="F46" s="12" t="n">
-        <v>426.65</v>
+        <v/>
       </c>
       <c r="G46" s="12" t="n">
-        <v>421.35</v>
+        <v/>
       </c>
       <c r="H46" s="12" t="n">
-        <v>426.1</v>
+        <v/>
       </c>
       <c r="I46" s="12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>0.97</v>
+        <v/>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2321,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1785.9</v>
+        <v>1784</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1786.9</v>
+        <v/>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1793.6</v>
+        <v/>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1767.1</v>
+        <v/>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1784</v>
+        <v/>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-1.9</v>
+        <v/>
       </c>
       <c r="J47" s="10" t="n">
-        <v>-0.11</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2355,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1854.8</v>
+        <v>1855.8</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>1854.8</v>
+        <v/>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1862.2</v>
+        <v/>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1835.4</v>
+        <v/>
       </c>
       <c r="H48" s="12" t="n">
-        <v>1855.8</v>
+        <v/>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>0.05</v>
+        <v/>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2389,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>466.3</v>
+        <v>461.5</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>467.8</v>
+        <v/>
       </c>
       <c r="F49" s="9" t="n">
-        <v>468.15</v>
+        <v/>
       </c>
       <c r="G49" s="9" t="n">
-        <v>458.55</v>
+        <v/>
       </c>
       <c r="H49" s="9" t="n">
-        <v>461.5</v>
+        <v/>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-4.8</v>
+        <v/>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-1.03</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2423,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1942.5</v>
+        <v>1963.9</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1942.5</v>
+        <v/>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1975</v>
+        <v/>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1934</v>
+        <v/>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1963.9</v>
+        <v/>
       </c>
       <c r="I50" s="12" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>1.1</v>
+        <v/>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2457,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>219.8</v>
+        <v>218.6</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>219.8</v>
+        <v/>
       </c>
       <c r="F51" s="9" t="n">
-        <v>221.75</v>
+        <v/>
       </c>
       <c r="G51" s="9" t="n">
-        <v>217.5</v>
+        <v/>
       </c>
       <c r="H51" s="9" t="n">
-        <v>218.6</v>
+        <v/>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-1.2</v>
+        <v/>
       </c>
       <c r="J51" s="10" t="n">
-        <v>-0.55</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2491,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>220.52</v>
+        <v>225.57</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>223.39</v>
+        <v/>
       </c>
       <c r="F52" s="12" t="n">
-        <v>227.11</v>
+        <v/>
       </c>
       <c r="G52" s="12" t="n">
-        <v>221.79</v>
+        <v/>
       </c>
       <c r="H52" s="12" t="n">
-        <v>225.57</v>
+        <v/>
       </c>
       <c r="I52" s="12" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>2.29</v>
+        <v/>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2525,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4973</v>
+        <v>4945</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>4972</v>
+        <v/>
       </c>
       <c r="F53" s="9" t="n">
-        <v>4991.5</v>
+        <v/>
       </c>
       <c r="G53" s="9" t="n">
-        <v>4922.5</v>
+        <v/>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4945</v>
+        <v/>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-28</v>
+        <v/>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2559,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>385.7</v>
+        <v>385.6</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>384.8</v>
+        <v/>
       </c>
       <c r="F54" s="12" t="n">
-        <v>386</v>
+        <v/>
       </c>
       <c r="G54" s="12" t="n">
-        <v>381.55</v>
+        <v/>
       </c>
       <c r="H54" s="12" t="n">
-        <v>385.6</v>
+        <v/>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-0.1</v>
+        <v/>
       </c>
       <c r="J54" s="10" t="n">
-        <v>-0.03</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2593,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1721.2</v>
+        <v>1700.2</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1746.2</v>
+        <v/>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1746.2</v>
+        <v/>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1680.7</v>
+        <v/>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1700.2</v>
+        <v/>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-21</v>
+        <v/>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-1.22</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2627,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1600.9</v>
+        <v>1587.1</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1601.1</v>
+        <v/>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1608.3</v>
+        <v/>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1575</v>
+        <v/>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1587.1</v>
+        <v/>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-13.8</v>
+        <v/>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-0.86</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2661,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>72.68000000000001</v>
+        <v>76.84</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>73.44</v>
+        <v/>
       </c>
       <c r="F57" s="9" t="n">
-        <v>77.89</v>
+        <v/>
       </c>
       <c r="G57" s="9" t="n">
-        <v>69.31</v>
+        <v/>
       </c>
       <c r="H57" s="9" t="n">
-        <v>76.84</v>
+        <v/>
       </c>
       <c r="I57" s="9" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>5.72</v>
+        <v/>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2695,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9602</v>
+        <v>9619.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>9602</v>
+        <v/>
       </c>
       <c r="F58" s="12" t="n">
-        <v>9668.5</v>
+        <v/>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9530</v>
+        <v/>
       </c>
       <c r="H58" s="12" t="n">
-        <v>9619.5</v>
+        <v/>
       </c>
       <c r="I58" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>0.18</v>
+        <v/>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2729,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13299</v>
+        <v>13390</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>13280</v>
+        <v/>
       </c>
       <c r="F59" s="9" t="n">
-        <v>13514</v>
+        <v/>
       </c>
       <c r="G59" s="9" t="n">
-        <v>13211</v>
+        <v/>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13390</v>
+        <v/>
       </c>
       <c r="I59" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>0.68</v>
+        <v/>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2763,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>670.4</v>
+        <v>683</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>671.2</v>
+        <v/>
       </c>
       <c r="F60" s="12" t="n">
-        <v>683.6</v>
+        <v/>
       </c>
       <c r="G60" s="12" t="n">
-        <v>670.6</v>
+        <v/>
       </c>
       <c r="H60" s="12" t="n">
-        <v>683</v>
+        <v/>
       </c>
       <c r="I60" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>1.88</v>
+        <v/>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2797,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1200.4</v>
+        <v>1201</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1204.5</v>
+        <v/>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1207.8</v>
+        <v/>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1193.4</v>
+        <v/>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1201</v>
+        <v/>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>0.05</v>
+        <v/>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2831,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7338.5</v>
+        <v>7360</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7340.5</v>
+        <v/>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7381</v>
+        <v/>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7305</v>
+        <v/>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7360</v>
+        <v/>
       </c>
       <c r="I62" s="12" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>0.29</v>
+        <v/>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2865,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2822.9</v>
+        <v>2855.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2822.9</v>
+        <v/>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2866.3</v>
+        <v/>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2817.1</v>
+        <v/>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2855.7</v>
+        <v/>
       </c>
       <c r="I63" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>1.16</v>
+        <v/>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2899,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>426.55</v>
+        <v>423.65</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>426.85</v>
+        <v/>
       </c>
       <c r="F64" s="12" t="n">
-        <v>431.7</v>
+        <v/>
       </c>
       <c r="G64" s="12" t="n">
-        <v>419.85</v>
+        <v/>
       </c>
       <c r="H64" s="12" t="n">
-        <v>423.65</v>
+        <v/>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-2.9</v>
+        <v/>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-0.68</v>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2933,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>329.5</v>
+        <v>322</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>327.5</v>
+        <v/>
       </c>
       <c r="F65" s="9" t="n">
-        <v>332.5</v>
+        <v/>
       </c>
       <c r="G65" s="9" t="n">
-        <v>319.5</v>
+        <v/>
       </c>
       <c r="H65" s="9" t="n">
-        <v>322</v>
+        <v/>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-7.5</v>
+        <v/>
       </c>
       <c r="J65" s="10" t="n">
-        <v>-2.28</v>
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2967,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>173.85</v>
+        <v>172.7</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>173.9</v>
+        <v/>
       </c>
       <c r="F66" s="12" t="n">
-        <v>173.98</v>
+        <v/>
       </c>
       <c r="G66" s="12" t="n">
-        <v>171.59</v>
+        <v/>
       </c>
       <c r="H66" s="12" t="n">
-        <v>172.7</v>
+        <v/>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-1.15</v>
+        <v/>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-0.66</v>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3001,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2430.4</v>
+        <v>2380</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2425</v>
+        <v/>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2435.2</v>
+        <v/>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2365.7</v>
+        <v/>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2380</v>
+        <v/>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-50.4</v>
+        <v/>
       </c>
       <c r="J67" s="10" t="n">
-        <v>-2.07</v>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3069,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>625.1</v>
+        <v>630.3</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>625.1</v>
+        <v/>
       </c>
       <c r="F69" s="9" t="n">
-        <v>636</v>
+        <v/>
       </c>
       <c r="G69" s="9" t="n">
-        <v>619</v>
+        <v/>
       </c>
       <c r="H69" s="9" t="n">
-        <v>630.3</v>
+        <v/>
       </c>
       <c r="I69" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>0.83</v>
+        <v/>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3103,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>873.35</v>
+        <v/>
       </c>
       <c r="F70" s="12" t="n">
-        <v>880.55</v>
+        <v/>
       </c>
       <c r="G70" s="12" t="n">
-        <v>871.45</v>
+        <v/>
       </c>
       <c r="H70" s="12" t="n">
-        <v>880</v>
+        <v/>
       </c>
       <c r="I70" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>0.57</v>
+        <v/>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3137,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1671.2</v>
+        <v>1700.1</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1666</v>
+        <v/>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1700.1</v>
+        <v/>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1666</v>
+        <v/>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1700.1</v>
+        <v/>
       </c>
       <c r="I71" s="9" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>1.73</v>
+        <v/>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3171,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>853</v>
+        <v>868.65</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>856.9</v>
+        <v/>
       </c>
       <c r="F72" s="12" t="n">
-        <v>875</v>
+        <v/>
       </c>
       <c r="G72" s="12" t="n">
-        <v>849.05</v>
+        <v/>
       </c>
       <c r="H72" s="12" t="n">
-        <v>868.65</v>
+        <v/>
       </c>
       <c r="I72" s="12" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>1.83</v>
+        <v/>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3205,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>3175</v>
+        <v/>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3212.5</v>
+        <v/>
       </c>
       <c r="G73" s="9" t="n">
-        <v>3161</v>
+        <v/>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3191</v>
+        <v/>
       </c>
       <c r="I73" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>0.77</v>
+        <v/>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3281,25 +3273,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4774.2</v>
+        <v>4800</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4774.2</v>
+        <v/>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4819.5</v>
+        <v/>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4760.1</v>
+        <v/>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4800</v>
+        <v/>
       </c>
       <c r="I75" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>0.54</v>
+        <v/>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3307,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1090</v>
+        <v>1096.5</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1085.2</v>
+        <v/>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1097.3</v>
+        <v/>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1085.2</v>
+        <v/>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1096.5</v>
+        <v/>
       </c>
       <c r="I76" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>0.6</v>
+        <v/>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3341,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1243.6</v>
+        <v>1258</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1241</v>
+        <v/>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1266.5</v>
+        <v/>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1234.6</v>
+        <v/>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1258</v>
+        <v/>
       </c>
       <c r="I77" s="9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>1.16</v>
+        <v/>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3375,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2380.3</v>
+        <v>2378</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2390</v>
+        <v/>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2395.5</v>
+        <v/>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2366.5</v>
+        <v/>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2378</v>
+        <v/>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-2.3</v>
+        <v/>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-0.1</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3409,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>728.9</v>
+        <v>735.6</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>723</v>
+        <v/>
       </c>
       <c r="F79" s="9" t="n">
-        <v>739.65</v>
+        <v/>
       </c>
       <c r="G79" s="9" t="n">
-        <v>723</v>
+        <v/>
       </c>
       <c r="H79" s="9" t="n">
-        <v>735.6</v>
+        <v/>
       </c>
       <c r="I79" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>0.92</v>
+        <v/>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3443,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>526.9</v>
+        <v>531</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>526.9</v>
+        <v/>
       </c>
       <c r="F80" s="12" t="n">
-        <v>535</v>
+        <v/>
       </c>
       <c r="G80" s="12" t="n">
-        <v>516.45</v>
+        <v/>
       </c>
       <c r="H80" s="12" t="n">
-        <v>531</v>
+        <v/>
       </c>
       <c r="I80" s="12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>0.78</v>
+        <v/>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3477,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5296</v>
+        <v>5360</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5340</v>
+        <v/>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5397</v>
+        <v/>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5304</v>
+        <v/>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5360</v>
+        <v/>
       </c>
       <c r="I81" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>1.21</v>
+        <v/>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3511,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>979.2</v>
+        <v/>
       </c>
       <c r="F82" s="12" t="n">
-        <v>983.4</v>
+        <v/>
       </c>
       <c r="G82" s="12" t="n">
-        <v>971.2</v>
+        <v/>
       </c>
       <c r="H82" s="12" t="n">
-        <v>977</v>
+        <v/>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-5</v>
+        <v/>
       </c>
       <c r="J82" s="10" t="n">
-        <v>-0.51</v>
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3545,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>495.7</v>
+        <v>494.65</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>496</v>
+        <v/>
       </c>
       <c r="F83" s="9" t="n">
-        <v>498.65</v>
+        <v/>
       </c>
       <c r="G83" s="9" t="n">
-        <v>489.4</v>
+        <v/>
       </c>
       <c r="H83" s="9" t="n">
-        <v>494.65</v>
+        <v/>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-1.05</v>
+        <v/>
       </c>
       <c r="J83" s="10" t="n">
-        <v>-0.21</v>
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3579,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>350.4</v>
+        <v>351</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>352.55</v>
+        <v/>
       </c>
       <c r="F84" s="12" t="n">
-        <v>353.8</v>
+        <v/>
       </c>
       <c r="G84" s="12" t="n">
-        <v>348.65</v>
+        <v/>
       </c>
       <c r="H84" s="12" t="n">
-        <v>351</v>
+        <v/>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>0.17</v>
+        <v/>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3613,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1933.5</v>
+        <v>1942.9</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>1933.5</v>
+        <v/>
       </c>
       <c r="F85" s="9" t="n">
-        <v>1942.9</v>
+        <v/>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1915</v>
+        <v/>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1942.9</v>
+        <v/>
       </c>
       <c r="I85" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>0.49</v>
+        <v/>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3647,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>33625</v>
+        <v>33865</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>33625</v>
+        <v/>
       </c>
       <c r="F86" s="12" t="n">
-        <v>33990</v>
+        <v/>
       </c>
       <c r="G86" s="12" t="n">
-        <v>33315</v>
+        <v/>
       </c>
       <c r="H86" s="12" t="n">
-        <v>33865</v>
+        <v/>
       </c>
       <c r="I86" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>0.71</v>
+        <v/>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3681,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>83.76000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>83.48</v>
+        <v/>
       </c>
       <c r="F87" s="9" t="n">
-        <v>84.25</v>
+        <v/>
       </c>
       <c r="G87" s="9" t="n">
-        <v>83.27</v>
+        <v/>
       </c>
       <c r="H87" s="9" t="n">
-        <v>83.8</v>
+        <v/>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>0.05</v>
+        <v/>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3715,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>111.2</v>
+        <v>112.7</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>111.38</v>
+        <v/>
       </c>
       <c r="F88" s="12" t="n">
-        <v>112.9</v>
+        <v/>
       </c>
       <c r="G88" s="12" t="n">
-        <v>110.89</v>
+        <v/>
       </c>
       <c r="H88" s="12" t="n">
-        <v>112.7</v>
+        <v/>
       </c>
       <c r="I88" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>1.35</v>
+        <v/>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3749,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>145.74</v>
+        <v>144.95</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>146</v>
+        <v/>
       </c>
       <c r="F89" s="9" t="n">
-        <v>146.48</v>
+        <v/>
       </c>
       <c r="G89" s="9" t="n">
-        <v>144.22</v>
+        <v/>
       </c>
       <c r="H89" s="9" t="n">
-        <v>144.95</v>
+        <v/>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-0.79</v>
+        <v/>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-0.54</v>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3783,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>728.8</v>
+        <v>726.8</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>726.1</v>
+        <v/>
       </c>
       <c r="F90" s="12" t="n">
-        <v>731.25</v>
+        <v/>
       </c>
       <c r="G90" s="12" t="n">
-        <v>721.95</v>
+        <v/>
       </c>
       <c r="H90" s="12" t="n">
-        <v>726.8</v>
+        <v/>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-2</v>
+        <v/>
       </c>
       <c r="J90" s="10" t="n">
-        <v>-0.27</v>
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3817,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1635.9</v>
+        <v>1642.1</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>1637.8</v>
+        <v/>
       </c>
       <c r="F91" s="9" t="n">
-        <v>1645</v>
+        <v/>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1625.9</v>
+        <v/>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1642.1</v>
+        <v/>
       </c>
       <c r="I91" s="9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>0.38</v>
+        <v/>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3851,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4890</v>
+        <v>4940</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4890</v>
+        <v/>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4956</v>
+        <v/>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4890</v>
+        <v/>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4940</v>
+        <v/>
       </c>
       <c r="I92" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>1.02</v>
+        <v/>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3885,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>919.5</v>
+        <v>912.2</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>919.5</v>
+        <v/>
       </c>
       <c r="F93" s="9" t="n">
-        <v>923.9</v>
+        <v/>
       </c>
       <c r="G93" s="9" t="n">
-        <v>906.9</v>
+        <v/>
       </c>
       <c r="H93" s="9" t="n">
-        <v>912.2</v>
+        <v/>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-7.3</v>
+        <v/>
       </c>
       <c r="J93" s="10" t="n">
-        <v>-0.79</v>
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3919,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>379.85</v>
+        <v>374.65</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>378</v>
+        <v/>
       </c>
       <c r="F94" s="12" t="n">
-        <v>379.25</v>
+        <v/>
       </c>
       <c r="G94" s="12" t="n">
-        <v>373.2</v>
+        <v/>
       </c>
       <c r="H94" s="12" t="n">
-        <v>374.65</v>
+        <v/>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-5.2</v>
+        <v/>
       </c>
       <c r="J94" s="10" t="n">
-        <v>-1.37</v>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3953,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1014.5</v>
+        <v>1000.2</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>999.5</v>
+        <v/>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1004.2</v>
+        <v/>
       </c>
       <c r="G95" s="9" t="n">
-        <v>991.6</v>
+        <v/>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1000.2</v>
+        <v/>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-14.3</v>
+        <v/>
       </c>
       <c r="J95" s="10" t="n">
-        <v>-1.41</v>
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3987,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>136.27</v>
+        <v>135.7</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>136.5</v>
+        <v/>
       </c>
       <c r="F96" s="12" t="n">
-        <v>137.06</v>
+        <v/>
       </c>
       <c r="G96" s="12" t="n">
-        <v>135.33</v>
+        <v/>
       </c>
       <c r="H96" s="12" t="n">
-        <v>135.7</v>
+        <v/>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.57</v>
+        <v/>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-0.42</v>
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4021,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1997.1</v>
+        <v>1970.8</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>2020</v>
+        <v/>
       </c>
       <c r="F97" s="9" t="n">
-        <v>2020</v>
+        <v/>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1950</v>
+        <v/>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1970.8</v>
+        <v/>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-26.3</v>
+        <v/>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-1.32</v>
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4055,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>461.2</v>
+        <v>458.7</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>461.2</v>
+        <v/>
       </c>
       <c r="F98" s="12" t="n">
-        <v>461.9</v>
+        <v/>
       </c>
       <c r="G98" s="12" t="n">
-        <v>457.7</v>
+        <v/>
       </c>
       <c r="H98" s="12" t="n">
-        <v>458.7</v>
+        <v/>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-2.5</v>
+        <v/>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-0.54</v>
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4089,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>268.1</v>
+        <v/>
       </c>
       <c r="F99" s="9" t="n">
-        <v>269</v>
+        <v/>
       </c>
       <c r="G99" s="9" t="n">
-        <v>266.3</v>
+        <v/>
       </c>
       <c r="H99" s="9" t="n">
-        <v>269</v>
+        <v/>
       </c>
       <c r="I99" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>0.37</v>
+        <v/>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4123,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1157.8</v>
+        <v>1164.8</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1154.4</v>
+        <v/>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1168.9</v>
+        <v/>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1137</v>
+        <v/>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1164.8</v>
+        <v/>
       </c>
       <c r="I100" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>0.6</v>
+        <v/>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4157,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5184.5</v>
+        <v>5000</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5165</v>
+        <v/>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5165</v>
+        <v/>
       </c>
       <c r="G101" s="9" t="n">
-        <v>4985</v>
+        <v/>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5000</v>
+        <v/>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-184.5</v>
+        <v/>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-3.56</v>
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4191,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>738.95</v>
+        <v>748.25</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>738</v>
+        <v/>
       </c>
       <c r="F102" s="12" t="n">
-        <v>752.85</v>
+        <v/>
       </c>
       <c r="G102" s="12" t="n">
-        <v>736</v>
+        <v/>
       </c>
       <c r="H102" s="12" t="n">
-        <v>748.25</v>
+        <v/>
       </c>
       <c r="I102" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>1.26</v>
+        <v/>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4225,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>510</v>
+        <v>506.55</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>510</v>
+        <v/>
       </c>
       <c r="F103" s="9" t="n">
-        <v>513.1</v>
+        <v/>
       </c>
       <c r="G103" s="9" t="n">
-        <v>503.15</v>
+        <v/>
       </c>
       <c r="H103" s="9" t="n">
-        <v>506.55</v>
+        <v/>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-3.45</v>
+        <v/>
       </c>
       <c r="J103" s="10" t="n">
-        <v>-0.68</v>
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4259,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1273.2</v>
+        <v>1277</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1279</v>
+        <v/>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1288.6</v>
+        <v/>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1266.3</v>
+        <v/>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1277</v>
+        <v/>
       </c>
       <c r="I104" s="12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>0.3</v>
+        <v/>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4293,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>478.9</v>
+        <v>484.55</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>478.5</v>
+        <v/>
       </c>
       <c r="F105" s="9" t="n">
-        <v>490</v>
+        <v/>
       </c>
       <c r="G105" s="9" t="n">
-        <v>474.1</v>
+        <v/>
       </c>
       <c r="H105" s="9" t="n">
-        <v>484.55</v>
+        <v/>
       </c>
       <c r="I105" s="9" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>1.18</v>
+        <v/>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4327,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1221.8</v>
+        <v>1218.1</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1214.7</v>
+        <v/>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1227</v>
+        <v/>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1213</v>
+        <v/>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1218.1</v>
+        <v/>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-3.7</v>
+        <v/>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-0.3</v>
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4361,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>406.9</v>
+        <v/>
       </c>
       <c r="F107" s="9" t="n">
-        <v>407.95</v>
+        <v/>
       </c>
       <c r="G107" s="9" t="n">
-        <v>399.3</v>
+        <v/>
       </c>
       <c r="H107" s="9" t="n">
-        <v>404</v>
+        <v/>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-1</v>
+        <v/>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-0.25</v>
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4395,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>516.85</v>
+        <v>519.4</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>517.95</v>
+        <v/>
       </c>
       <c r="F108" s="12" t="n">
-        <v>519.5</v>
+        <v/>
       </c>
       <c r="G108" s="12" t="n">
-        <v>507.8</v>
+        <v/>
       </c>
       <c r="H108" s="12" t="n">
-        <v>519.4</v>
+        <v/>
       </c>
       <c r="I108" s="12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>0.49</v>
+        <v/>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4429,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1961.3</v>
+        <v>1952.3</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1980</v>
+        <v/>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1986.8</v>
+        <v/>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1902.7</v>
+        <v/>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1952.3</v>
+        <v/>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-9</v>
+        <v/>
       </c>
       <c r="J109" s="10" t="n">
-        <v>-0.46</v>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4463,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>2026.2</v>
+        <v>2007</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>2026</v>
+        <v/>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1979.2</v>
+        <v/>
       </c>
       <c r="H110" s="12" t="n">
-        <v>2007</v>
+        <v/>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-19.2</v>
+        <v/>
       </c>
       <c r="J110" s="10" t="n">
-        <v>-0.95</v>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4497,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>564.75</v>
+        <v/>
       </c>
       <c r="F111" s="9" t="n">
-        <v>569.55</v>
+        <v/>
       </c>
       <c r="G111" s="9" t="n">
-        <v>558.6</v>
+        <v/>
       </c>
       <c r="H111" s="9" t="n">
-        <v>566</v>
+        <v/>
       </c>
       <c r="I111" s="9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>0.31</v>
+        <v/>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4531,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3865</v>
+        <v/>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3887.5</v>
+        <v/>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3842.4</v>
+        <v/>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3876.2</v>
+        <v/>
       </c>
       <c r="I112" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>0.46</v>
+        <v/>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4565,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>284.95</v>
+        <v/>
       </c>
       <c r="F113" s="9" t="n">
-        <v>285.75</v>
+        <v/>
       </c>
       <c r="G113" s="9" t="n">
-        <v>280.05</v>
+        <v/>
       </c>
       <c r="H113" s="9" t="n">
-        <v>284</v>
+        <v/>
       </c>
       <c r="I113" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>0.71</v>
+        <v/>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4633,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3209.1</v>
+        <v>3206.1</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3218.6</v>
+        <v/>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3229</v>
+        <v/>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3178</v>
+        <v/>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3206.1</v>
+        <v/>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-3</v>
+        <v/>
       </c>
       <c r="J115" s="10" t="n">
-        <v>-0.09</v>
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4667,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2100.7</v>
+        <v>2092</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2091.3</v>
+        <v/>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2095.7</v>
+        <v/>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2077.5</v>
+        <v/>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2092</v>
+        <v/>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-8.699999999999999</v>
+        <v/>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-0.41</v>
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4701,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2982.7</v>
+        <v>3035</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>2965</v>
+        <v/>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3045</v>
+        <v/>
       </c>
       <c r="G117" s="9" t="n">
-        <v>2965</v>
+        <v/>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3035</v>
+        <v/>
       </c>
       <c r="I117" s="9" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>1.75</v>
+        <v/>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4735,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>324.95</v>
+        <v>334</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>324.95</v>
+        <v/>
       </c>
       <c r="F118" s="12" t="n">
-        <v>334.25</v>
+        <v/>
       </c>
       <c r="G118" s="12" t="n">
-        <v>323.25</v>
+        <v/>
       </c>
       <c r="H118" s="12" t="n">
-        <v>334</v>
+        <v/>
       </c>
       <c r="I118" s="12" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>2.79</v>
+        <v/>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4769,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>824.55</v>
+        <v>819</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>822</v>
+        <v/>
       </c>
       <c r="F119" s="9" t="n">
-        <v>824</v>
+        <v/>
       </c>
       <c r="G119" s="9" t="n">
-        <v>807.05</v>
+        <v/>
       </c>
       <c r="H119" s="9" t="n">
-        <v>819</v>
+        <v/>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-5.55</v>
+        <v/>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-0.67</v>
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4803,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>11990</v>
+        <v>12065</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>11997</v>
+        <v/>
       </c>
       <c r="F120" s="12" t="n">
-        <v>12098</v>
+        <v/>
       </c>
       <c r="G120" s="12" t="n">
-        <v>11975</v>
+        <v/>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12065</v>
+        <v/>
       </c>
       <c r="I120" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>0.63</v>
+        <v/>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4871,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3427.7</v>
+        <v>3324.9</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3463.6</v>
+        <v/>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3481.4</v>
+        <v/>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3310</v>
+        <v/>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3324.9</v>
+        <v/>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-102.8</v>
+        <v/>
       </c>
       <c r="J122" s="10" t="n">
-        <v>-3</v>
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4905,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>582.95</v>
+        <v>582.6</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>584.95</v>
+        <v/>
       </c>
       <c r="F123" s="9" t="n">
-        <v>589.95</v>
+        <v/>
       </c>
       <c r="G123" s="9" t="n">
-        <v>572.1</v>
+        <v/>
       </c>
       <c r="H123" s="9" t="n">
-        <v>582.6</v>
+        <v/>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-0.35</v>
+        <v/>
       </c>
       <c r="J123" s="10" t="n">
-        <v>-0.06</v>
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4939,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1410</v>
+        <v>1458</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1390</v>
+        <v/>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1463.8</v>
+        <v/>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1390</v>
+        <v/>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1458</v>
+        <v/>
       </c>
       <c r="I124" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>3.4</v>
+        <v/>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4973,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1079.6</v>
+        <v>1071.3</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1076.5</v>
+        <v/>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1088</v>
+        <v/>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1062.9</v>
+        <v/>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1071.3</v>
+        <v/>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-8.300000000000001</v>
+        <v/>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-0.77</v>
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5007,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>162.5</v>
+        <v>165.71</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>162.6</v>
+        <v/>
       </c>
       <c r="F126" s="12" t="n">
-        <v>166.22</v>
+        <v/>
       </c>
       <c r="G126" s="12" t="n">
-        <v>160.72</v>
+        <v/>
       </c>
       <c r="H126" s="12" t="n">
-        <v>165.71</v>
+        <v/>
       </c>
       <c r="I126" s="12" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>1.98</v>
+        <v/>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5041,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2248.2</v>
+        <v>2234</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2235</v>
+        <v/>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2240</v>
+        <v/>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2203.6</v>
+        <v/>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2234</v>
+        <v/>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-14.2</v>
+        <v/>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-0.63</v>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5075,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>123985</v>
+        <v>124035</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>124480</v>
+        <v/>
       </c>
       <c r="F128" s="12" t="n">
-        <v>124480</v>
+        <v/>
       </c>
       <c r="G128" s="12" t="n">
-        <v>123440</v>
+        <v/>
       </c>
       <c r="H128" s="12" t="n">
-        <v>124035</v>
+        <v/>
       </c>
       <c r="I128" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>0.04</v>
+        <v/>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5109,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2825.3</v>
+        <v>2835</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>2830</v>
+        <v/>
       </c>
       <c r="F129" s="9" t="n">
-        <v>2839.6</v>
+        <v/>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2808</v>
+        <v/>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2835</v>
+        <v/>
       </c>
       <c r="I129" s="9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>0.34</v>
+        <v/>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5143,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>358.4</v>
+        <v>358.7</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>360.6</v>
+        <v/>
       </c>
       <c r="F130" s="12" t="n">
-        <v>362.9</v>
+        <v/>
       </c>
       <c r="G130" s="12" t="n">
-        <v>357.05</v>
+        <v/>
       </c>
       <c r="H130" s="12" t="n">
-        <v>358.7</v>
+        <v/>
       </c>
       <c r="I130" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>0.08</v>
+        <v/>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5177,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1224</v>
+        <v>1254.8</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1216.4</v>
+        <v/>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1259</v>
+        <v/>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1215.4</v>
+        <v/>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1254.8</v>
+        <v/>
       </c>
       <c r="I131" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>2.52</v>
+        <v/>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5211,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>8461</v>
+        <v>8584.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>8488.5</v>
+        <v/>
       </c>
       <c r="F132" s="12" t="n">
-        <v>8600</v>
+        <v/>
       </c>
       <c r="G132" s="12" t="n">
-        <v>8467</v>
+        <v/>
       </c>
       <c r="H132" s="12" t="n">
-        <v>8584.5</v>
+        <v/>
       </c>
       <c r="I132" s="12" t="n">
-        <v>123.5</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>1.46</v>
+        <v/>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5245,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1351</v>
+        <v>1362.6</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1357</v>
+        <v/>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1362.6</v>
+        <v/>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1348.3</v>
+        <v/>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1362.6</v>
+        <v/>
       </c>
       <c r="I133" s="9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>0.86</v>
+        <v/>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5279,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>80.81999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>80.76000000000001</v>
+        <v/>
       </c>
       <c r="F134" s="12" t="n">
-        <v>81.12</v>
+        <v/>
       </c>
       <c r="G134" s="12" t="n">
-        <v>79.56999999999999</v>
+        <v/>
       </c>
       <c r="H134" s="12" t="n">
-        <v>79.90000000000001</v>
+        <v/>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-0.92</v>
+        <v/>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-1.14</v>
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -5324,22 +5316,22 @@
         <v>326.6</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>327.3</v>
+        <v/>
       </c>
       <c r="F135" s="9" t="n">
-        <v>327.3</v>
+        <v/>
       </c>
       <c r="G135" s="9" t="n">
-        <v>323.5</v>
+        <v/>
       </c>
       <c r="H135" s="9" t="n">
-        <v>326.6</v>
+        <v/>
       </c>
       <c r="I135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5347,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1837.5</v>
+        <v>1858.5</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1837.5</v>
+        <v/>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1882.9</v>
+        <v/>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1837.5</v>
+        <v/>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1858.5</v>
+        <v/>
       </c>
       <c r="I136" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>1.14</v>
+        <v/>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5381,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>10925</v>
+        <v>10770</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>10782</v>
+        <v/>
       </c>
       <c r="F137" s="9" t="n">
-        <v>10805</v>
+        <v/>
       </c>
       <c r="G137" s="9" t="n">
-        <v>10332</v>
+        <v/>
       </c>
       <c r="H137" s="9" t="n">
-        <v>10770</v>
+        <v/>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-155</v>
+        <v/>
       </c>
       <c r="J137" s="10" t="n">
-        <v>-1.42</v>
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5415,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>239</v>
+        <v>235.86</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>238</v>
+        <v/>
       </c>
       <c r="F138" s="12" t="n">
-        <v>238</v>
+        <v/>
       </c>
       <c r="G138" s="12" t="n">
-        <v>234.71</v>
+        <v/>
       </c>
       <c r="H138" s="12" t="n">
-        <v>235.86</v>
+        <v/>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-3.14</v>
+        <v/>
       </c>
       <c r="J138" s="10" t="n">
-        <v>-1.31</v>
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5449,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37500</v>
+        <v>37695</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37350</v>
+        <v/>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37845</v>
+        <v/>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37350</v>
+        <v/>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37695</v>
+        <v/>
       </c>
       <c r="I139" s="9" t="n">
-        <v>195</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>0.52</v>
+        <v/>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5517,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5277</v>
+        <v>5372</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5277</v>
+        <v/>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5385</v>
+        <v/>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5230</v>
+        <v/>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5372</v>
+        <v/>
       </c>
       <c r="I141" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>1.8</v>
+        <v/>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5551,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>286.6</v>
+        <v>286.5</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>285.35</v>
+        <v/>
       </c>
       <c r="F142" s="12" t="n">
-        <v>286.5</v>
+        <v/>
       </c>
       <c r="G142" s="12" t="n">
-        <v>283.4</v>
+        <v/>
       </c>
       <c r="H142" s="12" t="n">
-        <v>286.5</v>
+        <v/>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-0.1</v>
+        <v/>
       </c>
       <c r="J142" s="10" t="n">
-        <v>-0.03</v>
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5585,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>339.35</v>
+        <v>338</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>340</v>
+        <v/>
       </c>
       <c r="F143" s="9" t="n">
-        <v>340.05</v>
+        <v/>
       </c>
       <c r="G143" s="9" t="n">
-        <v>336.3</v>
+        <v/>
       </c>
       <c r="H143" s="9" t="n">
-        <v>338</v>
+        <v/>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-1.35</v>
+        <v/>
       </c>
       <c r="J143" s="10" t="n">
-        <v>-0.4</v>
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5619,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1522</v>
+        <v>1517.2</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1525</v>
+        <v/>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1530</v>
+        <v/>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1495.7</v>
+        <v/>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1517.2</v>
+        <v/>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-4.8</v>
+        <v/>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-0.32</v>
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5653,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2393.5</v>
+        <v>2400</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2388.6</v>
+        <v/>
       </c>
       <c r="F145" s="9" t="n">
-        <v>2405.6</v>
+        <v/>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2362.6</v>
+        <v/>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2400</v>
+        <v/>
       </c>
       <c r="I145" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>0.27</v>
+        <v/>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5687,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>117.12</v>
+        <v/>
       </c>
       <c r="F146" s="12" t="n">
-        <v>118.01</v>
+        <v/>
       </c>
       <c r="G146" s="12" t="n">
-        <v>116.23</v>
+        <v/>
       </c>
       <c r="H146" s="12" t="n">
-        <v>116.6</v>
+        <v/>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.52</v>
+        <v/>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-0.44</v>
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5721,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8366.5</v>
+        <v>8408.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8394</v>
+        <v/>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8463</v>
+        <v/>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8350</v>
+        <v/>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8408.5</v>
+        <v/>
       </c>
       <c r="I147" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>0.5</v>
+        <v/>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5755,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>266.4</v>
+        <v>269.5</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>268.7</v>
+        <v/>
       </c>
       <c r="F148" s="12" t="n">
-        <v>269.75</v>
+        <v/>
       </c>
       <c r="G148" s="12" t="n">
-        <v>266.9</v>
+        <v/>
       </c>
       <c r="H148" s="12" t="n">
-        <v>269.5</v>
+        <v/>
       </c>
       <c r="I148" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>1.16</v>
+        <v/>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5789,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1256.7</v>
+        <v>1254.6</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1264.9</v>
+        <v/>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1292</v>
+        <v/>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1245</v>
+        <v/>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1254.6</v>
+        <v/>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-2.1</v>
+        <v/>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-0.17</v>
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5823,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>412.75</v>
+        <v>415.05</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>412.6</v>
+        <v/>
       </c>
       <c r="F150" s="12" t="n">
-        <v>416</v>
+        <v/>
       </c>
       <c r="G150" s="12" t="n">
-        <v>409.1</v>
+        <v/>
       </c>
       <c r="H150" s="12" t="n">
-        <v>415.05</v>
+        <v/>
       </c>
       <c r="I150" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v/>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5857,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>308.25</v>
+        <v>312.95</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>309.2</v>
+        <v/>
       </c>
       <c r="F151" s="9" t="n">
-        <v>312.95</v>
+        <v/>
       </c>
       <c r="G151" s="9" t="n">
-        <v>307.25</v>
+        <v/>
       </c>
       <c r="H151" s="9" t="n">
-        <v>312.95</v>
+        <v/>
       </c>
       <c r="I151" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>1.52</v>
+        <v/>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5891,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1210.5</v>
+        <v/>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1227.4</v>
+        <v/>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1210.5</v>
+        <v/>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1226</v>
+        <v/>
       </c>
       <c r="I152" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v/>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5925,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>184.64</v>
+        <v/>
       </c>
       <c r="F153" s="9" t="n">
-        <v>186.05</v>
+        <v/>
       </c>
       <c r="G153" s="9" t="n">
-        <v>182.77</v>
+        <v/>
       </c>
       <c r="H153" s="9" t="n">
-        <v>185</v>
+        <v/>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>0.54</v>
+        <v/>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5959,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>618.4</v>
+        <v>611.2</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>617</v>
+        <v/>
       </c>
       <c r="F154" s="12" t="n">
-        <v>621.65</v>
+        <v/>
       </c>
       <c r="G154" s="12" t="n">
-        <v>606.7</v>
+        <v/>
       </c>
       <c r="H154" s="12" t="n">
-        <v>611.2</v>
+        <v/>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-7.2</v>
+        <v/>
       </c>
       <c r="J154" s="10" t="n">
-        <v>-1.16</v>
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +5993,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1755</v>
+        <v/>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1758.4</v>
+        <v/>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1732.3</v>
+        <v/>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1742</v>
+        <v/>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-13</v>
+        <v/>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-0.74</v>
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6027,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>978.5</v>
+        <v>983</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>980.8</v>
+        <v/>
       </c>
       <c r="F156" s="12" t="n">
-        <v>985.7</v>
+        <v/>
       </c>
       <c r="G156" s="12" t="n">
-        <v>977</v>
+        <v/>
       </c>
       <c r="H156" s="12" t="n">
-        <v>983</v>
+        <v/>
       </c>
       <c r="I156" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>0.46</v>
+        <v/>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6061,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>22350</v>
+        <v>22520</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>22350</v>
+        <v/>
       </c>
       <c r="F157" s="9" t="n">
-        <v>22520</v>
+        <v/>
       </c>
       <c r="G157" s="9" t="n">
-        <v>22225</v>
+        <v/>
       </c>
       <c r="H157" s="9" t="n">
-        <v>22520</v>
+        <v/>
       </c>
       <c r="I157" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>0.76</v>
+        <v/>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6095,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>990</v>
+        <v>994.1</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>990</v>
+        <v/>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1002</v>
+        <v/>
       </c>
       <c r="G158" s="12" t="n">
-        <v>986.4</v>
+        <v/>
       </c>
       <c r="H158" s="12" t="n">
-        <v>994.1</v>
+        <v/>
       </c>
       <c r="I158" s="12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>0.41</v>
+        <v/>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6129,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3841.8</v>
+        <v>3877</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3841.1</v>
+        <v/>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3881.6</v>
+        <v/>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3828.1</v>
+        <v/>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3877</v>
+        <v/>
       </c>
       <c r="I159" s="9" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>0.92</v>
+        <v/>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6163,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2533.8</v>
+        <v>2540</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2535</v>
+        <v/>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2540</v>
+        <v/>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2495.1</v>
+        <v/>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2540</v>
+        <v/>
       </c>
       <c r="I160" s="12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>0.24</v>
+        <v/>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6197,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1849.9</v>
+        <v>1852.2</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1858.7</v>
+        <v/>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1858.7</v>
+        <v/>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1841.6</v>
+        <v/>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1852.2</v>
+        <v/>
       </c>
       <c r="I161" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>0.12</v>
+        <v/>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6231,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>512.7</v>
+        <v>513.2</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>511.35</v>
+        <v/>
       </c>
       <c r="F162" s="12" t="n">
-        <v>521.75</v>
+        <v/>
       </c>
       <c r="G162" s="12" t="n">
-        <v>504.55</v>
+        <v/>
       </c>
       <c r="H162" s="12" t="n">
-        <v>513.2</v>
+        <v/>
       </c>
       <c r="I162" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>0.1</v>
+        <v/>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6265,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>380.35</v>
+        <v>378.7</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>380.35</v>
+        <v/>
       </c>
       <c r="F163" s="9" t="n">
-        <v>381.85</v>
+        <v/>
       </c>
       <c r="G163" s="9" t="n">
-        <v>376.95</v>
+        <v/>
       </c>
       <c r="H163" s="9" t="n">
-        <v>378.7</v>
+        <v/>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-1.65</v>
+        <v/>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-0.43</v>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6299,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>652.2</v>
+        <v>643.75</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>654.65</v>
+        <v/>
       </c>
       <c r="F164" s="12" t="n">
-        <v>654.65</v>
+        <v/>
       </c>
       <c r="G164" s="12" t="n">
-        <v>633.6</v>
+        <v/>
       </c>
       <c r="H164" s="12" t="n">
-        <v>643.75</v>
+        <v/>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-8.449999999999999</v>
+        <v/>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-1.3</v>
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6333,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1670</v>
+        <v>1666.5</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1671.9</v>
+        <v/>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1682</v>
+        <v/>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1650.1</v>
+        <v/>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1666.5</v>
+        <v/>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-3.5</v>
+        <v/>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-0.21</v>
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6367,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>986.3</v>
+        <v>983.2</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>988</v>
+        <v/>
       </c>
       <c r="F166" s="12" t="n">
-        <v>989.9</v>
+        <v/>
       </c>
       <c r="G166" s="12" t="n">
-        <v>979.2</v>
+        <v/>
       </c>
       <c r="H166" s="12" t="n">
-        <v>983.2</v>
+        <v/>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-3.1</v>
+        <v/>
       </c>
       <c r="J166" s="10" t="n">
-        <v>-0.31</v>
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6435,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>363.45</v>
+        <v>367.5</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>363</v>
+        <v/>
       </c>
       <c r="F168" s="12" t="n">
-        <v>367.8</v>
+        <v/>
       </c>
       <c r="G168" s="12" t="n">
-        <v>362.65</v>
+        <v/>
       </c>
       <c r="H168" s="12" t="n">
-        <v>367.5</v>
+        <v/>
       </c>
       <c r="I168" s="12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>1.11</v>
+        <v/>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6469,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>188.02</v>
+        <v>187.97</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>188.57</v>
+        <v/>
       </c>
       <c r="F169" s="9" t="n">
-        <v>190.34</v>
+        <v/>
       </c>
       <c r="G169" s="9" t="n">
-        <v>187.01</v>
+        <v/>
       </c>
       <c r="H169" s="9" t="n">
-        <v>187.97</v>
+        <v/>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-0.05</v>
+        <v/>
       </c>
       <c r="J169" s="10" t="n">
-        <v>-0.03</v>
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6503,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2054</v>
+        <v/>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2090.2</v>
+        <v/>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2038.1</v>
+        <v/>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2082</v>
+        <v/>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-5</v>
+        <v/>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.24</v>
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6537,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1540</v>
+        <v/>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1554.7</v>
+        <v/>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1526.6</v>
+        <v/>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1548</v>
+        <v/>
       </c>
       <c r="I171" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>0.32</v>
+        <v/>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6571,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2540.5</v>
+        <v>2511.1</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2530</v>
+        <v/>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2547.8</v>
+        <v/>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2506.1</v>
+        <v/>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2511.1</v>
+        <v/>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-29.4</v>
+        <v/>
       </c>
       <c r="J172" s="10" t="n">
-        <v>-1.16</v>
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6605,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4855</v>
+        <v/>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4884</v>
+        <v/>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4821.5</v>
+        <v/>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4884</v>
+        <v/>
       </c>
       <c r="I173" s="9" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>1.07</v>
+        <v/>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6639,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4928.5</v>
+        <v>4988.5</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4911.5</v>
+        <v/>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4990.5</v>
+        <v/>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4906.5</v>
+        <v/>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4988.5</v>
+        <v/>
       </c>
       <c r="I174" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>1.22</v>
+        <v/>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6673,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1244.2</v>
+        <v>1254.6</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1244</v>
+        <v/>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1264.9</v>
+        <v/>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1233.8</v>
+        <v/>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1254.6</v>
+        <v/>
       </c>
       <c r="I175" s="9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>0.84</v>
+        <v/>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6707,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>2700</v>
+        <v>2669.3</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>2720</v>
+        <v/>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2720</v>
+        <v/>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2646</v>
+        <v/>
       </c>
       <c r="H176" s="12" t="n">
-        <v>2669.3</v>
+        <v/>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-30.7</v>
+        <v/>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-1.14</v>
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6741,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>4091</v>
+        <v>4157.3</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>4075</v>
+        <v/>
       </c>
       <c r="F177" s="9" t="n">
-        <v>4177.9</v>
+        <v/>
       </c>
       <c r="G177" s="9" t="n">
-        <v>4075</v>
+        <v/>
       </c>
       <c r="H177" s="9" t="n">
-        <v>4157.3</v>
+        <v/>
       </c>
       <c r="I177" s="9" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>1.62</v>
+        <v/>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6775,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1270.2</v>
+        <v>1251.3</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1270.2</v>
+        <v/>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1271.2</v>
+        <v/>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1243.2</v>
+        <v/>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1251.3</v>
+        <v/>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-18.9</v>
+        <v/>
       </c>
       <c r="J178" s="10" t="n">
-        <v>-1.49</v>
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6809,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11056</v>
+        <v>11155</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11100</v>
+        <v/>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11184</v>
+        <v/>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11027</v>
+        <v/>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11155</v>
+        <v/>
       </c>
       <c r="I179" s="9" t="n">
-        <v>99</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>0.9</v>
+        <v/>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6843,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>179.45</v>
+        <v>180.2</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>178.78</v>
+        <v/>
       </c>
       <c r="F180" s="12" t="n">
-        <v>180.72</v>
+        <v/>
       </c>
       <c r="G180" s="12" t="n">
-        <v>178.34</v>
+        <v/>
       </c>
       <c r="H180" s="12" t="n">
-        <v>180.2</v>
+        <v/>
       </c>
       <c r="I180" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>0.42</v>
+        <v/>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6877,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>549.6</v>
+        <v>550.05</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>548</v>
+        <v/>
       </c>
       <c r="F181" s="9" t="n">
-        <v>552</v>
+        <v/>
       </c>
       <c r="G181" s="9" t="n">
-        <v>543.6</v>
+        <v/>
       </c>
       <c r="H181" s="9" t="n">
-        <v>550.05</v>
+        <v/>
       </c>
       <c r="I181" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>0.08</v>
+        <v/>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6911,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>267.5</v>
+        <v>266.35</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>266.25</v>
+        <v/>
       </c>
       <c r="F182" s="12" t="n">
-        <v>267.25</v>
+        <v/>
       </c>
       <c r="G182" s="12" t="n">
-        <v>264.3</v>
+        <v/>
       </c>
       <c r="H182" s="12" t="n">
-        <v>266.35</v>
+        <v/>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-1.15</v>
+        <v/>
       </c>
       <c r="J182" s="10" t="n">
-        <v>-0.43</v>
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6945,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1113.4</v>
+        <v>1118.2</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1109.9</v>
+        <v/>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1122.1</v>
+        <v/>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1103.9</v>
+        <v/>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1118.2</v>
+        <v/>
       </c>
       <c r="I183" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>0.43</v>
+        <v/>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6979,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>163.64</v>
+        <v>164.02</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>163.05</v>
+        <v/>
       </c>
       <c r="F184" s="12" t="n">
-        <v>164.5</v>
+        <v/>
       </c>
       <c r="G184" s="12" t="n">
-        <v>161.66</v>
+        <v/>
       </c>
       <c r="H184" s="12" t="n">
-        <v>164.02</v>
+        <v/>
       </c>
       <c r="I184" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>0.23</v>
+        <v/>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7047,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>1180.3</v>
+        <v>1203.9</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>1185.5</v>
+        <v/>
       </c>
       <c r="F186" s="12" t="n">
-        <v>1208.6</v>
+        <v/>
       </c>
       <c r="G186" s="12" t="n">
-        <v>1182.4</v>
+        <v/>
       </c>
       <c r="H186" s="12" t="n">
-        <v>1203.9</v>
+        <v/>
       </c>
       <c r="I186" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>2</v>
+        <v/>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7094,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  25-Sep-2026 05:46 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  28-Sep-2026 08:00 PM</t>
         </is>
       </c>
     </row>
@@ -7256,14 +7248,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-Sep-2026 05:46 PM</t>
+          <t>28-Sep-2026 08:00 PM</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -64,7 +64,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +94,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -190,6 +195,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -567,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 28-Sep-2026 08:00 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 29-Sep-2026 06:27 PM</t>
         </is>
       </c>
     </row>
@@ -592,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>28-Sep-2026 08:00 PM</t>
+          <t>29-Sep-2026 06:27 PM</t>
         </is>
       </c>
     </row>
@@ -756,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  28-Sep-2026 08:00 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  29-Sep-2026 06:27 PM</t>
         </is>
       </c>
     </row>
@@ -825,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>489.25</v>
+        <v>476.6</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v/>
+        <v>475</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v/>
+        <v>482.9</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v/>
+        <v>468</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v/>
+        <v>469.9</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v/>
+        <v>-6.7</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v/>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="4">
@@ -859,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7052.5</v>
+        <v>6972.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v/>
+        <v>6950</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v/>
+        <v>6953</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v/>
+        <v>6660.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v/>
+        <v>6660.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v/>
+        <v>-312</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v/>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="5">
@@ -893,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26955</v>
+        <v>26740</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v/>
+        <v>26735</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v/>
+        <v>27850</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v/>
+        <v>26650</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v/>
+        <v>27270</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v/>
+        <v>530</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="6">
@@ -927,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>390</v>
+        <v>382.7</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v/>
+        <v>381</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v/>
+        <v>383</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v/>
+        <v>376.05</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v/>
+        <v>378</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v/>
+        <v>-4.7</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v/>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="7">
@@ -961,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.14</v>
+        <v>47.59</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v/>
+        <v>47.59</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v/>
+        <v>47.72</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v/>
+        <v>46</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v/>
+        <v>46.24</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v/>
+        <v>-1.35</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v/>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="8">
@@ -995,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1236.4</v>
+        <v>1213.5</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v/>
+        <v>1215.5</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v/>
+        <v>1224.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v/>
+        <v>1188.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v/>
+        <v>1202.6</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v/>
+        <v>-10.9</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v/>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="9">
@@ -1029,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2916.5</v>
+        <v>2831.1</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v/>
+        <v>2834.6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v/>
+        <v>2972.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v/>
+        <v>2793.7</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v/>
+        <v>2972.9</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v/>
+        <v>141.8</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>5.01</v>
       </c>
     </row>
     <row r="10">
@@ -1063,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1788</v>
+        <v>1743.7</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v/>
+        <v>1755.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v/>
+        <v>1822</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v/>
+        <v>1738.4</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v/>
+        <v>1822</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v/>
+        <v>78.3</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="11">
@@ -1097,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5274</v>
+        <v>5175</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v/>
+        <v>5166.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v/>
+        <v>5306.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v/>
+        <v>5152</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v/>
+        <v>5250</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="12">
@@ -1131,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>383.8</v>
+        <v>374.35</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v/>
+        <v>373.5</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v/>
+        <v>373.6</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v/>
+        <v>365.75</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v/>
+        <v>365.75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v/>
+        <v>-8.6</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="13">
@@ -1165,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>288</v>
+        <v>279.2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v/>
+        <v>279.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v/>
+        <v>280</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v/>
+        <v>273.5</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v/>
+        <v>273.5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v/>
+        <v>-5.7</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v/>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="14">
@@ -1199,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2214.7</v>
+        <v>2197</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v/>
+        <v>2191.9</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v/>
+        <v>2217.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v/>
+        <v>2172.1</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v/>
+        <v>2188.6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v/>
+        <v>-8.4</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v/>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="15">
@@ -1233,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8889</v>
+        <v>8860</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v/>
+        <v>8885</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v/>
+        <v>8906</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v/>
+        <v>8657.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v/>
+        <v>8659</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v/>
+        <v>-201</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v/>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="16">
@@ -1267,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>400.1</v>
+        <v>389.6</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v/>
+        <v>390.75</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v/>
+        <v>429</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v/>
+        <v>386.3</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v/>
+        <v>406.75</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v/>
+        <v>17.15</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="17">
@@ -1301,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>159.08</v>
+        <v>155.22</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v/>
+        <v>155.5</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v/>
+        <v>155.5</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v/>
+        <v>152.48</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v/>
+        <v>153.44</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v/>
+        <v>-1.78</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v/>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="18">
@@ -1335,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2444</v>
+        <v>2420</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v/>
+        <v>2417.5</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v/>
+        <v>2425.3</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v/>
+        <v>2381</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v/>
+        <v>2415</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v/>
+        <v>-5</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v/>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="19">
@@ -1369,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1399</v>
+        <v>1370.5</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v/>
+        <v>1370.5</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v/>
+        <v>1384.2</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v/>
+        <v>1346.5</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v/>
+        <v>1375</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v/>
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="20">
@@ -1403,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>611.65</v>
+        <v>594.45</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v/>
+        <v>598.1</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v/>
+        <v>599.4</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v/>
+        <v>586</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v/>
+        <v>588.4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v/>
+        <v>-6.05</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v/>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="21">
@@ -1437,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6070.5</v>
+        <v>5991</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v/>
+        <v>5975</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v/>
+        <v>6086.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v/>
+        <v>5950</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v/>
+        <v>5982.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v/>
+        <v>-8.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v/>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="22">
@@ -1471,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1018</v>
+        <v>995.3</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v/>
+        <v>990</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v/>
+        <v>1005.2</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v/>
+        <v>984.5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v/>
+        <v>1005.2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v/>
+        <v>9.9</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="23">
@@ -1505,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1712</v>
+        <v>1697.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v/>
+        <v>1697</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v/>
+        <v>1713.7</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v/>
+        <v>1690.7</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v/>
+        <v>1697.7</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v/>
+        <v>0.2</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="24">
@@ -1539,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1222.4</v>
+        <v>1209.9</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v/>
+        <v>1202</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v/>
+        <v>1212.1</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v/>
+        <v>1190.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v/>
+        <v>1212.1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v/>
+        <v>2.2</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="25">
@@ -1573,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>11281</v>
+        <v>11024</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v/>
+        <v>11016</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v/>
+        <v>11020</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v/>
+        <v>10805</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v/>
+        <v>10811</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v/>
+        <v>-213</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v/>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="26">
@@ -1607,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1771</v>
+        <v>1752</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v/>
+        <v>1758.8</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v/>
+        <v>1758.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v/>
+        <v>1730</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v/>
+        <v>1742.4</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v/>
+        <v>-9.6</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="27">
@@ -1641,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>996.9</v>
+        <v>985</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v/>
+        <v>977.5</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v/>
+        <v>979.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v/>
+        <v>961.4</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v/>
+        <v>973.8</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v/>
+        <v>-11.2</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v/>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="28">
@@ -1675,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2185.3</v>
+        <v>2153.8</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v/>
+        <v>2151.3</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v/>
+        <v>2162.8</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v/>
+        <v>2115.8</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v/>
+        <v>2126.2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v/>
+        <v>-27.6</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v/>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="29">
@@ -1709,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>685.8</v>
+        <v>680.7</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v/>
+        <v>680.7</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v/>
+        <v>681.5</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v/>
+        <v>670</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v/>
+        <v>672.9</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v/>
+        <v>-7.8</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v/>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="30">
@@ -1743,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>187.7</v>
+        <v>181</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v/>
+        <v>181.2</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v/>
+        <v>185.31</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v/>
+        <v>179.3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v/>
+        <v>185.31</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v/>
+        <v>4.31</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="31">
@@ -1777,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>235.26</v>
+        <v>227.5</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v/>
+        <v>227.5</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v/>
+        <v>230.57</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v/>
+        <v>223.82</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v/>
+        <v>227.68</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v/>
+        <v>0.18</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="32">
@@ -1811,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>393.55</v>
+        <v>385.5</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v/>
+        <v>385.5</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v/>
+        <v>388</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v/>
+        <v>382.2</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v/>
+        <v>387.75</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v/>
+        <v>2.25</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="33">
@@ -1845,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>458.35</v>
+        <v>452.85</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v/>
+        <v>451.95</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v/>
+        <v>456.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v/>
+        <v>441.1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v/>
+        <v>448.2</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v/>
+        <v>-4.65</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v/>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="34">
@@ -1879,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1785.4</v>
+        <v>1771.4</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v/>
+        <v>1764</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v/>
+        <v>1787.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v/>
+        <v>1762</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v/>
+        <v>1771.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v/>
+        <v>-0.2</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v/>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="35">
@@ -1913,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>418.95</v>
+        <v>411.9</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v/>
+        <v>410.3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v/>
+        <v>414.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v/>
+        <v>402.6</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v/>
+        <v>413.35</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v/>
+        <v>1.45</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
@@ -1947,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>382.15</v>
+        <v>374.9</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v/>
+        <v>376.05</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v/>
+        <v>379.95</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v/>
+        <v>373.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v/>
+        <v>377</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v/>
+        <v>2.1</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1981,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>48250</v>
+        <v>47020</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v/>
+        <v>47145</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v/>
+        <v>47240</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v/>
+        <v>45700</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v/>
+        <v>45700</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v/>
+        <v>-1320</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v/>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="38">
@@ -2015,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>308.5</v>
+        <v>302.25</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v/>
+        <v>302.25</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v/>
+        <v>303.45</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v/>
+        <v>296.5</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v/>
+        <v>299.35</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v/>
+        <v>-2.9</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v/>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="39">
@@ -2049,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>4937.5</v>
+        <v>4915</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v/>
+        <v>4899</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v/>
+        <v>4907.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v/>
+        <v>4798</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v/>
+        <v>4835</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v/>
+        <v>-80</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v/>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="40">
@@ -2083,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>274.05</v>
+        <v>271.25</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v/>
+        <v>270.65</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v/>
+        <v>273.4</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v/>
+        <v>267.4</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v/>
+        <v>269.05</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v/>
+        <v>-2.2</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v/>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2117,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>124.99</v>
+        <v>120.65</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v/>
+        <v>120</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v/>
+        <v>120.34</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v/>
+        <v>118.03</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v/>
+        <v>119.51</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v/>
+        <v>-1.14</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v/>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2151,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>753.25</v>
+        <v>737.6</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v/>
+        <v>737.6</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v/>
+        <v>743.75</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v/>
+        <v>730</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v/>
+        <v>731.7</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v/>
+        <v>-5.9</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v/>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="43">
@@ -2185,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>417.95</v>
+        <v>418.45</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v/>
+        <v>417</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v/>
+        <v>417.8</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v/>
+        <v>411.7</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v/>
+        <v>413.55</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v/>
+        <v>-4.9</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v/>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="44">
@@ -2219,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1662.7</v>
+        <v>1634.2</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v/>
+        <v>1620</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v/>
+        <v>1644</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v/>
+        <v>1600.2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v/>
+        <v>1627.3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v/>
+        <v>-6.9</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v/>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="45">
@@ -2253,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1399.7</v>
+        <v>1383.7</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v/>
+        <v>1390</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v/>
+        <v>1401.8</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v/>
+        <v>1376.2</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v/>
+        <v>1379.3</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v/>
+        <v>-4.4</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v/>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="46">
@@ -2287,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>426.1</v>
+        <v>422.5</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v/>
+        <v>420.55</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v/>
+        <v>426</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v/>
+        <v>420.55</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v/>
+        <v>425</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v/>
+        <v>2.5</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="47">
@@ -2321,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
+        <v>1773</v>
+      </c>
+      <c r="E47" s="9" t="n">
         <v>1784</v>
       </c>
-      <c r="E47" s="9" t="n">
-        <v/>
-      </c>
       <c r="F47" s="9" t="n">
-        <v/>
+        <v>1813.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v/>
+        <v>1722</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v/>
+        <v>1722</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v/>
+        <v>-51</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v/>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="48">
@@ -2355,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1855.8</v>
+        <v>1845.9</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v/>
+        <v>1833.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v/>
+        <v>1836</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v/>
+        <v>1785.1</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v/>
+        <v>1785.1</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v/>
+        <v>-60.8</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v/>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="49">
@@ -2389,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>461.5</v>
+        <v>450</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v/>
+        <v>450</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v/>
+        <v>452.05</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v/>
+        <v>443.3</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v/>
+        <v>443.5</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v/>
+        <v>-6.5</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v/>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="50">
@@ -2423,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1963.9</v>
+        <v>1899.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v/>
+        <v>1900</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v/>
+        <v>1900.1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v/>
+        <v>1772.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v/>
+        <v>1792.9</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v/>
+        <v>-106.2</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v/>
+        <v>-5.59</v>
       </c>
     </row>
     <row r="51">
@@ -2457,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>218.6</v>
+        <v>218.8</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v/>
+        <v>219</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v/>
+        <v>219</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v/>
+        <v>211.37</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v/>
+        <v>211.37</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v/>
+        <v>-7.43</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v/>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="52">
@@ -2491,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>225.57</v>
+        <v>215.99</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v/>
+        <v>217.16</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v/>
+        <v>217.48</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v/>
+        <v>210.69</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v/>
+        <v>214.91</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v/>
+        <v>-1.08</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="53">
@@ -2525,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4945</v>
+        <v>4855</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v/>
+        <v>4850</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v/>
+        <v>4875</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v/>
+        <v>4795</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v/>
+        <v>4800</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v/>
+        <v>-55</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v/>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="54">
@@ -2559,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>385.6</v>
+        <v>385.75</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v/>
+        <v>383.85</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v/>
+        <v>384.45</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v/>
+        <v>378</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v/>
+        <v>380.4</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v/>
+        <v>-5.35</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v/>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="55">
@@ -2593,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1700.2</v>
+        <v>1651.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v/>
+        <v>1651.6</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v/>
+        <v>1664.3</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v/>
+        <v>1630.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v/>
+        <v>1637.4</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v/>
+        <v>-14.2</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v/>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="56">
@@ -2627,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1587.1</v>
+        <v>1550.8</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v/>
+        <v>1552.8</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v/>
+        <v>1555</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v/>
+        <v>1512.3</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v/>
+        <v>1529</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v/>
+        <v>-21.8</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v/>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="57">
@@ -2661,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>76.84</v>
+        <v>72.2</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v/>
+        <v>72.45</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v/>
+        <v>81.56</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v/>
+        <v>71.02</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v/>
+        <v>78.69</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v/>
+        <v>6.49</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>8.99</v>
       </c>
     </row>
     <row r="58">
@@ -2695,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>9619.5</v>
+        <v>9550</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v/>
+        <v>9562</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v/>
+        <v>9610.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v/>
+        <v>9431</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v/>
+        <v>9431</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v/>
+        <v>-119</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v/>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="59">
@@ -2729,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>13390</v>
+        <v>13640</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v/>
+        <v>13640</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v/>
+        <v>13686</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v/>
+        <v>13250</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v/>
+        <v>13250</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v/>
+        <v>-390</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v/>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="60">
@@ -2763,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>683</v>
+        <v>663.55</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v/>
+        <v>660.5</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v/>
+        <v>675</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v/>
+        <v>653</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v/>
+        <v>653</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v/>
+        <v>-10.55</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v/>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="61">
@@ -2797,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1201</v>
+        <v>1221</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v/>
+        <v>1243.2</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v/>
+        <v>1252.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v/>
+        <v>1229</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v/>
+        <v>1251.9</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v/>
+        <v>30.9</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>2.53</v>
       </c>
     </row>
     <row r="62">
@@ -2831,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7360</v>
+        <v>7213.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v/>
+        <v>7213.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v/>
+        <v>7268</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v/>
+        <v>7164.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v/>
+        <v>7179</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v/>
+        <v>-34.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v/>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="63">
@@ -2865,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2855.7</v>
+        <v>2740.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v/>
+        <v>2740.7</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v/>
+        <v>2761.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v/>
+        <v>2701</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v/>
+        <v>2706.2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v/>
+        <v>-34.5</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v/>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="64">
@@ -2899,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>423.65</v>
+        <v>411.75</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v/>
+        <v>411</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v/>
+        <v>414.5</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v/>
+        <v>403.15</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v/>
+        <v>407</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v/>
+        <v>-4.75</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v/>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="65">
@@ -2933,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v/>
+        <v>325.65</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v/>
+        <v>326.85</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v/>
+        <v>320.2</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v/>
+        <v>320.2</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v/>
+        <v>-4.8</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v/>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="66">
@@ -2967,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>172.7</v>
+        <v>172.45</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v/>
+        <v>172.34</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v/>
+        <v>173.26</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v/>
+        <v>168.43</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v/>
+        <v>170.04</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v/>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="67">
@@ -3001,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2380</v>
+        <v>2325.7</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v/>
+        <v>2330.4</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v/>
+        <v>2441.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v/>
+        <v>2292</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v/>
+        <v>2441.5</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v/>
+        <v>115.8</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>4.98</v>
       </c>
     </row>
     <row r="68">
@@ -3069,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>630.3</v>
+        <v>620.65</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v/>
+        <v>619</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v/>
+        <v>627.55</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v/>
+        <v>609.85</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v/>
+        <v>611.5</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v/>
+        <v>-9.15</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v/>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="70">
@@ -3103,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v/>
+        <v>868</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v/>
+        <v>870</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v/>
+        <v>850</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v/>
+        <v>855</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v/>
+        <v>-13</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="71">
@@ -3137,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1700.1</v>
+        <v>1669.8</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v/>
+        <v>1666</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v/>
+        <v>1671.3</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v/>
+        <v>1634.4</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v/>
+        <v>1634.4</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v/>
+        <v>-35.4</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v/>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="72">
@@ -3171,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>868.65</v>
+        <v>851.4</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v/>
+        <v>850</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v/>
+        <v>876.95</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v/>
+        <v>847</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v/>
+        <v>866.75</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v/>
+        <v>15.35</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="73">
@@ -3205,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3191</v>
+        <v>3150</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v/>
+        <v>3149.2</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v/>
+        <v>3151.5</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v/>
+        <v>3089</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v/>
+        <v>3100</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v/>
+        <v>-50</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v/>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="74">
@@ -3273,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4800</v>
+        <v>4738</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v/>
+        <v>4723</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v/>
+        <v>4723.1</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v/>
+        <v>4549.3</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v/>
+        <v>4549.3</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v/>
+        <v>-188.7</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v/>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="76">
@@ -3307,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1096.5</v>
+        <v>1085</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v/>
+        <v>1080.6</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v/>
+        <v>1081.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v/>
+        <v>1043.3</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v/>
+        <v>1043.3</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v/>
+        <v>-41.7</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v/>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="77">
@@ -3341,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1258</v>
+        <v>1252.6</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v/>
+        <v>1252.6</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v/>
+        <v>1261</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v/>
+        <v>1222</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v/>
+        <v>1222</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v/>
+        <v>-30.6</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v/>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="78">
@@ -3375,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2378</v>
+        <v>2302.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v/>
+        <v>2286.1</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v/>
+        <v>2303</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v/>
+        <v>2223.3</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v/>
+        <v>2223.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v/>
+        <v>-79</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v/>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="79">
@@ -3409,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>735.6</v>
+        <v>719.05</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v/>
+        <v>713.7</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v/>
+        <v>722.7</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v/>
+        <v>706.25</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v/>
+        <v>722.7</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v/>
+        <v>3.65</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="80">
@@ -3443,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>531</v>
+        <v>531.6</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v/>
+        <v>526.2</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v/>
+        <v>528.35</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v/>
+        <v>518.6</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v/>
+        <v>523.55</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v/>
+        <v>-8.050000000000001</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v/>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="81">
@@ -3477,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5360</v>
+        <v>5390</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v/>
+        <v>5375</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v/>
+        <v>5384</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v/>
+        <v>5208</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v/>
+        <v>5208</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v/>
+        <v>-182</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v/>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="82">
@@ -3511,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>977</v>
+        <v>955.9</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v/>
+        <v>955.9</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v/>
+        <v>963.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v/>
+        <v>947.1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v/>
+        <v>955.2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v/>
+        <v>-0.7</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v/>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3545,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>494.65</v>
+        <v>479.6</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v/>
+        <v>475.55</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v/>
+        <v>479.95</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v/>
+        <v>470</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v/>
+        <v>474.35</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v/>
+        <v>-5.25</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v/>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="84">
@@ -3579,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>351</v>
+        <v>342.45</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v/>
+        <v>340.7</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v/>
+        <v>349.35</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v/>
+        <v>337.2</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v/>
+        <v>349.2</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v/>
+        <v>6.75</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="85">
@@ -3613,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1942.9</v>
+        <v>1896</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v/>
+        <v>1896</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v/>
+        <v>1898.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v/>
+        <v>1863.8</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v/>
+        <v>1863.8</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v/>
+        <v>-32.2</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v/>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="86">
@@ -3647,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>33865</v>
+        <v>33855</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v/>
+        <v>33660</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v/>
+        <v>35470</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v/>
+        <v>33505</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v/>
+        <v>33980</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v/>
+        <v>125</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="87">
@@ -3681,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>83.8</v>
+        <v>80.55</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v/>
+        <v>80.40000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-       